--- a/docs/files/REPORT_FILTRI/Agente - Marcelli Emanuele.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Marcelli Emanuele.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W10</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>74</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>4989</v>
+        <v>6714</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>3576</v>
+        <v>4745</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1577</v>
+        <v>2235</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>435</v>
+        <v>579</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>341</v>
+        <v>451</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>298</v>
+        <v>381</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>142</v>
+        <v>203</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>381</v>
+        <v>516</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>31</v>
+        <v>61</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,31 +875,31 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>299</v>
+        <v>432</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>88</v>
+        <v>157</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>212</v>
+        <v>288</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>84</v>
+        <v>112</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>74</v>
+        <v>131</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>194</v>
+        <v>257</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>71</v>
+        <v>103</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -929,31 +929,31 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>276</v>
+        <v>377</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>145</v>
+        <v>199</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>314</v>
+        <v>430</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>118</v>
+        <v>191</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>192</v>
+        <v>266</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>78</v>
+        <v>105</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>83</v>
+        <v>110</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>167</v>
+        <v>219</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -983,31 +983,31 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>208</v>
+        <v>300</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>192</v>
+        <v>251</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>9</v>
+        <v>61</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>135</v>
+        <v>189</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>65</v>
+        <v>103</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>184</v>
+        <v>256</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1037,31 +1037,31 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>196</v>
+        <v>289</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>235</v>
+        <v>367</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>153</v>
+        <v>221</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>301</v>
+        <v>401</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -1091,31 +1091,31 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>195</v>
+        <v>260</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>250</v>
+        <v>392</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>146</v>
+        <v>193</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>212</v>
+        <v>294</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1145,31 +1145,31 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>183</v>
+        <v>246</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>202</v>
+        <v>303</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>209</v>
+        <v>275</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>243</v>
+        <v>372</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>144</v>
+        <v>199</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>155</v>
+        <v>227</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
@@ -1199,31 +1199,31 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>173</v>
+        <v>214</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>198</v>
+        <v>272</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>114</v>
+        <v>147</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>151</v>
+        <v>199</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>139</v>
+        <v>172</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>132</v>
+        <v>170</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
@@ -1234,12 +1234,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>00218</t>
+          <t>11745</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>VICOFORTE</t>
+          <t>BRESCIA</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1249,51 +1249,51 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>GIARRATANA SEARA</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>170</v>
+        <v>210</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>119</v>
+        <v>224</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>128</v>
+        <v>175</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="K19" s="12" t="n">
         <v>35</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>67</v>
+        <v>150</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>19</v>
+        <v>89</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>11745</t>
+          <t>00218</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA</t>
+          <t>VICOFORTE</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1303,35 +1303,35 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>GIARRATANA SEARA</t>
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>168</v>
+        <v>200</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="K20" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="L20" s="12" t="n">
+        <v>93</v>
+      </c>
+      <c r="M20" s="12" t="n">
         <v>31</v>
-      </c>
-      <c r="L20" s="12" t="n">
-        <v>108</v>
-      </c>
-      <c r="M20" s="12" t="n">
-        <v>67</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
@@ -1342,12 +1342,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>00209</t>
+          <t>01724</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>CUNEO</t>
+          <t>ORZIVECCHI</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1357,35 +1357,35 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>SCIALO' MARCO</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>135</v>
+        <v>185</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>140</v>
+        <v>84</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>9</v>
+        <v>95</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>97</v>
+        <v>152</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>107</v>
+        <v>59</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
@@ -1396,12 +1396,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>01527</t>
+          <t>00209</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>DALMINE</t>
+          <t>CUNEO</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1411,51 +1411,51 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>SCIALO' MARCO</t>
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>133</v>
+        <v>182</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>88</v>
+        <v>191</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>80</v>
+        <v>127</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>95</v>
+        <v>151</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>2</v>
+        <v>55</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>01724</t>
+          <t>01527</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>ORZIVECCHI</t>
+          <t>DALMINE</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1465,39 +1465,39 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>129</v>
+        <v>180</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>28</v>
+        <v>94</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>43</v>
+        <v>134</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1523,31 +1523,31 @@
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>129</v>
+        <v>165</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>159</v>
+        <v>201</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>154</v>
+        <v>200</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
@@ -1577,28 +1577,28 @@
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>123</v>
+        <v>163</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>196</v>
+        <v>273</v>
       </c>
       <c r="G25" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>65</v>
+        <v>92</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>132</v>
+        <v>173</v>
       </c>
       <c r="M25" s="12" t="n">
         <v>6</v>
@@ -1631,31 +1631,31 @@
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>114</v>
+        <v>140</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>72</v>
+        <v>103</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>97</v>
+        <v>130</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
@@ -1685,31 +1685,31 @@
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>103</v>
+        <v>135</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>162</v>
+        <v>222</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>230</v>
+        <v>328</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
@@ -1720,12 +1720,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>01525</t>
+          <t>01956</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>GAZZANIGA</t>
+          <t>CREMA</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1735,51 +1735,51 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="E28" s="12" t="n">
+        <v>117</v>
+      </c>
+      <c r="F28" s="12" t="n">
+        <v>165</v>
+      </c>
+      <c r="G28" s="12" t="n">
+        <v>94</v>
+      </c>
+      <c r="H28" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="I28" s="12" t="n">
         <v>93</v>
       </c>
-      <c r="F28" s="12" t="n">
-        <v>91</v>
-      </c>
-      <c r="G28" s="12" t="n">
-        <v>33</v>
-      </c>
-      <c r="H28" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="I28" s="12" t="n">
-        <v>46</v>
-      </c>
       <c r="J28" s="12" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>52</v>
+        <v>167</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>12</v>
+        <v>61</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>55496</t>
+          <t>01525</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>MOZZO</t>
+          <t>GAZZANIGA</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1793,31 +1793,31 @@
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>81</v>
+        <v>131</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="J29" s="12" t="n">
         <v>16</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
@@ -1828,12 +1828,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>01956</t>
+          <t>01968</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>CREMA</t>
+          <t>CREMONA</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1843,35 +1843,35 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>81</v>
+        <v>113</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>123</v>
+        <v>145</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>2</v>
+        <v>52</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>119</v>
+        <v>179</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
@@ -1882,12 +1882,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>51674</t>
+          <t>01008</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>CARAVAGGIO</t>
+          <t>GENOVA</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1897,35 +1897,35 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>DALLORTO ILARIA</t>
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="G31" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="H31" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="I31" s="12" t="n">
+        <v>58</v>
+      </c>
+      <c r="J31" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="K31" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="L31" s="12" t="n">
+        <v>128</v>
+      </c>
+      <c r="M31" s="12" t="n">
         <v>8</v>
-      </c>
-      <c r="H31" s="12" t="n">
-        <v>26</v>
-      </c>
-      <c r="I31" s="12" t="n">
-        <v>65</v>
-      </c>
-      <c r="J31" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="K31" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="L31" s="12" t="n">
-        <v>55</v>
-      </c>
-      <c r="M31" s="12" t="n">
-        <v>27</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
@@ -1936,12 +1936,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>01968</t>
+          <t>55496</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>CREMONA</t>
+          <t>MOZZO</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1951,51 +1951,51 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>132</v>
+        <v>90</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>01008</t>
+          <t>51674</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>GENOVA</t>
+          <t>CARAVAGGIO</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2005,51 +2005,51 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>DALLORTO ILARIA</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="E33" s="12" t="n">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>86</v>
+        <v>173</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>54</v>
+        <v>81</v>
       </c>
       <c r="J33" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="K33" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="K33" s="12" t="n">
-        <v>19</v>
-      </c>
       <c r="L33" s="12" t="n">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>01718</t>
+          <t>02036</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>PONTEVICO</t>
+          <t>CREMONA</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2063,47 +2063,47 @@
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>2</v>
+        <v>112</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>15</v>
+        <v>237</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>78</v>
+        <v>142</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>02036</t>
+          <t>01034</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>CREMONA</t>
+          <t>GENOVA</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2113,51 +2113,51 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>DALLORTO ILARIA</t>
         </is>
       </c>
       <c r="E35" s="12" t="n">
-        <v>71</v>
+        <v>91</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>73</v>
+        <v>110</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>175</v>
+        <v>218</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>01034</t>
+          <t>01718</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>GENOVA</t>
+          <t>PONTEVICO</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2167,35 +2167,35 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>DALLORTO ILARIA</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>56</v>
+        <v>87</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>73</v>
+        <v>134</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>83</v>
+        <v>2</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>151</v>
+        <v>27</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="E37" s="12" t="n">
-        <v>55</v>
+        <v>82</v>
       </c>
       <c r="F37" s="12" t="n">
         <v>0</v>
@@ -2237,35 +2237,35 @@
         <v>0</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>62</v>
+        <v>91</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>01007</t>
+          <t>01043</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>CHIAVARI</t>
+          <t>GENOVA</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2275,51 +2275,51 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>DALLORTO ILARIA</t>
         </is>
       </c>
       <c r="E38" s="12" t="n">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>27</v>
+        <v>57</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>01371</t>
+          <t>00215</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>SAVONA</t>
+          <t>SAVIGLIANO</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2329,35 +2329,35 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>DELUGAS NADIA</t>
+          <t>GIARRATANA SEARA</t>
         </is>
       </c>
       <c r="E39" s="12" t="n">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>97</v>
+        <v>129</v>
       </c>
       <c r="G39" s="12" t="n">
         <v>5</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
@@ -2387,31 +2387,31 @@
         </is>
       </c>
       <c r="E40" s="12" t="n">
+        <v>69</v>
+      </c>
+      <c r="F40" s="12" t="n">
+        <v>77</v>
+      </c>
+      <c r="G40" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H40" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I40" s="12" t="n">
         <v>53</v>
       </c>
-      <c r="F40" s="12" t="n">
-        <v>50</v>
-      </c>
-      <c r="G40" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H40" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I40" s="12" t="n">
-        <v>43</v>
-      </c>
       <c r="J40" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
@@ -2422,12 +2422,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>01043</t>
+          <t>01007</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>GENOVA</t>
+          <t>CHIAVARI</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -2437,51 +2437,51 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>DALLORTO ILARIA</t>
+          <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
       <c r="E41" s="12" t="n">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>91</v>
+        <v>157</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>12112</t>
+          <t>01378</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>MANTOVA</t>
+          <t>CARCARE</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -2491,51 +2491,51 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>DELUGAS NADIA</t>
         </is>
       </c>
       <c r="E42" s="12" t="n">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>45</v>
+        <v>82</v>
       </c>
       <c r="G42" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="H42" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="I42" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="J42" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="K42" s="12" t="n">
+        <v>34</v>
+      </c>
+      <c r="L42" s="12" t="n">
+        <v>62</v>
+      </c>
+      <c r="M42" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H42" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="I42" s="12" t="n">
-        <v>47</v>
-      </c>
-      <c r="J42" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="K42" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="L42" s="12" t="n">
-        <v>34</v>
-      </c>
-      <c r="M42" s="12" t="n">
-        <v>29</v>
-      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>01378</t>
+          <t>01371</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>CARCARE</t>
+          <t>SAVONA</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -2549,31 +2549,31 @@
         </is>
       </c>
       <c r="E43" s="12" t="n">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="F43" s="12" t="n">
-        <v>63</v>
+        <v>119</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I43" s="12" t="n">
+        <v>52</v>
+      </c>
+      <c r="J43" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="K43" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="L43" s="12" t="n">
+        <v>90</v>
+      </c>
+      <c r="M43" s="12" t="n">
         <v>23</v>
-      </c>
-      <c r="J43" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="K43" s="12" t="n">
-        <v>23</v>
-      </c>
-      <c r="L43" s="12" t="n">
-        <v>42</v>
-      </c>
-      <c r="M43" s="12" t="n">
-        <v>1</v>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
@@ -2584,12 +2584,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>00215</t>
+          <t>01577</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>SAVIGLIANO</t>
+          <t>ZANICA</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2599,39 +2599,39 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>GIARRATANA SEARA</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="E44" s="12" t="n">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2657,47 +2657,47 @@
         </is>
       </c>
       <c r="E45" s="12" t="n">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="F45" s="12" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="K45" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>01577</t>
+          <t>12112</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>ZANICA</t>
+          <t>MANTOVA</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -2707,51 +2707,51 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="E46" s="12" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="G46" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="K46" s="12" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>51570</t>
+          <t>01971</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>VENTIMIGLIA</t>
+          <t>CREMONA</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -2761,35 +2761,35 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>BARNABA SALVATORE</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="E47" s="12" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="F47" s="12" t="n">
         <v>51</v>
       </c>
       <c r="G47" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H47" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="H47" s="12" t="n">
-        <v>10</v>
-      </c>
       <c r="I47" s="12" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="K47" s="12" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
@@ -2800,12 +2800,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>01480</t>
+          <t>11455</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>ASTI</t>
+          <t>CASALE MONFERRATO</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -2819,47 +2819,47 @@
         </is>
       </c>
       <c r="E48" s="12" t="n">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>56</v>
+        <v>7</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="J48" s="12" t="n">
         <v>9</v>
       </c>
       <c r="K48" s="12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="M48" s="12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>01135</t>
+          <t>01480</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>GENOVA</t>
+          <t>ASTI</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -2869,51 +2869,51 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>DALLORTO ILARIA</t>
+          <t>VIGNADUZZO EDI</t>
         </is>
       </c>
       <c r="E49" s="12" t="n">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="F49" s="12" t="n">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>2</v>
+        <v>54</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>1</v>
+        <v>88</v>
       </c>
       <c r="I49" s="12" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="J49" s="12" t="n">
         <v>11</v>
       </c>
       <c r="K49" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="M49" s="12" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>01971</t>
+          <t>51570</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>CREMONA</t>
+          <t>VENTIMIGLIA</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -2923,51 +2923,51 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>BARNABA SALVATORE</t>
         </is>
       </c>
       <c r="E50" s="12" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>44</v>
+        <v>79</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J50" s="12" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K50" s="12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="M50" s="12" t="n">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>11455</t>
+          <t>59894</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>CASALE MONFERRATO</t>
+          <t>BRESCIA</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -2977,35 +2977,35 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>VIGNADUZZO EDI</t>
+          <t>SALVINELLI LUCA</t>
         </is>
       </c>
       <c r="E51" s="12" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="F51" s="12" t="n">
         <v>58</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H51" s="12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I51" s="12" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J51" s="12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K51" s="12" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="M51" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
@@ -3016,12 +3016,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>01637</t>
+          <t>01135</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>CURNO</t>
+          <t>GENOVA</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -3031,35 +3031,35 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>DALLORTO ILARIA</t>
         </is>
       </c>
       <c r="E52" s="12" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J52" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="K52" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="L52" s="12" t="n">
+        <v>65</v>
+      </c>
+      <c r="M52" s="12" t="n">
         <v>9</v>
-      </c>
-      <c r="K52" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="L52" s="12" t="n">
-        <v>41</v>
-      </c>
-      <c r="M52" s="12" t="n">
-        <v>3</v>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
@@ -3070,12 +3070,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>59894</t>
+          <t>01637</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA</t>
+          <t>CURNO</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -3085,35 +3085,35 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>SALVINELLI LUCA</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="E53" s="12" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H53" s="12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I53" s="12" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J53" s="12" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="K53" s="12" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="M53" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
@@ -3124,12 +3124,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>54151</t>
+          <t>01334</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>IMPERIA</t>
+          <t>FINALE LIGURE</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -3143,47 +3143,47 @@
         </is>
       </c>
       <c r="E54" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="F54" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="G54" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="H54" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="I54" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="F54" s="12" t="n">
-        <v>53</v>
-      </c>
-      <c r="G54" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="H54" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="I54" s="12" t="n">
-        <v>18</v>
-      </c>
       <c r="J54" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K54" s="12" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="M54" s="12" t="n">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>55864</t>
+          <t>54151</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>OVADA</t>
+          <t>IMPERIA</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -3193,51 +3193,51 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>DELUGAS NADIA</t>
+          <t>BARNABA SALVATORE</t>
         </is>
       </c>
       <c r="E55" s="12" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F55" s="12" t="n">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H55" s="12" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="I55" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="J55" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="K55" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="L55" s="12" t="n">
+        <v>64</v>
+      </c>
+      <c r="M55" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="J55" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="K55" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="L55" s="12" t="n">
-        <v>51</v>
-      </c>
-      <c r="M55" s="12" t="n">
-        <v>3</v>
-      </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>02075</t>
+          <t>11726</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>SUZZARA</t>
+          <t>REZZATO</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -3247,51 +3247,51 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
       <c r="E56" s="12" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J56" s="12" t="n">
         <v>7</v>
       </c>
       <c r="K56" s="12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="M56" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>01334</t>
+          <t>55864</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>FINALE LIGURE</t>
+          <t>OVADA</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -3301,51 +3301,51 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>BARNABA SALVATORE</t>
+          <t>DELUGAS NADIA</t>
         </is>
       </c>
       <c r="E57" s="12" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="F57" s="12" t="n">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="H57" s="12" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="I57" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J57" s="12" t="n">
         <v>5</v>
       </c>
       <c r="K57" s="12" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="L57" s="12" t="n">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="M57" s="12" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>01283</t>
+          <t>02075</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>SARZANA</t>
+          <t>SUZZARA</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -3355,39 +3355,39 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="E58" s="12" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="G58" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="H58" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="I58" s="12" t="n">
+        <v>34</v>
+      </c>
+      <c r="J58" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="H58" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="I58" s="12" t="n">
-        <v>22</v>
-      </c>
-      <c r="J58" s="12" t="n">
-        <v>5</v>
-      </c>
       <c r="K58" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" s="12" t="n">
+        <v>45</v>
+      </c>
+      <c r="M58" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="L58" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="M58" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -3413,31 +3413,31 @@
         </is>
       </c>
       <c r="E59" s="12" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F59" s="12" t="n">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="H59" s="12" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I59" s="12" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J59" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K59" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="M59" s="12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
@@ -3448,12 +3448,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>11726</t>
+          <t>01561</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>REZZATO</t>
+          <t>PONTIROLO NUOVO</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -3463,20 +3463,20 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>GRAZIOSI DAVIDE</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="E60" s="12" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I60" s="12" t="n">
         <v>13</v>
@@ -3485,13 +3485,13 @@
         <v>3</v>
       </c>
       <c r="K60" s="12" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="L60" s="12" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="M60" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
@@ -3502,12 +3502,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>01561</t>
+          <t>01283</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>PONTIROLO NUOVO</t>
+          <t>SARZANA</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -3517,51 +3517,51 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
       <c r="E61" s="12" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F61" s="12" t="n">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H61" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I61" s="12" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="J61" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K61" s="12" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="L61" s="12" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="M61" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>12082</t>
+          <t>01086</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>VIADANA</t>
+          <t>RECCO</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -3571,51 +3571,51 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
       <c r="E62" s="12" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J62" s="12" t="n">
         <v>6</v>
       </c>
       <c r="K62" s="12" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L62" s="12" t="n">
-        <v>11</v>
+        <v>98</v>
       </c>
       <c r="M62" s="12" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>01481</t>
+          <t>12082</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>VILLAFRANCA D'ASTI</t>
+          <t>VIADANA</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -3625,51 +3625,51 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>VIGNADUZZO EDI</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="E63" s="12" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F63" s="12" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="H63" s="12" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="I63" s="12" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J63" s="12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K63" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L63" s="12" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="M63" s="12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>01280</t>
+          <t>02024</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>LA SPEZIA</t>
+          <t>CASALMAGGIORE</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -3679,35 +3679,35 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="E64" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="F64" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="G64" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="H64" s="12" t="n">
         <v>15</v>
-      </c>
-      <c r="F64" s="12" t="n">
-        <v>27</v>
-      </c>
-      <c r="G64" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="H64" s="12" t="n">
-        <v>10</v>
       </c>
       <c r="I64" s="12" t="n">
         <v>18</v>
       </c>
       <c r="J64" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K64" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L64" s="12" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="M64" s="12" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
@@ -3718,12 +3718,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>00350</t>
+          <t>01280</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>BORGO SAN DALMAZZO</t>
+          <t>LA SPEZIA</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -3733,35 +3733,35 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>SCIALO' MARCO</t>
+          <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
       <c r="E65" s="12" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F65" s="12" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H65" s="12" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="I65" s="12" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="J65" s="12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K65" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L65" s="12" t="n">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="M65" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
@@ -3772,12 +3772,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>52510</t>
+          <t>01481</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>PORTO MANTOVANO</t>
+          <t>VILLAFRANCA D'ASTI</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -3787,51 +3787,51 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>VIGNADUZZO EDI</t>
         </is>
       </c>
       <c r="E66" s="12" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="I66" s="12" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="J66" s="12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K66" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L66" s="12" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="M66" s="12" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>02024</t>
+          <t>56297</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>CASALMAGGIORE</t>
+          <t>SAN PAOLO D'ARGON</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -3841,35 +3841,35 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="E67" s="12" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F67" s="12" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="H67" s="12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I67" s="12" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="J67" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K67" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L67" s="12" t="n">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="M67" s="12" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
@@ -3880,12 +3880,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>01086</t>
+          <t>02004</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>RECCO</t>
+          <t>RIVOLTA D'ADDA</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -3895,51 +3895,51 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="E68" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="F68" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="G68" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I68" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="F68" s="12" t="n">
-        <v>46</v>
-      </c>
-      <c r="G68" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="H68" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="I68" s="12" t="n">
-        <v>9</v>
-      </c>
       <c r="J68" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K68" s="12" t="n">
         <v>5</v>
       </c>
       <c r="L68" s="12" t="n">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="M68" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>02004</t>
+          <t>52510</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>RIVOLTA D'ADDA</t>
+          <t>PORTO MANTOVANO</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -3949,51 +3949,51 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="E69" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="F69" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="J69" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="K69" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="F69" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="G69" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H69" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I69" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="J69" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K69" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="L69" s="12" t="n">
-        <v>30</v>
-      </c>
       <c r="M69" s="12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>56297</t>
+          <t>54290</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>SAN PAOLO D'ARGON</t>
+          <t>GENOVA</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -4003,35 +4003,35 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>DALLORTO ILARIA</t>
         </is>
       </c>
       <c r="E70" s="12" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F70" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="H70" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I70" s="12" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="J70" s="12" t="n">
         <v>2</v>
       </c>
       <c r="K70" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L70" s="12" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="M70" s="12" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
@@ -4042,12 +4042,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>01288</t>
+          <t>00350</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>BOLANO</t>
+          <t>BORGO SAN DALMAZZO</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -4057,51 +4057,51 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>SCIALO' MARCO</t>
         </is>
       </c>
       <c r="E71" s="12" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F71" s="12" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H71" s="12" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="I71" s="12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J71" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K71" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L71" s="12" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="M71" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>54290</t>
+          <t>11725</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>GENOVA</t>
+          <t>GAVARDO</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -4111,51 +4111,51 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>DALLORTO ILARIA</t>
+          <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
       <c r="E72" s="12" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F72" s="12" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="H72" s="12" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I72" s="12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J72" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K72" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="L72" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="M72" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="K72" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L72" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="M72" s="12" t="n">
-        <v>17</v>
-      </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>01578</t>
+          <t>11719</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>VERDELLO</t>
+          <t>MONTICHIARI</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -4165,51 +4165,51 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="E73" s="12" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F73" s="12" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H73" s="12" t="n">
-        <v>2</v>
+        <v>78</v>
       </c>
       <c r="I73" s="12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J73" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K73" s="12" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L73" s="12" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="M73" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>01671</t>
+          <t>01288</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA</t>
+          <t>BOLANO</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -4219,32 +4219,32 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>GRAZIOSI DAVIDE</t>
+          <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
       <c r="E74" s="12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F74" s="12" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="G74" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="H74" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="I74" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="J74" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K74" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" s="12" t="n">
         <v>18</v>
-      </c>
-      <c r="H74" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="I74" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="J74" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K74" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L74" s="12" t="n">
-        <v>8</v>
       </c>
       <c r="M74" s="12" t="n">
         <v>0</v>
@@ -4258,12 +4258,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>02074</t>
+          <t>01578</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>GOITO</t>
+          <t>VERDELLO</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -4273,51 +4273,51 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="E75" s="12" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="F75" s="12" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H75" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I75" s="12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J75" s="12" t="n">
         <v>3</v>
       </c>
       <c r="K75" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L75" s="12" t="n">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="M75" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>11719</t>
+          <t>01671</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>MONTICHIARI</t>
+          <t>BRESCIA</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -4327,51 +4327,51 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
       <c r="E76" s="12" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F76" s="12" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="G76" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="H76" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="I76" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="J76" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H76" s="12" t="n">
-        <v>53</v>
-      </c>
-      <c r="I76" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="J76" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="K76" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L76" s="12" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="M76" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>11725</t>
+          <t>02074</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>GAVARDO</t>
+          <t>GOITO</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -4381,39 +4381,39 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>GRAZIOSI DAVIDE</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="E77" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F77" s="12" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="H77" s="12" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="I77" s="12" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J77" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K77" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L77" s="12" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="M77" s="12" t="n">
         <v>2</v>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="E78" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F78" s="12" t="n">
         <v>0</v>
@@ -4451,7 +4451,7 @@
         <v>0</v>
       </c>
       <c r="I78" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J78" s="12" t="n">
         <v>0</v>
@@ -4460,14 +4460,14 @@
         <v>0</v>
       </c>
       <c r="L78" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M78" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -4496,13 +4496,13 @@
         <v>0</v>
       </c>
       <c r="F79" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G79" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H79" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I79" s="12" t="n">
         <v>0</v>
@@ -4550,13 +4550,13 @@
         <v>0</v>
       </c>
       <c r="F80" s="12" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="G80" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H80" s="12" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="I80" s="12" t="n">
         <v>0</v>
@@ -4604,13 +4604,13 @@
         <v>0</v>
       </c>
       <c r="F81" s="12" t="n">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="G81" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H81" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I81" s="12" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
         <v>0</v>
       </c>
       <c r="F82" s="12" t="n">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="G82" s="12" t="n">
         <v>0</v>
@@ -4712,7 +4712,7 @@
         <v>0</v>
       </c>
       <c r="F83" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G83" s="12" t="n">
         <v>0</v>
@@ -4737,7 +4737,7 @@
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -4766,13 +4766,13 @@
         <v>0</v>
       </c>
       <c r="F84" s="12" t="n">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="G84" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H84" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I84" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/Agente - Marcelli Emanuele.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Marcelli Emanuele.xlsx
@@ -535,7 +535,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -845,7 +845,7 @@
         <v>516</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>0.1182170542635659</v>
+        <v>61</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>257</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>0.4007782101167315</v>
+        <v>103</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         <v>219</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>0.0228310502283105</v>
+        <v>5</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>256</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>0.1796875</v>
+        <v>46</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>401</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>0.04738154613466334</v>
+        <v>19</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>294</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>0.1530612244897959</v>
+        <v>45</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         <v>227</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>0.03083700440528634</v>
+        <v>7</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>170</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>0.2529411764705882</v>
+        <v>43</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         <v>150</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>0.5933333333333334</v>
+        <v>89</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>93</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>0.3333333333333333</v>
+        <v>31</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>59</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>0.1864406779661017</v>
+        <v>11</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v>151</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>0.3642384105960265</v>
+        <v>55</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>134</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>0.03731343283582089</v>
+        <v>5</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>200</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>0.235</v>
+        <v>47</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>173</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>0.03468208092485549</v>
+        <v>6</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>130</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>0.1615384615384615</v>
+        <v>21</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>328</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>0.02134146341463415</v>
+        <v>7</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>167</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>0.3652694610778443</v>
+        <v>61</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>67</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>0.1791044776119403</v>
+        <v>12</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>179</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>0.08379888268156424</v>
+        <v>15</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>128</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>0.0625</v>
+        <v>8</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>90</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>0.1222222222222222</v>
+        <v>11</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>83</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>0.4096385542168675</v>
+        <v>34</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>142</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>0.2253521126760563</v>
+        <v>32</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>114</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>0.04385964912280702</v>
+        <v>5</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>96</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>0.07291666666666667</v>
+        <v>7</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>91</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>0.07692307692307693</v>
+        <v>7</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>117</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>0.1282051282051282</v>
+        <v>15</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>74</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>0.1891891891891892</v>
+        <v>14</v>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
         <v>71</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>0.04225352112676056</v>
+        <v>3</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         <v>157</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>0.286624203821656</v>
+        <v>45</v>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>62</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>0.01612903225806452</v>
+        <v>1</v>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         <v>90</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>0.2555555555555555</v>
+        <v>23</v>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>66</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>0.7424242424242424</v>
+        <v>49</v>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
         <v>40</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>0.8</v>
+        <v>32</v>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>56</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>0.75</v>
+        <v>42</v>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
@@ -2843,7 +2843,7 @@
         <v>69</v>
       </c>
       <c r="M48" s="12" t="n">
-        <v>0.1449275362318841</v>
+        <v>10</v>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
@@ -2897,7 +2897,7 @@
         <v>52</v>
       </c>
       <c r="M49" s="12" t="n">
-        <v>0.07692307692307693</v>
+        <v>4</v>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
@@ -2951,7 +2951,7 @@
         <v>36</v>
       </c>
       <c r="M50" s="12" t="n">
-        <v>0.25</v>
+        <v>9</v>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>33</v>
       </c>
       <c r="M51" s="12" t="n">
-        <v>0.0303030303030303</v>
+        <v>1</v>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         <v>65</v>
       </c>
       <c r="M52" s="12" t="n">
-        <v>0.1384615384615385</v>
+        <v>9</v>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
@@ -3113,7 +3113,7 @@
         <v>57</v>
       </c>
       <c r="M53" s="12" t="n">
-        <v>0.05263157894736842</v>
+        <v>3</v>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         <v>48</v>
       </c>
       <c r="M54" s="12" t="n">
-        <v>0.7708333333333334</v>
+        <v>37</v>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
         <v>64</v>
       </c>
       <c r="M55" s="12" t="n">
-        <v>0.265625</v>
+        <v>17</v>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>40</v>
       </c>
       <c r="M56" s="12" t="n">
-        <v>0.075</v>
+        <v>3</v>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>65</v>
       </c>
       <c r="M57" s="12" t="n">
-        <v>0.04615384615384616</v>
+        <v>3</v>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>45</v>
       </c>
       <c r="M58" s="12" t="n">
-        <v>0.02222222222222222</v>
+        <v>1</v>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         <v>55</v>
       </c>
       <c r="M59" s="12" t="n">
-        <v>0.2363636363636364</v>
+        <v>13</v>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>98</v>
       </c>
       <c r="M62" s="12" t="n">
-        <v>0.03061224489795918</v>
+        <v>3</v>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
         <v>15</v>
       </c>
       <c r="M63" s="12" t="n">
-        <v>0.6666666666666666</v>
+        <v>10</v>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         <v>28</v>
       </c>
       <c r="M64" s="12" t="n">
-        <v>0.8571428571428571</v>
+        <v>24</v>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         <v>48</v>
       </c>
       <c r="M65" s="12" t="n">
-        <v>0.04166666666666666</v>
+        <v>2</v>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
@@ -3815,7 +3815,7 @@
         <v>23</v>
       </c>
       <c r="M66" s="12" t="n">
-        <v>0.6956521739130435</v>
+        <v>16</v>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
@@ -3869,7 +3869,7 @@
         <v>43</v>
       </c>
       <c r="M67" s="12" t="n">
-        <v>0.06976744186046512</v>
+        <v>3</v>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         <v>36</v>
       </c>
       <c r="M68" s="12" t="n">
-        <v>0.05555555555555555</v>
+        <v>2</v>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
@@ -3977,7 +3977,7 @@
         <v>13</v>
       </c>
       <c r="M69" s="12" t="n">
-        <v>0.5384615384615384</v>
+        <v>7</v>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         <v>33</v>
       </c>
       <c r="M70" s="12" t="n">
-        <v>0.5757575757575758</v>
+        <v>19</v>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
@@ -4085,7 +4085,7 @@
         <v>9</v>
       </c>
       <c r="M71" s="12" t="n">
-        <v>0.1111111111111111</v>
+        <v>1</v>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
         <v>25</v>
       </c>
       <c r="M72" s="12" t="n">
-        <v>0.08</v>
+        <v>2</v>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
@@ -4409,7 +4409,7 @@
         <v>10</v>
       </c>
       <c r="M77" s="12" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>

--- a/docs/files/REPORT_FILTRI/Agente - Marcelli Emanuele.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Marcelli Emanuele.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>74</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>6714</v>
+        <v>7114</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>4745</v>
+        <v>5027</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>2235</v>
+        <v>2399</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>579</v>
+        <v>622</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>451</v>
+        <v>479</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>381</v>
+        <v>400</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>203</v>
+        <v>227</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>516</v>
+        <v>542</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,35 +875,35 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>432</v>
+        <v>454</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>157</v>
+        <v>171</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>288</v>
+        <v>304</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>257</v>
+        <v>277</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -929,28 +929,28 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>199</v>
+        <v>215</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>430</v>
+        <v>452</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>191</v>
+        <v>219</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="M13" s="12" t="n">
         <v>5</v>
@@ -983,31 +983,31 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>300</v>
+        <v>321</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>251</v>
+        <v>272</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>256</v>
+        <v>273</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1037,31 +1037,31 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>289</v>
+        <v>304</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>367</v>
+        <v>401</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>401</v>
+        <v>432</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -1091,31 +1091,31 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>260</v>
+        <v>274</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>392</v>
+        <v>430</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>294</v>
+        <v>318</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1145,28 +1145,28 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>246</v>
+        <v>266</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>303</v>
+        <v>332</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>275</v>
+        <v>293</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>199</v>
+        <v>218</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>7</v>
@@ -1199,31 +1199,31 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>272</v>
+        <v>288</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>199</v>
+        <v>217</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
@@ -1234,12 +1234,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>11745</t>
+          <t>00218</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA</t>
+          <t>VICOFORTE</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1249,51 +1249,51 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>GIARRATANA SEARA</t>
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>210</v>
+        <v>223</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>224</v>
+        <v>177</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>29</v>
+        <v>71</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>5</v>
+        <v>72</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>150</v>
+        <v>99</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>89</v>
+        <v>31</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>00218</t>
+          <t>11745</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>VICOFORTE</t>
+          <t>BRESCIA</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1303,35 +1303,35 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>GIARRATANA SEARA</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>200</v>
+        <v>222</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>161</v>
+        <v>255</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>64</v>
+        <v>11</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>153</v>
+        <v>187</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>93</v>
+        <v>155</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>31</v>
+        <v>91</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
@@ -1342,12 +1342,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>01724</t>
+          <t>00209</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>ORZIVECCHI</t>
+          <t>CUNEO</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1357,35 +1357,35 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>SCIALO' MARCO</t>
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>84</v>
+        <v>201</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>95</v>
+        <v>11</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>152</v>
+        <v>134</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>59</v>
+        <v>161</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>11</v>
+        <v>57</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
@@ -1396,12 +1396,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>00209</t>
+          <t>01724</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>CUNEO</t>
+          <t>ORZIVECCHI</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1411,35 +1411,35 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>SCIALO' MARCO</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>191</v>
+        <v>88</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>9</v>
+        <v>98</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>127</v>
+        <v>155</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>151</v>
+        <v>60</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>55</v>
+        <v>12</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
@@ -1469,10 +1469,10 @@
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>132</v>
+        <v>151</v>
       </c>
       <c r="G23" s="12" t="n">
         <v>25</v>
@@ -1481,23 +1481,23 @@
         <v>5</v>
       </c>
       <c r="I23" s="12" t="n">
+        <v>99</v>
+      </c>
+      <c r="J23" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="K23" s="12" t="n">
         <v>96</v>
       </c>
-      <c r="J23" s="12" t="n">
-        <v>26</v>
-      </c>
-      <c r="K23" s="12" t="n">
-        <v>94</v>
-      </c>
       <c r="L23" s="12" t="n">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="M23" s="12" t="n">
         <v>5</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1523,10 +1523,10 @@
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="G24" s="12" t="n">
         <v>26</v>
@@ -1535,19 +1535,19 @@
         <v>26</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
@@ -1577,10 +1577,10 @@
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="G25" s="12" t="n">
         <v>1</v>
@@ -1589,16 +1589,16 @@
         <v>6</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="M25" s="12" t="n">
         <v>6</v>
@@ -1631,31 +1631,31 @@
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
@@ -1685,28 +1685,28 @@
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>328</v>
+        <v>345</v>
       </c>
       <c r="M27" s="12" t="n">
         <v>7</v>
@@ -1720,12 +1720,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>01956</t>
+          <t>01525</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>CREMA</t>
+          <t>GAZZANIGA</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1735,51 +1735,51 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>165</v>
+        <v>139</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>94</v>
+        <v>47</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>93</v>
+        <v>70</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>167</v>
+        <v>71</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>61</v>
+        <v>12</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>01525</t>
+          <t>01956</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>GAZZANIGA</t>
+          <t>CREMA</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1789,39 +1789,39 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>131</v>
+        <v>172</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>43</v>
+        <v>98</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>67</v>
+        <v>173</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1847,31 +1847,31 @@
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="G30" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K30" s="12" t="n">
         <v>33</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
@@ -1901,10 +1901,10 @@
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="G31" s="12" t="n">
         <v>4</v>
@@ -1913,19 +1913,19 @@
         <v>9</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K31" s="12" t="n">
         <v>46</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
@@ -1936,12 +1936,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>55496</t>
+          <t>51674</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>MOZZO</t>
+          <t>CARAVAGGIO</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1951,51 +1951,51 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>109</v>
+        <v>181</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>44</v>
+        <v>89</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="L32" s="12" t="n">
         <v>90</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>51674</t>
+          <t>55496</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>CARAVAGGIO</t>
+          <t>MOZZO</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2005,39 +2005,39 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="E33" s="12" t="n">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>173</v>
+        <v>118</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>81</v>
+        <v>46</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="K33" s="12" t="n">
+        <v>63</v>
+      </c>
+      <c r="L33" s="12" t="n">
+        <v>98</v>
+      </c>
+      <c r="M33" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="L33" s="12" t="n">
-        <v>83</v>
-      </c>
-      <c r="M33" s="12" t="n">
-        <v>34</v>
-      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2063,31 +2063,31 @@
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>142</v>
+        <v>157</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
@@ -2117,28 +2117,28 @@
         </is>
       </c>
       <c r="E35" s="12" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="M35" s="12" t="n">
         <v>5</v>
@@ -2171,10 +2171,10 @@
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="G36" s="12" t="n">
         <v>2</v>
@@ -2183,19 +2183,19 @@
         <v>27</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
@@ -2225,35 +2225,35 @@
         </is>
       </c>
       <c r="E37" s="12" t="n">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="F37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="M37" s="12" t="n">
         <v>7</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2279,35 +2279,35 @@
         </is>
       </c>
       <c r="E38" s="12" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="M38" s="12" t="n">
         <v>15</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2333,16 +2333,16 @@
         </is>
       </c>
       <c r="E39" s="12" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="G39" s="12" t="n">
         <v>5</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="I39" s="12" t="n">
         <v>45</v>
@@ -2351,10 +2351,10 @@
         <v>14</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="M39" s="12" t="n">
         <v>14</v>
@@ -2368,12 +2368,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>51037</t>
+          <t>01007</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>ACQUI TERME</t>
+          <t>CHIAVARI</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2383,51 +2383,51 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>DELUGAS NADIA</t>
+          <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
       <c r="E40" s="12" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>71</v>
+        <v>170</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>01007</t>
+          <t>51037</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>CHIAVARI</t>
+          <t>ACQUI TERME</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -2437,51 +2437,51 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>DELUGAS NADIA</t>
         </is>
       </c>
       <c r="E41" s="12" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>157</v>
+        <v>76</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>01378</t>
+          <t>01371</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>CARCARE</t>
+          <t>SAVONA</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -2495,31 +2495,31 @@
         </is>
       </c>
       <c r="E42" s="12" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>82</v>
+        <v>132</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="K42" s="12" t="n">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
@@ -2530,12 +2530,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>01371</t>
+          <t>01378</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>SAVONA</t>
+          <t>CARCARE</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -2549,31 +2549,31 @@
         </is>
       </c>
       <c r="E43" s="12" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="F43" s="12" t="n">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
@@ -2603,28 +2603,28 @@
         </is>
       </c>
       <c r="E44" s="12" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="M44" s="12" t="n">
         <v>0</v>
@@ -2657,35 +2657,35 @@
         </is>
       </c>
       <c r="E45" s="12" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F45" s="12" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="J45" s="12" t="n">
         <v>27</v>
       </c>
       <c r="K45" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M45" s="12" t="n">
         <v>49</v>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2711,28 +2711,28 @@
         </is>
       </c>
       <c r="E46" s="12" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="G46" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K46" s="12" t="n">
         <v>3</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="M46" s="12" t="n">
         <v>32</v>
@@ -2746,12 +2746,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>01971</t>
+          <t>01480</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>CREMONA</t>
+          <t>ASTI</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -2761,39 +2761,39 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>VIGNADUZZO EDI</t>
         </is>
       </c>
       <c r="E47" s="12" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>3</v>
+        <v>57</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>6</v>
+        <v>91</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K47" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2819,10 +2819,10 @@
         </is>
       </c>
       <c r="E48" s="12" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G48" s="12" t="n">
         <v>17</v>
@@ -2831,7 +2831,7 @@
         <v>7</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J48" s="12" t="n">
         <v>9</v>
@@ -2840,7 +2840,7 @@
         <v>7</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="M48" s="12" t="n">
         <v>10</v>
@@ -2854,12 +2854,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>01480</t>
+          <t>01971</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>ASTI</t>
+          <t>CREMONA</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -2869,39 +2869,39 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>VIGNADUZZO EDI</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="E49" s="12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F49" s="12" t="n">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>54</v>
+        <v>3</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>88</v>
+        <v>6</v>
       </c>
       <c r="I49" s="12" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J49" s="12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K49" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="M49" s="12" t="n">
-        <v>4</v>
+        <v>46</v>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2927,16 +2927,16 @@
         </is>
       </c>
       <c r="E50" s="12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="G50" s="12" t="n">
         <v>6</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I50" s="12" t="n">
         <v>35</v>
@@ -2945,13 +2945,13 @@
         <v>8</v>
       </c>
       <c r="K50" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="M50" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>43</v>
       </c>
       <c r="F51" s="12" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G51" s="12" t="n">
         <v>2</v>
@@ -3038,32 +3038,32 @@
         <v>39</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G52" s="12" t="n">
         <v>7</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I52" s="12" t="n">
         <v>27</v>
       </c>
       <c r="J52" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K52" s="12" t="n">
         <v>12</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="M52" s="12" t="n">
         <v>9</v>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -3089,19 +3089,19 @@
         </is>
       </c>
       <c r="E53" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G53" s="12" t="n">
         <v>3</v>
       </c>
       <c r="H53" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I53" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J53" s="12" t="n">
         <v>10</v>
@@ -3110,14 +3110,14 @@
         <v>13</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="M53" s="12" t="n">
         <v>3</v>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -3143,19 +3143,19 @@
         </is>
       </c>
       <c r="E54" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F54" s="12" t="n">
         <v>36</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H54" s="12" t="n">
         <v>33</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J54" s="12" t="n">
         <v>8</v>
@@ -3164,10 +3164,10 @@
         <v>9</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="M54" s="12" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
@@ -3197,19 +3197,19 @@
         </is>
       </c>
       <c r="E55" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F55" s="12" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H55" s="12" t="n">
         <v>7</v>
       </c>
       <c r="I55" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J55" s="12" t="n">
         <v>7</v>
@@ -3218,10 +3218,10 @@
         <v>14</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="M55" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
@@ -3232,12 +3232,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>11726</t>
+          <t>55864</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>REZZATO</t>
+          <t>OVADA</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -3247,51 +3247,51 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>GRAZIOSI DAVIDE</t>
+          <t>DELUGAS NADIA</t>
         </is>
       </c>
       <c r="E56" s="12" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="G56" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="H56" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="H56" s="12" t="n">
-        <v>4</v>
-      </c>
       <c r="I56" s="12" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J56" s="12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K56" s="12" t="n">
         <v>13</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="M56" s="12" t="n">
         <v>3</v>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>55864</t>
+          <t>02075</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>OVADA</t>
+          <t>SUZZARA</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -3301,35 +3301,35 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>DELUGAS NADIA</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="E57" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F57" s="12" t="n">
         <v>46</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="H57" s="12" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="I57" s="12" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="J57" s="12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K57" s="12" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="L57" s="12" t="n">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="M57" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
@@ -3340,12 +3340,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>02075</t>
+          <t>11726</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>SUZZARA</t>
+          <t>REZZATO</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -3355,51 +3355,51 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
       <c r="E58" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="J58" s="12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K58" s="12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L58" s="12" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="M58" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>01142</t>
+          <t>01561</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>SESTRI LEVANTE</t>
+          <t>PONTIROLO NUOVO</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -3409,51 +3409,51 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="E59" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F59" s="12" t="n">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="H59" s="12" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="I59" s="12" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="J59" s="12" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K59" s="12" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="M59" s="12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>01561</t>
+          <t>01283</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>PONTIROLO NUOVO</t>
+          <t>SARZANA</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -3463,51 +3463,51 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
       <c r="E60" s="12" t="n">
         <v>31</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="G60" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="H60" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I60" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="J60" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="K60" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H60" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I60" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="J60" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="K60" s="12" t="n">
-        <v>19</v>
-      </c>
       <c r="L60" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M60" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>01283</t>
+          <t>01142</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>SARZANA</t>
+          <t>SESTRI LEVANTE</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -3521,31 +3521,31 @@
         </is>
       </c>
       <c r="E61" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F61" s="12" t="n">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="H61" s="12" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="I61" s="12" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J61" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K61" s="12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L61" s="12" t="n">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="M61" s="12" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
@@ -3578,13 +3578,13 @@
         <v>27</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I62" s="12" t="n">
         <v>18</v>
@@ -3596,7 +3596,7 @@
         <v>9</v>
       </c>
       <c r="L62" s="12" t="n">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="M62" s="12" t="n">
         <v>3</v>
@@ -3629,47 +3629,47 @@
         </is>
       </c>
       <c r="E63" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="F63" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="H63" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="F63" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G63" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="H63" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I63" s="12" t="n">
-        <v>21</v>
-      </c>
       <c r="J63" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K63" s="12" t="n">
         <v>2</v>
       </c>
       <c r="L63" s="12" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="M63" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>02024</t>
+          <t>56297</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>CASALMAGGIORE</t>
+          <t>SAN PAOLO D'ARGON</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -3679,51 +3679,51 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="E64" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J64" s="12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K64" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="L64" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="M64" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="L64" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="M64" s="12" t="n">
-        <v>24</v>
-      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>01280</t>
+          <t>02004</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>LA SPEZIA</t>
+          <t>RIVOLTA D'ADDA</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -3733,32 +3733,32 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="E65" s="12" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F65" s="12" t="n">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H65" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I65" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="I65" s="12" t="n">
-        <v>23</v>
-      </c>
       <c r="J65" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K65" s="12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L65" s="12" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="M65" s="12" t="n">
         <v>2</v>
@@ -3772,12 +3772,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>01481</t>
+          <t>01280</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>VILLAFRANCA D'ASTI</t>
+          <t>LA SPEZIA</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -3787,51 +3787,51 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>VIGNADUZZO EDI</t>
+          <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
       <c r="E66" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="I66" s="12" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J66" s="12" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K66" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L66" s="12" t="n">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="M66" s="12" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>56297</t>
+          <t>52510</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>SAN PAOLO D'ARGON</t>
+          <t>PORTO MANTOVANO</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -3841,51 +3841,51 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="E67" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F67" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H67" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I67" s="12" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J67" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K67" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L67" s="12" t="n">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="M67" s="12" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>02004</t>
+          <t>11719</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>RIVOLTA D'ADDA</t>
+          <t>MONTICHIARI</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -3895,51 +3895,51 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="E68" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F68" s="12" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H68" s="12" t="n">
-        <v>3</v>
+        <v>84</v>
       </c>
       <c r="I68" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="J68" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="J68" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="K68" s="12" t="n">
-        <v>5</v>
-      </c>
       <c r="L68" s="12" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="M68" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>52510</t>
+          <t>01481</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>PORTO MANTOVANO</t>
+          <t>VILLAFRANCA D'ASTI</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -3949,51 +3949,51 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>VIGNADUZZO EDI</t>
         </is>
       </c>
       <c r="E69" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F69" s="12" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H69" s="12" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="I69" s="12" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J69" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K69" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L69" s="12" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="M69" s="12" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>54290</t>
+          <t>02024</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>GENOVA</t>
+          <t>CASALMAGGIORE</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -4003,51 +4003,51 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>DALLORTO ILARIA</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="E70" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="F70" s="12" t="n">
+        <v>37</v>
+      </c>
+      <c r="G70" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="H70" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="I70" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="F70" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G70" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="H70" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I70" s="12" t="n">
-        <v>15</v>
-      </c>
       <c r="J70" s="12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K70" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L70" s="12" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="M70" s="12" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>00350</t>
+          <t>54290</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>BORGO SAN DALMAZZO</t>
+          <t>GENOVA</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -4057,39 +4057,39 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>SCIALO' MARCO</t>
+          <t>DALLORTO ILARIA</t>
         </is>
       </c>
       <c r="E71" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="F71" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="H71" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="F71" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="G71" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H71" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="I71" s="12" t="n">
-        <v>15</v>
-      </c>
       <c r="J71" s="12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K71" s="12" t="n">
         <v>2</v>
       </c>
       <c r="L71" s="12" t="n">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="M71" s="12" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -4115,16 +4115,16 @@
         </is>
       </c>
       <c r="E72" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F72" s="12" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G72" s="12" t="n">
         <v>24</v>
       </c>
       <c r="H72" s="12" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="I72" s="12" t="n">
         <v>9</v>
@@ -4133,10 +4133,10 @@
         <v>1</v>
       </c>
       <c r="K72" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L72" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M72" s="12" t="n">
         <v>2</v>
@@ -4150,12 +4150,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>11719</t>
+          <t>00350</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>MONTICHIARI</t>
+          <t>BORGO SAN DALMAZZO</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -4165,39 +4165,39 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>SCIALO' MARCO</t>
         </is>
       </c>
       <c r="E73" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="F73" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="G73" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="I73" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="F73" s="12" t="n">
-        <v>30</v>
-      </c>
-      <c r="G73" s="12" t="n">
+      <c r="J73" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="H73" s="12" t="n">
-        <v>78</v>
-      </c>
-      <c r="I73" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="J73" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="K73" s="12" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="L73" s="12" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="M73" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -4226,13 +4226,13 @@
         <v>13</v>
       </c>
       <c r="F74" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G74" s="12" t="n">
         <v>16</v>
       </c>
       <c r="H74" s="12" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I74" s="12" t="n">
         <v>14</v>
@@ -4251,7 +4251,7 @@
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -4337,10 +4337,10 @@
         <v>10</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="H76" s="12" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="I76" s="12" t="n">
         <v>8</v>
@@ -4352,7 +4352,7 @@
         <v>0</v>
       </c>
       <c r="L76" s="12" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="M76" s="12" t="n">
         <v>0</v>
@@ -4413,7 +4413,7 @@
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -4445,7 +4445,7 @@
         <v>0</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H78" s="12" t="n">
         <v>0</v>
@@ -4460,14 +4460,14 @@
         <v>0</v>
       </c>
       <c r="L78" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M78" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -4550,13 +4550,13 @@
         <v>0</v>
       </c>
       <c r="F80" s="12" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="G80" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H80" s="12" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="I80" s="12" t="n">
         <v>0</v>
@@ -4604,7 +4604,7 @@
         <v>0</v>
       </c>
       <c r="F81" s="12" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G81" s="12" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
         <v>0</v>
       </c>
       <c r="F82" s="12" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G82" s="12" t="n">
         <v>0</v>
@@ -4766,13 +4766,13 @@
         <v>0</v>
       </c>
       <c r="F84" s="12" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G84" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H84" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I84" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/Agente - Marcelli Emanuele.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Marcelli Emanuele.xlsx
@@ -209,8 +209,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N84" headerRowCount="1">
-  <autoFilter ref="A10:N84"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N90" headerRowCount="1">
+  <autoFilter ref="A10:N90"/>
   <tableColumns count="14">
     <tableColumn id="1" name="PDV"/>
     <tableColumn id="2" name="Città"/>
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N84"/>
+  <dimension ref="A1:N90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -673,16 +673,16 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>7114</v>
+        <v>7490</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>5027</v>
+        <v>5311</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>2399</v>
+        <v>2481</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -1342,12 +1342,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>00209</t>
+          <t>04203</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>CUNEO</t>
+          <t>PORDENONE</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1357,35 +1357,35 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>SCIALO' MARCO</t>
+          <t>DI FILIPPO SIMONE</t>
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>161</v>
+        <v>244</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
@@ -1396,12 +1396,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>01724</t>
+          <t>00209</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>ORZIVECCHI</t>
+          <t>CUNEO</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1411,35 +1411,35 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>SCIALO' MARCO</t>
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>88</v>
+        <v>201</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>98</v>
+        <v>11</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>155</v>
+        <v>134</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>60</v>
+        <v>161</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>12</v>
+        <v>57</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
@@ -1450,12 +1450,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>01527</t>
+          <t>01724</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>DALMINE</t>
+          <t>ORZIVECCHI</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1465,51 +1465,51 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>151</v>
+        <v>88</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>25</v>
+        <v>98</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>99</v>
+        <v>155</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>96</v>
+        <v>41</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>141</v>
+        <v>60</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>01640</t>
+          <t>01527</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>SERIATE</t>
+          <t>DALMINE</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1519,51 +1519,51 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>218</v>
+        <v>151</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>209</v>
+        <v>141</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>01638</t>
+          <t>01640</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>GRUMELLO DEL MONTE</t>
+          <t>SERIATE</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1577,31 +1577,31 @@
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>278</v>
+        <v>218</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>181</v>
+        <v>209</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
@@ -1612,12 +1612,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>01351</t>
+          <t>01638</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>SAVONA</t>
+          <t>GRUMELLO DEL MONTE</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1627,51 +1627,51 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>BARNABA SALVATORE</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>114</v>
+        <v>278</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>56</v>
+        <v>6</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>111</v>
+        <v>74</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>38</v>
+        <v>93</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>138</v>
+        <v>181</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>01032</t>
+          <t>01837</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>GENOVA</t>
+          <t>LECCO</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1681,51 +1681,51 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>DALLORTO ILARIA</t>
+          <t>ADINOLFI VINCENZO</t>
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>228</v>
+        <v>166</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>345</v>
+        <v>153</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>01525</t>
+          <t>01351</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>GAZZANIGA</t>
+          <t>SAVONA</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1735,35 +1735,35 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>BARNABA SALVATORE</t>
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>124</v>
+        <v>152</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>139</v>
+        <v>114</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>70</v>
+        <v>111</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>71</v>
+        <v>138</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
@@ -1774,12 +1774,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>01956</t>
+          <t>01032</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>CREMA</t>
+          <t>GENOVA</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1789,35 +1789,35 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>DALLORTO ILARIA</t>
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>122</v>
+        <v>148</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>172</v>
+        <v>228</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>98</v>
+        <v>46</v>
       </c>
       <c r="H29" s="12" t="n">
+        <v>58</v>
+      </c>
+      <c r="I29" s="12" t="n">
+        <v>107</v>
+      </c>
+      <c r="J29" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="K29" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="L29" s="12" t="n">
+        <v>345</v>
+      </c>
+      <c r="M29" s="12" t="n">
         <v>7</v>
-      </c>
-      <c r="I29" s="12" t="n">
-        <v>97</v>
-      </c>
-      <c r="J29" s="12" t="n">
-        <v>30</v>
-      </c>
-      <c r="K29" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="L29" s="12" t="n">
-        <v>173</v>
-      </c>
-      <c r="M29" s="12" t="n">
-        <v>64</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
@@ -1828,12 +1828,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>01968</t>
+          <t>01525</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>CREMONA</t>
+          <t>GAZZANIGA</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1843,51 +1843,51 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>188</v>
+        <v>71</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>01008</t>
+          <t>01956</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>GENOVA</t>
+          <t>CREMA</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1897,35 +1897,35 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>DALLORTO ILARIA</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>126</v>
+        <v>172</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>4</v>
+        <v>98</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>63</v>
+        <v>97</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>140</v>
+        <v>173</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>9</v>
+        <v>64</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
@@ -1936,12 +1936,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>51674</t>
+          <t>01968</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>CARAVAGGIO</t>
+          <t>CREMONA</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1951,35 +1951,35 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>181</v>
+        <v>154</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>90</v>
+        <v>188</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
@@ -1990,12 +1990,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>55496</t>
+          <t>01008</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>MOZZO</t>
+          <t>GENOVA</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2005,51 +2005,51 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>DALLORTO ILARIA</t>
         </is>
       </c>
       <c r="E33" s="12" t="n">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I33" s="12" t="n">
+        <v>63</v>
+      </c>
+      <c r="J33" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="K33" s="12" t="n">
         <v>46</v>
       </c>
-      <c r="J33" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="K33" s="12" t="n">
-        <v>63</v>
-      </c>
       <c r="L33" s="12" t="n">
-        <v>98</v>
+        <v>140</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>02036</t>
+          <t>51674</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>CREMONA</t>
+          <t>CARAVAGGIO</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2059,51 +2059,51 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>107</v>
+        <v>181</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>129</v>
+        <v>11</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>249</v>
+        <v>44</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>157</v>
+        <v>90</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>01034</t>
+          <t>55496</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>GENOVA</t>
+          <t>MOZZO</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2113,51 +2113,51 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>DALLORTO ILARIA</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="E35" s="12" t="n">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>96</v>
+        <v>3</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>232</v>
+        <v>7</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>122</v>
+        <v>98</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>01718</t>
+          <t>02036</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>PONTEVICO</t>
+          <t>CREMONA</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2171,47 +2171,47 @@
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>143</v>
+        <v>107</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>2</v>
+        <v>129</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>27</v>
+        <v>249</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>105</v>
+        <v>157</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>01574</t>
+          <t>01034</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>TREVIGLIO</t>
+          <t>GENOVA</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2221,51 +2221,51 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>DALLORTO ILARIA</t>
         </is>
       </c>
       <c r="E37" s="12" t="n">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>2</v>
+        <v>96</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>0</v>
+        <v>232</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>96</v>
+        <v>122</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>01043</t>
+          <t>01718</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>GENOVA</t>
+          <t>PONTEVICO</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2275,51 +2275,51 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>DALLORTO ILARIA</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="E38" s="12" t="n">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>64</v>
+        <v>143</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>00215</t>
+          <t>01574</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>SAVIGLIANO</t>
+          <t>TREVIGLIO</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2329,51 +2329,51 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>GIARRATANA SEARA</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="E39" s="12" t="n">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>142</v>
+        <v>0</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>01007</t>
+          <t>01043</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>CHIAVARI</t>
+          <t>GENOVA</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2383,35 +2383,35 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>DALLORTO ILARIA</t>
         </is>
       </c>
       <c r="E40" s="12" t="n">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>170</v>
+        <v>127</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
@@ -2422,12 +2422,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>51037</t>
+          <t>00215</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>ACQUI TERME</t>
+          <t>SAVIGLIANO</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -2437,51 +2437,51 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>DELUGAS NADIA</t>
+          <t>GIARRATANA SEARA</t>
         </is>
       </c>
       <c r="E41" s="12" t="n">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="F41" s="12" t="n">
+        <v>142</v>
+      </c>
+      <c r="G41" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="H41" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="I41" s="12" t="n">
+        <v>45</v>
+      </c>
+      <c r="J41" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="K41" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="L41" s="12" t="n">
         <v>82</v>
       </c>
-      <c r="G41" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="H41" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="I41" s="12" t="n">
-        <v>56</v>
-      </c>
-      <c r="J41" s="12" t="n">
-        <v>23</v>
-      </c>
-      <c r="K41" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="L41" s="12" t="n">
-        <v>76</v>
-      </c>
       <c r="M41" s="12" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>01371</t>
+          <t>01007</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>SAVONA</t>
+          <t>CHIAVARI</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -2491,51 +2491,51 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>DELUGAS NADIA</t>
+          <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
       <c r="E42" s="12" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="K42" s="12" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>94</v>
+        <v>170</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>01378</t>
+          <t>51037</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>CARCARE</t>
+          <t>ACQUI TERME</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -2549,47 +2549,47 @@
         </is>
       </c>
       <c r="E43" s="12" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F43" s="12" t="n">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>01577</t>
+          <t>01371</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>ZANICA</t>
+          <t>SAVONA</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2599,51 +2599,51 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>DELUGAS NADIA</t>
         </is>
       </c>
       <c r="E44" s="12" t="n">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>83</v>
+        <v>132</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>11421</t>
+          <t>01378</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>CASALE MONFERRATO</t>
+          <t>CARCARE</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -2653,51 +2653,51 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>VIGNADUZZO EDI</t>
+          <t>DELUGAS NADIA</t>
         </is>
       </c>
       <c r="E45" s="12" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="F45" s="12" t="n">
-        <v>55</v>
+        <v>96</v>
       </c>
       <c r="G45" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="H45" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="I45" s="12" t="n">
+        <v>34</v>
+      </c>
+      <c r="J45" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="K45" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="H45" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="I45" s="12" t="n">
-        <v>52</v>
-      </c>
-      <c r="J45" s="12" t="n">
-        <v>27</v>
-      </c>
-      <c r="K45" s="12" t="n">
-        <v>6</v>
-      </c>
       <c r="L45" s="12" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>12112</t>
+          <t>01577</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>MANTOVA</t>
+          <t>ZANICA</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -2707,51 +2707,51 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="E46" s="12" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="K46" s="12" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>01480</t>
+          <t>11421</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>ASTI</t>
+          <t>CASALE MONFERRATO</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -2765,47 +2765,47 @@
         </is>
       </c>
       <c r="E47" s="12" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>91</v>
+        <v>14</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="K47" s="12" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>4</v>
+        <v>49</v>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>11455</t>
+          <t>12112</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>CASALE MONFERRATO</t>
+          <t>MANTOVA</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -2815,51 +2815,51 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>VIGNADUZZO EDI</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="E48" s="12" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="F48" s="12" t="n">
         <v>73</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="J48" s="12" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="K48" s="12" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="M48" s="12" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>01971</t>
+          <t>01480</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>CREMONA</t>
+          <t>ASTI</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -2869,51 +2869,51 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>VIGNADUZZO EDI</t>
         </is>
       </c>
       <c r="E49" s="12" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F49" s="12" t="n">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>3</v>
+        <v>57</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>6</v>
+        <v>91</v>
       </c>
       <c r="I49" s="12" t="n">
         <v>42</v>
       </c>
       <c r="J49" s="12" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K49" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="M49" s="12" t="n">
-        <v>46</v>
+        <v>4</v>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>51570</t>
+          <t>11455</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>VENTIMIGLIA</t>
+          <t>CASALE MONFERRATO</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -2923,51 +2923,51 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>BARNABA SALVATORE</t>
+          <t>VIGNADUZZO EDI</t>
         </is>
       </c>
       <c r="E50" s="12" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="J50" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K50" s="12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="M50" s="12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>59894</t>
+          <t>01971</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA</t>
+          <t>CREMONA</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -2977,35 +2977,35 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>SALVINELLI LUCA</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="E51" s="12" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="F51" s="12" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H51" s="12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I51" s="12" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="J51" s="12" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="K51" s="12" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="M51" s="12" t="n">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
@@ -3016,12 +3016,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>01135</t>
+          <t>51570</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>GENOVA</t>
+          <t>VENTIMIGLIA</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -3031,51 +3031,51 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>DALLORTO ILARIA</t>
+          <t>BARNABA SALVATORE</t>
         </is>
       </c>
       <c r="E52" s="12" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>30</v>
+        <v>84</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="J52" s="12" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K52" s="12" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="M52" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>01637</t>
+          <t>59894</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>CURNO</t>
+          <t>BRESCIA</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -3085,51 +3085,51 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>SALVINELLI LUCA</t>
         </is>
       </c>
       <c r="E53" s="12" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H53" s="12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I53" s="12" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J53" s="12" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="K53" s="12" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>61</v>
+        <v>33</v>
       </c>
       <c r="M53" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>01334</t>
+          <t>01135</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>FINALE LIGURE</t>
+          <t>GENOVA</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -3139,35 +3139,35 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>BARNABA SALVATORE</t>
+          <t>DALLORTO ILARIA</t>
         </is>
       </c>
       <c r="E54" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="J54" s="12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K54" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="L54" s="12" t="n">
+        <v>73</v>
+      </c>
+      <c r="M54" s="12" t="n">
         <v>9</v>
-      </c>
-      <c r="L54" s="12" t="n">
-        <v>53</v>
-      </c>
-      <c r="M54" s="12" t="n">
-        <v>40</v>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
@@ -3178,12 +3178,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>54151</t>
+          <t>01637</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>IMPERIA</t>
+          <t>CURNO</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -3193,35 +3193,35 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>BARNABA SALVATORE</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="E55" s="12" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F55" s="12" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="H55" s="12" t="n">
         <v>7</v>
       </c>
       <c r="I55" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J55" s="12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K55" s="12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="M55" s="12" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
@@ -3232,12 +3232,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>55864</t>
+          <t>01334</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>OVADA</t>
+          <t>FINALE LIGURE</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -3247,51 +3247,51 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>DELUGAS NADIA</t>
+          <t>BARNABA SALVATORE</t>
         </is>
       </c>
       <c r="E56" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J56" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K56" s="12" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="M56" s="12" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>02075</t>
+          <t>00259</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>SUZZARA</t>
+          <t>TETTO GARETTO</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -3301,51 +3301,51 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>SCIALO' MARCO</t>
         </is>
       </c>
       <c r="E57" s="12" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F57" s="12" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G57" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H57" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I57" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="H57" s="12" t="n">
-        <v>38</v>
-      </c>
-      <c r="I57" s="12" t="n">
-        <v>36</v>
-      </c>
       <c r="J57" s="12" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="K57" s="12" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L57" s="12" t="n">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="M57" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>11726</t>
+          <t>54151</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>REZZATO</t>
+          <t>IMPERIA</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -3355,51 +3355,51 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>GRAZIOSI DAVIDE</t>
+          <t>BARNABA SALVATORE</t>
         </is>
       </c>
       <c r="E58" s="12" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>27</v>
+        <v>74</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J58" s="12" t="n">
         <v>7</v>
       </c>
       <c r="K58" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L58" s="12" t="n">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="M58" s="12" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>01561</t>
+          <t>55864</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>PONTIROLO NUOVO</t>
+          <t>OVADA</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -3409,51 +3409,51 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>DELUGAS NADIA</t>
         </is>
       </c>
       <c r="E59" s="12" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="F59" s="12" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H59" s="12" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="I59" s="12" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="J59" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="K59" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="L59" s="12" t="n">
+        <v>69</v>
+      </c>
+      <c r="M59" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="K59" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="L59" s="12" t="n">
-        <v>27</v>
-      </c>
-      <c r="M59" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>01283</t>
+          <t>02075</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>SARZANA</t>
+          <t>SUZZARA</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -3463,35 +3463,35 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="E60" s="12" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="I60" s="12" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="J60" s="12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K60" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L60" s="12" t="n">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="M60" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
@@ -3502,12 +3502,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>01142</t>
+          <t>01561</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>SESTRI LEVANTE</t>
+          <t>PONTIROLO NUOVO</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -3517,51 +3517,51 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="E61" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F61" s="12" t="n">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="H61" s="12" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="I61" s="12" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="J61" s="12" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K61" s="12" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="L61" s="12" t="n">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="M61" s="12" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>01086</t>
+          <t>01283</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>RECCO</t>
+          <t>SARZANA</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -3575,31 +3575,31 @@
         </is>
       </c>
       <c r="E62" s="12" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J62" s="12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K62" s="12" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="L62" s="12" t="n">
-        <v>103</v>
+        <v>28</v>
       </c>
       <c r="M62" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
@@ -3610,12 +3610,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>12082</t>
+          <t>01142</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>VIADANA</t>
+          <t>SESTRI LEVANTE</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -3625,51 +3625,51 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
       <c r="E63" s="12" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F63" s="12" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="H63" s="12" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="I63" s="12" t="n">
         <v>23</v>
       </c>
       <c r="J63" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K63" s="12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L63" s="12" t="n">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="M63" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>56297</t>
+          <t>03827</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>SAN PAOLO D'ARGON</t>
+          <t>SAN BONIFACIO</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -3679,11 +3679,11 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>MARCONI ANDREA</t>
         </is>
       </c>
       <c r="E64" s="12" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F64" s="12" t="n">
         <v>0</v>
@@ -3695,19 +3695,19 @@
         <v>0</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J64" s="12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K64" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L64" s="12" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="M64" s="12" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
@@ -3718,12 +3718,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>02004</t>
+          <t>01086</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>RIVOLTA D'ADDA</t>
+          <t>RECCO</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -3733,51 +3733,51 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
       <c r="E65" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="F65" s="12" t="n">
+        <v>62</v>
+      </c>
+      <c r="G65" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="F65" s="12" t="n">
-        <v>45</v>
-      </c>
-      <c r="G65" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H65" s="12" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="I65" s="12" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J65" s="12" t="n">
         <v>6</v>
       </c>
       <c r="K65" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L65" s="12" t="n">
-        <v>41</v>
+        <v>103</v>
       </c>
       <c r="M65" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>01280</t>
+          <t>12082</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>LA SPEZIA</t>
+          <t>VIADANA</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -3787,51 +3787,51 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="E66" s="12" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G66" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="H66" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="J66" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="K66" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="L66" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="M66" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="H66" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="I66" s="12" t="n">
-        <v>24</v>
-      </c>
-      <c r="J66" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="K66" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L66" s="12" t="n">
-        <v>52</v>
-      </c>
-      <c r="M66" s="12" t="n">
-        <v>2</v>
-      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>52510</t>
+          <t>56297</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>PORTO MANTOVANO</t>
+          <t>SAN PAOLO D'ARGON</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -3841,35 +3841,35 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="E67" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F67" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H67" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I67" s="12" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J67" s="12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K67" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L67" s="12" t="n">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="M67" s="12" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
@@ -3880,12 +3880,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>11719</t>
+          <t>02004</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>MONTICHIARI</t>
+          <t>RIVOLTA D'ADDA</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -3895,51 +3895,51 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="E68" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F68" s="12" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H68" s="12" t="n">
-        <v>84</v>
+        <v>3</v>
       </c>
       <c r="I68" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="J68" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="K68" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="J68" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K68" s="12" t="n">
-        <v>14</v>
-      </c>
       <c r="L68" s="12" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="M68" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>01481</t>
+          <t>01280</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>VILLAFRANCA D'ASTI</t>
+          <t>LA SPEZIA</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -3949,51 +3949,51 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>VIGNADUZZO EDI</t>
+          <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
       <c r="E69" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F69" s="12" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H69" s="12" t="n">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="I69" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J69" s="12" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K69" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L69" s="12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="M69" s="12" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>02024</t>
+          <t>52510</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>CASALMAGGIORE</t>
+          <t>PORTO MANTOVANO</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -4007,47 +4007,47 @@
         </is>
       </c>
       <c r="E70" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F70" s="12" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I70" s="12" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J70" s="12" t="n">
         <v>6</v>
       </c>
       <c r="K70" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L70" s="12" t="n">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="M70" s="12" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>54290</t>
+          <t>11719</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>GENOVA</t>
+          <t>MONTICHIARI</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -4057,51 +4057,51 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>DALLORTO ILARIA</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="E71" s="12" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F71" s="12" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="H71" s="12" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="I71" s="12" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="J71" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K71" s="12" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="L71" s="12" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="M71" s="12" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>11725</t>
+          <t>01481</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>GAVARDO</t>
+          <t>VILLAFRANCA D'ASTI</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -4111,35 +4111,35 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>GRAZIOSI DAVIDE</t>
+          <t>VIGNADUZZO EDI</t>
         </is>
       </c>
       <c r="E72" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="F72" s="12" t="n">
+        <v>41</v>
+      </c>
+      <c r="G72" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="F72" s="12" t="n">
-        <v>36</v>
-      </c>
-      <c r="G72" s="12" t="n">
+      <c r="H72" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="I72" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="J72" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="K72" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="H72" s="12" t="n">
-        <v>56</v>
-      </c>
-      <c r="I72" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="J72" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K72" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="L72" s="12" t="n">
-        <v>26</v>
-      </c>
       <c r="M72" s="12" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
@@ -4150,12 +4150,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>00350</t>
+          <t>02024</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>BORGO SAN DALMAZZO</t>
+          <t>CASALMAGGIORE</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -4165,35 +4165,35 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>SCIALO' MARCO</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="E73" s="12" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F73" s="12" t="n">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="H73" s="12" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="I73" s="12" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J73" s="12" t="n">
         <v>6</v>
       </c>
       <c r="K73" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L73" s="12" t="n">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="M73" s="12" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
@@ -4204,12 +4204,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>01288</t>
+          <t>54290</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>BOLANO</t>
+          <t>GENOVA</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -4219,51 +4219,51 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>DALLORTO ILARIA</t>
         </is>
       </c>
       <c r="E74" s="12" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F74" s="12" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G74" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="H74" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="H74" s="12" t="n">
-        <v>21</v>
-      </c>
-      <c r="I74" s="12" t="n">
-        <v>14</v>
-      </c>
       <c r="J74" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K74" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L74" s="12" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="M74" s="12" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>01578</t>
+          <t>00350</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>VERDELLO</t>
+          <t>BORGO SAN DALMAZZO</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -4273,51 +4273,51 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>SCIALO' MARCO</t>
         </is>
       </c>
       <c r="E75" s="12" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F75" s="12" t="n">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="G75" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="I75" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="J75" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="K75" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="L75" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="M75" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H75" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="I75" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="J75" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="K75" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="L75" s="12" t="n">
-        <v>29</v>
-      </c>
-      <c r="M75" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>01671</t>
+          <t>01288</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA</t>
+          <t>BOLANO</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -4327,26 +4327,26 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>GRAZIOSI DAVIDE</t>
+          <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
       <c r="E76" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F76" s="12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="H76" s="12" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="I76" s="12" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="J76" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K76" s="12" t="n">
         <v>0</v>
@@ -4359,19 +4359,19 @@
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>02074</t>
+          <t>01578</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>GOITO</t>
+          <t>VERDELLO</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -4381,51 +4381,51 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="E77" s="12" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F77" s="12" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H77" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I77" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J77" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K77" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L77" s="12" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="M77" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>11348</t>
+          <t>01671</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>VADO LIGURE</t>
+          <t>BRESCIA</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -4435,51 +4435,51 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>DELUGAS NADIA</t>
+          <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
       <c r="E78" s="12" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="F78" s="12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G78" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="H78" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="I78" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="J78" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H78" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I78" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="J78" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="K78" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L78" s="12" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="M78" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>01339</t>
+          <t>02074</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>ALASSIO</t>
+          <t>GOITO</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -4489,35 +4489,35 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>BARNABA SALVATORE</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="E79" s="12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F79" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G79" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H79" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="J79" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K79" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="M79" s="12" t="n">
         <v>2</v>
-      </c>
-      <c r="I79" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J79" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K79" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L79" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M79" s="12" t="n">
-        <v>0</v>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
@@ -4528,12 +4528,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>01416</t>
+          <t>11348</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>SERRAVALLE SCRIVIA</t>
+          <t>VADO LIGURE</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -4547,19 +4547,19 @@
         </is>
       </c>
       <c r="E80" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F80" s="12" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H80" s="12" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="I80" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J80" s="12" t="n">
         <v>0</v>
@@ -4568,26 +4568,26 @@
         <v>0</v>
       </c>
       <c r="L80" s="12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M80" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>01522</t>
+          <t>00926</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>CASAZZA</t>
+          <t>GASSINO TORINESE</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -4597,20 +4597,20 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>BRESCIA FEDERICO</t>
         </is>
       </c>
       <c r="E81" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F81" s="12" t="n">
-        <v>56</v>
+        <v>6</v>
       </c>
       <c r="G81" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H81" s="12" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="I81" s="12" t="n">
         <v>0</v>
@@ -4629,19 +4629,19 @@
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>01639</t>
+          <t>01339</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>PIANICO</t>
+          <t>ALASSIO</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -4651,20 +4651,20 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>BARNABA SALVATORE</t>
         </is>
       </c>
       <c r="E82" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F82" s="12" t="n">
-        <v>78</v>
+        <v>8</v>
       </c>
       <c r="G82" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H82" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I82" s="12" t="n">
         <v>0</v>
@@ -4683,19 +4683,19 @@
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>02053</t>
+          <t>01416</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>BAGNOLO SAN VITO</t>
+          <t>SERRAVALLE SCRIVIA</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -4705,20 +4705,20 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>DELUGAS NADIA</t>
         </is>
       </c>
       <c r="E83" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F83" s="12" t="n">
-        <v>11</v>
+        <v>53</v>
       </c>
       <c r="G83" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H83" s="12" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="I83" s="12" t="n">
         <v>0</v>
@@ -4737,61 +4737,385 @@
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>01522</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>CASAZZA</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>BRIGNOLI STEFANO</t>
+        </is>
+      </c>
+      <c r="E84" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" s="12" t="n">
+        <v>56</v>
+      </c>
+      <c r="G84" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I84" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>01639</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>PIANICO</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>BRIGNOLI STEFANO</t>
+        </is>
+      </c>
+      <c r="E85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" s="12" t="n">
+        <v>78</v>
+      </c>
+      <c r="G85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>02053</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>BAGNOLO SAN VITO</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>CARMINATI SIMONE</t>
+        </is>
+      </c>
+      <c r="E86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="G86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>Da seguire</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>02970</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>FIDENZA</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>IACONA GIOVANNI</t>
+        </is>
+      </c>
+      <c r="E87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="G87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>Bene</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>05511</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>MEDICINA</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>MURGO LORENZO</t>
+        </is>
+      </c>
+      <c r="E88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>Bene</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
           <t>10241</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
         <is>
           <t>ALBA</t>
         </is>
       </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Emanuele</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>GIARRATANA SEARA</t>
         </is>
       </c>
-      <c r="E84" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F84" s="12" t="n">
+      <c r="E89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" s="12" t="n">
         <v>74</v>
       </c>
-      <c r="G84" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H84" s="12" t="n">
+      <c r="G89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="I84" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J84" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K84" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L84" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M84" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N84" s="2" t="inlineStr">
+      <c r="I89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N89" s="2" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>15548</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>PIANORO</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>MURGO LORENZO</t>
+        </is>
+      </c>
+      <c r="E90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>Bene</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/Agente - Marcelli Emanuele.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Marcelli Emanuele.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W16</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>80</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>7490</v>
+        <v>7956</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>5311</v>
+        <v>5634</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>2481</v>
+        <v>2690</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>622</v>
+        <v>678</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>479</v>
+        <v>497</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>400</v>
+        <v>438</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>227</v>
+        <v>245</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>542</v>
+        <v>574</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,31 +875,31 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>454</v>
+        <v>480</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>171</v>
+        <v>191</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>304</v>
+        <v>323</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>277</v>
+        <v>295</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -929,35 +929,35 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>384</v>
+        <v>408</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>452</v>
+        <v>487</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>272</v>
+        <v>285</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="M13" s="12" t="n">
         <v>5</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -983,31 +983,31 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>321</v>
+        <v>336</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1037,31 +1037,31 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>401</v>
+        <v>415</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="J15" s="12" t="n">
+        <v>77</v>
+      </c>
+      <c r="K15" s="12" t="n">
         <v>75</v>
       </c>
-      <c r="K15" s="12" t="n">
-        <v>72</v>
-      </c>
       <c r="L15" s="12" t="n">
-        <v>432</v>
+        <v>454</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -1091,31 +1091,31 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>274</v>
+        <v>288</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>430</v>
+        <v>451</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H16" s="12" t="n">
         <v>8</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>318</v>
+        <v>340</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1145,28 +1145,28 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>266</v>
+        <v>284</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>332</v>
+        <v>351</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>293</v>
+        <v>307</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>406</v>
+        <v>434</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>218</v>
+        <v>234</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>237</v>
+        <v>260</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>7</v>
@@ -1199,31 +1199,31 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="K18" s="12" t="n">
         <v>50</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
@@ -1253,35 +1253,35 @@
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>176</v>
+        <v>193</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="K19" s="12" t="n">
         <v>40</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M19" s="12" t="n">
         <v>31</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1307,31 +1307,31 @@
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>255</v>
+        <v>271</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
@@ -1361,47 +1361,47 @@
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="H21" s="12" t="n">
         <v>14</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>00209</t>
+          <t>01724</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>CUNEO</t>
+          <t>ORZIVECCHI</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1411,51 +1411,51 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>SCIALO' MARCO</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>195</v>
+        <v>212</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>201</v>
+        <v>91</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>11</v>
+        <v>105</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>134</v>
+        <v>164</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>161</v>
+        <v>62</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>01724</t>
+          <t>00209</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>ORZIVECCHI</t>
+          <t>CUNEO</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1465,35 +1465,35 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>SCIALO' MARCO</t>
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>88</v>
+        <v>210</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>98</v>
+        <v>12</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>60</v>
+        <v>173</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>12</v>
+        <v>59</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
@@ -1523,28 +1523,28 @@
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="J24" s="12" t="n">
         <v>28</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="M24" s="12" t="n">
         <v>5</v>
@@ -1577,10 +1577,10 @@
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="G25" s="12" t="n">
         <v>26</v>
@@ -1589,23 +1589,23 @@
         <v>26</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1631,10 +1631,10 @@
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="G26" s="12" t="n">
         <v>1</v>
@@ -1643,19 +1643,19 @@
         <v>6</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
@@ -1666,12 +1666,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>01837</t>
+          <t>01032</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>LECCO</t>
+          <t>GENOVA</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1681,39 +1681,39 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>ADINOLFI VINCENZO</t>
+          <t>DALLORTO ILARIA</t>
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>166</v>
+        <v>238</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>153</v>
+        <v>377</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1739,31 +1739,31 @@
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
@@ -1774,12 +1774,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>01032</t>
+          <t>01837</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>GENOVA</t>
+          <t>LECCO</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1789,39 +1789,39 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>DALLORTO ILARIA</t>
+          <t>ADINOLFI VINCENZO</t>
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>228</v>
+        <v>172</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>46</v>
+        <v>86</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>345</v>
+        <v>165</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1847,31 +1847,31 @@
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="F30" s="12" t="n">
         <v>139</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H30" s="12" t="n">
         <v>44</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
@@ -1882,12 +1882,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>01956</t>
+          <t>01968</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>CREMA</t>
+          <t>CREMONA</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1897,35 +1897,35 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>98</v>
+        <v>1</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>7</v>
+        <v>58</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>173</v>
+        <v>198</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
@@ -1936,12 +1936,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>01968</t>
+          <t>01956</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>CREMONA</t>
+          <t>CREMA</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1951,35 +1951,35 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>154</v>
+        <v>176</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>1</v>
+        <v>104</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>54</v>
+        <v>7</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
@@ -2009,35 +2009,35 @@
         </is>
       </c>
       <c r="E33" s="12" t="n">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H33" s="12" t="n">
         <v>9</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2063,31 +2063,31 @@
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="G34" s="12" t="n">
         <v>11</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
@@ -2117,35 +2117,35 @@
         </is>
       </c>
       <c r="E35" s="12" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="G35" s="12" t="n">
         <v>3</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2171,31 +2171,31 @@
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K36" s="12" t="n">
         <v>14</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
@@ -2206,12 +2206,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>01034</t>
+          <t>01718</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>GENOVA</t>
+          <t>PONTEVICO</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2221,35 +2221,35 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>DALLORTO ILARIA</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="E37" s="12" t="n">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>114</v>
+        <v>155</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>96</v>
+        <v>2</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>232</v>
+        <v>29</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
@@ -2260,12 +2260,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>01718</t>
+          <t>01034</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>PONTEVICO</t>
+          <t>GENOVA</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2275,35 +2275,35 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>DALLORTO ILARIA</t>
         </is>
       </c>
       <c r="E38" s="12" t="n">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>2</v>
+        <v>98</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>27</v>
+        <v>246</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>105</v>
+        <v>136</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
@@ -2333,35 +2333,35 @@
         </is>
       </c>
       <c r="E39" s="12" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2387,35 +2387,35 @@
         </is>
       </c>
       <c r="E40" s="12" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="M40" s="12" t="n">
         <v>15</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2441,19 +2441,19 @@
         </is>
       </c>
       <c r="E41" s="12" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="G41" s="12" t="n">
         <v>5</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J41" s="12" t="n">
         <v>14</v>
@@ -2462,7 +2462,7 @@
         <v>33</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="M41" s="12" t="n">
         <v>14</v>
@@ -2495,28 +2495,28 @@
         </is>
       </c>
       <c r="E42" s="12" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F42" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H42" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K42" s="12" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="M42" s="12" t="n">
         <v>48</v>
@@ -2549,10 +2549,10 @@
         </is>
       </c>
       <c r="E43" s="12" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F43" s="12" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G43" s="12" t="n">
         <v>4</v>
@@ -2561,19 +2561,19 @@
         <v>2</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K43" s="12" t="n">
         <v>17</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
@@ -2603,10 +2603,10 @@
         </is>
       </c>
       <c r="E44" s="12" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="G44" s="12" t="n">
         <v>5</v>
@@ -2615,19 +2615,19 @@
         <v>9</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K44" s="12" t="n">
         <v>15</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
@@ -2657,10 +2657,10 @@
         </is>
       </c>
       <c r="E45" s="12" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F45" s="12" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G45" s="12" t="n">
         <v>7</v>
@@ -2669,16 +2669,16 @@
         <v>15</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K45" s="12" t="n">
         <v>35</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="M45" s="12" t="n">
         <v>1</v>
@@ -2711,10 +2711,10 @@
         </is>
       </c>
       <c r="E46" s="12" t="n">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G46" s="12" t="n">
         <v>3</v>
@@ -2723,16 +2723,16 @@
         <v>7</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J46" s="12" t="n">
         <v>3</v>
       </c>
       <c r="K46" s="12" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M46" s="12" t="n">
         <v>0</v>
@@ -2765,31 +2765,31 @@
         </is>
       </c>
       <c r="E47" s="12" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H47" s="12" t="n">
         <v>14</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K47" s="12" t="n">
         <v>6</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
@@ -2800,12 +2800,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>12112</t>
+          <t>01480</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>MANTOVA</t>
+          <t>ASTI</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -2815,35 +2815,35 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>VIGNADUZZO EDI</t>
         </is>
       </c>
       <c r="E48" s="12" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>8</v>
+        <v>94</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="J48" s="12" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="K48" s="12" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="M48" s="12" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
@@ -2854,12 +2854,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>01480</t>
+          <t>12112</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>ASTI</t>
+          <t>MANTOVA</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -2869,35 +2869,35 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>VIGNADUZZO EDI</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="E49" s="12" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F49" s="12" t="n">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>57</v>
+        <v>1</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>91</v>
+        <v>8</v>
       </c>
       <c r="I49" s="12" t="n">
+        <v>55</v>
+      </c>
+      <c r="J49" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="K49" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="L49" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="J49" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="K49" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="L49" s="12" t="n">
-        <v>58</v>
-      </c>
       <c r="M49" s="12" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
@@ -2908,12 +2908,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>11455</t>
+          <t>01971</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>CASALE MONFERRATO</t>
+          <t>CREMONA</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -2923,51 +2923,51 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>VIGNADUZZO EDI</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="E50" s="12" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J50" s="12" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="K50" s="12" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="M50" s="12" t="n">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>01971</t>
+          <t>11455</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>CREMONA</t>
+          <t>CASALE MONFERRATO</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -2977,35 +2977,35 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>VIGNADUZZO EDI</t>
         </is>
       </c>
       <c r="E51" s="12" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F51" s="12" t="n">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="H51" s="12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I51" s="12" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="J51" s="12" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K51" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="L51" s="12" t="n">
+        <v>79</v>
+      </c>
+      <c r="M51" s="12" t="n">
         <v>12</v>
-      </c>
-      <c r="L51" s="12" t="n">
-        <v>63</v>
-      </c>
-      <c r="M51" s="12" t="n">
-        <v>46</v>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
@@ -3038,13 +3038,13 @@
         <v>46</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G52" s="12" t="n">
         <v>6</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I52" s="12" t="n">
         <v>35</v>
@@ -3124,12 +3124,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>01135</t>
+          <t>01637</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>GENOVA</t>
+          <t>CURNO</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -3139,51 +3139,51 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>DALLORTO ILARIA</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="E54" s="12" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>30</v>
+        <v>72</v>
       </c>
       <c r="G54" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="H54" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="H54" s="12" t="n">
+      <c r="I54" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="J54" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="K54" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="L54" s="12" t="n">
+        <v>63</v>
+      </c>
+      <c r="M54" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I54" s="12" t="n">
-        <v>27</v>
-      </c>
-      <c r="J54" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="K54" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="L54" s="12" t="n">
-        <v>73</v>
-      </c>
-      <c r="M54" s="12" t="n">
-        <v>9</v>
-      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>01637</t>
+          <t>01334</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>CURNO</t>
+          <t>FINALE LIGURE</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -3193,51 +3193,51 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>BARNABA SALVATORE</t>
         </is>
       </c>
       <c r="E55" s="12" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F55" s="12" t="n">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="H55" s="12" t="n">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="I55" s="12" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="J55" s="12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K55" s="12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="M55" s="12" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>01334</t>
+          <t>01135</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>FINALE LIGURE</t>
+          <t>GENOVA</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -3247,35 +3247,35 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>BARNABA SALVATORE</t>
+          <t>DALLORTO ILARIA</t>
         </is>
       </c>
       <c r="E56" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="J56" s="12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K56" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="L56" s="12" t="n">
+        <v>76</v>
+      </c>
+      <c r="M56" s="12" t="n">
         <v>9</v>
-      </c>
-      <c r="L56" s="12" t="n">
-        <v>53</v>
-      </c>
-      <c r="M56" s="12" t="n">
-        <v>40</v>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
@@ -3286,12 +3286,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>00259</t>
+          <t>54151</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>TETTO GARETTO</t>
+          <t>IMPERIA</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -3301,51 +3301,51 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>SCIALO' MARCO</t>
+          <t>BARNABA SALVATORE</t>
         </is>
       </c>
       <c r="E57" s="12" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F57" s="12" t="n">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="H57" s="12" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I57" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J57" s="12" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K57" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L57" s="12" t="n">
-        <v>31</v>
+        <v>71</v>
       </c>
       <c r="M57" s="12" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>54151</t>
+          <t>00259</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>IMPERIA</t>
+          <t>TETTO GARETTO</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -3355,51 +3355,51 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>BARNABA SALVATORE</t>
+          <t>SCIALO' MARCO</t>
         </is>
       </c>
       <c r="E58" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I58" s="12" t="n">
         <v>24</v>
       </c>
       <c r="J58" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K58" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="L58" s="12" t="n">
+        <v>34</v>
+      </c>
+      <c r="M58" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="K58" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="L58" s="12" t="n">
-        <v>68</v>
-      </c>
-      <c r="M58" s="12" t="n">
-        <v>19</v>
-      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>55864</t>
+          <t>01142</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>OVADA</t>
+          <t>SESTRI LEVANTE</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -3409,35 +3409,35 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>DELUGAS NADIA</t>
+          <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
       <c r="E59" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F59" s="12" t="n">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="H59" s="12" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I59" s="12" t="n">
         <v>24</v>
       </c>
       <c r="J59" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K59" s="12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="M59" s="12" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
@@ -3448,12 +3448,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>02075</t>
+          <t>55864</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>SUZZARA</t>
+          <t>OVADA</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -3463,35 +3463,35 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>DELUGAS NADIA</t>
         </is>
       </c>
       <c r="E60" s="12" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G60" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="H60" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="I60" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="H60" s="12" t="n">
-        <v>38</v>
-      </c>
-      <c r="I60" s="12" t="n">
-        <v>36</v>
-      </c>
       <c r="J60" s="12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K60" s="12" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L60" s="12" t="n">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="M60" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
@@ -3502,12 +3502,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>01561</t>
+          <t>02075</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>PONTIROLO NUOVO</t>
+          <t>SUZZARA</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -3517,39 +3517,39 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="E61" s="12" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F61" s="12" t="n">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="H61" s="12" t="n">
+        <v>39</v>
+      </c>
+      <c r="I61" s="12" t="n">
+        <v>37</v>
+      </c>
+      <c r="J61" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="K61" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" s="12" t="n">
+        <v>49</v>
+      </c>
+      <c r="M61" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I61" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="J61" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="K61" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="L61" s="12" t="n">
-        <v>27</v>
-      </c>
-      <c r="M61" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -3575,19 +3575,19 @@
         </is>
       </c>
       <c r="E62" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H62" s="12" t="n">
         <v>3</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J62" s="12" t="n">
         <v>5</v>
@@ -3610,12 +3610,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>01142</t>
+          <t>01561</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>SESTRI LEVANTE</t>
+          <t>PONTIROLO NUOVO</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -3625,39 +3625,39 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="E63" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F63" s="12" t="n">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="H63" s="12" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="I63" s="12" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="J63" s="12" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K63" s="12" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="L63" s="12" t="n">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="M63" s="12" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -3683,19 +3683,19 @@
         </is>
       </c>
       <c r="E64" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="F64" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="H64" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" s="12" t="n">
         <v>29</v>
-      </c>
-      <c r="F64" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G64" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="H64" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I64" s="12" t="n">
-        <v>27</v>
       </c>
       <c r="J64" s="12" t="n">
         <v>8</v>
@@ -3704,10 +3704,10 @@
         <v>3</v>
       </c>
       <c r="L64" s="12" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="M64" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
@@ -3737,28 +3737,28 @@
         </is>
       </c>
       <c r="E65" s="12" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F65" s="12" t="n">
         <v>62</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H65" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I65" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J65" s="12" t="n">
         <v>6</v>
       </c>
       <c r="K65" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L65" s="12" t="n">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="M65" s="12" t="n">
         <v>3</v>
@@ -3791,25 +3791,25 @@
         </is>
       </c>
       <c r="E66" s="12" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F66" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H66" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I66" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J66" s="12" t="n">
         <v>7</v>
       </c>
       <c r="K66" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L66" s="12" t="n">
         <v>18</v>
@@ -3819,7 +3819,7 @@
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="E67" s="12" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F67" s="12" t="n">
         <v>0</v>
@@ -3860,13 +3860,13 @@
         <v>19</v>
       </c>
       <c r="J67" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K67" s="12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L67" s="12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M67" s="12" t="n">
         <v>3</v>
@@ -3880,12 +3880,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>02004</t>
+          <t>11719</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>RIVOLTA D'ADDA</t>
+          <t>MONTICHIARI</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -3895,35 +3895,35 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="E68" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F68" s="12" t="n">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="H68" s="12" t="n">
-        <v>3</v>
+        <v>94</v>
       </c>
       <c r="I68" s="12" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J68" s="12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K68" s="12" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="L68" s="12" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="M68" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
@@ -3934,12 +3934,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>01280</t>
+          <t>01481</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>LA SPEZIA</t>
+          <t>VILLAFRANCA D'ASTI</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -3949,51 +3949,51 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>VIGNADUZZO EDI</t>
         </is>
       </c>
       <c r="E69" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F69" s="12" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="H69" s="12" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="I69" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="J69" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="K69" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="J69" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="K69" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L69" s="12" t="n">
-        <v>52</v>
-      </c>
       <c r="M69" s="12" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>52510</t>
+          <t>02004</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>PORTO MANTOVANO</t>
+          <t>RIVOLTA D'ADDA</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -4003,51 +4003,51 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="E70" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F70" s="12" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I70" s="12" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="J70" s="12" t="n">
         <v>6</v>
       </c>
       <c r="K70" s="12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L70" s="12" t="n">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="M70" s="12" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>11719</t>
+          <t>01280</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>MONTICHIARI</t>
+          <t>LA SPEZIA</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -4057,51 +4057,51 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
       <c r="E71" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F71" s="12" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H71" s="12" t="n">
-        <v>84</v>
+        <v>16</v>
       </c>
       <c r="I71" s="12" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="J71" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K71" s="12" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="L71" s="12" t="n">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="M71" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>01481</t>
+          <t>52510</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>VILLAFRANCA D'ASTI</t>
+          <t>PORTO MANTOVANO</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -4111,39 +4111,39 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>VIGNADUZZO EDI</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="E72" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F72" s="12" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="H72" s="12" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="I72" s="12" t="n">
         <v>22</v>
       </c>
       <c r="J72" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="K72" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="M72" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="K72" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L72" s="12" t="n">
-        <v>24</v>
-      </c>
-      <c r="M72" s="12" t="n">
-        <v>17</v>
-      </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -4175,7 +4175,7 @@
         <v>37</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="H73" s="12" t="n">
         <v>15</v>
@@ -4190,10 +4190,10 @@
         <v>3</v>
       </c>
       <c r="L73" s="12" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="M73" s="12" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="E74" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F74" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H74" s="12" t="n">
         <v>0</v>
@@ -4241,13 +4241,13 @@
         <v>2</v>
       </c>
       <c r="K74" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L74" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M74" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         <v>16</v>
       </c>
       <c r="F75" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G75" s="12" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
         <v>16</v>
       </c>
       <c r="H76" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I76" s="12" t="n">
         <v>14</v>
@@ -4352,7 +4352,7 @@
         <v>0</v>
       </c>
       <c r="L76" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M76" s="12" t="n">
         <v>0</v>
@@ -4388,7 +4388,7 @@
         <v>13</v>
       </c>
       <c r="F77" s="12" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G77" s="12" t="n">
         <v>1</v>
@@ -4442,13 +4442,13 @@
         <v>11</v>
       </c>
       <c r="F78" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H78" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I78" s="12" t="n">
         <v>8</v>
@@ -4514,7 +4514,7 @@
         <v>0</v>
       </c>
       <c r="L79" s="12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="M79" s="12" t="n">
         <v>2</v>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="E80" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F80" s="12" t="n">
         <v>0</v>
@@ -4559,7 +4559,7 @@
         <v>0</v>
       </c>
       <c r="I80" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J80" s="12" t="n">
         <v>0</v>
@@ -4712,13 +4712,13 @@
         <v>0</v>
       </c>
       <c r="F83" s="12" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G83" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H83" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I83" s="12" t="n">
         <v>0</v>
@@ -4766,13 +4766,13 @@
         <v>0</v>
       </c>
       <c r="F84" s="12" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G84" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H84" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I84" s="12" t="n">
         <v>0</v>
@@ -4820,7 +4820,7 @@
         <v>0</v>
       </c>
       <c r="F85" s="12" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="G85" s="12" t="n">
         <v>0</v>
@@ -5036,7 +5036,7 @@
         <v>0</v>
       </c>
       <c r="F89" s="12" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G89" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/Agente - Marcelli Emanuele.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Marcelli Emanuele.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W16</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>80</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>7956</v>
+        <v>8374</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>5634</v>
+        <v>5933</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>2690</v>
+        <v>2864</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>678</v>
+        <v>715</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>497</v>
+        <v>517</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="H11" s="12" t="n">
         <v>54</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>438</v>
+        <v>465</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>574</v>
+        <v>597</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,35 +875,35 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>480</v>
+        <v>500</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="H12" s="12" t="n">
         <v>27</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>323</v>
+        <v>336</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>295</v>
+        <v>314</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -929,28 +929,28 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>408</v>
+        <v>433</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>487</v>
+        <v>517</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>285</v>
+        <v>304</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="M13" s="12" t="n">
         <v>5</v>
@@ -983,35 +983,35 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>336</v>
+        <v>353</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>283</v>
+        <v>304</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1037,31 +1037,31 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>313</v>
+        <v>328</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>415</v>
+        <v>440</v>
       </c>
       <c r="G15" s="12" t="n">
+        <v>84</v>
+      </c>
+      <c r="H15" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="I15" s="12" t="n">
+        <v>250</v>
+      </c>
+      <c r="J15" s="12" t="n">
+        <v>78</v>
+      </c>
+      <c r="K15" s="12" t="n">
         <v>81</v>
       </c>
-      <c r="H15" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="I15" s="12" t="n">
-        <v>241</v>
-      </c>
-      <c r="J15" s="12" t="n">
-        <v>77</v>
-      </c>
-      <c r="K15" s="12" t="n">
-        <v>75</v>
-      </c>
       <c r="L15" s="12" t="n">
-        <v>454</v>
+        <v>478</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -1072,12 +1072,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>01507</t>
+          <t>01024</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>BERGAMO</t>
+          <t>GENOVA</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1087,35 +1087,35 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>DALLORTO ILARIA</t>
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>288</v>
+        <v>302</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>451</v>
+        <v>358</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>37</v>
+        <v>322</v>
       </c>
       <c r="H16" s="12" t="n">
+        <v>452</v>
+      </c>
+      <c r="I16" s="12" t="n">
+        <v>248</v>
+      </c>
+      <c r="J16" s="12" t="n">
+        <v>86</v>
+      </c>
+      <c r="K16" s="12" t="n">
+        <v>56</v>
+      </c>
+      <c r="L16" s="12" t="n">
+        <v>273</v>
+      </c>
+      <c r="M16" s="12" t="n">
         <v>8</v>
-      </c>
-      <c r="I16" s="12" t="n">
-        <v>218</v>
-      </c>
-      <c r="J16" s="12" t="n">
-        <v>88</v>
-      </c>
-      <c r="K16" s="12" t="n">
-        <v>73</v>
-      </c>
-      <c r="L16" s="12" t="n">
-        <v>340</v>
-      </c>
-      <c r="M16" s="12" t="n">
-        <v>60</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1126,12 +1126,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>01024</t>
+          <t>01507</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>GENOVA</t>
+          <t>BERGAMO</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1141,35 +1141,35 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>DALLORTO ILARIA</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>351</v>
+        <v>482</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>307</v>
+        <v>37</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>434</v>
+        <v>8</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>260</v>
+        <v>340</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>7</v>
+        <v>60</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
@@ -1180,12 +1180,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>11418</t>
+          <t>11745</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>ASTI</t>
+          <t>BRESCIA</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1195,39 +1195,39 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>VIGNADUZZO EDI</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>240</v>
+        <v>266</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>294</v>
+        <v>305</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>174</v>
+        <v>51</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>223</v>
+        <v>15</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>194</v>
+        <v>221</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>188</v>
+        <v>166</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>46</v>
+        <v>97</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1253,31 +1253,31 @@
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>182</v>
+        <v>208</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
@@ -1288,12 +1288,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>11745</t>
+          <t>11418</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA</t>
+          <t>ASTI</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1303,39 +1303,39 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>VIGNADUZZO EDI</t>
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>236</v>
+        <v>249</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>271</v>
+        <v>312</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>42</v>
+        <v>178</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>13</v>
+        <v>234</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="J20" s="12" t="n">
+        <v>82</v>
+      </c>
+      <c r="K20" s="12" t="n">
         <v>56</v>
       </c>
-      <c r="K20" s="12" t="n">
-        <v>42</v>
-      </c>
       <c r="L20" s="12" t="n">
-        <v>159</v>
+        <v>199</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>94</v>
+        <v>46</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1361,47 +1361,47 @@
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>01724</t>
+          <t>00209</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>ORZIVECCHI</t>
+          <t>CUNEO</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1411,51 +1411,51 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>SCIALO' MARCO</t>
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>91</v>
+        <v>220</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>105</v>
+        <v>12</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="L22" s="12" t="n">
+        <v>182</v>
+      </c>
+      <c r="M22" s="12" t="n">
         <v>62</v>
       </c>
-      <c r="M22" s="12" t="n">
-        <v>13</v>
-      </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>00209</t>
+          <t>01724</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>CUNEO</t>
+          <t>ORZIVECCHI</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1465,35 +1465,35 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>SCIALO' MARCO</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>210</v>
+        <v>95</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>12</v>
+        <v>110</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>146</v>
+        <v>170</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="K23" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="L23" s="12" t="n">
         <v>64</v>
       </c>
-      <c r="L23" s="12" t="n">
-        <v>173</v>
-      </c>
       <c r="M23" s="12" t="n">
-        <v>59</v>
+        <v>14</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
@@ -1504,12 +1504,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>01527</t>
+          <t>01640</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>DALMINE</t>
+          <t>SERIATE</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1519,51 +1519,51 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>159</v>
+        <v>240</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>147</v>
+        <v>226</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>01640</t>
+          <t>01527</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>SERIATE</t>
+          <t>DALMINE</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1573,35 +1573,35 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>221</v>
+        <v>165</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>84</v>
+        <v>101</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>221</v>
+        <v>156</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
@@ -1631,10 +1631,10 @@
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="G26" s="12" t="n">
         <v>1</v>
@@ -1643,19 +1643,19 @@
         <v>6</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
@@ -1666,12 +1666,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>01032</t>
+          <t>01351</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>GENOVA</t>
+          <t>SAVONA</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1681,51 +1681,51 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>DALLORTO ILARIA</t>
+          <t>BARNABA SALVATORE</t>
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>238</v>
+        <v>139</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>377</v>
+        <v>159</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>01351</t>
+          <t>01837</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>SAVONA</t>
+          <t>LECCO</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1735,35 +1735,35 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>BARNABA SALVATORE</t>
+          <t>ADINOLFI VINCENZO</t>
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>128</v>
+        <v>190</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>18</v>
+        <v>96</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>118</v>
+        <v>138</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>148</v>
+        <v>171</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
@@ -1774,12 +1774,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>01837</t>
+          <t>01032</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>LECCO</t>
+          <t>GENOVA</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1789,51 +1789,51 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>ADINOLFI VINCENZO</t>
+          <t>DALLORTO ILARIA</t>
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>172</v>
+        <v>242</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>86</v>
+        <v>59</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>165</v>
+        <v>403</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>01525</t>
+          <t>01968</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>GAZZANIGA</t>
+          <t>CREMONA</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1843,51 +1843,51 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>139</v>
+        <v>176</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>79</v>
+        <v>209</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>01968</t>
+          <t>01525</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>CREMONA</t>
+          <t>GAZZANIGA</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1897,51 +1897,51 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>198</v>
+        <v>89</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>01956</t>
+          <t>01008</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>CREMA</t>
+          <t>GENOVA</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1951,51 +1951,51 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>DALLORTO ILARIA</t>
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>176</v>
+        <v>142</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>104</v>
+        <v>5</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>67</v>
+        <v>10</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>01008</t>
+          <t>01956</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>GENOVA</t>
+          <t>CREMA</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2005,39 +2005,39 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>DALLORTO ILARIA</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="E33" s="12" t="n">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>132</v>
+        <v>186</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>5</v>
+        <v>116</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>67</v>
+        <v>105</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>159</v>
+        <v>191</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>10</v>
+        <v>78</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2063,31 +2063,31 @@
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
@@ -2098,12 +2098,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>55496</t>
+          <t>02036</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>MOZZO</t>
+          <t>CREMONA</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2113,51 +2113,51 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="E35" s="12" t="n">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>3</v>
+        <v>153</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>8</v>
+        <v>268</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>49</v>
+        <v>101</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>64</v>
+        <v>15</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>102</v>
+        <v>175</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>14</v>
+        <v>55</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>02036</t>
+          <t>55496</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>CREMONA</t>
+          <t>MOZZO</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2167,51 +2167,51 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>144</v>
+        <v>3</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>258</v>
+        <v>8</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>95</v>
+        <v>51</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>14</v>
+        <v>64</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>167</v>
+        <v>108</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>01718</t>
+          <t>01034</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>PONTEVICO</t>
+          <t>GENOVA</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2221,35 +2221,35 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>DALLORTO ILARIA</t>
         </is>
       </c>
       <c r="E37" s="12" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>155</v>
+        <v>126</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>29</v>
+        <v>261</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>124</v>
+        <v>141</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
@@ -2260,12 +2260,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>01034</t>
+          <t>01718</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>GENOVA</t>
+          <t>PONTEVICO</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2275,35 +2275,35 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>DALLORTO ILARIA</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="E38" s="12" t="n">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>120</v>
+        <v>163</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>98</v>
+        <v>2</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>246</v>
+        <v>30</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="E39" s="12" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F39" s="12" t="n">
         <v>0</v>
@@ -2345,7 +2345,7 @@
         <v>0</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="J39" s="12" t="n">
         <v>16</v>
@@ -2354,7 +2354,7 @@
         <v>16</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="M39" s="12" t="n">
         <v>8</v>
@@ -2387,19 +2387,19 @@
         </is>
       </c>
       <c r="E40" s="12" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="J40" s="12" t="n">
         <v>26</v>
@@ -2408,14 +2408,14 @@
         <v>24</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2441,31 +2441,31 @@
         </is>
       </c>
       <c r="E41" s="12" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>149</v>
+        <v>165</v>
       </c>
       <c r="G41" s="12" t="n">
         <v>5</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="E42" s="12" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F42" s="12" t="n">
         <v>0</v>
@@ -2507,7 +2507,7 @@
         <v>0</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J42" s="12" t="n">
         <v>8</v>
@@ -2516,26 +2516,26 @@
         <v>44</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>51037</t>
+          <t>01378</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>ACQUI TERME</t>
+          <t>CARCARE</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -2549,47 +2549,47 @@
         </is>
       </c>
       <c r="E43" s="12" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F43" s="12" t="n">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>01371</t>
+          <t>51037</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>SAVONA</t>
+          <t>ACQUI TERME</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2603,47 +2603,47 @@
         </is>
       </c>
       <c r="E44" s="12" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>136</v>
+        <v>96</v>
       </c>
       <c r="G44" s="12" t="n">
         <v>5</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>01378</t>
+          <t>01371</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>CARCARE</t>
+          <t>SAVONA</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -2657,31 +2657,31 @@
         </is>
       </c>
       <c r="E45" s="12" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F45" s="12" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="K45" s="12" t="n">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>70</v>
+        <v>104</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
@@ -2711,28 +2711,28 @@
         </is>
       </c>
       <c r="E46" s="12" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H46" s="12" t="n">
         <v>7</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J46" s="12" t="n">
         <v>3</v>
       </c>
       <c r="K46" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="M46" s="12" t="n">
         <v>0</v>
@@ -2765,47 +2765,47 @@
         </is>
       </c>
       <c r="E47" s="12" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K47" s="12" t="n">
         <v>6</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>01480</t>
+          <t>12112</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>ASTI</t>
+          <t>MANTOVA</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -2815,35 +2815,35 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>VIGNADUZZO EDI</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="E48" s="12" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>94</v>
+        <v>8</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="J48" s="12" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="K48" s="12" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="M48" s="12" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
@@ -2854,12 +2854,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>12112</t>
+          <t>11455</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>MANTOVA</t>
+          <t>CASALE MONFERRATO</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -2869,51 +2869,51 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>VIGNADUZZO EDI</t>
         </is>
       </c>
       <c r="E49" s="12" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F49" s="12" t="n">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="I49" s="12" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="J49" s="12" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="K49" s="12" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>42</v>
+        <v>82</v>
       </c>
       <c r="M49" s="12" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>01971</t>
+          <t>01480</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>CREMONA</t>
+          <t>ASTI</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -2923,51 +2923,51 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>VIGNADUZZO EDI</t>
         </is>
       </c>
       <c r="E50" s="12" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>61</v>
+        <v>89</v>
       </c>
       <c r="G50" s="12" t="n">
+        <v>60</v>
+      </c>
+      <c r="H50" s="12" t="n">
+        <v>98</v>
+      </c>
+      <c r="I50" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="J50" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="K50" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="L50" s="12" t="n">
+        <v>60</v>
+      </c>
+      <c r="M50" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="H50" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="I50" s="12" t="n">
-        <v>47</v>
-      </c>
-      <c r="J50" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="K50" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="L50" s="12" t="n">
-        <v>65</v>
-      </c>
-      <c r="M50" s="12" t="n">
-        <v>48</v>
-      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>11455</t>
+          <t>01971</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>CASALE MONFERRATO</t>
+          <t>CREMONA</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -2977,35 +2977,35 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>VIGNADUZZO EDI</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="E51" s="12" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F51" s="12" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="H51" s="12" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I51" s="12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J51" s="12" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="K51" s="12" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="M51" s="12" t="n">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
@@ -3035,31 +3035,31 @@
         </is>
       </c>
       <c r="E52" s="12" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G52" s="12" t="n">
         <v>6</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="J52" s="12" t="n">
         <v>8</v>
       </c>
       <c r="K52" s="12" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M52" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
@@ -3070,12 +3070,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>59894</t>
+          <t>01637</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA</t>
+          <t>CURNO</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -3085,35 +3085,35 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>SALVINELLI LUCA</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="E53" s="12" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H53" s="12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I53" s="12" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J53" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="K53" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="L53" s="12" t="n">
+        <v>66</v>
+      </c>
+      <c r="M53" s="12" t="n">
         <v>4</v>
-      </c>
-      <c r="K53" s="12" t="n">
-        <v>23</v>
-      </c>
-      <c r="L53" s="12" t="n">
-        <v>33</v>
-      </c>
-      <c r="M53" s="12" t="n">
-        <v>1</v>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
@@ -3124,12 +3124,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>01637</t>
+          <t>55864</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>CURNO</t>
+          <t>OVADA</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -3139,51 +3139,51 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>DELUGAS NADIA</t>
         </is>
       </c>
       <c r="E54" s="12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="G54" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="H54" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="I54" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="J54" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="H54" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="I54" s="12" t="n">
-        <v>26</v>
-      </c>
-      <c r="J54" s="12" t="n">
-        <v>10</v>
-      </c>
       <c r="K54" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="M54" s="12" t="n">
         <v>3</v>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>01334</t>
+          <t>59894</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>FINALE LIGURE</t>
+          <t>BRESCIA</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -3193,51 +3193,51 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>BARNABA SALVATORE</t>
+          <t>SALVINELLI LUCA</t>
         </is>
       </c>
       <c r="E55" s="12" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F55" s="12" t="n">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="H55" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="J55" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K55" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="L55" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="I55" s="12" t="n">
-        <v>31</v>
-      </c>
-      <c r="J55" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="K55" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="L55" s="12" t="n">
-        <v>55</v>
-      </c>
       <c r="M55" s="12" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>01135</t>
+          <t>01334</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>GENOVA</t>
+          <t>FINALE LIGURE</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -3247,51 +3247,51 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>DALLORTO ILARIA</t>
+          <t>BARNABA SALVATORE</t>
         </is>
       </c>
       <c r="E56" s="12" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="G56" s="12" t="n">
+        <v>41</v>
+      </c>
+      <c r="H56" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="I56" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="J56" s="12" t="n">
         <v>8</v>
-      </c>
-      <c r="H56" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="I56" s="12" t="n">
-        <v>27</v>
-      </c>
-      <c r="J56" s="12" t="n">
-        <v>12</v>
       </c>
       <c r="K56" s="12" t="n">
         <v>12</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="M56" s="12" t="n">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>54151</t>
+          <t>01135</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>IMPERIA</t>
+          <t>GENOVA</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -3301,51 +3301,51 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>BARNABA SALVATORE</t>
+          <t>DALLORTO ILARIA</t>
         </is>
       </c>
       <c r="E57" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F57" s="12" t="n">
-        <v>76</v>
+        <v>34</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H57" s="12" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I57" s="12" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J57" s="12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K57" s="12" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="L57" s="12" t="n">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="M57" s="12" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>00259</t>
+          <t>01142</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>TETTO GARETTO</t>
+          <t>SESTRI LEVANTE</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -3355,51 +3355,51 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>SCIALO' MARCO</t>
+          <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
       <c r="E58" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J58" s="12" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K58" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="L58" s="12" t="n">
+        <v>64</v>
+      </c>
+      <c r="M58" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="L58" s="12" t="n">
-        <v>34</v>
-      </c>
-      <c r="M58" s="12" t="n">
-        <v>7</v>
-      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>01142</t>
+          <t>54151</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>SESTRI LEVANTE</t>
+          <t>IMPERIA</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -3409,35 +3409,35 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>BARNABA SALVATORE</t>
         </is>
       </c>
       <c r="E59" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F59" s="12" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="H59" s="12" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="I59" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J59" s="12" t="n">
         <v>8</v>
       </c>
       <c r="K59" s="12" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="M59" s="12" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
@@ -3448,12 +3448,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>55864</t>
+          <t>00259</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>OVADA</t>
+          <t>TETTO GARETTO</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -3463,39 +3463,39 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>DELUGAS NADIA</t>
+          <t>SCIALO' MARCO</t>
         </is>
       </c>
       <c r="E60" s="12" t="n">
         <v>38</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="I60" s="12" t="n">
         <v>24</v>
       </c>
       <c r="J60" s="12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K60" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L60" s="12" t="n">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="M60" s="12" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -3524,13 +3524,13 @@
         <v>35</v>
       </c>
       <c r="F61" s="12" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G61" s="12" t="n">
         <v>25</v>
       </c>
       <c r="H61" s="12" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I61" s="12" t="n">
         <v>37</v>
@@ -3542,7 +3542,7 @@
         <v>0</v>
       </c>
       <c r="L61" s="12" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="M61" s="12" t="n">
         <v>1</v>
@@ -3556,12 +3556,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>01283</t>
+          <t>01561</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>SARZANA</t>
+          <t>PONTIROLO NUOVO</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -3571,51 +3571,51 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="E62" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="H62" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I62" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="J62" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I62" s="12" t="n">
-        <v>30</v>
-      </c>
-      <c r="J62" s="12" t="n">
-        <v>5</v>
-      </c>
       <c r="K62" s="12" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="L62" s="12" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="M62" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>01561</t>
+          <t>01283</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>PONTIROLO NUOVO</t>
+          <t>SARZANA</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -3625,29 +3625,29 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
       <c r="E63" s="12" t="n">
         <v>33</v>
       </c>
       <c r="F63" s="12" t="n">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="G63" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="H63" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I63" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="J63" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="K63" s="12" t="n">
         <v>2</v>
-      </c>
-      <c r="H63" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I63" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="J63" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="K63" s="12" t="n">
-        <v>19</v>
       </c>
       <c r="L63" s="12" t="n">
         <v>30</v>
@@ -3657,19 +3657,19 @@
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>03827</t>
+          <t>12082</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>SAN BONIFACIO</t>
+          <t>VIADANA</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -3679,35 +3679,35 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>MARCONI ANDREA</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="E64" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F64" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="H64" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J64" s="12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K64" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L64" s="12" t="n">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="M64" s="12" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
@@ -3718,12 +3718,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>01086</t>
+          <t>11719</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>RECCO</t>
+          <t>MONTICHIARI</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -3733,51 +3733,51 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="E65" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F65" s="12" t="n">
-        <v>62</v>
+        <v>34</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H65" s="12" t="n">
-        <v>18</v>
+        <v>100</v>
       </c>
       <c r="I65" s="12" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="J65" s="12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K65" s="12" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="L65" s="12" t="n">
-        <v>107</v>
+        <v>37</v>
       </c>
       <c r="M65" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>12082</t>
+          <t>01086</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>VIADANA</t>
+          <t>RECCO</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -3787,51 +3787,51 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
       <c r="E66" s="12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="I66" s="12" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J66" s="12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K66" s="12" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="L66" s="12" t="n">
-        <v>18</v>
+        <v>113</v>
       </c>
       <c r="M66" s="12" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>56297</t>
+          <t>03827</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>SAN PAOLO D'ARGON</t>
+          <t>SAN BONIFACIO</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -3841,51 +3841,51 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>MARCONI ANDREA</t>
         </is>
       </c>
       <c r="E67" s="12" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F67" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H67" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I67" s="12" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J67" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K67" s="12" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L67" s="12" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="M67" s="12" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>11719</t>
+          <t>56297</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>MONTICHIARI</t>
+          <t>SAN PAOLO D'ARGON</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -3895,35 +3895,35 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="E68" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F68" s="12" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="H68" s="12" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="I68" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="J68" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="K68" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="J68" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K68" s="12" t="n">
-        <v>17</v>
-      </c>
       <c r="L68" s="12" t="n">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="M68" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
@@ -3953,22 +3953,22 @@
         </is>
       </c>
       <c r="E69" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="F69" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="G69" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="F69" s="12" t="n">
-        <v>42</v>
-      </c>
-      <c r="G69" s="12" t="n">
-        <v>21</v>
-      </c>
       <c r="H69" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I69" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J69" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K69" s="12" t="n">
         <v>0</v>
@@ -3988,12 +3988,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>02004</t>
+          <t>02024</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>RIVOLTA D'ADDA</t>
+          <t>CASALMAGGIORE</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -4003,35 +4003,35 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="E70" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F70" s="12" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="I70" s="12" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J70" s="12" t="n">
         <v>6</v>
       </c>
       <c r="K70" s="12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L70" s="12" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="M70" s="12" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
@@ -4042,12 +4042,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>01280</t>
+          <t>02004</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>LA SPEZIA</t>
+          <t>RIVOLTA D'ADDA</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -4057,32 +4057,32 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="E71" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F71" s="12" t="n">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H71" s="12" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="I71" s="12" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="J71" s="12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K71" s="12" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L71" s="12" t="n">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="M71" s="12" t="n">
         <v>2</v>
@@ -4096,12 +4096,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>52510</t>
+          <t>01280</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>PORTO MANTOVANO</t>
+          <t>LA SPEZIA</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -4111,51 +4111,51 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
       <c r="E72" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F72" s="12" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G72" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="H72" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="I72" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="J72" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K72" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H72" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I72" s="12" t="n">
-        <v>22</v>
-      </c>
-      <c r="J72" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="K72" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="L72" s="12" t="n">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="M72" s="12" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>02024</t>
+          <t>52510</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>CASALMAGGIORE</t>
+          <t>PORTO MANTOVANO</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -4169,35 +4169,35 @@
         </is>
       </c>
       <c r="E73" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F73" s="12" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="H73" s="12" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I73" s="12" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J73" s="12" t="n">
         <v>6</v>
       </c>
       <c r="K73" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L73" s="12" t="n">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="M73" s="12" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -4223,19 +4223,19 @@
         </is>
       </c>
       <c r="E74" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F74" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H74" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I74" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J74" s="12" t="n">
         <v>2</v>
@@ -4244,7 +4244,7 @@
         <v>3</v>
       </c>
       <c r="L74" s="12" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M74" s="12" t="n">
         <v>20</v>
@@ -4280,7 +4280,7 @@
         <v>16</v>
       </c>
       <c r="F75" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G75" s="12" t="n">
         <v>0</v>
@@ -4331,19 +4331,19 @@
         </is>
       </c>
       <c r="E76" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F76" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H76" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I76" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J76" s="12" t="n">
         <v>3</v>
@@ -4388,7 +4388,7 @@
         <v>13</v>
       </c>
       <c r="F77" s="12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G77" s="12" t="n">
         <v>1</v>
@@ -4448,7 +4448,7 @@
         <v>30</v>
       </c>
       <c r="H78" s="12" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I78" s="12" t="n">
         <v>8</v>
@@ -4514,10 +4514,10 @@
         <v>0</v>
       </c>
       <c r="L79" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M79" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
@@ -4547,22 +4547,22 @@
         </is>
       </c>
       <c r="E80" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F80" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G80" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H80" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="J80" s="12" t="n">
         <v>1</v>
-      </c>
-      <c r="H80" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I80" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="J80" s="12" t="n">
-        <v>0</v>
       </c>
       <c r="K80" s="12" t="n">
         <v>0</v>
@@ -4712,13 +4712,13 @@
         <v>0</v>
       </c>
       <c r="F83" s="12" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G83" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H83" s="12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I83" s="12" t="n">
         <v>0</v>
@@ -4820,7 +4820,7 @@
         <v>0</v>
       </c>
       <c r="F85" s="12" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G85" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/Agente - Marcelli Emanuele.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Marcelli Emanuele.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>80</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>8374</v>
+        <v>8810</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>5933</v>
+        <v>6247</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>2864</v>
+        <v>3041</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>715</v>
+        <v>758</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>517</v>
+        <v>550</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>465</v>
+        <v>482</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>255</v>
+        <v>281</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>597</v>
+        <v>641</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,35 +875,35 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>500</v>
+        <v>524</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>203</v>
+        <v>228</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>336</v>
+        <v>355</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>314</v>
+        <v>335</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -929,35 +929,35 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>433</v>
+        <v>453</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>517</v>
+        <v>543</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>236</v>
+        <v>263</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -983,31 +983,31 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>353</v>
+        <v>377</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>225</v>
+        <v>244</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1037,31 +1037,31 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>328</v>
+        <v>345</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>440</v>
+        <v>465</v>
       </c>
       <c r="G15" s="12" t="n">
+        <v>90</v>
+      </c>
+      <c r="H15" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="I15" s="12" t="n">
+        <v>265</v>
+      </c>
+      <c r="J15" s="12" t="n">
         <v>84</v>
       </c>
-      <c r="H15" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="I15" s="12" t="n">
-        <v>250</v>
-      </c>
-      <c r="J15" s="12" t="n">
-        <v>78</v>
-      </c>
       <c r="K15" s="12" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>478</v>
+        <v>500</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -1091,31 +1091,31 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>358</v>
+        <v>371</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>452</v>
+        <v>475</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>273</v>
+        <v>288</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1145,31 +1145,31 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>288</v>
+        <v>311</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>482</v>
+        <v>516</v>
       </c>
       <c r="G17" s="12" t="n">
         <v>37</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>340</v>
+        <v>377</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
@@ -1199,35 +1199,35 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>266</v>
+        <v>285</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>305</v>
+        <v>341</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>221</v>
+        <v>239</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1253,35 +1253,35 @@
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>250</v>
+        <v>265</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="G19" s="12" t="n">
+        <v>92</v>
+      </c>
+      <c r="H19" s="12" t="n">
+        <v>92</v>
+      </c>
+      <c r="I19" s="12" t="n">
+        <v>212</v>
+      </c>
+      <c r="J19" s="12" t="n">
         <v>84</v>
       </c>
-      <c r="H19" s="12" t="n">
-        <v>87</v>
-      </c>
-      <c r="I19" s="12" t="n">
-        <v>199</v>
-      </c>
-      <c r="J19" s="12" t="n">
-        <v>79</v>
-      </c>
       <c r="K19" s="12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1307,31 +1307,31 @@
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>312</v>
+        <v>328</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
@@ -1361,35 +1361,35 @@
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="H21" s="12" t="n">
         <v>15</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>270</v>
+        <v>289</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1415,31 +1415,31 @@
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>223</v>
+        <v>242</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
@@ -1469,35 +1469,35 @@
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="K23" s="12" t="n">
         <v>50</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1523,35 +1523,35 @@
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>201</v>
+        <v>220</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1577,19 +1577,19 @@
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="H25" s="12" t="n">
         <v>7</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="J25" s="12" t="n">
         <v>28</v>
@@ -1598,14 +1598,14 @@
         <v>101</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>156</v>
+        <v>172</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1631,10 +1631,10 @@
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="G26" s="12" t="n">
         <v>1</v>
@@ -1643,16 +1643,16 @@
         <v>6</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="J26" s="12" t="n">
         <v>23</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="M26" s="12" t="n">
         <v>9</v>
@@ -1666,12 +1666,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>01351</t>
+          <t>01837</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>SAVONA</t>
+          <t>LECCO</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1681,35 +1681,35 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>BARNABA SALVATORE</t>
+          <t>ADINOLFI VINCENZO</t>
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>139</v>
+        <v>209</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>19</v>
+        <v>105</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>68</v>
+        <v>26</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>128</v>
+        <v>149</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>159</v>
+        <v>183</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
@@ -1720,12 +1720,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>01837</t>
+          <t>01351</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>LECCO</t>
+          <t>SAVONA</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1735,35 +1735,35 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>ADINOLFI VINCENZO</t>
+          <t>BARNABA SALVATORE</t>
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>190</v>
+        <v>152</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>96</v>
+        <v>21</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>25</v>
+        <v>74</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
@@ -1793,31 +1793,31 @@
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
@@ -1847,28 +1847,28 @@
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>176</v>
+        <v>217</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>209</v>
+        <v>230</v>
       </c>
       <c r="M30" s="12" t="n">
         <v>16</v>
@@ -1882,12 +1882,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>01525</t>
+          <t>01956</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>GAZZANIGA</t>
+          <t>CREMA</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1897,39 +1897,39 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>152</v>
+        <v>194</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>53</v>
+        <v>125</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>89</v>
+        <v>205</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>19</v>
+        <v>83</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1955,10 +1955,10 @@
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="G32" s="12" t="n">
         <v>5</v>
@@ -1967,16 +1967,16 @@
         <v>9</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K32" s="12" t="n">
         <v>51</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="M32" s="12" t="n">
         <v>10</v>
@@ -1990,12 +1990,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>01956</t>
+          <t>01525</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>CREMA</t>
+          <t>GAZZANIGA</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2005,35 +2005,35 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="E33" s="12" t="n">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>186</v>
+        <v>173</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>116</v>
+        <v>53</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>7</v>
+        <v>58</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>191</v>
+        <v>89</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>78</v>
+        <v>19</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
@@ -2063,19 +2063,19 @@
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="G34" s="12" t="n">
         <v>12</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="J34" s="12" t="n">
         <v>30</v>
@@ -2084,7 +2084,7 @@
         <v>23</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M34" s="12" t="n">
         <v>38</v>
@@ -2117,31 +2117,31 @@
         </is>
       </c>
       <c r="E35" s="12" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>268</v>
+        <v>282</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="J35" s="12" t="n">
         <v>38</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
@@ -2171,10 +2171,10 @@
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="G36" s="12" t="n">
         <v>3</v>
@@ -2183,16 +2183,16 @@
         <v>8</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="M36" s="12" t="n">
         <v>15</v>
@@ -2225,16 +2225,16 @@
         </is>
       </c>
       <c r="E37" s="12" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>261</v>
+        <v>276</v>
       </c>
       <c r="I37" s="12" t="n">
         <v>79</v>
@@ -2243,10 +2243,10 @@
         <v>22</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="M37" s="12" t="n">
         <v>5</v>
@@ -2282,13 +2282,13 @@
         <v>108</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="G38" s="12" t="n">
         <v>2</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I38" s="12" t="n">
         <v>77</v>
@@ -2314,12 +2314,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>01574</t>
+          <t>01043</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>TREVIGLIO</t>
+          <t>GENOVA</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2329,51 +2329,51 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>DALLORTO ILARIA</t>
         </is>
       </c>
       <c r="E39" s="12" t="n">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>114</v>
+        <v>154</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>01043</t>
+          <t>01574</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>GENOVA</t>
+          <t>TREVIGLIO</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2383,35 +2383,35 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>DALLORTO ILARIA</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="E40" s="12" t="n">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="G40" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="12" t="n">
+        <v>88</v>
+      </c>
+      <c r="J40" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="H40" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="I40" s="12" t="n">
-        <v>68</v>
-      </c>
-      <c r="J40" s="12" t="n">
-        <v>26</v>
-      </c>
       <c r="K40" s="12" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>145</v>
+        <v>117</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
@@ -2441,31 +2441,31 @@
         </is>
       </c>
       <c r="E41" s="12" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H41" s="12" t="n">
         <v>34</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K41" s="12" t="n">
         <v>34</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="E42" s="12" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F42" s="12" t="n">
         <v>0</v>
@@ -2507,7 +2507,7 @@
         <v>0</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J42" s="12" t="n">
         <v>8</v>
@@ -2516,26 +2516,26 @@
         <v>44</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>01378</t>
+          <t>51037</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>CARCARE</t>
+          <t>ACQUI TERME</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -2549,47 +2549,47 @@
         </is>
       </c>
       <c r="E43" s="12" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F43" s="12" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>51037</t>
+          <t>01378</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>ACQUI TERME</t>
+          <t>CARCARE</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2603,35 +2603,35 @@
         </is>
       </c>
       <c r="E44" s="12" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2657,19 +2657,19 @@
         </is>
       </c>
       <c r="E45" s="12" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F45" s="12" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="G45" s="12" t="n">
         <v>6</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J45" s="12" t="n">
         <v>23</v>
@@ -2678,7 +2678,7 @@
         <v>16</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="M45" s="12" t="n">
         <v>24</v>
@@ -2711,19 +2711,19 @@
         </is>
       </c>
       <c r="E46" s="12" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="J46" s="12" t="n">
         <v>3</v>
@@ -2732,7 +2732,7 @@
         <v>35</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="M46" s="12" t="n">
         <v>0</v>
@@ -2765,35 +2765,35 @@
         </is>
       </c>
       <c r="E47" s="12" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F47" s="12" t="n">
         <v>60</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K47" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2819,10 +2819,10 @@
         </is>
       </c>
       <c r="E48" s="12" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G48" s="12" t="n">
         <v>1</v>
@@ -2831,16 +2831,16 @@
         <v>8</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="J48" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K48" s="12" t="n">
         <v>4</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M48" s="12" t="n">
         <v>32</v>
@@ -2873,31 +2873,31 @@
         </is>
       </c>
       <c r="E49" s="12" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F49" s="12" t="n">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I49" s="12" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="J49" s="12" t="n">
         <v>10</v>
       </c>
       <c r="K49" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="M49" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
@@ -2927,19 +2927,19 @@
         </is>
       </c>
       <c r="E50" s="12" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J50" s="12" t="n">
         <v>11</v>
@@ -2948,7 +2948,7 @@
         <v>14</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="M50" s="12" t="n">
         <v>4</v>
@@ -2962,12 +2962,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>01971</t>
+          <t>51570</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>CREMONA</t>
+          <t>VENTIMIGLIA</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -2977,51 +2977,51 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>BARNABA SALVATORE</t>
         </is>
       </c>
       <c r="E51" s="12" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F51" s="12" t="n">
-        <v>65</v>
+        <v>93</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H51" s="12" t="n">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="I51" s="12" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="J51" s="12" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="K51" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="M51" s="12" t="n">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>51570</t>
+          <t>01971</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>VENTIMIGLIA</t>
+          <t>CREMONA</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -3031,39 +3031,39 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>BARNABA SALVATORE</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="E52" s="12" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>89</v>
+        <v>66</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="J52" s="12" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="K52" s="12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="M52" s="12" t="n">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -3089,10 +3089,10 @@
         </is>
       </c>
       <c r="E53" s="12" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G53" s="12" t="n">
         <v>5</v>
@@ -3101,7 +3101,7 @@
         <v>7</v>
       </c>
       <c r="I53" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J53" s="12" t="n">
         <v>11</v>
@@ -3110,7 +3110,7 @@
         <v>21</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="M53" s="12" t="n">
         <v>4</v>
@@ -3143,35 +3143,35 @@
         </is>
       </c>
       <c r="E54" s="12" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H54" s="12" t="n">
         <v>17</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J54" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K54" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="M54" s="12" t="n">
         <v>3</v>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -3200,7 +3200,7 @@
         <v>43</v>
       </c>
       <c r="F55" s="12" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G55" s="12" t="n">
         <v>2</v>
@@ -3254,13 +3254,13 @@
         <v>42</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I56" s="12" t="n">
         <v>32</v>
@@ -3272,10 +3272,10 @@
         <v>12</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M56" s="12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
@@ -3286,12 +3286,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>01135</t>
+          <t>01142</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>GENOVA</t>
+          <t>SESTRI LEVANTE</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -3301,51 +3301,51 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>DALLORTO ILARIA</t>
+          <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
       <c r="E57" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F57" s="12" t="n">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="G57" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="H57" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="I57" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="J57" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="H57" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="I57" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="J57" s="12" t="n">
-        <v>12</v>
-      </c>
       <c r="K57" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L57" s="12" t="n">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="M57" s="12" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>01142</t>
+          <t>54151</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>SESTRI LEVANTE</t>
+          <t>IMPERIA</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -3355,20 +3355,20 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>BARNABA SALVATORE</t>
         </is>
       </c>
       <c r="E58" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="I58" s="12" t="n">
         <v>25</v>
@@ -3377,13 +3377,13 @@
         <v>8</v>
       </c>
       <c r="K58" s="12" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="L58" s="12" t="n">
-        <v>64</v>
+        <v>87</v>
       </c>
       <c r="M58" s="12" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
@@ -3394,12 +3394,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>54151</t>
+          <t>01135</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>IMPERIA</t>
+          <t>GENOVA</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -3409,39 +3409,39 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>BARNABA SALVATORE</t>
+          <t>DALLORTO ILARIA</t>
         </is>
       </c>
       <c r="E59" s="12" t="n">
         <v>40</v>
       </c>
       <c r="F59" s="12" t="n">
-        <v>80</v>
+        <v>36</v>
       </c>
       <c r="G59" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="H59" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="I59" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="J59" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="H59" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="I59" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="J59" s="12" t="n">
-        <v>8</v>
-      </c>
       <c r="K59" s="12" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="M59" s="12" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -3467,10 +3467,10 @@
         </is>
       </c>
       <c r="E60" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G60" s="12" t="n">
         <v>3</v>
@@ -3479,7 +3479,7 @@
         <v>1</v>
       </c>
       <c r="I60" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J60" s="12" t="n">
         <v>3</v>
@@ -3488,7 +3488,7 @@
         <v>15</v>
       </c>
       <c r="L60" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="M60" s="12" t="n">
         <v>9</v>
@@ -3502,12 +3502,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>02075</t>
+          <t>01561</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>SUZZARA</t>
+          <t>PONTIROLO NUOVO</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -3517,51 +3517,51 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="E61" s="12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F61" s="12" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="H61" s="12" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="I61" s="12" t="n">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="J61" s="12" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="K61" s="12" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="L61" s="12" t="n">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="M61" s="12" t="n">
         <v>1</v>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>01561</t>
+          <t>11719</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>PONTIROLO NUOVO</t>
+          <t>MONTICHIARI</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -3571,32 +3571,32 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="E62" s="12" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>1</v>
+        <v>106</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J62" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K62" s="12" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="L62" s="12" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="M62" s="12" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>01283</t>
+          <t>02075</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>SARZANA</t>
+          <t>SUZZARA</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -3625,35 +3625,35 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="E63" s="12" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F63" s="12" t="n">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="H63" s="12" t="n">
-        <v>3</v>
+        <v>47</v>
       </c>
       <c r="I63" s="12" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="J63" s="12" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="K63" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L63" s="12" t="n">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="M63" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
@@ -3664,12 +3664,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>12082</t>
+          <t>03827</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>VIADANA</t>
+          <t>SAN BONIFACIO</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -3679,35 +3679,35 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>MARCONI ANDREA</t>
         </is>
       </c>
       <c r="E64" s="12" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F64" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="H64" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="J64" s="12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K64" s="12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L64" s="12" t="n">
-        <v>18</v>
+        <v>62</v>
       </c>
       <c r="M64" s="12" t="n">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
@@ -3718,12 +3718,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>11719</t>
+          <t>12082</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>MONTICHIARI</t>
+          <t>VIADANA</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -3733,35 +3733,35 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="E65" s="12" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F65" s="12" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="H65" s="12" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I65" s="12" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="J65" s="12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K65" s="12" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="L65" s="12" t="n">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="M65" s="12" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
@@ -3791,10 +3791,10 @@
         </is>
       </c>
       <c r="E66" s="12" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="G66" s="12" t="n">
         <v>25</v>
@@ -3809,10 +3809,10 @@
         <v>6</v>
       </c>
       <c r="K66" s="12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="L66" s="12" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M66" s="12" t="n">
         <v>3</v>
@@ -3826,12 +3826,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>03827</t>
+          <t>01283</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>SAN BONIFACIO</t>
+          <t>SARZANA</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -3841,39 +3841,39 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>MARCONI ANDREA</t>
+          <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
       <c r="E67" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F67" s="12" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="G67" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="H67" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I67" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="J67" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="H67" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I67" s="12" t="n">
-        <v>29</v>
-      </c>
-      <c r="J67" s="12" t="n">
-        <v>8</v>
-      </c>
       <c r="K67" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L67" s="12" t="n">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="M67" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="E68" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F68" s="12" t="n">
         <v>0</v>
@@ -3911,23 +3911,23 @@
         <v>0</v>
       </c>
       <c r="I68" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J68" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K68" s="12" t="n">
         <v>8</v>
       </c>
       <c r="L68" s="12" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="M68" s="12" t="n">
         <v>3</v>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -3956,10 +3956,10 @@
         <v>26</v>
       </c>
       <c r="F69" s="12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H69" s="12" t="n">
         <v>33</v>
@@ -3974,10 +3974,10 @@
         <v>0</v>
       </c>
       <c r="L69" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M69" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
@@ -3988,12 +3988,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>02024</t>
+          <t>02004</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>CASALMAGGIORE</t>
+          <t>RIVOLTA D'ADDA</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -4003,35 +4003,35 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="E70" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F70" s="12" t="n">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="I70" s="12" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J70" s="12" t="n">
         <v>6</v>
       </c>
       <c r="K70" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L70" s="12" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="M70" s="12" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
@@ -4042,12 +4042,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>02004</t>
+          <t>02024</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>RIVOLTA D'ADDA</t>
+          <t>CASALMAGGIORE</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -4057,35 +4057,35 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="E71" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F71" s="12" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="H71" s="12" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="I71" s="12" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J71" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K71" s="12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L71" s="12" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="M71" s="12" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
@@ -4115,19 +4115,19 @@
         </is>
       </c>
       <c r="E72" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F72" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G72" s="12" t="n">
         <v>12</v>
       </c>
       <c r="H72" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I72" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J72" s="12" t="n">
         <v>2</v>
@@ -4136,7 +4136,7 @@
         <v>1</v>
       </c>
       <c r="L72" s="12" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="M72" s="12" t="n">
         <v>2</v>
@@ -4150,12 +4150,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>52510</t>
+          <t>54290</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>PORTO MANTOVANO</t>
+          <t>GENOVA</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -4165,35 +4165,35 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>DALLORTO ILARIA</t>
         </is>
       </c>
       <c r="E73" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F73" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="H73" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I73" s="12" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J73" s="12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K73" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L73" s="12" t="n">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="M73" s="12" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
@@ -4204,12 +4204,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>54290</t>
+          <t>52510</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>GENOVA</t>
+          <t>PORTO MANTOVANO</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -4219,35 +4219,35 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>DALLORTO ILARIA</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="E74" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F74" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="H74" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I74" s="12" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J74" s="12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K74" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L74" s="12" t="n">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="M74" s="12" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         <v>16</v>
       </c>
       <c r="F75" s="12" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G75" s="12" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
         <v>17</v>
       </c>
       <c r="H76" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I76" s="12" t="n">
         <v>15</v>
@@ -4352,7 +4352,7 @@
         <v>0</v>
       </c>
       <c r="L76" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="M76" s="12" t="n">
         <v>0</v>
@@ -4388,7 +4388,7 @@
         <v>13</v>
       </c>
       <c r="F77" s="12" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G77" s="12" t="n">
         <v>1</v>
@@ -4442,13 +4442,13 @@
         <v>11</v>
       </c>
       <c r="F78" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G78" s="12" t="n">
         <v>30</v>
       </c>
       <c r="H78" s="12" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="I78" s="12" t="n">
         <v>8</v>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="E80" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F80" s="12" t="n">
         <v>0</v>
@@ -4559,7 +4559,7 @@
         <v>0</v>
       </c>
       <c r="I80" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J80" s="12" t="n">
         <v>1</v>
@@ -4575,7 +4575,7 @@
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -4712,13 +4712,13 @@
         <v>0</v>
       </c>
       <c r="F83" s="12" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G83" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H83" s="12" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="I83" s="12" t="n">
         <v>0</v>
@@ -4730,7 +4730,7 @@
         <v>0</v>
       </c>
       <c r="L83" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M83" s="12" t="n">
         <v>0</v>
@@ -4820,7 +4820,7 @@
         <v>0</v>
       </c>
       <c r="F85" s="12" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G85" s="12" t="n">
         <v>0</v>
@@ -4874,7 +4874,7 @@
         <v>0</v>
       </c>
       <c r="F86" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G86" s="12" t="n">
         <v>0</v>
@@ -5036,13 +5036,13 @@
         <v>0</v>
       </c>
       <c r="F89" s="12" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G89" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H89" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I89" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/Agente - Marcelli Emanuele.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Marcelli Emanuele.xlsx
@@ -209,8 +209,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N90" headerRowCount="1">
-  <autoFilter ref="A10:N90"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N91" headerRowCount="1">
+  <autoFilter ref="A10:N91"/>
   <tableColumns count="14">
     <tableColumn id="1" name="PDV"/>
     <tableColumn id="2" name="Città"/>
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N90"/>
+  <dimension ref="A1:N91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -673,16 +673,16 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>8810</v>
+        <v>8818</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>6247</v>
+        <v>6255</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>3041</v>
+        <v>3042</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -4528,12 +4528,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>11348</t>
+          <t>01631</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>VADO LIGURE</t>
+          <t>TELGATE</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -4543,35 +4543,35 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>DELUGAS NADIA</t>
+          <t>SALVINELLI LUCA</t>
         </is>
       </c>
       <c r="E80" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F80" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H80" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I80" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J80" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K80" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L80" s="12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M80" s="12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
@@ -4582,12 +4582,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>00926</t>
+          <t>11348</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>GASSINO TORINESE</t>
+          <t>VADO LIGURE</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -4597,51 +4597,51 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA FEDERICO</t>
+          <t>DELUGAS NADIA</t>
         </is>
       </c>
       <c r="E81" s="12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F81" s="12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H81" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="J81" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I81" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J81" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="K81" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L81" s="12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M81" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>01339</t>
+          <t>00926</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>ALASSIO</t>
+          <t>GASSINO TORINESE</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -4651,20 +4651,20 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>BARNABA SALVATORE</t>
+          <t>BRESCIA FEDERICO</t>
         </is>
       </c>
       <c r="E82" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F82" s="12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G82" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H82" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I82" s="12" t="n">
         <v>0</v>
@@ -4690,12 +4690,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>01416</t>
+          <t>01339</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>SERRAVALLE SCRIVIA</t>
+          <t>ALASSIO</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -4705,20 +4705,20 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>DELUGAS NADIA</t>
+          <t>BARNABA SALVATORE</t>
         </is>
       </c>
       <c r="E83" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F83" s="12" t="n">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="G83" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H83" s="12" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="I83" s="12" t="n">
         <v>0</v>
@@ -4730,26 +4730,26 @@
         <v>0</v>
       </c>
       <c r="L83" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M83" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>01522</t>
+          <t>01416</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>CASAZZA</t>
+          <t>SERRAVALLE SCRIVIA</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -4759,20 +4759,20 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>DELUGAS NADIA</t>
         </is>
       </c>
       <c r="E84" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F84" s="12" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G84" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H84" s="12" t="n">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="I84" s="12" t="n">
         <v>0</v>
@@ -4784,7 +4784,7 @@
         <v>0</v>
       </c>
       <c r="L84" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M84" s="12" t="n">
         <v>0</v>
@@ -4798,12 +4798,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>01639</t>
+          <t>01522</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>PIANICO</t>
+          <t>CASAZZA</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -4820,13 +4820,13 @@
         <v>0</v>
       </c>
       <c r="F85" s="12" t="n">
-        <v>86</v>
+        <v>57</v>
       </c>
       <c r="G85" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H85" s="12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I85" s="12" t="n">
         <v>0</v>
@@ -4852,12 +4852,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>02053</t>
+          <t>01639</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>BAGNOLO SAN VITO</t>
+          <t>PIANICO</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -4867,14 +4867,14 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="E86" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F86" s="12" t="n">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="G86" s="12" t="n">
         <v>0</v>
@@ -4899,19 +4899,19 @@
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>02970</t>
+          <t>02053</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>FIDENZA</t>
+          <t>BAGNOLO SAN VITO</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -4921,14 +4921,14 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="E87" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F87" s="12" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="G87" s="12" t="n">
         <v>0</v>
@@ -4953,19 +4953,19 @@
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>05511</t>
+          <t>02970</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>MEDICINA</t>
+          <t>FIDENZA</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -4975,14 +4975,14 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="E88" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F88" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G88" s="12" t="n">
         <v>0</v>
@@ -5014,12 +5014,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>10241</t>
+          <t>05511</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>ALBA</t>
+          <t>MEDICINA</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -5029,20 +5029,20 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>GIARRATANA SEARA</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E89" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F89" s="12" t="n">
-        <v>79</v>
+        <v>2</v>
       </c>
       <c r="G89" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H89" s="12" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I89" s="12" t="n">
         <v>0</v>
@@ -5061,59 +5061,113 @@
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>10241</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>ALBA</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>GIARRATANA SEARA</t>
+        </is>
+      </c>
+      <c r="E90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" s="12" t="n">
+        <v>79</v>
+      </c>
+      <c r="G90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
           <t>15548</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
         <is>
           <t>PIANORO</t>
         </is>
       </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Emanuele</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>MURGO LORENZO</t>
         </is>
       </c>
-      <c r="E90" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F90" s="12" t="n">
+      <c r="E91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G90" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H90" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I90" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J90" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K90" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L90" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M90" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N90" s="2" t="inlineStr">
+      <c r="G91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>

--- a/docs/files/REPORT_FILTRI/Agente - Marcelli Emanuele.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Marcelli Emanuele.xlsx
@@ -209,8 +209,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N91" headerRowCount="1">
-  <autoFilter ref="A10:N91"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N80" headerRowCount="1">
+  <autoFilter ref="A10:N80"/>
   <tableColumns count="14">
     <tableColumn id="1" name="PDV"/>
     <tableColumn id="2" name="Città"/>
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N91"/>
+  <dimension ref="A1:N80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -673,16 +673,16 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>8818</v>
+        <v>7957</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>6255</v>
+        <v>5595</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>3042</v>
+        <v>2679</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -1288,12 +1288,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>11418</t>
+          <t>04203</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>ASTI</t>
+          <t>PORDENONE</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1303,51 +1303,51 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>VIGNADUZZO EDI</t>
+          <t>DI FILIPPO SIMONE</t>
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>259</v>
+        <v>248</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>328</v>
+        <v>240</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>189</v>
+        <v>69</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>245</v>
+        <v>15</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>204</v>
+        <v>170</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>83</v>
+        <v>53</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>213</v>
+        <v>289</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>04203</t>
+          <t>01724</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>PORDENONE</t>
+          <t>ORZIVECCHI</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1357,35 +1357,35 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>DI FILIPPO SIMONE</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>248</v>
+        <v>230</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>240</v>
+        <v>96</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>69</v>
+        <v>117</v>
       </c>
       <c r="H21" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="I21" s="12" t="n">
+        <v>182</v>
+      </c>
+      <c r="J21" s="12" t="n">
+        <v>79</v>
+      </c>
+      <c r="K21" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="L21" s="12" t="n">
+        <v>70</v>
+      </c>
+      <c r="M21" s="12" t="n">
         <v>15</v>
-      </c>
-      <c r="I21" s="12" t="n">
-        <v>170</v>
-      </c>
-      <c r="J21" s="12" t="n">
-        <v>53</v>
-      </c>
-      <c r="K21" s="12" t="n">
-        <v>76</v>
-      </c>
-      <c r="L21" s="12" t="n">
-        <v>289</v>
-      </c>
-      <c r="M21" s="12" t="n">
-        <v>60</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
@@ -1396,12 +1396,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>00209</t>
+          <t>01640</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>CUNEO</t>
+          <t>SERIATE</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1411,35 +1411,35 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>SCIALO' MARCO</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>242</v>
+        <v>220</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>173</v>
+        <v>124</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>196</v>
+        <v>239</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
@@ -1450,12 +1450,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>01724</t>
+          <t>01527</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>ORZIVECCHI</t>
+          <t>DALMINE</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1465,35 +1465,35 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>230</v>
+        <v>197</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>96</v>
+        <v>173</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>117</v>
+        <v>32</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>46</v>
+        <v>7</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>182</v>
+        <v>106</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>50</v>
+        <v>101</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>70</v>
+        <v>172</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
@@ -1504,12 +1504,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>01640</t>
+          <t>01638</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>SERIATE</t>
+          <t>GRUMELLO DEL MONTE</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1523,47 +1523,47 @@
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>220</v>
+        <v>197</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>245</v>
+        <v>300</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>124</v>
+        <v>80</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>239</v>
+        <v>219</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>01527</t>
+          <t>01837</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>DALMINE</t>
+          <t>LECCO</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1573,51 +1573,51 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>ADINOLFI VINCENZO</t>
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>197</v>
+        <v>180</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>173</v>
+        <v>209</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>32</v>
+        <v>105</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>106</v>
+        <v>149</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>101</v>
+        <v>33</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>01638</t>
+          <t>01351</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>GRUMELLO DEL MONTE</t>
+          <t>SAVONA</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1627,51 +1627,51 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>BARNABA SALVATORE</t>
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>197</v>
+        <v>179</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>300</v>
+        <v>152</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>80</v>
+        <v>134</v>
       </c>
       <c r="J26" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="K26" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="L26" s="12" t="n">
+        <v>168</v>
+      </c>
+      <c r="M26" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="K26" s="12" t="n">
-        <v>118</v>
-      </c>
-      <c r="L26" s="12" t="n">
-        <v>219</v>
-      </c>
-      <c r="M26" s="12" t="n">
-        <v>9</v>
-      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>01837</t>
+          <t>01032</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>LECCO</t>
+          <t>GENOVA</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1681,51 +1681,51 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>ADINOLFI VINCENZO</t>
+          <t>DALLORTO ILARIA</t>
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>209</v>
+        <v>249</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>105</v>
+        <v>66</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>26</v>
+        <v>68</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>183</v>
+        <v>426</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>01351</t>
+          <t>01968</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>SAVONA</t>
+          <t>CREMONA</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1735,51 +1735,51 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>BARNABA SALVATORE</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>179</v>
+        <v>148</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>152</v>
+        <v>217</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="H28" s="12" t="n">
         <v>74</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>134</v>
+        <v>108</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>168</v>
+        <v>230</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>01032</t>
+          <t>01956</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>GENOVA</t>
+          <t>CREMA</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1789,35 +1789,35 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>DALLORTO ILARIA</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>172</v>
+        <v>143</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>249</v>
+        <v>194</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>66</v>
+        <v>125</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>68</v>
+        <v>7</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>426</v>
+        <v>205</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>16</v>
+        <v>83</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
@@ -1828,12 +1828,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>01968</t>
+          <t>01008</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>CREMONA</t>
+          <t>GENOVA</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1843,51 +1843,51 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>DALLORTO ILARIA</t>
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>217</v>
+        <v>151</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>74</v>
+        <v>9</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>108</v>
+        <v>84</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>230</v>
+        <v>177</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>01956</t>
+          <t>01525</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>CREMA</t>
+          <t>GAZZANIGA</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1897,35 +1897,35 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>194</v>
+        <v>173</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>125</v>
+        <v>53</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>7</v>
+        <v>58</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>205</v>
+        <v>89</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>83</v>
+        <v>19</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
@@ -1936,12 +1936,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>01008</t>
+          <t>51674</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>GENOVA</t>
+          <t>CARAVAGGIO</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1951,51 +1951,51 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>DALLORTO ILARIA</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>151</v>
+        <v>201</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>9</v>
+        <v>47</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>177</v>
+        <v>102</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>01525</t>
+          <t>02036</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>GAZZANIGA</t>
+          <t>CREMONA</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2005,51 +2005,51 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="E33" s="12" t="n">
-        <v>139</v>
+        <v>120</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>173</v>
+        <v>122</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>53</v>
+        <v>160</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>58</v>
+        <v>282</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="K33" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="L33" s="12" t="n">
+        <v>185</v>
+      </c>
+      <c r="M33" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="L33" s="12" t="n">
-        <v>89</v>
-      </c>
-      <c r="M33" s="12" t="n">
-        <v>19</v>
-      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>51674</t>
+          <t>55496</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>CARAVAGGIO</t>
+          <t>MOZZO</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2059,35 +2059,35 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>201</v>
+        <v>136</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>99</v>
+        <v>55</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>23</v>
+        <v>66</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
@@ -2098,12 +2098,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>02036</t>
+          <t>01034</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>CREMONA</t>
+          <t>GENOVA</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2113,51 +2113,51 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>DALLORTO ILARIA</t>
         </is>
       </c>
       <c r="E35" s="12" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>160</v>
+        <v>101</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>185</v>
+        <v>148</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>55496</t>
+          <t>01718</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>MOZZO</t>
+          <t>PONTEVICO</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2167,35 +2167,35 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>136</v>
+        <v>170</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>66</v>
+        <v>32</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>01034</t>
+          <t>01043</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2225,47 +2225,47 @@
         </is>
       </c>
       <c r="E37" s="12" t="n">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>132</v>
+        <v>89</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>101</v>
+        <v>17</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>276</v>
+        <v>19</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>01718</t>
+          <t>01574</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>PONTEVICO</t>
+          <t>TREVIGLIO</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2275,51 +2275,51 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="E38" s="12" t="n">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>01043</t>
+          <t>01007</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>GENOVA</t>
+          <t>CHIAVARI</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2329,35 +2329,35 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>DALLORTO ILARIA</t>
+          <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
       <c r="E39" s="12" t="n">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>154</v>
+        <v>194</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
@@ -2368,12 +2368,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>01574</t>
+          <t>51037</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>TREVIGLIO</t>
+          <t>ACQUI TERME</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2383,51 +2383,51 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>DELUGAS NADIA</t>
         </is>
       </c>
       <c r="E40" s="12" t="n">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>88</v>
+        <v>62</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>117</v>
+        <v>83</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>00215</t>
+          <t>01378</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>SAVIGLIANO</t>
+          <t>CARCARE</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -2437,35 +2437,35 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>GIARRATANA SEARA</t>
+          <t>DELUGAS NADIA</t>
         </is>
       </c>
       <c r="E41" s="12" t="n">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>178</v>
+        <v>98</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>106</v>
+        <v>76</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
@@ -2476,12 +2476,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>01007</t>
+          <t>01371</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>CHIAVARI</t>
+          <t>SAVONA</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -2491,51 +2491,51 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>DELUGAS NADIA</t>
         </is>
       </c>
       <c r="E42" s="12" t="n">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>0</v>
+        <v>142</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="K42" s="12" t="n">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>194</v>
+        <v>112</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>51037</t>
+          <t>01577</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>ACQUI TERME</t>
+          <t>ZANICA</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -2545,35 +2545,35 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>DELUGAS NADIA</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="E43" s="12" t="n">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="F43" s="12" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
@@ -2584,12 +2584,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>01378</t>
+          <t>12112</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>CARCARE</t>
+          <t>MANTOVA</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2599,35 +2599,35 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>DELUGAS NADIA</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="E44" s="12" t="n">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>76</v>
+        <v>45</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
@@ -2638,12 +2638,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>01371</t>
+          <t>51570</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>SAVONA</t>
+          <t>VENTIMIGLIA</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -2653,35 +2653,35 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>DELUGAS NADIA</t>
+          <t>BARNABA SALVATORE</t>
         </is>
       </c>
       <c r="E45" s="12" t="n">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="F45" s="12" t="n">
-        <v>142</v>
+        <v>93</v>
       </c>
       <c r="G45" s="12" t="n">
         <v>6</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="K45" s="12" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>112</v>
+        <v>42</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
@@ -2692,12 +2692,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>01577</t>
+          <t>01971</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>ZANICA</t>
+          <t>CREMONA</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -2707,51 +2707,51 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="E46" s="12" t="n">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>91</v>
+        <v>66</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="K46" s="12" t="n">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>11421</t>
+          <t>01637</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>CASALE MONFERRATO</t>
+          <t>CURNO</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -2761,51 +2761,51 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>VIGNADUZZO EDI</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="E47" s="12" t="n">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="K47" s="12" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>12112</t>
+          <t>55864</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>MANTOVA</t>
+          <t>OVADA</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -2815,35 +2815,35 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>DELUGAS NADIA</t>
         </is>
       </c>
       <c r="E48" s="12" t="n">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>87</v>
+        <v>57</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="J48" s="12" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="K48" s="12" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="M48" s="12" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
@@ -2854,12 +2854,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>11455</t>
+          <t>59894</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>CASALE MONFERRATO</t>
+          <t>BRESCIA</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -2869,35 +2869,35 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>VIGNADUZZO EDI</t>
+          <t>SALVINELLI LUCA</t>
         </is>
       </c>
       <c r="E49" s="12" t="n">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="F49" s="12" t="n">
-        <v>92</v>
+        <v>65</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="H49" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="I49" s="12" t="n">
-        <v>55</v>
-      </c>
       <c r="J49" s="12" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="K49" s="12" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>85</v>
+        <v>33</v>
       </c>
       <c r="M49" s="12" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
@@ -2908,12 +2908,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>01480</t>
+          <t>01334</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>ASTI</t>
+          <t>FINALE LIGURE</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -2923,51 +2923,51 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>VIGNADUZZO EDI</t>
+          <t>BARNABA SALVATORE</t>
         </is>
       </c>
       <c r="E50" s="12" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>95</v>
+        <v>50</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>102</v>
+        <v>37</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="J50" s="12" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K50" s="12" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="M50" s="12" t="n">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>51570</t>
+          <t>01142</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>VENTIMIGLIA</t>
+          <t>SESTRI LEVANTE</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -2977,35 +2977,35 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>BARNABA SALVATORE</t>
+          <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
       <c r="E51" s="12" t="n">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="F51" s="12" t="n">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="H51" s="12" t="n">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="I51" s="12" t="n">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="J51" s="12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K51" s="12" t="n">
         <v>13</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="M51" s="12" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
@@ -3016,12 +3016,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>01971</t>
+          <t>54151</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>CREMONA</t>
+          <t>IMPERIA</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -3031,51 +3031,51 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>BARNABA SALVATORE</t>
         </is>
       </c>
       <c r="E52" s="12" t="n">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="J52" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="K52" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="K52" s="12" t="n">
-        <v>12</v>
-      </c>
       <c r="L52" s="12" t="n">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="M52" s="12" t="n">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>01637</t>
+          <t>01135</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>CURNO</t>
+          <t>GENOVA</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -3085,35 +3085,35 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>DALLORTO ILARIA</t>
         </is>
       </c>
       <c r="E53" s="12" t="n">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>74</v>
+        <v>36</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H53" s="12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I53" s="12" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J53" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K53" s="12" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="M53" s="12" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
@@ -3124,12 +3124,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>55864</t>
+          <t>01561</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>OVADA</t>
+          <t>PONTIROLO NUOVO</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -3139,51 +3139,51 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>DELUGAS NADIA</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="E54" s="12" t="n">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H54" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I54" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="I54" s="12" t="n">
-        <v>29</v>
-      </c>
       <c r="J54" s="12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K54" s="12" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="M54" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>59894</t>
+          <t>11719</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA</t>
+          <t>MONTICHIARI</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -3193,35 +3193,35 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>SALVINELLI LUCA</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="E55" s="12" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F55" s="12" t="n">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="H55" s="12" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="I55" s="12" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="J55" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K55" s="12" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="M55" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
@@ -3232,12 +3232,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>01334</t>
+          <t>02075</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>FINALE LIGURE</t>
+          <t>SUZZARA</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -3247,51 +3247,51 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>BARNABA SALVATORE</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="E56" s="12" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="J56" s="12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K56" s="12" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L56" s="12" t="n">
         <v>58</v>
       </c>
       <c r="M56" s="12" t="n">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>01142</t>
+          <t>03827</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>SESTRI LEVANTE</t>
+          <t>SAN BONIFACIO</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -3301,51 +3301,51 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>MARCONI ANDREA</t>
         </is>
       </c>
       <c r="E57" s="12" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F57" s="12" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="H57" s="12" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="I57" s="12" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J57" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K57" s="12" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="L57" s="12" t="n">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="M57" s="12" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>54151</t>
+          <t>12082</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>IMPERIA</t>
+          <t>VIADANA</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -3355,51 +3355,51 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>BARNABA SALVATORE</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="E58" s="12" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J58" s="12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K58" s="12" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="L58" s="12" t="n">
-        <v>87</v>
+        <v>18</v>
       </c>
       <c r="M58" s="12" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>01135</t>
+          <t>01086</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>GENOVA</t>
+          <t>RECCO</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -3409,51 +3409,51 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>DALLORTO ILARIA</t>
+          <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
       <c r="E59" s="12" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F59" s="12" t="n">
-        <v>36</v>
+        <v>73</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="H59" s="12" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="I59" s="12" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J59" s="12" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="K59" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>83</v>
+        <v>116</v>
       </c>
       <c r="M59" s="12" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>00259</t>
+          <t>01283</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>TETTO GARETTO</t>
+          <t>SARZANA</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -3463,51 +3463,51 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>SCIALO' MARCO</t>
+          <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
       <c r="E60" s="12" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="G60" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="H60" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H60" s="12" t="n">
-        <v>1</v>
-      </c>
       <c r="I60" s="12" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J60" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K60" s="12" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="L60" s="12" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="M60" s="12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>01561</t>
+          <t>56297</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>PONTIROLO NUOVO</t>
+          <t>SAN PAOLO D'ARGON</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -3517,51 +3517,51 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="E61" s="12" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="F61" s="12" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="G61" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="H61" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="J61" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="K61" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="L61" s="12" t="n">
+        <v>54</v>
+      </c>
+      <c r="M61" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H61" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I61" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="J61" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="K61" s="12" t="n">
-        <v>22</v>
-      </c>
-      <c r="L61" s="12" t="n">
-        <v>44</v>
-      </c>
-      <c r="M61" s="12" t="n">
-        <v>1</v>
-      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>11719</t>
+          <t>02004</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>MONTICHIARI</t>
+          <t>RIVOLTA D'ADDA</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -3571,35 +3571,35 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="E62" s="12" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>106</v>
+        <v>3</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="J62" s="12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K62" s="12" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="L62" s="12" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="M62" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
@@ -3610,12 +3610,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>02075</t>
+          <t>02024</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>SUZZARA</t>
+          <t>CASALMAGGIORE</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -3629,47 +3629,47 @@
         </is>
       </c>
       <c r="E63" s="12" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F63" s="12" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="H63" s="12" t="n">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="I63" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="J63" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="K63" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="L63" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="J63" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="K63" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L63" s="12" t="n">
-        <v>58</v>
-      </c>
       <c r="M63" s="12" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>03827</t>
+          <t>01280</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>SAN BONIFACIO</t>
+          <t>LA SPEZIA</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -3679,51 +3679,51 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>MARCONI ANDREA</t>
+          <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
       <c r="E64" s="12" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="J64" s="12" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="K64" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L64" s="12" t="n">
         <v>62</v>
       </c>
       <c r="M64" s="12" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>12082</t>
+          <t>54290</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>VIADANA</t>
+          <t>GENOVA</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -3733,51 +3733,51 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>DALLORTO ILARIA</t>
         </is>
       </c>
       <c r="E65" s="12" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="F65" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="H65" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I65" s="12" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="J65" s="12" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K65" s="12" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L65" s="12" t="n">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="M65" s="12" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>01086</t>
+          <t>52510</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>RECCO</t>
+          <t>PORTO MANTOVANO</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -3787,51 +3787,51 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="E66" s="12" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I66" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J66" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K66" s="12" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="L66" s="12" t="n">
-        <v>116</v>
+        <v>16</v>
       </c>
       <c r="M66" s="12" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>01283</t>
+          <t>01288</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>SARZANA</t>
+          <t>BOLANO</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -3845,28 +3845,28 @@
         </is>
       </c>
       <c r="E67" s="12" t="n">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="F67" s="12" t="n">
-        <v>68</v>
+        <v>26</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H67" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="I67" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="J67" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I67" s="12" t="n">
-        <v>30</v>
-      </c>
-      <c r="J67" s="12" t="n">
-        <v>5</v>
-      </c>
       <c r="K67" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L67" s="12" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="M67" s="12" t="n">
         <v>0</v>
@@ -3880,12 +3880,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>56297</t>
+          <t>01578</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>SAN PAOLO D'ARGON</t>
+          <t>VERDELLO</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -3895,51 +3895,51 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="E68" s="12" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="F68" s="12" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="G68" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H68" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="H68" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I68" s="12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J68" s="12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K68" s="12" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L68" s="12" t="n">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="M68" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>01481</t>
+          <t>01671</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>VILLAFRANCA D'ASTI</t>
+          <t>BRESCIA</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -3949,51 +3949,51 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>VIGNADUZZO EDI</t>
+          <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
       <c r="E69" s="12" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="F69" s="12" t="n">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H69" s="12" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="I69" s="12" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="J69" s="12" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K69" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L69" s="12" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="M69" s="12" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>02004</t>
+          <t>02074</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>RIVOLTA D'ADDA</t>
+          <t>GOITO</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -4003,51 +4003,51 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="E70" s="12" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="F70" s="12" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="G70" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H70" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="J70" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K70" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="M70" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I70" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="J70" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="K70" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="L70" s="12" t="n">
-        <v>43</v>
-      </c>
-      <c r="M70" s="12" t="n">
-        <v>2</v>
-      </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>02024</t>
+          <t>01631</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>CASALMAGGIORE</t>
+          <t>TELGATE</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -4057,35 +4057,35 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>SALVINELLI LUCA</t>
         </is>
       </c>
       <c r="E71" s="12" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="F71" s="12" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="H71" s="12" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I71" s="12" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J71" s="12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K71" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L71" s="12" t="n">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="M71" s="12" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
@@ -4096,12 +4096,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>01280</t>
+          <t>11348</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>LA SPEZIA</t>
+          <t>VADO LIGURE</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -4111,51 +4111,51 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>DELUGAS NADIA</t>
         </is>
       </c>
       <c r="E72" s="12" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="F72" s="12" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="H72" s="12" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I72" s="12" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="J72" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K72" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L72" s="12" t="n">
-        <v>62</v>
+        <v>7</v>
       </c>
       <c r="M72" s="12" t="n">
         <v>2</v>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>54290</t>
+          <t>00926</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>GENOVA</t>
+          <t>GASSINO TORINESE</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -4165,35 +4165,35 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>DALLORTO ILARIA</t>
+          <t>BRESCIA FEDERICO</t>
         </is>
       </c>
       <c r="E73" s="12" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="F73" s="12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="H73" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I73" s="12" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J73" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K73" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L73" s="12" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="M73" s="12" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
@@ -4204,12 +4204,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>52510</t>
+          <t>01339</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>PORTO MANTOVANO</t>
+          <t>ALASSIO</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -4219,35 +4219,35 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>BARNABA SALVATORE</t>
         </is>
       </c>
       <c r="E74" s="12" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="F74" s="12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H74" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I74" s="12" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="J74" s="12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K74" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L74" s="12" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M74" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
@@ -4258,12 +4258,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>00350</t>
+          <t>01522</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>BORGO SAN DALMAZZO</t>
+          <t>CASAZZA</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -4273,51 +4273,51 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>SCIALO' MARCO</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="E75" s="12" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="F75" s="12" t="n">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="G75" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H75" s="12" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I75" s="12" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J75" s="12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K75" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L75" s="12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M75" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>01288</t>
+          <t>01639</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>BOLANO</t>
+          <t>PIANICO</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -4327,32 +4327,32 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="E76" s="12" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F76" s="12" t="n">
-        <v>26</v>
+        <v>86</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H76" s="12" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I76" s="12" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J76" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K76" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L76" s="12" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="M76" s="12" t="n">
         <v>0</v>
@@ -4366,12 +4366,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>01578</t>
+          <t>02053</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>VERDELLO</t>
+          <t>BAGNOLO SAN VITO</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -4381,51 +4381,51 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="E77" s="12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="F77" s="12" t="n">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H77" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I77" s="12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J77" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K77" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L77" s="12" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="M77" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>01671</t>
+          <t>02970</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA</t>
+          <t>FIDENZA</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -4435,51 +4435,51 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>GRAZIOSI DAVIDE</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="E78" s="12" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F78" s="12" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H78" s="12" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="I78" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J78" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K78" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L78" s="12" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="M78" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>02074</t>
+          <t>05511</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>GOITO</t>
+          <t>MEDICINA</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -4489,14 +4489,14 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E79" s="12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F79" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G79" s="12" t="n">
         <v>0</v>
@@ -4505,19 +4505,19 @@
         <v>0</v>
       </c>
       <c r="I79" s="12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J79" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K79" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L79" s="12" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="M79" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
@@ -4528,12 +4528,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>01631</t>
+          <t>15548</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>TELGATE</t>
+          <t>PIANORO</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -4543,23 +4543,23 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>SALVINELLI LUCA</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E80" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F80" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H80" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I80" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J80" s="12" t="n">
         <v>0</v>
@@ -4568,606 +4568,12 @@
         <v>0</v>
       </c>
       <c r="L80" s="12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M80" s="12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N80" s="2" t="inlineStr">
-        <is>
-          <t>Da seguire</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>11348</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>VADO LIGURE</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Emanuele</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
-        <is>
-          <t>DELUGAS NADIA</t>
-        </is>
-      </c>
-      <c r="E81" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="F81" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G81" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="H81" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I81" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="J81" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K81" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L81" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="M81" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="N81" s="2" t="inlineStr">
-        <is>
-          <t>Da seguire</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>00926</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>GASSINO TORINESE</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Emanuele</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>BRESCIA FEDERICO</t>
-        </is>
-      </c>
-      <c r="E82" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F82" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="G82" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H82" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I82" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J82" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K82" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L82" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M82" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N82" s="2" t="inlineStr">
-        <is>
-          <t>Bene</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>01339</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>ALASSIO</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Emanuele</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>BARNABA SALVATORE</t>
-        </is>
-      </c>
-      <c r="E83" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F83" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="G83" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H83" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="I83" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J83" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K83" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L83" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M83" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N83" s="2" t="inlineStr">
-        <is>
-          <t>Bene</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>01416</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>SERRAVALLE SCRIVIA</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Emanuele</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>DELUGAS NADIA</t>
-        </is>
-      </c>
-      <c r="E84" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F84" s="12" t="n">
-        <v>60</v>
-      </c>
-      <c r="G84" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H84" s="12" t="n">
-        <v>50</v>
-      </c>
-      <c r="I84" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J84" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K84" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L84" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M84" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N84" s="2" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>01522</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>CASAZZA</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Emanuele</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>BRIGNOLI STEFANO</t>
-        </is>
-      </c>
-      <c r="E85" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F85" s="12" t="n">
-        <v>57</v>
-      </c>
-      <c r="G85" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H85" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="I85" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J85" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K85" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L85" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M85" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N85" s="2" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t>01639</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>PIANICO</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Emanuele</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
-        <is>
-          <t>BRIGNOLI STEFANO</t>
-        </is>
-      </c>
-      <c r="E86" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F86" s="12" t="n">
-        <v>86</v>
-      </c>
-      <c r="G86" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H86" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I86" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J86" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K86" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L86" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M86" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N86" s="2" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
-        <is>
-          <t>02053</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>BAGNOLO SAN VITO</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Emanuele</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
-        <is>
-          <t>CARMINATI SIMONE</t>
-        </is>
-      </c>
-      <c r="E87" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F87" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="G87" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H87" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I87" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J87" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K87" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L87" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M87" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N87" s="2" t="inlineStr">
-        <is>
-          <t>Da seguire</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
-        <is>
-          <t>02970</t>
-        </is>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>FIDENZA</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Emanuele</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
-        <is>
-          <t>IACONA GIOVANNI</t>
-        </is>
-      </c>
-      <c r="E88" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F88" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="G88" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H88" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I88" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J88" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K88" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L88" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M88" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N88" s="2" t="inlineStr">
-        <is>
-          <t>Bene</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
-        <is>
-          <t>05511</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>MEDICINA</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Emanuele</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
-        <is>
-          <t>MURGO LORENZO</t>
-        </is>
-      </c>
-      <c r="E89" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F89" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="G89" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H89" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I89" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J89" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K89" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L89" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M89" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N89" s="2" t="inlineStr">
-        <is>
-          <t>Bene</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
-        <is>
-          <t>10241</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>ALBA</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Emanuele</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
-        <is>
-          <t>GIARRATANA SEARA</t>
-        </is>
-      </c>
-      <c r="E90" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F90" s="12" t="n">
-        <v>79</v>
-      </c>
-      <c r="G90" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H90" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="I90" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J90" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K90" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L90" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M90" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N90" s="2" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
-        <is>
-          <t>15548</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>PIANORO</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Emanuele</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>MURGO LORENZO</t>
-        </is>
-      </c>
-      <c r="E91" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F91" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="G91" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H91" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I91" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J91" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K91" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L91" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M91" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N91" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>

--- a/docs/files/REPORT_FILTRI/Agente - Marcelli Emanuele.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Marcelli Emanuele.xlsx
@@ -209,8 +209,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N80" headerRowCount="1">
-  <autoFilter ref="A10:N80"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N69" headerRowCount="1">
+  <autoFilter ref="A10:N69"/>
   <tableColumns count="14">
     <tableColumn id="1" name="PDV"/>
     <tableColumn id="2" name="Città"/>
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N80"/>
+  <dimension ref="A1:N69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -673,16 +673,16 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>7957</v>
+        <v>7493</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>5595</v>
+        <v>5244</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>2679</v>
+        <v>2499</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -1288,12 +1288,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>04203</t>
+          <t>01724</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>PORDENONE</t>
+          <t>ORZIVECCHI</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1303,35 +1303,35 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>DI FILIPPO SIMONE</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>248</v>
+        <v>230</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>240</v>
+        <v>96</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>69</v>
+        <v>117</v>
       </c>
       <c r="H20" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="I20" s="12" t="n">
+        <v>182</v>
+      </c>
+      <c r="J20" s="12" t="n">
+        <v>79</v>
+      </c>
+      <c r="K20" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="L20" s="12" t="n">
+        <v>70</v>
+      </c>
+      <c r="M20" s="12" t="n">
         <v>15</v>
-      </c>
-      <c r="I20" s="12" t="n">
-        <v>170</v>
-      </c>
-      <c r="J20" s="12" t="n">
-        <v>53</v>
-      </c>
-      <c r="K20" s="12" t="n">
-        <v>76</v>
-      </c>
-      <c r="L20" s="12" t="n">
-        <v>289</v>
-      </c>
-      <c r="M20" s="12" t="n">
-        <v>60</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
@@ -1342,12 +1342,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>01724</t>
+          <t>01640</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>ORZIVECCHI</t>
+          <t>SERIATE</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1357,51 +1357,51 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>96</v>
+        <v>245</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>117</v>
+        <v>30</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>182</v>
+        <v>124</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>79</v>
+        <v>29</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>50</v>
+        <v>97</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>70</v>
+        <v>239</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>15</v>
+        <v>59</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>01640</t>
+          <t>01527</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>SERIATE</t>
+          <t>DALMINE</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1411,51 +1411,51 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>220</v>
+        <v>197</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>245</v>
+        <v>173</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>239</v>
+        <v>172</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>59</v>
+        <v>7</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>01527</t>
+          <t>01638</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>DALMINE</t>
+          <t>GRUMELLO DEL MONTE</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1465,51 +1465,51 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="E23" s="12" t="n">
         <v>197</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>173</v>
+        <v>300</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>106</v>
+        <v>80</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>172</v>
+        <v>219</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>01638</t>
+          <t>01351</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>GRUMELLO DEL MONTE</t>
+          <t>SAVONA</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1519,51 +1519,51 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>BARNABA SALVATORE</t>
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>197</v>
+        <v>179</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>300</v>
+        <v>152</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>80</v>
+        <v>134</v>
       </c>
       <c r="J24" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="K24" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="L24" s="12" t="n">
+        <v>168</v>
+      </c>
+      <c r="M24" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="K24" s="12" t="n">
-        <v>118</v>
-      </c>
-      <c r="L24" s="12" t="n">
-        <v>219</v>
-      </c>
-      <c r="M24" s="12" t="n">
-        <v>9</v>
-      </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>01837</t>
+          <t>01032</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>LECCO</t>
+          <t>GENOVA</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1573,51 +1573,51 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>ADINOLFI VINCENZO</t>
+          <t>DALLORTO ILARIA</t>
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>209</v>
+        <v>249</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>105</v>
+        <v>66</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>26</v>
+        <v>68</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>183</v>
+        <v>426</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>01351</t>
+          <t>01968</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>SAVONA</t>
+          <t>CREMONA</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1627,51 +1627,51 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>BARNABA SALVATORE</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>179</v>
+        <v>148</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>152</v>
+        <v>217</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="H26" s="12" t="n">
         <v>74</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>134</v>
+        <v>108</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>168</v>
+        <v>230</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>01032</t>
+          <t>01956</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>GENOVA</t>
+          <t>CREMA</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1681,35 +1681,35 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>DALLORTO ILARIA</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>172</v>
+        <v>143</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>249</v>
+        <v>194</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>66</v>
+        <v>125</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>68</v>
+        <v>7</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>426</v>
+        <v>205</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>16</v>
+        <v>83</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
@@ -1720,12 +1720,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>01968</t>
+          <t>01008</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>CREMONA</t>
+          <t>GENOVA</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1735,51 +1735,51 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>DALLORTO ILARIA</t>
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>217</v>
+        <v>151</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>74</v>
+        <v>9</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>108</v>
+        <v>84</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>230</v>
+        <v>177</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>01956</t>
+          <t>01525</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>CREMA</t>
+          <t>GAZZANIGA</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1789,35 +1789,35 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>194</v>
+        <v>173</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>125</v>
+        <v>53</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>7</v>
+        <v>58</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>205</v>
+        <v>89</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>83</v>
+        <v>19</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
@@ -1828,12 +1828,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>01008</t>
+          <t>51674</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>GENOVA</t>
+          <t>CARAVAGGIO</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1843,51 +1843,51 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>DALLORTO ILARIA</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>151</v>
+        <v>201</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>9</v>
+        <v>47</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>177</v>
+        <v>102</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>01525</t>
+          <t>02036</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>GAZZANIGA</t>
+          <t>CREMONA</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1897,51 +1897,51 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>139</v>
+        <v>120</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>173</v>
+        <v>122</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>53</v>
+        <v>160</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>58</v>
+        <v>282</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="K31" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="L31" s="12" t="n">
+        <v>185</v>
+      </c>
+      <c r="M31" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="L31" s="12" t="n">
-        <v>89</v>
-      </c>
-      <c r="M31" s="12" t="n">
-        <v>19</v>
-      </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>51674</t>
+          <t>55496</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>CARAVAGGIO</t>
+          <t>MOZZO</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1951,35 +1951,35 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>201</v>
+        <v>136</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>99</v>
+        <v>55</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>23</v>
+        <v>66</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
@@ -1990,12 +1990,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>02036</t>
+          <t>01034</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>CREMONA</t>
+          <t>GENOVA</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2005,51 +2005,51 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>DALLORTO ILARIA</t>
         </is>
       </c>
       <c r="E33" s="12" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>160</v>
+        <v>101</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>185</v>
+        <v>148</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>55496</t>
+          <t>01718</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>MOZZO</t>
+          <t>PONTEVICO</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2059,35 +2059,35 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>136</v>
+        <v>170</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>66</v>
+        <v>32</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>01034</t>
+          <t>01043</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2117,47 +2117,47 @@
         </is>
       </c>
       <c r="E35" s="12" t="n">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>132</v>
+        <v>89</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>101</v>
+        <v>17</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>276</v>
+        <v>19</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>01718</t>
+          <t>01574</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>PONTEVICO</t>
+          <t>TREVIGLIO</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2167,51 +2167,51 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>01043</t>
+          <t>01007</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>GENOVA</t>
+          <t>CHIAVARI</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2221,35 +2221,35 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>DALLORTO ILARIA</t>
+          <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
       <c r="E37" s="12" t="n">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>154</v>
+        <v>194</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
@@ -2260,12 +2260,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>01574</t>
+          <t>51037</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>TREVIGLIO</t>
+          <t>ACQUI TERME</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2275,51 +2275,51 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>DELUGAS NADIA</t>
         </is>
       </c>
       <c r="E38" s="12" t="n">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>88</v>
+        <v>62</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>117</v>
+        <v>83</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>01007</t>
+          <t>01378</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>CHIAVARI</t>
+          <t>CARCARE</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2329,51 +2329,51 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>DELUGAS NADIA</t>
         </is>
       </c>
       <c r="E39" s="12" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>194</v>
+        <v>76</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>51037</t>
+          <t>01371</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>ACQUI TERME</t>
+          <t>SAVONA</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2387,47 +2387,47 @@
         </is>
       </c>
       <c r="E40" s="12" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>99</v>
+        <v>142</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>83</v>
+        <v>112</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>01378</t>
+          <t>01577</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>CARCARE</t>
+          <t>ZANICA</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -2437,51 +2437,51 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>DELUGAS NADIA</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="E41" s="12" t="n">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="G41" s="12" t="n">
         <v>9</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>01371</t>
+          <t>12112</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>SAVONA</t>
+          <t>MANTOVA</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -2491,35 +2491,35 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>DELUGAS NADIA</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="E42" s="12" t="n">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>142</v>
+        <v>87</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K42" s="12" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>112</v>
+        <v>45</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
@@ -2530,12 +2530,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>01577</t>
+          <t>51570</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>ZANICA</t>
+          <t>VENTIMIGLIA</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -2545,51 +2545,51 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>BARNABA SALVATORE</t>
         </is>
       </c>
       <c r="E43" s="12" t="n">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="F43" s="12" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>89</v>
+        <v>42</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>12112</t>
+          <t>01971</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>MANTOVA</t>
+          <t>CREMONA</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2599,51 +2599,51 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="E44" s="12" t="n">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>87</v>
+        <v>66</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>51570</t>
+          <t>01637</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>VENTIMIGLIA</t>
+          <t>CURNO</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -2653,51 +2653,51 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>BARNABA SALVATORE</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="E45" s="12" t="n">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="F45" s="12" t="n">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K45" s="12" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>01971</t>
+          <t>55864</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>CREMONA</t>
+          <t>OVADA</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -2707,51 +2707,51 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>DELUGAS NADIA</t>
         </is>
       </c>
       <c r="E46" s="12" t="n">
+        <v>47</v>
+      </c>
+      <c r="F46" s="12" t="n">
         <v>57</v>
-      </c>
-      <c r="F46" s="12" t="n">
-        <v>66</v>
       </c>
       <c r="G46" s="12" t="n">
         <v>5</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="K46" s="12" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>01637</t>
+          <t>59894</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>CURNO</t>
+          <t>BRESCIA</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -2761,35 +2761,35 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>SALVINELLI LUCA</t>
         </is>
       </c>
       <c r="E47" s="12" t="n">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="K47" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>71</v>
+        <v>33</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
@@ -2800,12 +2800,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>55864</t>
+          <t>01334</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>OVADA</t>
+          <t>FINALE LIGURE</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -2815,51 +2815,51 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>DELUGAS NADIA</t>
+          <t>BARNABA SALVATORE</t>
         </is>
       </c>
       <c r="E48" s="12" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J48" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K48" s="12" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="M48" s="12" t="n">
-        <v>3</v>
+        <v>44</v>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>59894</t>
+          <t>01142</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA</t>
+          <t>SESTRI LEVANTE</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -2869,51 +2869,51 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>SALVINELLI LUCA</t>
+          <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
       <c r="E49" s="12" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F49" s="12" t="n">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="I49" s="12" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J49" s="12" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K49" s="12" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>33</v>
+        <v>70</v>
       </c>
       <c r="M49" s="12" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>01334</t>
+          <t>54151</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>FINALE LIGURE</t>
+          <t>IMPERIA</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -2927,47 +2927,47 @@
         </is>
       </c>
       <c r="E50" s="12" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>50</v>
+        <v>92</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="J50" s="12" t="n">
         <v>8</v>
       </c>
       <c r="K50" s="12" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>58</v>
+        <v>87</v>
       </c>
       <c r="M50" s="12" t="n">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>01142</t>
+          <t>01135</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>SESTRI LEVANTE</t>
+          <t>GENOVA</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -2977,51 +2977,51 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>DALLORTO ILARIA</t>
         </is>
       </c>
       <c r="E51" s="12" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F51" s="12" t="n">
-        <v>79</v>
+        <v>36</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="H51" s="12" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="I51" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J51" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="K51" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="L51" s="12" t="n">
+        <v>83</v>
+      </c>
+      <c r="M51" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="K51" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="L51" s="12" t="n">
-        <v>70</v>
-      </c>
-      <c r="M51" s="12" t="n">
-        <v>19</v>
-      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>54151</t>
+          <t>01561</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>IMPERIA</t>
+          <t>PONTIROLO NUOVO</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -3031,51 +3031,51 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>BARNABA SALVATORE</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="E52" s="12" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>92</v>
+        <v>59</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J52" s="12" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K52" s="12" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>87</v>
+        <v>44</v>
       </c>
       <c r="M52" s="12" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>01135</t>
+          <t>11719</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>GENOVA</t>
+          <t>MONTICHIARI</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -3085,35 +3085,35 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>DALLORTO ILARIA</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="E53" s="12" t="n">
+        <v>38</v>
+      </c>
+      <c r="F53" s="12" t="n">
+        <v>38</v>
+      </c>
+      <c r="G53" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="H53" s="12" t="n">
+        <v>106</v>
+      </c>
+      <c r="I53" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="J53" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="L53" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="F53" s="12" t="n">
-        <v>36</v>
-      </c>
-      <c r="G53" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="H53" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="I53" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="J53" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="K53" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="L53" s="12" t="n">
-        <v>83</v>
-      </c>
       <c r="M53" s="12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
@@ -3124,12 +3124,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>01561</t>
+          <t>02075</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>PONTIROLO NUOVO</t>
+          <t>SUZZARA</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -3139,51 +3139,51 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="E54" s="12" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="J54" s="12" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="K54" s="12" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="M54" s="12" t="n">
         <v>1</v>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>11719</t>
+          <t>12082</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>MONTICHIARI</t>
+          <t>VIADANA</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -3193,35 +3193,35 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="E55" s="12" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F55" s="12" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H55" s="12" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="I55" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="J55" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="K55" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="L55" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="M55" s="12" t="n">
         <v>12</v>
-      </c>
-      <c r="J55" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" s="12" t="n">
-        <v>26</v>
-      </c>
-      <c r="L55" s="12" t="n">
-        <v>40</v>
-      </c>
-      <c r="M55" s="12" t="n">
-        <v>0</v>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
@@ -3232,12 +3232,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>02075</t>
+          <t>01086</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>SUZZARA</t>
+          <t>RECCO</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -3247,35 +3247,35 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
       <c r="E56" s="12" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="J56" s="12" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="K56" s="12" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>58</v>
+        <v>116</v>
       </c>
       <c r="M56" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
@@ -3286,12 +3286,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>03827</t>
+          <t>01283</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>SAN BONIFACIO</t>
+          <t>SARZANA</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -3301,51 +3301,51 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>MARCONI ANDREA</t>
+          <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
       <c r="E57" s="12" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F57" s="12" t="n">
+        <v>68</v>
+      </c>
+      <c r="G57" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="H57" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I57" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="J57" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="K57" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="L57" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="M57" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="G57" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="H57" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" s="12" t="n">
-        <v>32</v>
-      </c>
-      <c r="J57" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="K57" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="L57" s="12" t="n">
-        <v>62</v>
-      </c>
-      <c r="M57" s="12" t="n">
-        <v>31</v>
-      </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>12082</t>
+          <t>56297</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>VIADANA</t>
+          <t>SAN PAOLO D'ARGON</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -3355,51 +3355,51 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="E58" s="12" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="F58" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="H58" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J58" s="12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K58" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L58" s="12" t="n">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="M58" s="12" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>01086</t>
+          <t>02004</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>RECCO</t>
+          <t>RIVOLTA D'ADDA</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -3409,51 +3409,51 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="E59" s="12" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="F59" s="12" t="n">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H59" s="12" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="I59" s="12" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J59" s="12" t="n">
         <v>6</v>
       </c>
       <c r="K59" s="12" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>116</v>
+        <v>43</v>
       </c>
       <c r="M59" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>01283</t>
+          <t>02024</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>SARZANA</t>
+          <t>CASALMAGGIORE</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -3463,51 +3463,51 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="E60" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="F60" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="G60" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="F60" s="12" t="n">
-        <v>68</v>
-      </c>
-      <c r="G60" s="12" t="n">
-        <v>14</v>
-      </c>
       <c r="H60" s="12" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="I60" s="12" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="J60" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="K60" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="K60" s="12" t="n">
-        <v>2</v>
-      </c>
       <c r="L60" s="12" t="n">
+        <v>39</v>
+      </c>
+      <c r="M60" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="M60" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>56297</t>
+          <t>01280</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>SAN PAOLO D'ARGON</t>
+          <t>LA SPEZIA</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -3517,51 +3517,51 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
       <c r="E61" s="12" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F61" s="12" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="H61" s="12" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I61" s="12" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J61" s="12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K61" s="12" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L61" s="12" t="n">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="M61" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>02004</t>
+          <t>54290</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>RIVOLTA D'ADDA</t>
+          <t>GENOVA</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -3571,51 +3571,51 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>DALLORTO ILARIA</t>
         </is>
       </c>
       <c r="E62" s="12" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="G62" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="H62" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H62" s="12" t="n">
+      <c r="I62" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="J62" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I62" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="J62" s="12" t="n">
-        <v>6</v>
-      </c>
       <c r="K62" s="12" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L62" s="12" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="M62" s="12" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>02024</t>
+          <t>52510</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>CASALMAGGIORE</t>
+          <t>PORTO MANTOVANO</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -3629,47 +3629,47 @@
         </is>
       </c>
       <c r="E63" s="12" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F63" s="12" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="H63" s="12" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I63" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J63" s="12" t="n">
         <v>7</v>
       </c>
       <c r="K63" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L63" s="12" t="n">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="M63" s="12" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>01280</t>
+          <t>01288</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>LA SPEZIA</t>
+          <t>BOLANO</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -3683,31 +3683,31 @@
         </is>
       </c>
       <c r="E64" s="12" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="J64" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K64" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L64" s="12" t="n">
-        <v>62</v>
+        <v>22</v>
       </c>
       <c r="M64" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
@@ -3718,12 +3718,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>54290</t>
+          <t>01578</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>GENOVA</t>
+          <t>VERDELLO</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -3733,23 +3733,23 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>DALLORTO ILARIA</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="E65" s="12" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F65" s="12" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="H65" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I65" s="12" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="J65" s="12" t="n">
         <v>3</v>
@@ -3758,26 +3758,26 @@
         <v>3</v>
       </c>
       <c r="L65" s="12" t="n">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="M65" s="12" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>52510</t>
+          <t>01671</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>PORTO MANTOVANO</t>
+          <t>BRESCIA</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -3787,51 +3787,51 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
       <c r="E66" s="12" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G66" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="H66" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="I66" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="J66" s="12" t="n">
         <v>1</v>
-      </c>
-      <c r="H66" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I66" s="12" t="n">
-        <v>22</v>
-      </c>
-      <c r="J66" s="12" t="n">
-        <v>7</v>
       </c>
       <c r="K66" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L66" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M66" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>01288</t>
+          <t>02074</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>BOLANO</t>
+          <t>GOITO</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -3841,51 +3841,51 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="E67" s="12" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F67" s="12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H67" s="12" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I67" s="12" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="J67" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K67" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L67" s="12" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="M67" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>01578</t>
+          <t>01631</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>VERDELLO</t>
+          <t>TELGATE</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -3895,51 +3895,51 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>SALVINELLI LUCA</t>
         </is>
       </c>
       <c r="E68" s="12" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F68" s="12" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="G68" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H68" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I68" s="12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J68" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K68" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L68" s="12" t="n">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="M68" s="12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>01671</t>
+          <t>11348</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA</t>
+          <t>VADO LIGURE</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -3949,23 +3949,23 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>GRAZIOSI DAVIDE</t>
+          <t>DELUGAS NADIA</t>
         </is>
       </c>
       <c r="E69" s="12" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F69" s="12" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="H69" s="12" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="I69" s="12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J69" s="12" t="n">
         <v>1</v>
@@ -3974,608 +3974,14 @@
         <v>0</v>
       </c>
       <c r="L69" s="12" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="M69" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>02074</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>GOITO</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Emanuele</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>CARMINATI SIMONE</t>
-        </is>
-      </c>
-      <c r="E70" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="F70" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G70" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H70" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I70" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="J70" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="K70" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L70" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="M70" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="N70" s="2" t="inlineStr">
-        <is>
-          <t>Bene</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>01631</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>TELGATE</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Emanuele</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t>SALVINELLI LUCA</t>
-        </is>
-      </c>
-      <c r="E71" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="F71" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G71" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H71" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I71" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="J71" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K71" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L71" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="M71" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="N71" s="2" t="inlineStr">
-        <is>
-          <t>Da seguire</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>11348</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>VADO LIGURE</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Emanuele</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>DELUGAS NADIA</t>
-        </is>
-      </c>
-      <c r="E72" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="F72" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G72" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="H72" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I72" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="J72" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K72" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L72" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="M72" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="N72" s="2" t="inlineStr">
-        <is>
-          <t>Da seguire</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>00926</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>GASSINO TORINESE</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Emanuele</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>BRESCIA FEDERICO</t>
-        </is>
-      </c>
-      <c r="E73" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F73" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="G73" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H73" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I73" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K73" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L73" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M73" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N73" s="2" t="inlineStr">
-        <is>
-          <t>Bene</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>01339</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>ALASSIO</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Emanuele</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>BARNABA SALVATORE</t>
-        </is>
-      </c>
-      <c r="E74" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F74" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="G74" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H74" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="I74" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J74" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K74" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L74" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M74" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N74" s="2" t="inlineStr">
-        <is>
-          <t>Bene</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>01522</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>CASAZZA</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Emanuele</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>BRIGNOLI STEFANO</t>
-        </is>
-      </c>
-      <c r="E75" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F75" s="12" t="n">
-        <v>57</v>
-      </c>
-      <c r="G75" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H75" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="I75" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J75" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K75" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L75" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M75" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N75" s="2" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>01639</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>PIANICO</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Emanuele</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
-          <t>BRIGNOLI STEFANO</t>
-        </is>
-      </c>
-      <c r="E76" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F76" s="12" t="n">
-        <v>86</v>
-      </c>
-      <c r="G76" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H76" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I76" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J76" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K76" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L76" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M76" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N76" s="2" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>02053</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>BAGNOLO SAN VITO</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Emanuele</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>CARMINATI SIMONE</t>
-        </is>
-      </c>
-      <c r="E77" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F77" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="G77" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H77" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I77" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J77" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K77" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L77" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M77" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N77" s="2" t="inlineStr">
-        <is>
-          <t>Da seguire</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>02970</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>FIDENZA</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Emanuele</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
-          <t>IACONA GIOVANNI</t>
-        </is>
-      </c>
-      <c r="E78" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F78" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="G78" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H78" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I78" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J78" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K78" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L78" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M78" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N78" s="2" t="inlineStr">
-        <is>
-          <t>Bene</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>05511</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>MEDICINA</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Emanuele</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
-        <is>
-          <t>MURGO LORENZO</t>
-        </is>
-      </c>
-      <c r="E79" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F79" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="G79" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H79" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I79" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J79" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K79" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L79" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M79" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N79" s="2" t="inlineStr">
-        <is>
-          <t>Bene</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>15548</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>PIANORO</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Emanuele</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
-        <is>
-          <t>MURGO LORENZO</t>
-        </is>
-      </c>
-      <c r="E80" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F80" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="G80" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H80" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I80" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J80" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K80" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L80" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M80" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N80" s="2" t="inlineStr">
-        <is>
-          <t>Bene</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/Agente - Marcelli Emanuele.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Marcelli Emanuele.xlsx
@@ -209,8 +209,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N69" headerRowCount="1">
-  <autoFilter ref="A10:N69"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N74" headerRowCount="1">
+  <autoFilter ref="A10:N74"/>
   <tableColumns count="14">
     <tableColumn id="1" name="PDV"/>
     <tableColumn id="2" name="Città"/>
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N69"/>
+  <dimension ref="A1:N74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -673,16 +673,16 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>7493</v>
+        <v>7665</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>5244</v>
+        <v>5358</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>2499</v>
+        <v>2675</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -2638,12 +2638,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>01637</t>
+          <t>01717</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>CURNO</t>
+          <t>PAITONE</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -2653,35 +2653,35 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
       <c r="E45" s="12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F45" s="12" t="n">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>5</v>
+        <v>85</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>7</v>
+        <v>73</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="J45" s="12" t="n">
         <v>11</v>
       </c>
       <c r="K45" s="12" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
@@ -2692,12 +2692,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>55864</t>
+          <t>01637</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>OVADA</t>
+          <t>CURNO</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -2707,51 +2707,51 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>DELUGAS NADIA</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="E46" s="12" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="G46" s="12" t="n">
         <v>5</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="I46" s="12" t="n">
         <v>29</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="K46" s="12" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>59894</t>
+          <t>55864</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA</t>
+          <t>OVADA</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -2761,51 +2761,51 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>SALVINELLI LUCA</t>
+          <t>DELUGAS NADIA</t>
         </is>
       </c>
       <c r="E47" s="12" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K47" s="12" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>33</v>
+        <v>76</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>01334</t>
+          <t>59894</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>FINALE LIGURE</t>
+          <t>BRESCIA</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -2815,35 +2815,35 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>BARNABA SALVATORE</t>
+          <t>SALVINELLI LUCA</t>
         </is>
       </c>
       <c r="E48" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="J48" s="12" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K48" s="12" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="M48" s="12" t="n">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
@@ -2854,12 +2854,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>01142</t>
+          <t>01334</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>SESTRI LEVANTE</t>
+          <t>FINALE LIGURE</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -2869,51 +2869,51 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>BARNABA SALVATORE</t>
         </is>
       </c>
       <c r="E49" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F49" s="12" t="n">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="I49" s="12" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J49" s="12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K49" s="12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="M49" s="12" t="n">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>54151</t>
+          <t>01142</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>IMPERIA</t>
+          <t>SESTRI LEVANTE</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -2923,35 +2923,35 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>BARNABA SALVATORE</t>
+          <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
       <c r="E50" s="12" t="n">
         <v>41</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J50" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K50" s="12" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="M50" s="12" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
@@ -2962,12 +2962,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>01135</t>
+          <t>54151</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>GENOVA</t>
+          <t>IMPERIA</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -2977,51 +2977,51 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>DALLORTO ILARIA</t>
+          <t>BARNABA SALVATORE</t>
         </is>
       </c>
       <c r="E51" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F51" s="12" t="n">
-        <v>36</v>
+        <v>92</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="H51" s="12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I51" s="12" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J51" s="12" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K51" s="12" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="M51" s="12" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>01561</t>
+          <t>11726</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>PONTIROLO NUOVO</t>
+          <t>REZZATO</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -3031,51 +3031,51 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
       <c r="E52" s="12" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="G52" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="H52" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="I52" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="J52" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="K52" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="L52" s="12" t="n">
+        <v>45</v>
+      </c>
+      <c r="M52" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H52" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I52" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="J52" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="K52" s="12" t="n">
-        <v>22</v>
-      </c>
-      <c r="L52" s="12" t="n">
-        <v>44</v>
-      </c>
-      <c r="M52" s="12" t="n">
-        <v>1</v>
-      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>11719</t>
+          <t>01135</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>MONTICHIARI</t>
+          <t>GENOVA</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -3085,35 +3085,35 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>DALLORTO ILARIA</t>
         </is>
       </c>
       <c r="E53" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="H53" s="12" t="n">
-        <v>106</v>
+        <v>4</v>
       </c>
       <c r="I53" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="J53" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="K53" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="J53" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" s="12" t="n">
-        <v>26</v>
-      </c>
       <c r="L53" s="12" t="n">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="M53" s="12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
@@ -3124,12 +3124,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>02075</t>
+          <t>55973</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>SUZZARA</t>
+          <t>BOTTICINO</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -3139,51 +3139,51 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
       <c r="E54" s="12" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>47</v>
+        <v>1</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="J54" s="12" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="K54" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="L54" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="M54" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="L54" s="12" t="n">
-        <v>58</v>
-      </c>
-      <c r="M54" s="12" t="n">
-        <v>1</v>
-      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>12082</t>
+          <t>01561</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>VIADANA</t>
+          <t>PONTIROLO NUOVO</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -3193,35 +3193,35 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="E55" s="12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F55" s="12" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="H55" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I55" s="12" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="J55" s="12" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K55" s="12" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="M55" s="12" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
@@ -3232,12 +3232,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>01086</t>
+          <t>11719</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>RECCO</t>
+          <t>MONTICHIARI</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -3247,51 +3247,51 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="E56" s="12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>19</v>
+        <v>106</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="J56" s="12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K56" s="12" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>116</v>
+        <v>40</v>
       </c>
       <c r="M56" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>01283</t>
+          <t>02075</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>SARZANA</t>
+          <t>SUZZARA</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -3301,35 +3301,35 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="E57" s="12" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F57" s="12" t="n">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="H57" s="12" t="n">
-        <v>3</v>
+        <v>47</v>
       </c>
       <c r="I57" s="12" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="J57" s="12" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="K57" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L57" s="12" t="n">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="M57" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
@@ -3340,12 +3340,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>56297</t>
+          <t>12082</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>SAN PAOLO D'ARGON</t>
+          <t>VIADANA</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -3355,51 +3355,51 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="E58" s="12" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="F58" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="H58" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J58" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K58" s="12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L58" s="12" t="n">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="M58" s="12" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>02004</t>
+          <t>01086</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>RIVOLTA D'ADDA</t>
+          <t>RECCO</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -3409,51 +3409,51 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
       <c r="E59" s="12" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F59" s="12" t="n">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H59" s="12" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="I59" s="12" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J59" s="12" t="n">
         <v>6</v>
       </c>
       <c r="K59" s="12" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>43</v>
+        <v>116</v>
       </c>
       <c r="M59" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>02024</t>
+          <t>01283</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>CASALMAGGIORE</t>
+          <t>SARZANA</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -3463,51 +3463,51 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
       <c r="E60" s="12" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="I60" s="12" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J60" s="12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K60" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L60" s="12" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="M60" s="12" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>01280</t>
+          <t>56297</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>LA SPEZIA</t>
+          <t>SAN PAOLO D'ARGON</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -3517,51 +3517,51 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="E61" s="12" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F61" s="12" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="H61" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="I61" s="12" t="n">
-        <v>26</v>
-      </c>
       <c r="J61" s="12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K61" s="12" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L61" s="12" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="M61" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>54290</t>
+          <t>02004</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>GENOVA</t>
+          <t>RIVOLTA D'ADDA</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -3571,51 +3571,51 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>DALLORTO ILARIA</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="E62" s="12" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F62" s="12" t="n">
+        <v>51</v>
+      </c>
+      <c r="G62" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="G62" s="12" t="n">
-        <v>23</v>
-      </c>
       <c r="H62" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J62" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K62" s="12" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L62" s="12" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M62" s="12" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>52510</t>
+          <t>02024</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>PORTO MANTOVANO</t>
+          <t>CASALMAGGIORE</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -3629,47 +3629,47 @@
         </is>
       </c>
       <c r="E63" s="12" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F63" s="12" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="H63" s="12" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I63" s="12" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J63" s="12" t="n">
         <v>7</v>
       </c>
       <c r="K63" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L63" s="12" t="n">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="M63" s="12" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>01288</t>
+          <t>11725</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>BOLANO</t>
+          <t>GAVARDO</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -3679,35 +3679,35 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
       <c r="E64" s="12" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F64" s="12" t="n">
+        <v>39</v>
+      </c>
+      <c r="G64" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="G64" s="12" t="n">
-        <v>17</v>
-      </c>
       <c r="H64" s="12" t="n">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J64" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K64" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="L64" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="M64" s="12" t="n">
         <v>3</v>
-      </c>
-      <c r="K64" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L64" s="12" t="n">
-        <v>22</v>
-      </c>
-      <c r="M64" s="12" t="n">
-        <v>0</v>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
@@ -3718,12 +3718,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>01578</t>
+          <t>01280</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>VERDELLO</t>
+          <t>LA SPEZIA</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -3733,35 +3733,35 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
       <c r="E65" s="12" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="F65" s="12" t="n">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="G65" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="H65" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="I65" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="J65" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K65" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H65" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="I65" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="J65" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="K65" s="12" t="n">
-        <v>3</v>
-      </c>
       <c r="L65" s="12" t="n">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="M65" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
@@ -3772,12 +3772,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>01671</t>
+          <t>54290</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA</t>
+          <t>GENOVA</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -3787,51 +3787,51 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>GRAZIOSI DAVIDE</t>
+          <t>DALLORTO ILARIA</t>
         </is>
       </c>
       <c r="E66" s="12" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="I66" s="12" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="J66" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K66" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L66" s="12" t="n">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="M66" s="12" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>02074</t>
+          <t>52510</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>GOITO</t>
+          <t>PORTO MANTOVANO</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -3845,31 +3845,31 @@
         </is>
       </c>
       <c r="E67" s="12" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="F67" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H67" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I67" s="12" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="J67" s="12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K67" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L67" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M67" s="12" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
@@ -3880,12 +3880,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>01631</t>
+          <t>01523</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>TELGATE</t>
+          <t>CISANO BERGAMASCO</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -3895,51 +3895,51 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>SALVINELLI LUCA</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="E68" s="12" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F68" s="12" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="H68" s="12" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="I68" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J68" s="12" t="n">
         <v>0</v>
       </c>
       <c r="K68" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="L68" s="12" t="n">
+        <v>59</v>
+      </c>
+      <c r="M68" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="L68" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="M68" s="12" t="n">
-        <v>6</v>
-      </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>11348</t>
+          <t>01288</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>VADO LIGURE</t>
+          <t>BOLANO</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -3949,37 +3949,307 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>DELUGAS NADIA</t>
+          <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
       <c r="E69" s="12" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="F69" s="12" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="H69" s="12" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I69" s="12" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="J69" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K69" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L69" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="M69" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>01578</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>VERDELLO</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>VINCENZI STEFANO</t>
+        </is>
+      </c>
+      <c r="E70" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="F70" s="12" t="n">
+        <v>53</v>
+      </c>
+      <c r="G70" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H70" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="I70" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="J70" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K70" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="L70" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="M70" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>01671</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>BRESCIA</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>GRAZIOSI DAVIDE</t>
+        </is>
+      </c>
+      <c r="E71" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="F71" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="G71" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="H71" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="I71" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="J71" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K71" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="M71" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>Da seguire</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>02074</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>GOITO</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>CARMINATI SIMONE</t>
+        </is>
+      </c>
+      <c r="E72" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="F72" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="J72" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K72" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="M72" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>Bene</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>01631</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>TELGATE</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>SALVINELLI LUCA</t>
+        </is>
+      </c>
+      <c r="E73" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="F73" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H73" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="J73" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="M73" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>Da seguire</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>11348</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>VADO LIGURE</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>DELUGAS NADIA</t>
+        </is>
+      </c>
+      <c r="E74" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="M69" s="12" t="n">
+      <c r="F74" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="N69" s="2" t="inlineStr">
+      <c r="H74" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="J74" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K74" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="M74" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>

--- a/docs/files/REPORT_FILTRI/Agente - Marcelli Emanuele.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Marcelli Emanuele.xlsx
@@ -209,23 +209,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N74" headerRowCount="1">
-  <autoFilter ref="A10:N74"/>
-  <tableColumns count="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:O74" headerRowCount="1">
+  <autoFilter ref="A10:O74"/>
+  <tableColumns count="15">
     <tableColumn id="1" name="PDV"/>
     <tableColumn id="2" name="Città"/>
-    <tableColumn id="3" name="Agente"/>
-    <tableColumn id="4" name="CR"/>
-    <tableColumn id="5" name="Vend 2026"/>
-    <tableColumn id="6" name="Vend 2025"/>
-    <tableColumn id="7" name="Ass 2026"/>
-    <tableColumn id="8" name="Ass 2025"/>
-    <tableColumn id="9" name="Prospect"/>
-    <tableColumn id="10" name="Twin"/>
-    <tableColumn id="11" name="Business"/>
-    <tableColumn id="12" name="Sost anno"/>
-    <tableColumn id="13" name="UP EU"/>
-    <tableColumn id="14" name="Stato"/>
+    <tableColumn id="3" name="Indirizzo"/>
+    <tableColumn id="4" name="Agente"/>
+    <tableColumn id="5" name="CR"/>
+    <tableColumn id="6" name="Vend 2026"/>
+    <tableColumn id="7" name="Vend 2025"/>
+    <tableColumn id="8" name="Ass 2026"/>
+    <tableColumn id="9" name="Ass 2025"/>
+    <tableColumn id="10" name="Prospect"/>
+    <tableColumn id="11" name="Twin"/>
+    <tableColumn id="12" name="Business"/>
+    <tableColumn id="13" name="Sost anno"/>
+    <tableColumn id="14" name="UP EU"/>
+    <tableColumn id="15" name="Stato"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -520,23 +521,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N74"/>
+  <dimension ref="A1:O74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -558,6 +560,7 @@
       <c r="L1" s="2" t="n"/>
       <c r="M1" s="2" t="n"/>
       <c r="N1" s="2" t="n"/>
+      <c r="O1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n"/>
@@ -574,6 +577,7 @@
       <c r="L2" s="2" t="n"/>
       <c r="M2" s="2" t="n"/>
       <c r="N2" s="2" t="n"/>
+      <c r="O2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -598,6 +602,7 @@
       <c r="L3" s="2" t="n"/>
       <c r="M3" s="2" t="n"/>
       <c r="N3" s="2" t="n"/>
+      <c r="O3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -622,6 +627,7 @@
       <c r="L4" s="2" t="n"/>
       <c r="M4" s="2" t="n"/>
       <c r="N4" s="2" t="n"/>
+      <c r="O4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n"/>
@@ -638,6 +644,7 @@
       <c r="L5" s="2" t="n"/>
       <c r="M5" s="2" t="n"/>
       <c r="N5" s="2" t="n"/>
+      <c r="O5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -670,6 +677,7 @@
       <c r="L6" s="2" t="n"/>
       <c r="M6" s="2" t="n"/>
       <c r="N6" s="2" t="n"/>
+      <c r="O6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -694,6 +702,7 @@
       <c r="L7" s="2" t="n"/>
       <c r="M7" s="2" t="n"/>
       <c r="N7" s="2" t="n"/>
+      <c r="O7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n"/>
@@ -710,6 +719,7 @@
       <c r="L8" s="2" t="n"/>
       <c r="M8" s="2" t="n"/>
       <c r="N8" s="2" t="n"/>
+      <c r="O8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n"/>
@@ -726,6 +736,7 @@
       <c r="L9" s="2" t="n"/>
       <c r="M9" s="2" t="n"/>
       <c r="N9" s="2" t="n"/>
+      <c r="O9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
@@ -740,60 +751,65 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
+          <t>Indirizzo</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
           <t>Agente</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>CR</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
+      <c r="F10" s="11" t="inlineStr">
         <is>
           <t>Vend 2026</t>
         </is>
       </c>
-      <c r="F10" s="11" t="inlineStr">
+      <c r="G10" s="11" t="inlineStr">
         <is>
           <t>Vend 2025</t>
         </is>
       </c>
-      <c r="G10" s="11" t="inlineStr">
+      <c r="H10" s="11" t="inlineStr">
         <is>
           <t>Ass 2026</t>
         </is>
       </c>
-      <c r="H10" s="11" t="inlineStr">
+      <c r="I10" s="11" t="inlineStr">
         <is>
           <t>Ass 2025</t>
         </is>
       </c>
-      <c r="I10" s="11" t="inlineStr">
+      <c r="J10" s="11" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="J10" s="11" t="inlineStr">
+      <c r="K10" s="11" t="inlineStr">
         <is>
           <t>Twin</t>
         </is>
       </c>
-      <c r="K10" s="11" t="inlineStr">
+      <c r="L10" s="11" t="inlineStr">
         <is>
           <t>Business</t>
         </is>
       </c>
-      <c r="L10" s="11" t="inlineStr">
+      <c r="M10" s="11" t="inlineStr">
         <is>
           <t>Sost anno</t>
         </is>
       </c>
-      <c r="M10" s="11" t="inlineStr">
+      <c r="N10" s="11" t="inlineStr">
         <is>
           <t>UP EU</t>
         </is>
       </c>
-      <c r="N10" s="11" t="inlineStr">
+      <c r="O10" s="11" t="inlineStr">
         <is>
           <t>Stato</t>
         </is>
@@ -812,42 +828,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>VIA DALMAZIA 44</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
           <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="F11" s="12" t="n">
         <v>758</v>
       </c>
-      <c r="F11" s="12" t="n">
+      <c r="G11" s="12" t="n">
         <v>550</v>
       </c>
-      <c r="G11" s="12" t="n">
+      <c r="H11" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="H11" s="12" t="n">
+      <c r="I11" s="12" t="n">
         <v>75</v>
       </c>
-      <c r="I11" s="12" t="n">
+      <c r="J11" s="12" t="n">
         <v>482</v>
       </c>
-      <c r="J11" s="12" t="n">
+      <c r="K11" s="12" t="n">
         <v>159</v>
       </c>
-      <c r="K11" s="12" t="n">
+      <c r="L11" s="12" t="n">
         <v>281</v>
       </c>
-      <c r="L11" s="12" t="n">
+      <c r="M11" s="12" t="n">
         <v>641</v>
       </c>
-      <c r="M11" s="12" t="n">
+      <c r="N11" s="12" t="n">
         <v>75</v>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -866,42 +887,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>VIA BORGOSATOLLO 77</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>SALVINELLI LUCA</t>
         </is>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="F12" s="12" t="n">
         <v>524</v>
       </c>
-      <c r="F12" s="12" t="n">
+      <c r="G12" s="12" t="n">
         <v>228</v>
       </c>
-      <c r="G12" s="12" t="n">
+      <c r="H12" s="12" t="n">
         <v>71</v>
       </c>
-      <c r="H12" s="12" t="n">
+      <c r="I12" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="I12" s="12" t="n">
+      <c r="J12" s="12" t="n">
         <v>355</v>
       </c>
-      <c r="J12" s="12" t="n">
+      <c r="K12" s="12" t="n">
         <v>125</v>
       </c>
-      <c r="K12" s="12" t="n">
+      <c r="L12" s="12" t="n">
         <v>156</v>
       </c>
-      <c r="L12" s="12" t="n">
+      <c r="M12" s="12" t="n">
         <v>335</v>
       </c>
-      <c r="M12" s="12" t="n">
+      <c r="N12" s="12" t="n">
         <v>142</v>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -920,42 +946,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>S S 11 KM 224 + 521</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
-      <c r="E13" s="12" t="n">
+      <c r="F13" s="12" t="n">
         <v>453</v>
       </c>
-      <c r="F13" s="12" t="n">
+      <c r="G13" s="12" t="n">
         <v>248</v>
       </c>
-      <c r="G13" s="12" t="n">
+      <c r="H13" s="12" t="n">
         <v>543</v>
       </c>
-      <c r="H13" s="12" t="n">
+      <c r="I13" s="12" t="n">
         <v>263</v>
       </c>
-      <c r="I13" s="12" t="n">
+      <c r="J13" s="12" t="n">
         <v>318</v>
       </c>
-      <c r="J13" s="12" t="n">
+      <c r="K13" s="12" t="n">
         <v>123</v>
       </c>
-      <c r="K13" s="12" t="n">
+      <c r="L13" s="12" t="n">
         <v>134</v>
       </c>
-      <c r="L13" s="12" t="n">
+      <c r="M13" s="12" t="n">
         <v>261</v>
       </c>
-      <c r="M13" s="12" t="n">
+      <c r="N13" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -974,42 +1005,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>VIA PALAZZOLO S.S.469</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>DODI JACOPO</t>
         </is>
       </c>
-      <c r="E14" s="12" t="n">
+      <c r="F14" s="12" t="n">
         <v>377</v>
       </c>
-      <c r="F14" s="12" t="n">
+      <c r="G14" s="12" t="n">
         <v>304</v>
       </c>
-      <c r="G14" s="12" t="n">
+      <c r="H14" s="12" t="n">
         <v>76</v>
       </c>
-      <c r="H14" s="12" t="n">
+      <c r="I14" s="12" t="n">
         <v>81</v>
       </c>
-      <c r="I14" s="12" t="n">
+      <c r="J14" s="12" t="n">
         <v>244</v>
       </c>
-      <c r="J14" s="12" t="n">
+      <c r="K14" s="12" t="n">
         <v>77</v>
       </c>
-      <c r="K14" s="12" t="n">
+      <c r="L14" s="12" t="n">
         <v>125</v>
       </c>
-      <c r="L14" s="12" t="n">
+      <c r="M14" s="12" t="n">
         <v>315</v>
       </c>
-      <c r="M14" s="12" t="n">
+      <c r="N14" s="12" t="n">
         <v>70</v>
       </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1028,42 +1064,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>VIA G BRUNO 71</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
           <t>VIGNADUZZO EDI</t>
         </is>
       </c>
-      <c r="E15" s="12" t="n">
+      <c r="F15" s="12" t="n">
         <v>345</v>
       </c>
-      <c r="F15" s="12" t="n">
+      <c r="G15" s="12" t="n">
         <v>465</v>
       </c>
-      <c r="G15" s="12" t="n">
+      <c r="H15" s="12" t="n">
         <v>90</v>
       </c>
-      <c r="H15" s="12" t="n">
+      <c r="I15" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="I15" s="12" t="n">
+      <c r="J15" s="12" t="n">
         <v>265</v>
       </c>
-      <c r="J15" s="12" t="n">
+      <c r="K15" s="12" t="n">
         <v>84</v>
       </c>
-      <c r="K15" s="12" t="n">
+      <c r="L15" s="12" t="n">
         <v>83</v>
       </c>
-      <c r="L15" s="12" t="n">
+      <c r="M15" s="12" t="n">
         <v>500</v>
       </c>
-      <c r="M15" s="12" t="n">
+      <c r="N15" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1082,42 +1123,47 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>VIA CANTORE 20 A ROSSO</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>DALLORTO ILARIA</t>
         </is>
       </c>
-      <c r="E16" s="12" t="n">
+      <c r="F16" s="12" t="n">
         <v>312</v>
       </c>
-      <c r="F16" s="12" t="n">
+      <c r="G16" s="12" t="n">
         <v>371</v>
       </c>
-      <c r="G16" s="12" t="n">
+      <c r="H16" s="12" t="n">
         <v>330</v>
       </c>
-      <c r="H16" s="12" t="n">
+      <c r="I16" s="12" t="n">
         <v>475</v>
       </c>
-      <c r="I16" s="12" t="n">
+      <c r="J16" s="12" t="n">
         <v>256</v>
       </c>
-      <c r="J16" s="12" t="n">
+      <c r="K16" s="12" t="n">
         <v>88</v>
       </c>
-      <c r="K16" s="12" t="n">
+      <c r="L16" s="12" t="n">
         <v>58</v>
       </c>
-      <c r="L16" s="12" t="n">
+      <c r="M16" s="12" t="n">
         <v>288</v>
       </c>
-      <c r="M16" s="12" t="n">
+      <c r="N16" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1136,42 +1182,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>VIA BROSETA</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
           <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
-      <c r="E17" s="12" t="n">
+      <c r="F17" s="12" t="n">
         <v>311</v>
       </c>
-      <c r="F17" s="12" t="n">
+      <c r="G17" s="12" t="n">
         <v>516</v>
       </c>
-      <c r="G17" s="12" t="n">
+      <c r="H17" s="12" t="n">
         <v>37</v>
       </c>
-      <c r="H17" s="12" t="n">
+      <c r="I17" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="I17" s="12" t="n">
+      <c r="J17" s="12" t="n">
         <v>235</v>
       </c>
-      <c r="J17" s="12" t="n">
+      <c r="K17" s="12" t="n">
         <v>98</v>
       </c>
-      <c r="K17" s="12" t="n">
+      <c r="L17" s="12" t="n">
         <v>79</v>
       </c>
-      <c r="L17" s="12" t="n">
+      <c r="M17" s="12" t="n">
         <v>377</v>
       </c>
-      <c r="M17" s="12" t="n">
+      <c r="N17" s="12" t="n">
         <v>72</v>
       </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1190,42 +1241,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>VIA MONTELUNGO, 10  - TANG. OVEST PALAZZOLI</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
-      <c r="E18" s="12" t="n">
+      <c r="F18" s="12" t="n">
         <v>285</v>
       </c>
-      <c r="F18" s="12" t="n">
+      <c r="G18" s="12" t="n">
         <v>341</v>
       </c>
-      <c r="G18" s="12" t="n">
+      <c r="H18" s="12" t="n">
         <v>58</v>
       </c>
-      <c r="H18" s="12" t="n">
+      <c r="I18" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="I18" s="12" t="n">
+      <c r="J18" s="12" t="n">
         <v>239</v>
       </c>
-      <c r="J18" s="12" t="n">
+      <c r="K18" s="12" t="n">
         <v>72</v>
       </c>
-      <c r="K18" s="12" t="n">
+      <c r="L18" s="12" t="n">
         <v>46</v>
       </c>
-      <c r="L18" s="12" t="n">
+      <c r="M18" s="12" t="n">
         <v>180</v>
       </c>
-      <c r="M18" s="12" t="n">
+      <c r="N18" s="12" t="n">
         <v>109</v>
       </c>
-      <c r="N18" s="2" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1244,42 +1300,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>SS 28 SUD KM. 25 FRAZ.SANTUARIO</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
           <t>GIARRATANA SEARA</t>
         </is>
       </c>
-      <c r="E19" s="12" t="n">
+      <c r="F19" s="12" t="n">
         <v>265</v>
       </c>
-      <c r="F19" s="12" t="n">
+      <c r="G19" s="12" t="n">
         <v>219</v>
-      </c>
-      <c r="G19" s="12" t="n">
-        <v>92</v>
       </c>
       <c r="H19" s="12" t="n">
         <v>92</v>
       </c>
       <c r="I19" s="12" t="n">
+        <v>92</v>
+      </c>
+      <c r="J19" s="12" t="n">
         <v>212</v>
       </c>
-      <c r="J19" s="12" t="n">
+      <c r="K19" s="12" t="n">
         <v>84</v>
       </c>
-      <c r="K19" s="12" t="n">
+      <c r="L19" s="12" t="n">
         <v>46</v>
       </c>
-      <c r="L19" s="12" t="n">
+      <c r="M19" s="12" t="n">
         <v>110</v>
       </c>
-      <c r="M19" s="12" t="n">
+      <c r="N19" s="12" t="n">
         <v>37</v>
       </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1298,42 +1359,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>VIA PICCINELLI 78</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>DODI JACOPO</t>
         </is>
       </c>
-      <c r="E20" s="12" t="n">
+      <c r="F20" s="12" t="n">
         <v>230</v>
       </c>
-      <c r="F20" s="12" t="n">
+      <c r="G20" s="12" t="n">
         <v>96</v>
       </c>
-      <c r="G20" s="12" t="n">
+      <c r="H20" s="12" t="n">
         <v>117</v>
       </c>
-      <c r="H20" s="12" t="n">
+      <c r="I20" s="12" t="n">
         <v>46</v>
       </c>
-      <c r="I20" s="12" t="n">
+      <c r="J20" s="12" t="n">
         <v>182</v>
       </c>
-      <c r="J20" s="12" t="n">
+      <c r="K20" s="12" t="n">
         <v>79</v>
       </c>
-      <c r="K20" s="12" t="n">
+      <c r="L20" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="L20" s="12" t="n">
+      <c r="M20" s="12" t="n">
         <v>70</v>
       </c>
-      <c r="M20" s="12" t="n">
+      <c r="N20" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1352,42 +1418,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>VIA STELLA ALPINA</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
           <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
-      <c r="E21" s="12" t="n">
+      <c r="F21" s="12" t="n">
         <v>220</v>
       </c>
-      <c r="F21" s="12" t="n">
+      <c r="G21" s="12" t="n">
         <v>245</v>
-      </c>
-      <c r="G21" s="12" t="n">
-        <v>30</v>
       </c>
       <c r="H21" s="12" t="n">
         <v>30</v>
       </c>
       <c r="I21" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="J21" s="12" t="n">
         <v>124</v>
       </c>
-      <c r="J21" s="12" t="n">
+      <c r="K21" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="K21" s="12" t="n">
+      <c r="L21" s="12" t="n">
         <v>97</v>
       </c>
-      <c r="L21" s="12" t="n">
+      <c r="M21" s="12" t="n">
         <v>239</v>
       </c>
-      <c r="M21" s="12" t="n">
+      <c r="N21" s="12" t="n">
         <v>59</v>
       </c>
-      <c r="N21" s="2" t="inlineStr">
+      <c r="O21" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1406,42 +1477,47 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>STRADA PROVINCIALE 84</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>VINCENZI STEFANO</t>
         </is>
       </c>
-      <c r="E22" s="12" t="n">
+      <c r="F22" s="12" t="n">
         <v>197</v>
       </c>
-      <c r="F22" s="12" t="n">
+      <c r="G22" s="12" t="n">
         <v>173</v>
       </c>
-      <c r="G22" s="12" t="n">
+      <c r="H22" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="H22" s="12" t="n">
+      <c r="I22" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="I22" s="12" t="n">
+      <c r="J22" s="12" t="n">
         <v>106</v>
       </c>
-      <c r="J22" s="12" t="n">
+      <c r="K22" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="K22" s="12" t="n">
+      <c r="L22" s="12" t="n">
         <v>101</v>
       </c>
-      <c r="L22" s="12" t="n">
+      <c r="M22" s="12" t="n">
         <v>172</v>
       </c>
-      <c r="M22" s="12" t="n">
+      <c r="N22" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1460,42 +1536,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>VIA LEGA LOMBARDA 2</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
           <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
-      <c r="E23" s="12" t="n">
+      <c r="F23" s="12" t="n">
         <v>197</v>
       </c>
-      <c r="F23" s="12" t="n">
+      <c r="G23" s="12" t="n">
         <v>300</v>
       </c>
-      <c r="G23" s="12" t="n">
+      <c r="H23" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H23" s="12" t="n">
+      <c r="I23" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I23" s="12" t="n">
+      <c r="J23" s="12" t="n">
         <v>80</v>
       </c>
-      <c r="J23" s="12" t="n">
+      <c r="K23" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="K23" s="12" t="n">
+      <c r="L23" s="12" t="n">
         <v>118</v>
       </c>
-      <c r="L23" s="12" t="n">
+      <c r="M23" s="12" t="n">
         <v>219</v>
       </c>
-      <c r="M23" s="12" t="n">
+      <c r="N23" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="N23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1514,42 +1595,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>STALINGRADO</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
           <t>BARNABA SALVATORE</t>
         </is>
       </c>
-      <c r="E24" s="12" t="n">
+      <c r="F24" s="12" t="n">
         <v>179</v>
       </c>
-      <c r="F24" s="12" t="n">
+      <c r="G24" s="12" t="n">
         <v>152</v>
       </c>
-      <c r="G24" s="12" t="n">
+      <c r="H24" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="H24" s="12" t="n">
+      <c r="I24" s="12" t="n">
         <v>74</v>
       </c>
-      <c r="I24" s="12" t="n">
+      <c r="J24" s="12" t="n">
         <v>134</v>
       </c>
-      <c r="J24" s="12" t="n">
+      <c r="K24" s="12" t="n">
         <v>46</v>
       </c>
-      <c r="K24" s="12" t="n">
+      <c r="L24" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="L24" s="12" t="n">
+      <c r="M24" s="12" t="n">
         <v>168</v>
       </c>
-      <c r="M24" s="12" t="n">
+      <c r="N24" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="N24" s="2" t="inlineStr">
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1568,42 +1654,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>VIA BRIGATE PARTIGIANE, 1/R</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
           <t>DALLORTO ILARIA</t>
         </is>
       </c>
-      <c r="E25" s="12" t="n">
+      <c r="F25" s="12" t="n">
         <v>172</v>
       </c>
-      <c r="F25" s="12" t="n">
+      <c r="G25" s="12" t="n">
         <v>249</v>
       </c>
-      <c r="G25" s="12" t="n">
+      <c r="H25" s="12" t="n">
         <v>66</v>
       </c>
-      <c r="H25" s="12" t="n">
+      <c r="I25" s="12" t="n">
         <v>68</v>
       </c>
-      <c r="I25" s="12" t="n">
+      <c r="J25" s="12" t="n">
         <v>129</v>
       </c>
-      <c r="J25" s="12" t="n">
+      <c r="K25" s="12" t="n">
         <v>37</v>
       </c>
-      <c r="K25" s="12" t="n">
+      <c r="L25" s="12" t="n">
         <v>45</v>
       </c>
-      <c r="L25" s="12" t="n">
+      <c r="M25" s="12" t="n">
         <v>426</v>
       </c>
-      <c r="M25" s="12" t="n">
+      <c r="N25" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="N25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1622,42 +1713,47 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>MANTOVA SS 10</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
           <t>DODI JACOPO</t>
         </is>
       </c>
-      <c r="E26" s="12" t="n">
+      <c r="F26" s="12" t="n">
         <v>148</v>
       </c>
-      <c r="F26" s="12" t="n">
+      <c r="G26" s="12" t="n">
         <v>217</v>
       </c>
-      <c r="G26" s="12" t="n">
+      <c r="H26" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H26" s="12" t="n">
+      <c r="I26" s="12" t="n">
         <v>74</v>
       </c>
-      <c r="I26" s="12" t="n">
+      <c r="J26" s="12" t="n">
         <v>108</v>
       </c>
-      <c r="J26" s="12" t="n">
+      <c r="K26" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="K26" s="12" t="n">
+      <c r="L26" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="L26" s="12" t="n">
+      <c r="M26" s="12" t="n">
         <v>230</v>
       </c>
-      <c r="M26" s="12" t="n">
+      <c r="N26" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="N26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1676,42 +1772,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>VIA PIACENZA, 50</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
           <t>VINCENZI STEFANO</t>
         </is>
       </c>
-      <c r="E27" s="12" t="n">
+      <c r="F27" s="12" t="n">
         <v>143</v>
       </c>
-      <c r="F27" s="12" t="n">
+      <c r="G27" s="12" t="n">
         <v>194</v>
       </c>
-      <c r="G27" s="12" t="n">
+      <c r="H27" s="12" t="n">
         <v>125</v>
       </c>
-      <c r="H27" s="12" t="n">
+      <c r="I27" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="I27" s="12" t="n">
+      <c r="J27" s="12" t="n">
         <v>114</v>
       </c>
-      <c r="J27" s="12" t="n">
+      <c r="K27" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="K27" s="12" t="n">
+      <c r="L27" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="L27" s="12" t="n">
+      <c r="M27" s="12" t="n">
         <v>205</v>
       </c>
-      <c r="M27" s="12" t="n">
+      <c r="N27" s="12" t="n">
         <v>83</v>
       </c>
-      <c r="N27" s="2" t="inlineStr">
+      <c r="O27" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1730,42 +1831,47 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>VIA FERRIERE BRUZZO 13</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>DALLORTO ILARIA</t>
         </is>
       </c>
-      <c r="E28" s="12" t="n">
+      <c r="F28" s="12" t="n">
         <v>139</v>
       </c>
-      <c r="F28" s="12" t="n">
+      <c r="G28" s="12" t="n">
         <v>151</v>
       </c>
-      <c r="G28" s="12" t="n">
+      <c r="H28" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="H28" s="12" t="n">
+      <c r="I28" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="I28" s="12" t="n">
+      <c r="J28" s="12" t="n">
         <v>84</v>
       </c>
-      <c r="J28" s="12" t="n">
+      <c r="K28" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="K28" s="12" t="n">
+      <c r="L28" s="12" t="n">
         <v>51</v>
       </c>
-      <c r="L28" s="12" t="n">
+      <c r="M28" s="12" t="n">
         <v>177</v>
       </c>
-      <c r="M28" s="12" t="n">
+      <c r="N28" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="N28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1784,42 +1890,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>CESARE BATTISTI</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
           <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
-      <c r="E29" s="12" t="n">
+      <c r="F29" s="12" t="n">
         <v>139</v>
       </c>
-      <c r="F29" s="12" t="n">
+      <c r="G29" s="12" t="n">
         <v>173</v>
       </c>
-      <c r="G29" s="12" t="n">
+      <c r="H29" s="12" t="n">
         <v>53</v>
       </c>
-      <c r="H29" s="12" t="n">
+      <c r="I29" s="12" t="n">
         <v>58</v>
       </c>
-      <c r="I29" s="12" t="n">
+      <c r="J29" s="12" t="n">
         <v>80</v>
       </c>
-      <c r="J29" s="12" t="n">
+      <c r="K29" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="K29" s="12" t="n">
+      <c r="L29" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="L29" s="12" t="n">
+      <c r="M29" s="12" t="n">
         <v>89</v>
       </c>
-      <c r="M29" s="12" t="n">
+      <c r="N29" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="N29" s="2" t="inlineStr">
+      <c r="O29" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1838,42 +1949,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>SS 11 PADANA SUPERIORE KM. 182+719</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
           <t>VINCENZI STEFANO</t>
         </is>
       </c>
-      <c r="E30" s="12" t="n">
+      <c r="F30" s="12" t="n">
         <v>125</v>
       </c>
-      <c r="F30" s="12" t="n">
+      <c r="G30" s="12" t="n">
         <v>201</v>
       </c>
-      <c r="G30" s="12" t="n">
+      <c r="H30" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="H30" s="12" t="n">
+      <c r="I30" s="12" t="n">
         <v>47</v>
       </c>
-      <c r="I30" s="12" t="n">
+      <c r="J30" s="12" t="n">
         <v>99</v>
       </c>
-      <c r="J30" s="12" t="n">
+      <c r="K30" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="K30" s="12" t="n">
+      <c r="L30" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="L30" s="12" t="n">
+      <c r="M30" s="12" t="n">
         <v>102</v>
       </c>
-      <c r="M30" s="12" t="n">
+      <c r="N30" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="N30" s="2" t="inlineStr">
+      <c r="O30" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1892,42 +2008,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>VIA CASTELLEONE, 47</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
           <t>DODI JACOPO</t>
         </is>
       </c>
-      <c r="E31" s="12" t="n">
+      <c r="F31" s="12" t="n">
         <v>120</v>
       </c>
-      <c r="F31" s="12" t="n">
+      <c r="G31" s="12" t="n">
         <v>122</v>
       </c>
-      <c r="G31" s="12" t="n">
+      <c r="H31" s="12" t="n">
         <v>160</v>
       </c>
-      <c r="H31" s="12" t="n">
+      <c r="I31" s="12" t="n">
         <v>282</v>
       </c>
-      <c r="I31" s="12" t="n">
+      <c r="J31" s="12" t="n">
         <v>104</v>
       </c>
-      <c r="J31" s="12" t="n">
+      <c r="K31" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="K31" s="12" t="n">
+      <c r="L31" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="L31" s="12" t="n">
+      <c r="M31" s="12" t="n">
         <v>185</v>
       </c>
-      <c r="M31" s="12" t="n">
+      <c r="N31" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="N31" s="2" t="inlineStr">
+      <c r="O31" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1946,42 +2067,47 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>SS 470 KM 5 0000</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
           <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
-      <c r="E32" s="12" t="n">
+      <c r="F32" s="12" t="n">
         <v>119</v>
       </c>
-      <c r="F32" s="12" t="n">
+      <c r="G32" s="12" t="n">
         <v>136</v>
       </c>
-      <c r="G32" s="12" t="n">
+      <c r="H32" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H32" s="12" t="n">
+      <c r="I32" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="I32" s="12" t="n">
+      <c r="J32" s="12" t="n">
         <v>55</v>
       </c>
-      <c r="J32" s="12" t="n">
+      <c r="K32" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="K32" s="12" t="n">
+      <c r="L32" s="12" t="n">
         <v>66</v>
       </c>
-      <c r="L32" s="12" t="n">
+      <c r="M32" s="12" t="n">
         <v>114</v>
       </c>
-      <c r="M32" s="12" t="n">
+      <c r="N32" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="N32" s="2" t="inlineStr">
+      <c r="O32" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2000,42 +2126,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>LUNGOBISAGNO D'ISTRIA</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
           <t>DALLORTO ILARIA</t>
         </is>
       </c>
-      <c r="E33" s="12" t="n">
+      <c r="F33" s="12" t="n">
         <v>110</v>
       </c>
-      <c r="F33" s="12" t="n">
+      <c r="G33" s="12" t="n">
         <v>132</v>
       </c>
-      <c r="G33" s="12" t="n">
+      <c r="H33" s="12" t="n">
         <v>101</v>
       </c>
-      <c r="H33" s="12" t="n">
+      <c r="I33" s="12" t="n">
         <v>276</v>
       </c>
-      <c r="I33" s="12" t="n">
+      <c r="J33" s="12" t="n">
         <v>79</v>
       </c>
-      <c r="J33" s="12" t="n">
+      <c r="K33" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="K33" s="12" t="n">
+      <c r="L33" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="L33" s="12" t="n">
+      <c r="M33" s="12" t="n">
         <v>148</v>
       </c>
-      <c r="M33" s="12" t="n">
+      <c r="N33" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="N33" s="2" t="inlineStr">
+      <c r="O33" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2054,42 +2185,47 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>SS 45 BIS KM 16+700</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
           <t>DODI JACOPO</t>
         </is>
       </c>
-      <c r="E34" s="12" t="n">
+      <c r="F34" s="12" t="n">
         <v>108</v>
       </c>
-      <c r="F34" s="12" t="n">
+      <c r="G34" s="12" t="n">
         <v>170</v>
       </c>
-      <c r="G34" s="12" t="n">
+      <c r="H34" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H34" s="12" t="n">
+      <c r="I34" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="I34" s="12" t="n">
+      <c r="J34" s="12" t="n">
         <v>77</v>
       </c>
-      <c r="J34" s="12" t="n">
+      <c r="K34" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="K34" s="12" t="n">
+      <c r="L34" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="L34" s="12" t="n">
+      <c r="M34" s="12" t="n">
         <v>124</v>
       </c>
-      <c r="M34" s="12" t="n">
+      <c r="N34" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="N34" s="2" t="inlineStr">
+      <c r="O34" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2108,42 +2244,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>VIA RIGHETTI 1 R</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
           <t>DALLORTO ILARIA</t>
         </is>
       </c>
-      <c r="E35" s="12" t="n">
+      <c r="F35" s="12" t="n">
         <v>105</v>
       </c>
-      <c r="F35" s="12" t="n">
+      <c r="G35" s="12" t="n">
         <v>89</v>
       </c>
-      <c r="G35" s="12" t="n">
+      <c r="H35" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="H35" s="12" t="n">
+      <c r="I35" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="I35" s="12" t="n">
+      <c r="J35" s="12" t="n">
         <v>70</v>
       </c>
-      <c r="J35" s="12" t="n">
+      <c r="K35" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="K35" s="12" t="n">
+      <c r="L35" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="L35" s="12" t="n">
+      <c r="M35" s="12" t="n">
         <v>154</v>
       </c>
-      <c r="M35" s="12" t="n">
+      <c r="N35" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="N35" s="2" t="inlineStr">
+      <c r="O35" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -2162,42 +2303,47 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>VIALE MANZONI, 11</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
           <t>VINCENZI STEFANO</t>
         </is>
       </c>
-      <c r="E36" s="12" t="n">
+      <c r="F36" s="12" t="n">
         <v>101</v>
       </c>
-      <c r="F36" s="12" t="n">
+      <c r="G36" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="G36" s="12" t="n">
+      <c r="H36" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H36" s="12" t="n">
+      <c r="I36" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="I36" s="12" t="n">
+      <c r="J36" s="12" t="n">
         <v>88</v>
-      </c>
-      <c r="J36" s="12" t="n">
-        <v>17</v>
       </c>
       <c r="K36" s="12" t="n">
         <v>17</v>
       </c>
       <c r="L36" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="M36" s="12" t="n">
         <v>117</v>
       </c>
-      <c r="M36" s="12" t="n">
+      <c r="N36" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="N36" s="2" t="inlineStr">
+      <c r="O36" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -2216,42 +2362,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>CORSO GENOVA 40</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
           <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
-      <c r="E37" s="12" t="n">
+      <c r="F37" s="12" t="n">
         <v>85</v>
       </c>
-      <c r="F37" s="12" t="n">
+      <c r="G37" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="G37" s="12" t="n">
+      <c r="H37" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="H37" s="12" t="n">
+      <c r="I37" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="I37" s="12" t="n">
+      <c r="J37" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="J37" s="12" t="n">
+      <c r="K37" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="K37" s="12" t="n">
+      <c r="L37" s="12" t="n">
         <v>44</v>
       </c>
-      <c r="L37" s="12" t="n">
+      <c r="M37" s="12" t="n">
         <v>194</v>
       </c>
-      <c r="M37" s="12" t="n">
+      <c r="N37" s="12" t="n">
         <v>52</v>
       </c>
-      <c r="N37" s="2" t="inlineStr">
+      <c r="O37" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -2270,42 +2421,47 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>VIA NIZZA 152</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
           <t>DELUGAS NADIA</t>
         </is>
       </c>
-      <c r="E38" s="12" t="n">
+      <c r="F38" s="12" t="n">
         <v>81</v>
       </c>
-      <c r="F38" s="12" t="n">
+      <c r="G38" s="12" t="n">
         <v>99</v>
       </c>
-      <c r="G38" s="12" t="n">
+      <c r="H38" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="H38" s="12" t="n">
+      <c r="I38" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I38" s="12" t="n">
+      <c r="J38" s="12" t="n">
         <v>62</v>
       </c>
-      <c r="J38" s="12" t="n">
+      <c r="K38" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="K38" s="12" t="n">
+      <c r="L38" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="L38" s="12" t="n">
+      <c r="M38" s="12" t="n">
         <v>83</v>
       </c>
-      <c r="M38" s="12" t="n">
+      <c r="N38" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="N38" s="2" t="inlineStr">
+      <c r="O38" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -2324,42 +2480,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>VIA VITTORIO VENETO 52</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
           <t>DELUGAS NADIA</t>
         </is>
       </c>
-      <c r="E39" s="12" t="n">
+      <c r="F39" s="12" t="n">
         <v>81</v>
       </c>
-      <c r="F39" s="12" t="n">
+      <c r="G39" s="12" t="n">
         <v>98</v>
       </c>
-      <c r="G39" s="12" t="n">
+      <c r="H39" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="H39" s="12" t="n">
+      <c r="I39" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="I39" s="12" t="n">
+      <c r="J39" s="12" t="n">
         <v>43</v>
       </c>
-      <c r="J39" s="12" t="n">
+      <c r="K39" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="K39" s="12" t="n">
+      <c r="L39" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="L39" s="12" t="n">
+      <c r="M39" s="12" t="n">
         <v>76</v>
       </c>
-      <c r="M39" s="12" t="n">
+      <c r="N39" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N39" s="2" t="inlineStr">
+      <c r="O39" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2378,42 +2539,47 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>VIA NAZIONALE PIEMONTE 68 R</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
           <t>DELUGAS NADIA</t>
         </is>
       </c>
-      <c r="E40" s="12" t="n">
+      <c r="F40" s="12" t="n">
         <v>77</v>
       </c>
-      <c r="F40" s="12" t="n">
+      <c r="G40" s="12" t="n">
         <v>142</v>
       </c>
-      <c r="G40" s="12" t="n">
+      <c r="H40" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="H40" s="12" t="n">
+      <c r="I40" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="I40" s="12" t="n">
+      <c r="J40" s="12" t="n">
         <v>61</v>
       </c>
-      <c r="J40" s="12" t="n">
+      <c r="K40" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="K40" s="12" t="n">
+      <c r="L40" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="L40" s="12" t="n">
+      <c r="M40" s="12" t="n">
         <v>112</v>
       </c>
-      <c r="M40" s="12" t="n">
+      <c r="N40" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="N40" s="2" t="inlineStr">
+      <c r="O40" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2432,42 +2598,47 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>VIA PROVINCIALE</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
           <t>VINCENZI STEFANO</t>
         </is>
       </c>
-      <c r="E41" s="12" t="n">
+      <c r="F41" s="12" t="n">
         <v>76</v>
       </c>
-      <c r="F41" s="12" t="n">
+      <c r="G41" s="12" t="n">
         <v>91</v>
       </c>
-      <c r="G41" s="12" t="n">
+      <c r="H41" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="H41" s="12" t="n">
+      <c r="I41" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="I41" s="12" t="n">
+      <c r="J41" s="12" t="n">
         <v>41</v>
       </c>
-      <c r="J41" s="12" t="n">
+      <c r="K41" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="K41" s="12" t="n">
+      <c r="L41" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="L41" s="12" t="n">
+      <c r="M41" s="12" t="n">
         <v>89</v>
       </c>
-      <c r="M41" s="12" t="n">
+      <c r="N41" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N41" s="2" t="inlineStr">
+      <c r="O41" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -2486,42 +2657,47 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>VIA FRANCESCO VAINI</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
           <t>CARMINATI SIMONE</t>
         </is>
       </c>
-      <c r="E42" s="12" t="n">
+      <c r="F42" s="12" t="n">
         <v>65</v>
       </c>
-      <c r="F42" s="12" t="n">
+      <c r="G42" s="12" t="n">
         <v>87</v>
       </c>
-      <c r="G42" s="12" t="n">
+      <c r="H42" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H42" s="12" t="n">
+      <c r="I42" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="I42" s="12" t="n">
+      <c r="J42" s="12" t="n">
         <v>63</v>
       </c>
-      <c r="J42" s="12" t="n">
+      <c r="K42" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="K42" s="12" t="n">
+      <c r="L42" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="L42" s="12" t="n">
+      <c r="M42" s="12" t="n">
         <v>45</v>
       </c>
-      <c r="M42" s="12" t="n">
+      <c r="N42" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="N42" s="2" t="inlineStr">
+      <c r="O42" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2540,42 +2716,47 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>CSO LIMONE PIEMONTE 1</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
           <t>BARNABA SALVATORE</t>
         </is>
       </c>
-      <c r="E43" s="12" t="n">
+      <c r="F43" s="12" t="n">
         <v>58</v>
       </c>
-      <c r="F43" s="12" t="n">
+      <c r="G43" s="12" t="n">
         <v>93</v>
       </c>
-      <c r="G43" s="12" t="n">
+      <c r="H43" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="H43" s="12" t="n">
+      <c r="I43" s="12" t="n">
         <v>44</v>
       </c>
-      <c r="I43" s="12" t="n">
+      <c r="J43" s="12" t="n">
         <v>43</v>
       </c>
-      <c r="J43" s="12" t="n">
+      <c r="K43" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="K43" s="12" t="n">
+      <c r="L43" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="L43" s="12" t="n">
+      <c r="M43" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="M43" s="12" t="n">
+      <c r="N43" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="N43" s="2" t="inlineStr">
+      <c r="O43" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2594,42 +2775,47 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>VIA BERGAMO 47</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
           <t>DODI JACOPO</t>
         </is>
       </c>
-      <c r="E44" s="12" t="n">
+      <c r="F44" s="12" t="n">
         <v>57</v>
       </c>
-      <c r="F44" s="12" t="n">
+      <c r="G44" s="12" t="n">
         <v>66</v>
       </c>
-      <c r="G44" s="12" t="n">
+      <c r="H44" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="H44" s="12" t="n">
+      <c r="I44" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="I44" s="12" t="n">
+      <c r="J44" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="J44" s="12" t="n">
+      <c r="K44" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="K44" s="12" t="n">
+      <c r="L44" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="L44" s="12" t="n">
+      <c r="M44" s="12" t="n">
         <v>72</v>
       </c>
-      <c r="M44" s="12" t="n">
+      <c r="N44" s="12" t="n">
         <v>51</v>
       </c>
-      <c r="N44" s="2" t="inlineStr">
+      <c r="O44" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -2648,42 +2834,47 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>SS 45 BIS KM 55+370</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
           <t>GRAZIOSI DAVIDE</t>
         </is>
-      </c>
-      <c r="E45" s="12" t="n">
-        <v>52</v>
       </c>
       <c r="F45" s="12" t="n">
         <v>52</v>
       </c>
       <c r="G45" s="12" t="n">
+        <v>52</v>
+      </c>
+      <c r="H45" s="12" t="n">
         <v>85</v>
       </c>
-      <c r="H45" s="12" t="n">
+      <c r="I45" s="12" t="n">
         <v>73</v>
       </c>
-      <c r="I45" s="12" t="n">
+      <c r="J45" s="12" t="n">
         <v>37</v>
       </c>
-      <c r="J45" s="12" t="n">
+      <c r="K45" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="K45" s="12" t="n">
+      <c r="L45" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="L45" s="12" t="n">
+      <c r="M45" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="M45" s="12" t="n">
+      <c r="N45" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="N45" s="2" t="inlineStr">
+      <c r="O45" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -2702,42 +2893,47 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>SS671 VALSERIANA  KM0,9820</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
           <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
-      <c r="E46" s="12" t="n">
+      <c r="F46" s="12" t="n">
         <v>51</v>
       </c>
-      <c r="F46" s="12" t="n">
+      <c r="G46" s="12" t="n">
         <v>74</v>
       </c>
-      <c r="G46" s="12" t="n">
+      <c r="H46" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="H46" s="12" t="n">
+      <c r="I46" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="I46" s="12" t="n">
+      <c r="J46" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="J46" s="12" t="n">
+      <c r="K46" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="K46" s="12" t="n">
+      <c r="L46" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="L46" s="12" t="n">
+      <c r="M46" s="12" t="n">
         <v>71</v>
       </c>
-      <c r="M46" s="12" t="n">
+      <c r="N46" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="N46" s="2" t="inlineStr">
+      <c r="O46" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -2756,42 +2952,47 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>VIA GRAMSCI 9/A</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
           <t>DELUGAS NADIA</t>
         </is>
       </c>
-      <c r="E47" s="12" t="n">
+      <c r="F47" s="12" t="n">
         <v>47</v>
       </c>
-      <c r="F47" s="12" t="n">
+      <c r="G47" s="12" t="n">
         <v>57</v>
       </c>
-      <c r="G47" s="12" t="n">
+      <c r="H47" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="H47" s="12" t="n">
+      <c r="I47" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="I47" s="12" t="n">
+      <c r="J47" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="J47" s="12" t="n">
+      <c r="K47" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="K47" s="12" t="n">
+      <c r="L47" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="L47" s="12" t="n">
+      <c r="M47" s="12" t="n">
         <v>76</v>
       </c>
-      <c r="M47" s="12" t="n">
+      <c r="N47" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="N47" s="2" t="inlineStr">
+      <c r="O47" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2810,42 +3011,47 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>V. DE GASP./TANG. S KM 6+930</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
           <t>SALVINELLI LUCA</t>
         </is>
       </c>
-      <c r="E48" s="12" t="n">
+      <c r="F48" s="12" t="n">
         <v>43</v>
       </c>
-      <c r="F48" s="12" t="n">
+      <c r="G48" s="12" t="n">
         <v>65</v>
       </c>
-      <c r="G48" s="12" t="n">
+      <c r="H48" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H48" s="12" t="n">
+      <c r="I48" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="I48" s="12" t="n">
+      <c r="J48" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="J48" s="12" t="n">
+      <c r="K48" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="K48" s="12" t="n">
+      <c r="L48" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="L48" s="12" t="n">
+      <c r="M48" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="M48" s="12" t="n">
+      <c r="N48" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N48" s="2" t="inlineStr">
+      <c r="O48" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -2864,42 +3070,47 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>VIA MAZZINI</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
           <t>BARNABA SALVATORE</t>
         </is>
       </c>
-      <c r="E49" s="12" t="n">
+      <c r="F49" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="F49" s="12" t="n">
+      <c r="G49" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="G49" s="12" t="n">
+      <c r="H49" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="H49" s="12" t="n">
+      <c r="I49" s="12" t="n">
         <v>37</v>
       </c>
-      <c r="I49" s="12" t="n">
+      <c r="J49" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="J49" s="12" t="n">
+      <c r="K49" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="K49" s="12" t="n">
+      <c r="L49" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="L49" s="12" t="n">
+      <c r="M49" s="12" t="n">
         <v>58</v>
       </c>
-      <c r="M49" s="12" t="n">
+      <c r="N49" s="12" t="n">
         <v>44</v>
       </c>
-      <c r="N49" s="2" t="inlineStr">
+      <c r="O49" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -2918,42 +3129,47 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>VIA BRUNO PRIMI, 14</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
           <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
-      <c r="E50" s="12" t="n">
+      <c r="F50" s="12" t="n">
         <v>41</v>
       </c>
-      <c r="F50" s="12" t="n">
+      <c r="G50" s="12" t="n">
         <v>79</v>
       </c>
-      <c r="G50" s="12" t="n">
+      <c r="H50" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="H50" s="12" t="n">
+      <c r="I50" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="I50" s="12" t="n">
+      <c r="J50" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="J50" s="12" t="n">
+      <c r="K50" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="K50" s="12" t="n">
+      <c r="L50" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="L50" s="12" t="n">
+      <c r="M50" s="12" t="n">
         <v>70</v>
       </c>
-      <c r="M50" s="12" t="n">
+      <c r="N50" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="N50" s="2" t="inlineStr">
+      <c r="O50" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2972,42 +3188,47 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>SS 28 KM 136 + 600</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
           <t>BARNABA SALVATORE</t>
         </is>
       </c>
-      <c r="E51" s="12" t="n">
+      <c r="F51" s="12" t="n">
         <v>41</v>
       </c>
-      <c r="F51" s="12" t="n">
+      <c r="G51" s="12" t="n">
         <v>92</v>
       </c>
-      <c r="G51" s="12" t="n">
+      <c r="H51" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="H51" s="12" t="n">
+      <c r="I51" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="I51" s="12" t="n">
+      <c r="J51" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="J51" s="12" t="n">
+      <c r="K51" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="K51" s="12" t="n">
+      <c r="L51" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="L51" s="12" t="n">
+      <c r="M51" s="12" t="n">
         <v>87</v>
       </c>
-      <c r="M51" s="12" t="n">
+      <c r="N51" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="N51" s="2" t="inlineStr">
+      <c r="O51" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -3026,42 +3247,47 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>S.S.45 KM.49+300</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
           <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
-      <c r="E52" s="12" t="n">
+      <c r="F52" s="12" t="n">
         <v>41</v>
       </c>
-      <c r="F52" s="12" t="n">
+      <c r="G52" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="G52" s="12" t="n">
+      <c r="H52" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="H52" s="12" t="n">
+      <c r="I52" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I52" s="12" t="n">
+      <c r="J52" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="J52" s="12" t="n">
+      <c r="K52" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="K52" s="12" t="n">
+      <c r="L52" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="L52" s="12" t="n">
+      <c r="M52" s="12" t="n">
         <v>45</v>
       </c>
-      <c r="M52" s="12" t="n">
+      <c r="N52" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="N52" s="2" t="inlineStr">
+      <c r="O52" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -3080,42 +3306,47 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>VIA SIFFREDI, 62</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
           <t>DALLORTO ILARIA</t>
         </is>
       </c>
-      <c r="E53" s="12" t="n">
+      <c r="F53" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="F53" s="12" t="n">
+      <c r="G53" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="G53" s="12" t="n">
+      <c r="H53" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="H53" s="12" t="n">
+      <c r="I53" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I53" s="12" t="n">
+      <c r="J53" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="J53" s="12" t="n">
+      <c r="K53" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="K53" s="12" t="n">
+      <c r="L53" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="L53" s="12" t="n">
+      <c r="M53" s="12" t="n">
         <v>83</v>
       </c>
-      <c r="M53" s="12" t="n">
+      <c r="N53" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="N53" s="2" t="inlineStr">
+      <c r="O53" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -3134,42 +3365,47 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>GARIBALDI 18</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
           <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
-      <c r="E54" s="12" t="n">
+      <c r="F54" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="F54" s="12" t="n">
+      <c r="G54" s="12" t="n">
         <v>44</v>
       </c>
-      <c r="G54" s="12" t="n">
+      <c r="H54" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H54" s="12" t="n">
+      <c r="I54" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I54" s="12" t="n">
+      <c r="J54" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="J54" s="12" t="n">
+      <c r="K54" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="K54" s="12" t="n">
+      <c r="L54" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="L54" s="12" t="n">
+      <c r="M54" s="12" t="n">
         <v>43</v>
       </c>
-      <c r="M54" s="12" t="n">
+      <c r="N54" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N54" s="2" t="inlineStr">
+      <c r="O54" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -3188,42 +3424,47 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>STR PROVLE N 12</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
           <t>VINCENZI STEFANO</t>
         </is>
       </c>
-      <c r="E55" s="12" t="n">
+      <c r="F55" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="F55" s="12" t="n">
+      <c r="G55" s="12" t="n">
         <v>59</v>
       </c>
-      <c r="G55" s="12" t="n">
+      <c r="H55" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H55" s="12" t="n">
+      <c r="I55" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I55" s="12" t="n">
+      <c r="J55" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="J55" s="12" t="n">
+      <c r="K55" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="K55" s="12" t="n">
+      <c r="L55" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="L55" s="12" t="n">
+      <c r="M55" s="12" t="n">
         <v>44</v>
       </c>
-      <c r="M55" s="12" t="n">
+      <c r="N55" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N55" s="2" t="inlineStr">
+      <c r="O55" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -3242,42 +3483,47 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>S.S. 668 - VIA GHEDI</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
           <t>DODI JACOPO</t>
         </is>
-      </c>
-      <c r="E56" s="12" t="n">
-        <v>38</v>
       </c>
       <c r="F56" s="12" t="n">
         <v>38</v>
       </c>
       <c r="G56" s="12" t="n">
+        <v>38</v>
+      </c>
+      <c r="H56" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="H56" s="12" t="n">
+      <c r="I56" s="12" t="n">
         <v>106</v>
       </c>
-      <c r="I56" s="12" t="n">
+      <c r="J56" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="J56" s="12" t="n">
+      <c r="K56" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="K56" s="12" t="n">
+      <c r="L56" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="L56" s="12" t="n">
+      <c r="M56" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="M56" s="12" t="n">
+      <c r="N56" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N56" s="2" t="inlineStr">
+      <c r="O56" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -3296,42 +3542,47 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>S.S. N. 62 CISA - LOCALITA' CROCILE C.M.</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
           <t>CARMINATI SIMONE</t>
         </is>
       </c>
-      <c r="E57" s="12" t="n">
+      <c r="F57" s="12" t="n">
         <v>37</v>
       </c>
-      <c r="F57" s="12" t="n">
+      <c r="G57" s="12" t="n">
         <v>55</v>
       </c>
-      <c r="G57" s="12" t="n">
+      <c r="H57" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="H57" s="12" t="n">
+      <c r="I57" s="12" t="n">
         <v>47</v>
       </c>
-      <c r="I57" s="12" t="n">
+      <c r="J57" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="J57" s="12" t="n">
+      <c r="K57" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="K57" s="12" t="n">
+      <c r="L57" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="L57" s="12" t="n">
+      <c r="M57" s="12" t="n">
         <v>58</v>
       </c>
-      <c r="M57" s="12" t="n">
+      <c r="N57" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N57" s="2" t="inlineStr">
+      <c r="O57" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -3350,42 +3601,47 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>S.S. 358  KM 22+202</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
           <t>CARMINATI SIMONE</t>
         </is>
       </c>
-      <c r="E58" s="12" t="n">
+      <c r="F58" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="F58" s="12" t="n">
+      <c r="G58" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="G58" s="12" t="n">
+      <c r="H58" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="H58" s="12" t="n">
+      <c r="I58" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="I58" s="12" t="n">
+      <c r="J58" s="12" t="n">
         <v>28</v>
-      </c>
-      <c r="J58" s="12" t="n">
-        <v>7</v>
       </c>
       <c r="K58" s="12" t="n">
         <v>7</v>
       </c>
       <c r="L58" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="M58" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="M58" s="12" t="n">
+      <c r="N58" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="N58" s="2" t="inlineStr">
+      <c r="O58" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -3404,42 +3660,47 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>VIA ROMA</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
           <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
-      <c r="E59" s="12" t="n">
+      <c r="F59" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="F59" s="12" t="n">
+      <c r="G59" s="12" t="n">
         <v>73</v>
       </c>
-      <c r="G59" s="12" t="n">
+      <c r="H59" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="H59" s="12" t="n">
+      <c r="I59" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="I59" s="12" t="n">
+      <c r="J59" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="J59" s="12" t="n">
+      <c r="K59" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="K59" s="12" t="n">
+      <c r="L59" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="L59" s="12" t="n">
+      <c r="M59" s="12" t="n">
         <v>116</v>
       </c>
-      <c r="M59" s="12" t="n">
+      <c r="N59" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="N59" s="2" t="inlineStr">
+      <c r="O59" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -3458,42 +3719,47 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>LOCALITA' MONTECAVALLO - VIA AURELIA 67/A</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
           <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
-      <c r="E60" s="12" t="n">
+      <c r="F60" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="F60" s="12" t="n">
+      <c r="G60" s="12" t="n">
         <v>68</v>
       </c>
-      <c r="G60" s="12" t="n">
+      <c r="H60" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="H60" s="12" t="n">
+      <c r="I60" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I60" s="12" t="n">
+      <c r="J60" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="J60" s="12" t="n">
+      <c r="K60" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="K60" s="12" t="n">
+      <c r="L60" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="L60" s="12" t="n">
+      <c r="M60" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="M60" s="12" t="n">
+      <c r="N60" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N60" s="2" t="inlineStr">
+      <c r="O60" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -3512,42 +3778,47 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>SS 42</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
           <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
-      <c r="E61" s="12" t="n">
+      <c r="F61" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="F61" s="12" t="n">
+      <c r="G61" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="G61" s="12" t="n">
+      <c r="H61" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="H61" s="12" t="n">
+      <c r="I61" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="I61" s="12" t="n">
+      <c r="J61" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="J61" s="12" t="n">
+      <c r="K61" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="K61" s="12" t="n">
+      <c r="L61" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="L61" s="12" t="n">
+      <c r="M61" s="12" t="n">
         <v>54</v>
       </c>
-      <c r="M61" s="12" t="n">
+      <c r="N61" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="N61" s="2" t="inlineStr">
+      <c r="O61" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -3566,42 +3837,47 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>VIA GIUSEPPE DI VITTORIO 17</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
           <t>VINCENZI STEFANO</t>
         </is>
       </c>
-      <c r="E62" s="12" t="n">
+      <c r="F62" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="F62" s="12" t="n">
+      <c r="G62" s="12" t="n">
         <v>51</v>
       </c>
-      <c r="G62" s="12" t="n">
+      <c r="H62" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H62" s="12" t="n">
+      <c r="I62" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I62" s="12" t="n">
+      <c r="J62" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="J62" s="12" t="n">
+      <c r="K62" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="K62" s="12" t="n">
+      <c r="L62" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="L62" s="12" t="n">
+      <c r="M62" s="12" t="n">
         <v>43</v>
       </c>
-      <c r="M62" s="12" t="n">
+      <c r="N62" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="N62" s="2" t="inlineStr">
+      <c r="O62" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -3620,42 +3896,47 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>VIA ROMA 36</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
           <t>CARMINATI SIMONE</t>
         </is>
       </c>
-      <c r="E63" s="12" t="n">
+      <c r="F63" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="F63" s="12" t="n">
+      <c r="G63" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="G63" s="12" t="n">
+      <c r="H63" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="H63" s="12" t="n">
+      <c r="I63" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="I63" s="12" t="n">
+      <c r="J63" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="J63" s="12" t="n">
+      <c r="K63" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="K63" s="12" t="n">
+      <c r="L63" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="L63" s="12" t="n">
+      <c r="M63" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="M63" s="12" t="n">
+      <c r="N63" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="N63" s="2" t="inlineStr">
+      <c r="O63" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -3674,42 +3955,47 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>LOC. ROCCOLINO SS45 BIS</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
           <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
-      <c r="E64" s="12" t="n">
+      <c r="F64" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="F64" s="12" t="n">
+      <c r="G64" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="G64" s="12" t="n">
+      <c r="H64" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="H64" s="12" t="n">
+      <c r="I64" s="12" t="n">
         <v>65</v>
       </c>
-      <c r="I64" s="12" t="n">
+      <c r="J64" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="J64" s="12" t="n">
+      <c r="K64" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="K64" s="12" t="n">
+      <c r="L64" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="L64" s="12" t="n">
+      <c r="M64" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="M64" s="12" t="n">
+      <c r="N64" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="N64" s="2" t="inlineStr">
+      <c r="O64" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -3728,42 +4014,47 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>VIALE ITALIA 160</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
           <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
-      <c r="E65" s="12" t="n">
+      <c r="F65" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="F65" s="12" t="n">
+      <c r="G65" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="G65" s="12" t="n">
+      <c r="H65" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="H65" s="12" t="n">
+      <c r="I65" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="I65" s="12" t="n">
+      <c r="J65" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="J65" s="12" t="n">
+      <c r="K65" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="K65" s="12" t="n">
+      <c r="L65" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="L65" s="12" t="n">
+      <c r="M65" s="12" t="n">
         <v>62</v>
       </c>
-      <c r="M65" s="12" t="n">
+      <c r="N65" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="N65" s="2" t="inlineStr">
+      <c r="O65" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -3782,42 +4073,47 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>CORSO DE STEFANIS 215/R</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
           <t>DALLORTO ILARIA</t>
         </is>
       </c>
-      <c r="E66" s="12" t="n">
+      <c r="F66" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="F66" s="12" t="n">
+      <c r="G66" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="G66" s="12" t="n">
+      <c r="H66" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="H66" s="12" t="n">
+      <c r="I66" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="I66" s="12" t="n">
+      <c r="J66" s="12" t="n">
         <v>19</v>
-      </c>
-      <c r="J66" s="12" t="n">
-        <v>3</v>
       </c>
       <c r="K66" s="12" t="n">
         <v>3</v>
       </c>
       <c r="L66" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="M66" s="12" t="n">
         <v>41</v>
       </c>
-      <c r="M66" s="12" t="n">
+      <c r="N66" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="N66" s="2" t="inlineStr">
+      <c r="O66" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -3836,42 +4132,47 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>SR CISA 4 S. ANTONIO</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
           <t>CARMINATI SIMONE</t>
         </is>
       </c>
-      <c r="E67" s="12" t="n">
+      <c r="F67" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="F67" s="12" t="n">
+      <c r="G67" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="G67" s="12" t="n">
+      <c r="H67" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H67" s="12" t="n">
+      <c r="I67" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="I67" s="12" t="n">
+      <c r="J67" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="J67" s="12" t="n">
+      <c r="K67" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="K67" s="12" t="n">
+      <c r="L67" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="L67" s="12" t="n">
+      <c r="M67" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="M67" s="12" t="n">
+      <c r="N67" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="N67" s="2" t="inlineStr">
+      <c r="O67" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -3890,42 +4191,47 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>SS342 KM 18+640</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
           <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
-      <c r="E68" s="12" t="n">
+      <c r="F68" s="12" t="n">
         <v>15</v>
-      </c>
-      <c r="F68" s="12" t="n">
-        <v>46</v>
       </c>
       <c r="G68" s="12" t="n">
         <v>46</v>
       </c>
       <c r="H68" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="I68" s="12" t="n">
         <v>83</v>
       </c>
-      <c r="I68" s="12" t="n">
+      <c r="J68" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="J68" s="12" t="n">
+      <c r="K68" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="K68" s="12" t="n">
+      <c r="L68" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="L68" s="12" t="n">
+      <c r="M68" s="12" t="n">
         <v>59</v>
       </c>
-      <c r="M68" s="12" t="n">
+      <c r="N68" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N68" s="2" t="inlineStr">
+      <c r="O68" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -3944,42 +4250,47 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>VIA CISA 50</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
           <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
-      <c r="E69" s="12" t="n">
+      <c r="F69" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="F69" s="12" t="n">
+      <c r="G69" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="G69" s="12" t="n">
+      <c r="H69" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="H69" s="12" t="n">
+      <c r="I69" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="I69" s="12" t="n">
+      <c r="J69" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="J69" s="12" t="n">
+      <c r="K69" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="K69" s="12" t="n">
+      <c r="L69" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="L69" s="12" t="n">
+      <c r="M69" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="M69" s="12" t="n">
+      <c r="N69" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N69" s="2" t="inlineStr">
+      <c r="O69" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -3998,42 +4309,47 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>S S 42</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
           <t>VINCENZI STEFANO</t>
         </is>
       </c>
-      <c r="E70" s="12" t="n">
+      <c r="F70" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="F70" s="12" t="n">
+      <c r="G70" s="12" t="n">
         <v>53</v>
       </c>
-      <c r="G70" s="12" t="n">
+      <c r="H70" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H70" s="12" t="n">
+      <c r="I70" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I70" s="12" t="n">
+      <c r="J70" s="12" t="n">
         <v>10</v>
-      </c>
-      <c r="J70" s="12" t="n">
-        <v>3</v>
       </c>
       <c r="K70" s="12" t="n">
         <v>3</v>
       </c>
       <c r="L70" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="M70" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="M70" s="12" t="n">
+      <c r="N70" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N70" s="2" t="inlineStr">
+      <c r="O70" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -4052,42 +4368,47 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>VIALE BORNATA</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
           <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
-      <c r="E71" s="12" t="n">
+      <c r="F71" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="F71" s="12" t="n">
+      <c r="G71" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="G71" s="12" t="n">
+      <c r="H71" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="H71" s="12" t="n">
+      <c r="I71" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="I71" s="12" t="n">
+      <c r="J71" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="J71" s="12" t="n">
+      <c r="K71" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="K71" s="12" t="n">
+      <c r="L71" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="L71" s="12" t="n">
+      <c r="M71" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="M71" s="12" t="n">
+      <c r="N71" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N71" s="2" t="inlineStr">
+      <c r="O71" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -4106,19 +4427,21 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>S.S. N. 236 KM 14+332</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
           <t>CARMINATI SIMONE</t>
         </is>
       </c>
-      <c r="E72" s="12" t="n">
+      <c r="F72" s="12" t="n">
         <v>9</v>
-      </c>
-      <c r="F72" s="12" t="n">
-        <v>0</v>
       </c>
       <c r="G72" s="12" t="n">
         <v>0</v>
@@ -4127,21 +4450,24 @@
         <v>0</v>
       </c>
       <c r="I72" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="J72" s="12" t="n">
+      <c r="K72" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="K72" s="12" t="n">
+      <c r="L72" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="L72" s="12" t="n">
+      <c r="M72" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="M72" s="12" t="n">
+      <c r="N72" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="N72" s="2" t="inlineStr">
+      <c r="O72" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -4160,42 +4486,47 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>VIALE PAPA GIOVANNI</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
           <t>SALVINELLI LUCA</t>
         </is>
       </c>
-      <c r="E73" s="12" t="n">
+      <c r="F73" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="F73" s="12" t="n">
+      <c r="G73" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="G73" s="12" t="n">
+      <c r="H73" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H73" s="12" t="n">
+      <c r="I73" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="I73" s="12" t="n">
+      <c r="J73" s="12" t="n">
         <v>8</v>
-      </c>
-      <c r="J73" s="12" t="n">
-        <v>0</v>
       </c>
       <c r="K73" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L73" s="12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M73" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="N73" s="2" t="inlineStr">
+      <c r="N73" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -4214,42 +4545,47 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>VIA AURELIA 256</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
           <t>DELUGAS NADIA</t>
         </is>
       </c>
-      <c r="E74" s="12" t="n">
+      <c r="F74" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="F74" s="12" t="n">
+      <c r="G74" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="G74" s="12" t="n">
+      <c r="H74" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H74" s="12" t="n">
+      <c r="I74" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="I74" s="12" t="n">
+      <c r="J74" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="J74" s="12" t="n">
+      <c r="K74" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="K74" s="12" t="n">
+      <c r="L74" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="L74" s="12" t="n">
+      <c r="M74" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="M74" s="12" t="n">
+      <c r="N74" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="N74" s="2" t="inlineStr">
+      <c r="O74" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>

--- a/docs/files/REPORT_FILTRI/Agente - Marcelli Emanuele.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Marcelli Emanuele.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>64</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>7665</v>
+        <v>8070</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>5358</v>
+        <v>5615</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>2675</v>
+        <v>2873</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>758</v>
+        <v>801</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>550</v>
+        <v>579</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>482</v>
+        <v>510</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>281</v>
+        <v>296</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>641</v>
+        <v>678</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,35 +901,35 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>524</v>
+        <v>545</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>355</v>
+        <v>371</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>335</v>
+        <v>351</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -960,35 +960,35 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>453</v>
+        <v>473</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>543</v>
+        <v>576</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>261</v>
+        <v>277</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1019,35 +1019,35 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>377</v>
+        <v>398</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>244</v>
+        <v>261</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1078,31 +1078,31 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>345</v>
+        <v>374</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>465</v>
+        <v>497</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>265</v>
+        <v>285</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>500</v>
+        <v>520</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1137,31 +1137,31 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>312</v>
+        <v>333</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>371</v>
+        <v>390</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>330</v>
+        <v>346</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>475</v>
+        <v>502</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1196,31 +1196,31 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>311</v>
+        <v>326</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>516</v>
+        <v>550</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>377</v>
+        <v>400</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1255,31 +1255,31 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>341</v>
+        <v>371</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="L18" s="12" t="n">
         <v>46</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1314,35 +1314,35 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1373,31 +1373,31 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -1432,31 +1432,31 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="G21" s="12" t="n">
         <v>245</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I21" s="12" t="n">
         <v>30</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1491,28 +1491,28 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I22" s="12" t="n">
         <v>7</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="N22" s="12" t="n">
         <v>7</v>
@@ -1550,10 +1550,10 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="H23" s="12" t="n">
         <v>1</v>
@@ -1562,16 +1562,16 @@
         <v>6</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K23" s="12" t="n">
         <v>23</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="N23" s="12" t="n">
         <v>9</v>
@@ -1585,17 +1585,17 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>01351</t>
+          <t>01032</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>SAVONA</t>
+          <t>GENOVA</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>STALINGRADO</t>
+          <t>VIA BRIGATE PARTIGIANE, 1/R</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1605,56 +1605,56 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>BARNABA SALVATORE</t>
+          <t>DALLORTO ILARIA</t>
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>152</v>
+        <v>263</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>21</v>
+        <v>72</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>168</v>
+        <v>453</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>01032</t>
+          <t>01351</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>GENOVA</t>
+          <t>SAVONA</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>VIA BRIGATE PARTIGIANE, 1/R</t>
+          <t>STALINGRADO</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1664,39 +1664,39 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>DALLORTO ILARIA</t>
+          <t>BARNABA SALVATORE</t>
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>249</v>
+        <v>157</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>426</v>
+        <v>174</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1727,31 +1727,31 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="H26" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>230</v>
+        <v>251</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1786,31 +1786,31 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="I27" s="12" t="n">
         <v>7</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L27" s="12" t="n">
         <v>21</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
@@ -1845,35 +1845,35 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="H28" s="12" t="n">
         <v>5</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L28" s="12" t="n">
         <v>51</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="N28" s="12" t="n">
         <v>10</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1907,13 +1907,13 @@
         <v>139</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="H29" s="12" t="n">
         <v>53</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="J29" s="12" t="n">
         <v>80</v>
@@ -1939,17 +1939,17 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>51674</t>
+          <t>01034</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>CARAVAGGIO</t>
+          <t>GENOVA</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>SS 11 PADANA SUPERIORE KM. 182+719</t>
+          <t>LUNGOBISAGNO D'ISTRIA</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1959,56 +1959,56 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>DALLORTO ILARIA</t>
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>201</v>
+        <v>138</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>12</v>
+        <v>128</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>47</v>
+        <v>296</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>102</v>
+        <v>154</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>02036</t>
+          <t>51674</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>CREMONA</t>
+          <t>CARAVAGGIO</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>VIA CASTELLEONE, 47</t>
+          <t>SS 11 PADANA SUPERIORE KM. 182+719</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -2018,39 +2018,39 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>122</v>
+        <v>208</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>160</v>
+        <v>12</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>282</v>
+        <v>48</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>185</v>
+        <v>106</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2081,31 +2081,31 @@
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I32" s="12" t="n">
         <v>8</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
@@ -2116,17 +2116,17 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>01034</t>
+          <t>02036</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>GENOVA</t>
+          <t>CREMONA</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>LUNGOBISAGNO D'ISTRIA</t>
+          <t>VIA CASTELLEONE, 47</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2136,56 +2136,56 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>DALLORTO ILARIA</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>101</v>
+        <v>169</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>276</v>
+        <v>295</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>148</v>
+        <v>197</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>5</v>
+        <v>67</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>01718</t>
+          <t>01574</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>PONTEVICO</t>
+          <t>TREVIGLIO</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>SS 45 BIS KM 16+700</t>
+          <t>VIALE MANZONI, 11</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2195,56 +2195,56 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>01043</t>
+          <t>01718</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>GENOVA</t>
+          <t>PONTEVICO</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>VIA RIGHETTI 1 R</t>
+          <t>SS 45 BIS KM 16+700</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2254,56 +2254,56 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>DALLORTO ILARIA</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>89</v>
+        <v>172</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>154</v>
+        <v>124</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>01574</t>
+          <t>01043</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>TREVIGLIO</t>
+          <t>GENOVA</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>VIALE MANZONI, 11</t>
+          <t>VIA RIGHETTI 1 R</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2313,56 +2313,56 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>DALLORTO ILARIA</t>
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>117</v>
+        <v>165</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>01007</t>
+          <t>01378</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>CHIAVARI</t>
+          <t>CARCARE</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>CORSO GENOVA 40</t>
+          <t>VIA VITTORIO VENETO 52</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2372,56 +2372,56 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>DELUGAS NADIA</t>
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>194</v>
+        <v>79</v>
       </c>
       <c r="N37" s="12" t="n">
-        <v>52</v>
+        <v>2</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>51037</t>
+          <t>01007</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>ACQUI TERME</t>
+          <t>CHIAVARI</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>VIA NIZZA 152</t>
+          <t>CORSO GENOVA 40</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -2431,35 +2431,35 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>DELUGAS NADIA</t>
+          <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>83</v>
+        <v>204</v>
       </c>
       <c r="N38" s="12" t="n">
-        <v>4</v>
+        <v>53</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
@@ -2470,17 +2470,17 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>01378</t>
+          <t>51037</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>CARCARE</t>
+          <t>ACQUI TERME</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>VIA VITTORIO VENETO 52</t>
+          <t>VIA NIZZA 152</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -2494,52 +2494,52 @@
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="N39" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>01371</t>
+          <t>01577</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>SAVONA</t>
+          <t>ZANICA</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>VIA NAZIONALE PIEMONTE 68 R</t>
+          <t>VIA PROVINCIALE</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -2549,56 +2549,56 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>DELUGAS NADIA</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="F40" s="12" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>142</v>
+        <v>99</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="N40" s="12" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>01577</t>
+          <t>01371</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>ZANICA</t>
+          <t>SAVONA</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>VIA PROVINCIALE</t>
+          <t>VIA NAZIONALE PIEMONTE 68 R</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -2608,39 +2608,39 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>DELUGAS NADIA</t>
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>91</v>
+        <v>147</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>89</v>
+        <v>117</v>
       </c>
       <c r="N41" s="12" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="F42" s="12" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="H42" s="12" t="n">
         <v>1</v>
@@ -2683,7 +2683,7 @@
         <v>8</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K42" s="12" t="n">
         <v>25</v>
@@ -2692,10 +2692,10 @@
         <v>4</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="N42" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
@@ -2706,17 +2706,17 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>51570</t>
+          <t>01637</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>VENTIMIGLIA</t>
+          <t>CURNO</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>CSO LIMONE PIEMONTE 1</t>
+          <t>SS671 VALSERIANA  KM0,9820</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -2726,56 +2726,56 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>BARNABA SALVATORE</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="F43" s="12" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>42</v>
+        <v>77</v>
       </c>
       <c r="N43" s="12" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>01971</t>
+          <t>51570</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>CREMONA</t>
+          <t>VENTIMIGLIA</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>VIA BERGAMO 47</t>
+          <t>CSO LIMONE PIEMONTE 1</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -2785,56 +2785,56 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>BARNABA SALVATORE</t>
         </is>
       </c>
       <c r="F44" s="12" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>72</v>
+        <v>49</v>
       </c>
       <c r="N44" s="12" t="n">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>01717</t>
+          <t>01971</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>PAITONE</t>
+          <t>CREMONA</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>SS 45 BIS KM 55+370</t>
+          <t>VIA BERGAMO 47</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -2844,35 +2844,35 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>GRAZIOSI DAVIDE</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="F45" s="12" t="n">
+        <v>59</v>
+      </c>
+      <c r="G45" s="12" t="n">
+        <v>71</v>
+      </c>
+      <c r="H45" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="I45" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="J45" s="12" t="n">
         <v>52</v>
       </c>
-      <c r="G45" s="12" t="n">
-        <v>52</v>
-      </c>
-      <c r="H45" s="12" t="n">
-        <v>85</v>
-      </c>
-      <c r="I45" s="12" t="n">
-        <v>73</v>
-      </c>
-      <c r="J45" s="12" t="n">
-        <v>37</v>
-      </c>
       <c r="K45" s="12" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="N45" s="12" t="n">
-        <v>3</v>
+        <v>57</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
@@ -2883,17 +2883,17 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>01637</t>
+          <t>01717</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>CURNO</t>
+          <t>PAITONE</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>SS671 VALSERIANA  KM0,9820</t>
+          <t>SS 45 BIS KM 55+370</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -2903,56 +2903,56 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
       <c r="F46" s="12" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>5</v>
+        <v>88</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>7</v>
+        <v>78</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="K46" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="N46" s="12" t="n">
         <v>4</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>55864</t>
+          <t>59894</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>OVADA</t>
+          <t>BRESCIA</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>VIA GRAMSCI 9/A</t>
+          <t>V. DE GASP./TANG. S KM 6+930</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -2962,56 +2962,56 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>DELUGAS NADIA</t>
+          <t>SALVINELLI LUCA</t>
         </is>
       </c>
       <c r="F47" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="K47" s="12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>76</v>
+        <v>34</v>
       </c>
       <c r="N47" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>59894</t>
+          <t>55864</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA</t>
+          <t>OVADA</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>V. DE GASP./TANG. S KM 6+930</t>
+          <t>VIA GRAMSCI 9/A</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -3021,56 +3021,56 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>SALVINELLI LUCA</t>
+          <t>DELUGAS NADIA</t>
         </is>
       </c>
       <c r="F48" s="12" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J48" s="12" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="K48" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M48" s="12" t="n">
-        <v>33</v>
+        <v>82</v>
       </c>
       <c r="N48" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>01334</t>
+          <t>54151</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>FINALE LIGURE</t>
+          <t>IMPERIA</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>VIA MAZZINI</t>
+          <t>SS 28 KM 136 + 600</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -3084,52 +3084,52 @@
         </is>
       </c>
       <c r="F49" s="12" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>50</v>
+        <v>98</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="I49" s="12" t="n">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="J49" s="12" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K49" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="M49" s="12" t="n">
-        <v>58</v>
+        <v>91</v>
       </c>
       <c r="N49" s="12" t="n">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>01142</t>
+          <t>55973</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>SESTRI LEVANTE</t>
+          <t>BOTTICINO</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>VIA BRUNO PRIMI, 14</t>
+          <t>GARIBALDI 18</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -3139,56 +3139,56 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
       <c r="F50" s="12" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>79</v>
+        <v>46</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="J50" s="12" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="K50" s="12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M50" s="12" t="n">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="N50" s="12" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>54151</t>
+          <t>11726</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>IMPERIA</t>
+          <t>REZZATO</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>SS 28 KM 136 + 600</t>
+          <t>S.S.45 KM.49+300</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -3198,56 +3198,56 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>BARNABA SALVATORE</t>
+          <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
       <c r="F51" s="12" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>92</v>
+        <v>30</v>
       </c>
       <c r="H51" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I51" s="12" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J51" s="12" t="n">
         <v>25</v>
       </c>
       <c r="K51" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M51" s="12" t="n">
-        <v>87</v>
+        <v>46</v>
       </c>
       <c r="N51" s="12" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>11726</t>
+          <t>02075</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>REZZATO</t>
+          <t>SUZZARA</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>S.S.45 KM.49+300</t>
+          <t>S.S. N. 62 CISA - LOCALITA' CROCILE C.M.</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -3257,56 +3257,56 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>GRAZIOSI DAVIDE</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="F52" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>30</v>
+        <v>64</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="J52" s="12" t="n">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="K52" s="12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="M52" s="12" t="n">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="N52" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>01135</t>
+          <t>01334</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>GENOVA</t>
+          <t>FINALE LIGURE</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>VIA SIFFREDI, 62</t>
+          <t>VIA MAZZINI</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -3316,56 +3316,56 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>DALLORTO ILARIA</t>
+          <t>BARNABA SALVATORE</t>
         </is>
       </c>
       <c r="F53" s="12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="H53" s="12" t="n">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="I53" s="12" t="n">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="J53" s="12" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="K53" s="12" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="L53" s="12" t="n">
         <v>12</v>
       </c>
       <c r="M53" s="12" t="n">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="N53" s="12" t="n">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>55973</t>
+          <t>01142</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>BOTTICINO</t>
+          <t>SESTRI LEVANTE</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>GARIBALDI 18</t>
+          <t>VIA BRUNO PRIMI, 14</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -3375,56 +3375,56 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>GRAZIOSI DAVIDE</t>
+          <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
       <c r="F54" s="12" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="J54" s="12" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="K54" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="M54" s="12" t="n">
-        <v>43</v>
+        <v>77</v>
       </c>
       <c r="N54" s="12" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>01561</t>
+          <t>01135</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>PONTIROLO NUOVO</t>
+          <t>GENOVA</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>STR PROVLE N 12</t>
+          <t>VIA SIFFREDI, 62</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -3434,56 +3434,56 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>DALLORTO ILARIA</t>
         </is>
       </c>
       <c r="F55" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="H55" s="12" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I55" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J55" s="12" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="K55" s="12" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="M55" s="12" t="n">
-        <v>44</v>
+        <v>86</v>
       </c>
       <c r="N55" s="12" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>11719</t>
+          <t>01086</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>MONTICHIARI</t>
+          <t>RECCO</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>S.S. 668 - VIA GHEDI</t>
+          <t>VIA ROMA</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -3493,56 +3493,56 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
       <c r="F56" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>38</v>
+        <v>76</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>106</v>
+        <v>19</v>
       </c>
       <c r="J56" s="12" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="K56" s="12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="M56" s="12" t="n">
-        <v>40</v>
+        <v>122</v>
       </c>
       <c r="N56" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>02075</t>
+          <t>01561</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>SUZZARA</t>
+          <t>PONTIROLO NUOVO</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>S.S. N. 62 CISA - LOCALITA' CROCILE C.M.</t>
+          <t>STR PROVLE N 12</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -3552,56 +3552,56 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="F57" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="H57" s="12" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="I57" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J57" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="K57" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="L57" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="M57" s="12" t="n">
         <v>47</v>
       </c>
-      <c r="J57" s="12" t="n">
-        <v>39</v>
-      </c>
-      <c r="K57" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="L57" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M57" s="12" t="n">
-        <v>58</v>
-      </c>
       <c r="N57" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>12082</t>
+          <t>11719</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>VIADANA</t>
+          <t>MONTICHIARI</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>S.S. 358  KM 22+202</t>
+          <t>S.S. 668 - VIA GHEDI</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -3611,35 +3611,35 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="F58" s="12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G58" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="H58" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="I58" s="12" t="n">
+        <v>108</v>
+      </c>
+      <c r="J58" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="K58" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H58" s="12" t="n">
-        <v>35</v>
-      </c>
-      <c r="I58" s="12" t="n">
+      <c r="L58" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="M58" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="N58" s="12" t="n">
         <v>0</v>
-      </c>
-      <c r="J58" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="K58" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="L58" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="M58" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="N58" s="12" t="n">
-        <v>12</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
@@ -3650,17 +3650,17 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>01086</t>
+          <t>12082</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>RECCO</t>
+          <t>VIADANA</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>VIA ROMA</t>
+          <t>S.S. 358  KM 22+202</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -3670,56 +3670,56 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="F59" s="12" t="n">
         <v>35</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="H59" s="12" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="I59" s="12" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J59" s="12" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="K59" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="M59" s="12" t="n">
-        <v>116</v>
+        <v>18</v>
       </c>
       <c r="N59" s="12" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>01283</t>
+          <t>56297</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>SARZANA</t>
+          <t>SAN PAOLO D'ARGON</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>LOCALITA' MONTECAVALLO - VIA AURELIA 67/A</t>
+          <t>SS 42</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -3729,56 +3729,56 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="F60" s="12" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="H60" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="I60" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="K60" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="L60" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="I60" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="J60" s="12" t="n">
-        <v>30</v>
-      </c>
-      <c r="K60" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="L60" s="12" t="n">
-        <v>2</v>
-      </c>
       <c r="M60" s="12" t="n">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="N60" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>56297</t>
+          <t>01283</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>SAN PAOLO D'ARGON</t>
+          <t>SARZANA</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>SS 42</t>
+          <t>LOCALITA' MONTECAVALLO - VIA AURELIA 67/A</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -3788,39 +3788,39 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
       <c r="F61" s="12" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="G61" s="12" t="n">
+        <v>72</v>
+      </c>
+      <c r="H61" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="I61" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="J61" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="K61" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="L61" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="M61" s="12" t="n">
+        <v>34</v>
+      </c>
+      <c r="N61" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H61" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="I61" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J61" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="K61" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="L61" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="M61" s="12" t="n">
-        <v>54</v>
-      </c>
-      <c r="N61" s="12" t="n">
-        <v>3</v>
-      </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -3851,10 +3851,10 @@
         </is>
       </c>
       <c r="F62" s="12" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H62" s="12" t="n">
         <v>0</v>
@@ -3863,16 +3863,16 @@
         <v>3</v>
       </c>
       <c r="J62" s="12" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K62" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L62" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M62" s="12" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N62" s="12" t="n">
         <v>2</v>
@@ -3910,31 +3910,31 @@
         </is>
       </c>
       <c r="F63" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G63" s="12" t="n">
         <v>40</v>
       </c>
       <c r="H63" s="12" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="I63" s="12" t="n">
         <v>16</v>
       </c>
       <c r="J63" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K63" s="12" t="n">
         <v>7</v>
       </c>
       <c r="L63" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M63" s="12" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="N63" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
@@ -3969,16 +3969,16 @@
         </is>
       </c>
       <c r="F64" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H64" s="12" t="n">
         <v>26</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="J64" s="12" t="n">
         <v>13</v>
@@ -3987,10 +3987,10 @@
         <v>1</v>
       </c>
       <c r="L64" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M64" s="12" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="N64" s="12" t="n">
         <v>3</v>
@@ -4004,17 +4004,17 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>01280</t>
+          <t>54290</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>LA SPEZIA</t>
+          <t>GENOVA</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>VIALE ITALIA 160</t>
+          <t>CORSO DE STEFANIS 215/R</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -4024,56 +4024,56 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>DALLORTO ILARIA</t>
         </is>
       </c>
       <c r="F65" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="G65" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="G65" s="12" t="n">
-        <v>35</v>
-      </c>
-      <c r="H65" s="12" t="n">
-        <v>12</v>
-      </c>
       <c r="I65" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="J65" s="12" t="n">
-        <v>26</v>
-      </c>
       <c r="K65" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L65" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M65" s="12" t="n">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="N65" s="12" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>54290</t>
+          <t>01280</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>GENOVA</t>
+          <t>LA SPEZIA</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>CORSO DE STEFANIS 215/R</t>
+          <t>VIALE ITALIA 160</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -4083,39 +4083,39 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>DALLORTO ILARIA</t>
+          <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
       <c r="F66" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="I66" s="12" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="J66" s="12" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="K66" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L66" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M66" s="12" t="n">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="N66" s="12" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -4146,19 +4146,19 @@
         </is>
       </c>
       <c r="F67" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G67" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H67" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I67" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J67" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K67" s="12" t="n">
         <v>7</v>
@@ -4167,10 +4167,10 @@
         <v>0</v>
       </c>
       <c r="M67" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N67" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
@@ -4181,17 +4181,17 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>01523</t>
+          <t>01288</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>CISANO BERGAMASCO</t>
+          <t>BOLANO</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>SS342 KM 18+640</t>
+          <t>VIA CISA 50</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -4201,32 +4201,32 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
       <c r="F68" s="12" t="n">
         <v>15</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="H68" s="12" t="n">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="I68" s="12" t="n">
-        <v>83</v>
+        <v>26</v>
       </c>
       <c r="J68" s="12" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="K68" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="L68" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="L68" s="12" t="n">
-        <v>6</v>
-      </c>
       <c r="M68" s="12" t="n">
-        <v>59</v>
+        <v>24</v>
       </c>
       <c r="N68" s="12" t="n">
         <v>0</v>
@@ -4240,17 +4240,17 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>01288</t>
+          <t>01523</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>BOLANO</t>
+          <t>CISANO BERGAMASCO</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>VIA CISA 50</t>
+          <t>SS342 KM 18+640</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -4260,32 +4260,32 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="F69" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="H69" s="12" t="n">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="I69" s="12" t="n">
-        <v>25</v>
+        <v>85</v>
       </c>
       <c r="J69" s="12" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="K69" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L69" s="12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M69" s="12" t="n">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="N69" s="12" t="n">
         <v>0</v>
@@ -4326,7 +4326,7 @@
         <v>13</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="H70" s="12" t="n">
         <v>1</v>
@@ -4385,13 +4385,13 @@
         <v>11</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H71" s="12" t="n">
         <v>30</v>
       </c>
       <c r="I71" s="12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J71" s="12" t="n">
         <v>8</v>
@@ -4462,7 +4462,7 @@
         <v>0</v>
       </c>
       <c r="M72" s="12" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="N72" s="12" t="n">
         <v>3</v>
@@ -4500,7 +4500,7 @@
         </is>
       </c>
       <c r="F73" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G73" s="12" t="n">
         <v>0</v>
@@ -4512,7 +4512,7 @@
         <v>0</v>
       </c>
       <c r="J73" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K73" s="12" t="n">
         <v>0</v>
@@ -4521,14 +4521,14 @@
         <v>0</v>
       </c>
       <c r="M73" s="12" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="N73" s="12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -4580,7 +4580,7 @@
         <v>0</v>
       </c>
       <c r="M74" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N74" s="12" t="n">
         <v>2</v>

--- a/docs/files/REPORT_FILTRI/Agente - Marcelli Emanuele.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Marcelli Emanuele.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W20</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>64</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>8070</v>
+        <v>8425</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>5615</v>
+        <v>5885</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>2873</v>
+        <v>3047</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>801</v>
+        <v>832</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>579</v>
+        <v>606</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="I11" s="12" t="n">
         <v>83</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>510</v>
+        <v>529</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>678</v>
+        <v>718</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,31 +901,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>545</v>
+        <v>559</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>232</v>
+        <v>250</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>371</v>
+        <v>382</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>351</v>
+        <v>369</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -960,28 +960,28 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>473</v>
+        <v>493</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>576</v>
+        <v>602</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>273</v>
+        <v>287</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>328</v>
+        <v>342</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>277</v>
+        <v>294</v>
       </c>
       <c r="N13" s="12" t="n">
         <v>7</v>
@@ -1019,31 +1019,31 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>398</v>
+        <v>417</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>261</v>
+        <v>277</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>333</v>
+        <v>349</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1078,31 +1078,31 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>497</v>
+        <v>524</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>285</v>
+        <v>304</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>520</v>
+        <v>547</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1137,31 +1137,31 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>333</v>
+        <v>348</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>390</v>
+        <v>423</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>346</v>
+        <v>361</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>502</v>
+        <v>532</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>300</v>
+        <v>317</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1196,31 +1196,31 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>326</v>
+        <v>346</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>550</v>
+        <v>582</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I17" s="12" t="n">
         <v>14</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>400</v>
+        <v>428</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1255,31 +1255,31 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>296</v>
+        <v>315</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>371</v>
+        <v>406</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>250</v>
+        <v>267</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1314,35 +1314,35 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>273</v>
+        <v>291</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>233</v>
+        <v>257</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1373,35 +1373,35 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1432,31 +1432,31 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>245</v>
+        <v>270</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>251</v>
+        <v>271</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1467,17 +1467,17 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>01527</t>
+          <t>01638</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>DALMINE</t>
+          <t>GRUMELLO DEL MONTE</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>STRADA PROVINCIALE 84</t>
+          <t>VIA LEGA LOMBARDA 2</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1487,56 +1487,56 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>177</v>
+        <v>315</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="I22" s="12" t="n">
         <v>7</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>105</v>
+        <v>126</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>179</v>
+        <v>244</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>01638</t>
+          <t>01527</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>GRUMELLO DEL MONTE</t>
+          <t>DALMINE</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>VIA LEGA LOMBARDA 2</t>
+          <t>STRADA PROVINCIALE 84</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1546,39 +1546,39 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>304</v>
+        <v>178</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>81</v>
+        <v>114</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>229</v>
+        <v>193</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1609,31 +1609,31 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>187</v>
+        <v>206</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>263</v>
+        <v>276</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="I24" s="12" t="n">
         <v>68</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>453</v>
+        <v>475</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -1668,31 +1668,31 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L25" s="12" t="n">
         <v>42</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1727,31 +1727,31 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="H26" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="K26" s="12" t="n">
         <v>44</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>251</v>
+        <v>269</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1786,31 +1786,31 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
@@ -1845,10 +1845,10 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="H28" s="12" t="n">
         <v>5</v>
@@ -1857,19 +1857,19 @@
         <v>10</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K28" s="12" t="n">
         <v>21</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -1880,17 +1880,17 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>01525</t>
+          <t>01034</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>GAZZANIGA</t>
+          <t>GENOVA</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>CESARE BATTISTI</t>
+          <t>LUNGOBISAGNO D'ISTRIA</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1900,56 +1900,56 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>DALLORTO ILARIA</t>
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>178</v>
+        <v>142</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>53</v>
+        <v>130</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>61</v>
+        <v>309</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>89</v>
+        <v>154</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>01034</t>
+          <t>01525</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>GENOVA</t>
+          <t>GAZZANIGA</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>LUNGOBISAGNO D'ISTRIA</t>
+          <t>CESARE BATTISTI</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1959,56 +1959,56 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>DALLORTO ILARIA</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>138</v>
+        <v>193</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>128</v>
+        <v>53</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>296</v>
+        <v>66</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>154</v>
+        <v>89</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>51674</t>
+          <t>02036</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>CARAVAGGIO</t>
+          <t>CREMONA</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>SS 11 PADANA SUPERIORE KM. 182+719</t>
+          <t>VIA CASTELLEONE, 47</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -2018,39 +2018,39 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>208</v>
+        <v>136</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>12</v>
+        <v>173</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>48</v>
+        <v>314</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>106</v>
+        <v>200</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2081,19 +2081,19 @@
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I32" s="12" t="n">
         <v>8</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K32" s="12" t="n">
         <v>24</v>
@@ -2102,10 +2102,10 @@
         <v>67</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
@@ -2116,17 +2116,17 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>02036</t>
+          <t>51674</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>CREMONA</t>
+          <t>CARAVAGGIO</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>VIA CASTELLEONE, 47</t>
+          <t>SS 11 PADANA SUPERIORE KM. 182+719</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2136,39 +2136,39 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>128</v>
+        <v>230</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>169</v>
+        <v>12</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>295</v>
+        <v>50</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="K33" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="L33" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="M33" s="12" t="n">
+        <v>106</v>
+      </c>
+      <c r="N33" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="L33" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="M33" s="12" t="n">
-        <v>197</v>
-      </c>
-      <c r="N33" s="12" t="n">
-        <v>67</v>
-      </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2199,7 +2199,7 @@
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="G34" s="12" t="n">
         <v>0</v>
@@ -2211,40 +2211,40 @@
         <v>0</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K34" s="12" t="n">
         <v>22</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="N34" s="12" t="n">
         <v>9</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>01718</t>
+          <t>01043</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>PONTEVICO</t>
+          <t>GENOVA</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>SS 45 BIS KM 16+700</t>
+          <t>VIA RIGHETTI 1 R</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2254,56 +2254,56 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>DALLORTO ILARIA</t>
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>172</v>
+        <v>107</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>01043</t>
+          <t>01718</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>GENOVA</t>
+          <t>PONTEVICO</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>VIA RIGHETTI 1 R</t>
+          <t>SS 45 BIS KM 16+700</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2313,39 +2313,39 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>DALLORTO ILARIA</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>98</v>
+        <v>179</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>165</v>
+        <v>124</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2376,10 +2376,10 @@
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="H37" s="12" t="n">
         <v>9</v>
@@ -2388,16 +2388,16 @@
         <v>15</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K37" s="12" t="n">
         <v>17</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="N37" s="12" t="n">
         <v>2</v>
@@ -2411,17 +2411,17 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>01007</t>
+          <t>51037</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>CHIAVARI</t>
+          <t>ACQUI TERME</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>CORSO GENOVA 40</t>
+          <t>VIA NIZZA 152</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -2431,35 +2431,35 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>DELUGAS NADIA</t>
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>204</v>
+        <v>96</v>
       </c>
       <c r="N38" s="12" t="n">
-        <v>53</v>
+        <v>6</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
@@ -2470,17 +2470,17 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>51037</t>
+          <t>01577</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>ACQUI TERME</t>
+          <t>ZANICA</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>VIA NIZZA 152</t>
+          <t>VIA PROVINCIALE</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -2490,35 +2490,35 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>DELUGAS NADIA</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="I39" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="J39" s="12" t="n">
+        <v>54</v>
+      </c>
+      <c r="K39" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="L39" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="M39" s="12" t="n">
+        <v>99</v>
+      </c>
+      <c r="N39" s="12" t="n">
         <v>2</v>
-      </c>
-      <c r="J39" s="12" t="n">
-        <v>64</v>
-      </c>
-      <c r="K39" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="L39" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="M39" s="12" t="n">
-        <v>89</v>
-      </c>
-      <c r="N39" s="12" t="n">
-        <v>6</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
@@ -2529,17 +2529,17 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>01577</t>
+          <t>01007</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>ZANICA</t>
+          <t>CHIAVARI</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>VIA PROVINCIALE</t>
+          <t>CORSO GENOVA 40</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -2549,39 +2549,39 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
       <c r="F40" s="12" t="n">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="H40" s="12" t="n">
         <v>13</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>94</v>
+        <v>213</v>
       </c>
       <c r="N40" s="12" t="n">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2612,28 +2612,28 @@
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="H41" s="12" t="n">
         <v>7</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="N41" s="12" t="n">
         <v>25</v>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="F42" s="12" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="H42" s="12" t="n">
         <v>1</v>
@@ -2683,7 +2683,7 @@
         <v>8</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="K42" s="12" t="n">
         <v>25</v>
@@ -2692,10 +2692,10 @@
         <v>4</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="N42" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
@@ -2706,17 +2706,17 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>01637</t>
+          <t>01971</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>CURNO</t>
+          <t>CREMONA</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>SS671 VALSERIANA  KM0,9820</t>
+          <t>VIA BERGAMO 47</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -2726,35 +2726,35 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="F43" s="12" t="n">
+        <v>64</v>
+      </c>
+      <c r="G43" s="12" t="n">
+        <v>83</v>
+      </c>
+      <c r="H43" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="I43" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="J43" s="12" t="n">
+        <v>57</v>
+      </c>
+      <c r="K43" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="L43" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="M43" s="12" t="n">
+        <v>86</v>
+      </c>
+      <c r="N43" s="12" t="n">
         <v>61</v>
-      </c>
-      <c r="G43" s="12" t="n">
-        <v>82</v>
-      </c>
-      <c r="H43" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="I43" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="J43" s="12" t="n">
-        <v>30</v>
-      </c>
-      <c r="K43" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="L43" s="12" t="n">
-        <v>30</v>
-      </c>
-      <c r="M43" s="12" t="n">
-        <v>77</v>
-      </c>
-      <c r="N43" s="12" t="n">
-        <v>4</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
@@ -2789,31 +2789,31 @@
         </is>
       </c>
       <c r="F44" s="12" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="H44" s="12" t="n">
         <v>7</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N44" s="12" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
@@ -2824,17 +2824,17 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>01971</t>
+          <t>01637</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>CREMONA</t>
+          <t>CURNO</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>VIA BERGAMO 47</t>
+          <t>SS671 VALSERIANA  KM0,9820</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -2844,14 +2844,14 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="F45" s="12" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="H45" s="12" t="n">
         <v>5</v>
@@ -2860,19 +2860,19 @@
         <v>7</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="K45" s="12" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="N45" s="12" t="n">
-        <v>57</v>
+        <v>4</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
@@ -2907,28 +2907,28 @@
         </is>
       </c>
       <c r="F46" s="12" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="K46" s="12" t="n">
         <v>13</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N46" s="12" t="n">
         <v>4</v>
@@ -2942,17 +2942,17 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>59894</t>
+          <t>54151</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA</t>
+          <t>IMPERIA</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>V. DE GASP./TANG. S KM 6+930</t>
+          <t>SS 28 KM 136 + 600</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -2962,39 +2962,39 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>SALVINELLI LUCA</t>
+          <t>BARNABA SALVATORE</t>
         </is>
       </c>
       <c r="F47" s="12" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>66</v>
+        <v>104</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="K47" s="12" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>34</v>
+        <v>92</v>
       </c>
       <c r="N47" s="12" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -3025,52 +3025,52 @@
         </is>
       </c>
       <c r="F48" s="12" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G48" s="12" t="n">
         <v>61</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I48" s="12" t="n">
         <v>18</v>
       </c>
       <c r="J48" s="12" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="K48" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L48" s="12" t="n">
         <v>18</v>
       </c>
       <c r="M48" s="12" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="N48" s="12" t="n">
         <v>3</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>54151</t>
+          <t>59894</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>IMPERIA</t>
+          <t>BRESCIA</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>SS 28 KM 136 + 600</t>
+          <t>V. DE GASP./TANG. S KM 6+930</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -3080,56 +3080,56 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>BARNABA SALVATORE</t>
+          <t>SALVINELLI LUCA</t>
         </is>
       </c>
       <c r="F49" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>98</v>
+        <v>72</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="I49" s="12" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J49" s="12" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K49" s="12" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="M49" s="12" t="n">
-        <v>91</v>
+        <v>35</v>
       </c>
       <c r="N49" s="12" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>55973</t>
+          <t>01142</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>BOTTICINO</t>
+          <t>SESTRI LEVANTE</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>GARIBALDI 18</t>
+          <t>VIA BRUNO PRIMI, 14</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -3139,56 +3139,56 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>GRAZIOSI DAVIDE</t>
+          <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
       <c r="F50" s="12" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>46</v>
+        <v>83</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="J50" s="12" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K50" s="12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M50" s="12" t="n">
-        <v>47</v>
+        <v>82</v>
       </c>
       <c r="N50" s="12" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>11726</t>
+          <t>11719</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>REZZATO</t>
+          <t>MONTICHIARI</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>S.S.45 KM.49+300</t>
+          <t>S.S. 668 - VIA GHEDI</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -3198,35 +3198,35 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>GRAZIOSI DAVIDE</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="F51" s="12" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G51" s="12" t="n">
+        <v>45</v>
+      </c>
+      <c r="H51" s="12" t="n">
+        <v>37</v>
+      </c>
+      <c r="I51" s="12" t="n">
+        <v>114</v>
+      </c>
+      <c r="J51" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="K51" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="H51" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="I51" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="J51" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="K51" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="L51" s="12" t="n">
-        <v>18</v>
-      </c>
       <c r="M51" s="12" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N51" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
@@ -3237,17 +3237,17 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>02075</t>
+          <t>55973</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>SUZZARA</t>
+          <t>BOTTICINO</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>S.S. N. 62 CISA - LOCALITA' CROCILE C.M.</t>
+          <t>GARIBALDI 18</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -3257,39 +3257,39 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
       <c r="F52" s="12" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>55</v>
+        <v>1</v>
       </c>
       <c r="J52" s="12" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="K52" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="L52" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="L52" s="12" t="n">
+      <c r="M52" s="12" t="n">
+        <v>49</v>
+      </c>
+      <c r="N52" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="M52" s="12" t="n">
-        <v>63</v>
-      </c>
-      <c r="N52" s="12" t="n">
-        <v>1</v>
-      </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -3320,52 +3320,52 @@
         </is>
       </c>
       <c r="F53" s="12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="H53" s="12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I53" s="12" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="J53" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K53" s="12" t="n">
         <v>8</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M53" s="12" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="N53" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>01142</t>
+          <t>11726</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>SESTRI LEVANTE</t>
+          <t>REZZATO</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>VIA BRUNO PRIMI, 14</t>
+          <t>S.S.45 KM.49+300</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -3375,56 +3375,56 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
       <c r="F54" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>80</v>
+        <v>31</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="J54" s="12" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="K54" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="M54" s="12" t="n">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="N54" s="12" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>01135</t>
+          <t>02075</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>GENOVA</t>
+          <t>SUZZARA</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>VIA SIFFREDI, 62</t>
+          <t>S.S. N. 62 CISA - LOCALITA' CROCILE C.M.</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -3434,56 +3434,56 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>DALLORTO ILARIA</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="F55" s="12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="H55" s="12" t="n">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="I55" s="12" t="n">
-        <v>4</v>
+        <v>59</v>
       </c>
       <c r="J55" s="12" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="K55" s="12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M55" s="12" t="n">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="N55" s="12" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>01086</t>
+          <t>01135</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>RECCO</t>
+          <t>GENOVA</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>VIA ROMA</t>
+          <t>VIA SIFFREDI, 62</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -3493,56 +3493,56 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>DALLORTO ILARIA</t>
         </is>
       </c>
       <c r="F56" s="12" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>76</v>
+        <v>37</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="J56" s="12" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="K56" s="12" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="M56" s="12" t="n">
-        <v>122</v>
+        <v>96</v>
       </c>
       <c r="N56" s="12" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>01561</t>
+          <t>01086</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>PONTIROLO NUOVO</t>
+          <t>RECCO</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>STR PROVLE N 12</t>
+          <t>VIA ROMA</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -3552,56 +3552,56 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
       <c r="F57" s="12" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="H57" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="I57" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="J57" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="K57" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="L57" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="M57" s="12" t="n">
+        <v>125</v>
+      </c>
+      <c r="N57" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I57" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J57" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="K57" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="L57" s="12" t="n">
-        <v>22</v>
-      </c>
-      <c r="M57" s="12" t="n">
-        <v>47</v>
-      </c>
-      <c r="N57" s="12" t="n">
-        <v>2</v>
-      </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>11719</t>
+          <t>12082</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>MONTICHIARI</t>
+          <t>VIADANA</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>S.S. 668 - VIA GHEDI</t>
+          <t>S.S. 358  KM 22+202</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -3611,56 +3611,56 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="F58" s="12" t="n">
         <v>38</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="J58" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="K58" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="L58" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="M58" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="N58" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="K58" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L58" s="12" t="n">
-        <v>26</v>
-      </c>
-      <c r="M58" s="12" t="n">
-        <v>43</v>
-      </c>
-      <c r="N58" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>12082</t>
+          <t>01561</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>VIADANA</t>
+          <t>PONTIROLO NUOVO</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>S.S. 358  KM 22+202</t>
+          <t>STR PROVLE N 12</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -3670,35 +3670,35 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="F59" s="12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="H59" s="12" t="n">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="I59" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J59" s="12" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="K59" s="12" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="M59" s="12" t="n">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="N59" s="12" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
@@ -3733,7 +3733,7 @@
         </is>
       </c>
       <c r="F60" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G60" s="12" t="n">
         <v>0</v>
@@ -3745,23 +3745,23 @@
         <v>0</v>
       </c>
       <c r="J60" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K60" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L60" s="12" t="n">
         <v>14</v>
       </c>
       <c r="M60" s="12" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="N60" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -3795,7 +3795,7 @@
         <v>34</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H61" s="12" t="n">
         <v>15</v>
@@ -3813,7 +3813,7 @@
         <v>2</v>
       </c>
       <c r="M61" s="12" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="N61" s="12" t="n">
         <v>0</v>
@@ -3851,19 +3851,19 @@
         </is>
       </c>
       <c r="F62" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I62" s="12" t="n">
         <v>3</v>
       </c>
       <c r="J62" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K62" s="12" t="n">
         <v>7</v>
@@ -3872,10 +3872,10 @@
         <v>9</v>
       </c>
       <c r="M62" s="12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="N62" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
@@ -3886,17 +3886,17 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>02024</t>
+          <t>52510</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>CASALMAGGIORE</t>
+          <t>PORTO MANTOVANO</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>VIA ROMA 36</t>
+          <t>SR CISA 4 S. ANTONIO</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -3910,52 +3910,52 @@
         </is>
       </c>
       <c r="F63" s="12" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H63" s="12" t="n">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="I63" s="12" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J63" s="12" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="K63" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L63" s="12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M63" s="12" t="n">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="N63" s="12" t="n">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>11725</t>
+          <t>02024</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>GAVARDO</t>
+          <t>CASALMAGGIORE</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>LOC. ROCCOLINO SS45 BIS</t>
+          <t>VIA ROMA 36</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -3965,56 +3965,56 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>GRAZIOSI DAVIDE</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="F64" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v>70</v>
+        <v>16</v>
       </c>
       <c r="J64" s="12" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="K64" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L64" s="12" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="M64" s="12" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="N64" s="12" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>54290</t>
+          <t>11725</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>GENOVA</t>
+          <t>GAVARDO</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>CORSO DE STEFANIS 215/R</t>
+          <t>LOC. ROCCOLINO SS45 BIS</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -4024,39 +4024,39 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>DALLORTO ILARIA</t>
+          <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
       <c r="F65" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="H65" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I65" s="12" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="J65" s="12" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K65" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L65" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="M65" s="12" t="n">
+        <v>47</v>
+      </c>
+      <c r="N65" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="M65" s="12" t="n">
-        <v>43</v>
-      </c>
-      <c r="N65" s="12" t="n">
-        <v>20</v>
-      </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -4087,19 +4087,19 @@
         </is>
       </c>
       <c r="F66" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I66" s="12" t="n">
         <v>21</v>
       </c>
       <c r="J66" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K66" s="12" t="n">
         <v>2</v>
@@ -4108,10 +4108,10 @@
         <v>1</v>
       </c>
       <c r="M66" s="12" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="N66" s="12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
@@ -4122,17 +4122,17 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>52510</t>
+          <t>54290</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>PORTO MANTOVANO</t>
+          <t>GENOVA</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>SR CISA 4 S. ANTONIO</t>
+          <t>CORSO DE STEFANIS 215/R</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -4142,39 +4142,39 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>DALLORTO ILARIA</t>
         </is>
       </c>
       <c r="F67" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G67" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H67" s="12" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="I67" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J67" s="12" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K67" s="12" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L67" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M67" s="12" t="n">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="N67" s="12" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -4205,13 +4205,13 @@
         </is>
       </c>
       <c r="F68" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H68" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I68" s="12" t="n">
         <v>26</v>
@@ -4223,10 +4223,10 @@
         <v>4</v>
       </c>
       <c r="L68" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M68" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="N68" s="12" t="n">
         <v>0</v>
@@ -4264,19 +4264,19 @@
         </is>
       </c>
       <c r="F69" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H69" s="12" t="n">
         <v>46</v>
       </c>
       <c r="I69" s="12" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J69" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K69" s="12" t="n">
         <v>0</v>
@@ -4326,7 +4326,7 @@
         <v>13</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="H70" s="12" t="n">
         <v>1</v>
@@ -4391,7 +4391,7 @@
         <v>30</v>
       </c>
       <c r="I71" s="12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J71" s="12" t="n">
         <v>8</v>
@@ -4417,17 +4417,17 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>02074</t>
+          <t>01631</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>GOITO</t>
+          <t>TELGATE</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>S.S. N. 236 KM 14+332</t>
+          <t>VIALE PAPA GIOVANNI</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -4437,35 +4437,35 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>SALVINELLI LUCA</t>
         </is>
       </c>
       <c r="F72" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G72" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H72" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I72" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J72" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K72" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L72" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M72" s="12" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="N72" s="12" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
@@ -4476,17 +4476,17 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>01631</t>
+          <t>02074</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>TELGATE</t>
+          <t>GOITO</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>VIALE PAPA GIOVANNI</t>
+          <t>S.S. N. 236 KM 14+332</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>SALVINELLI LUCA</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="F73" s="12" t="n">
@@ -4506,7 +4506,7 @@
         <v>0</v>
       </c>
       <c r="H73" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I73" s="12" t="n">
         <v>0</v>
@@ -4515,16 +4515,16 @@
         <v>9</v>
       </c>
       <c r="K73" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L73" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M73" s="12" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="N73" s="12" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
@@ -4580,14 +4580,14 @@
         <v>0</v>
       </c>
       <c r="M74" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N74" s="12" t="n">
         <v>2</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/Agente - Marcelli Emanuele.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Marcelli Emanuele.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W20</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>64</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>8425</v>
+        <v>8829</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>5885</v>
+        <v>6151</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>3047</v>
+        <v>3227</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>832</v>
+        <v>877</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>606</v>
+        <v>652</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>529</v>
+        <v>559</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>308</v>
+        <v>323</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>718</v>
+        <v>762</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,35 +901,35 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>559</v>
+        <v>590</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>382</v>
+        <v>398</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>164</v>
+        <v>180</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>369</v>
+        <v>391</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -960,35 +960,35 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>493</v>
+        <v>510</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>267</v>
+        <v>281</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>602</v>
+        <v>637</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>287</v>
+        <v>304</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>342</v>
+        <v>353</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>294</v>
+        <v>310</v>
       </c>
       <c r="N13" s="12" t="n">
         <v>7</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1019,31 +1019,31 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>417</v>
+        <v>435</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>322</v>
+        <v>338</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>349</v>
+        <v>376</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1078,31 +1078,31 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>394</v>
+        <v>414</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>524</v>
+        <v>560</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>304</v>
+        <v>321</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>547</v>
+        <v>577</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1113,17 +1113,17 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>01024</t>
+          <t>01507</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>GENOVA</t>
+          <t>BERGAMO</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>VIA CANTORE 20 A ROSSO</t>
+          <t>VIA BROSETA</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1133,35 +1133,35 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>DALLORTO ILARIA</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>348</v>
+        <v>376</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>423</v>
+        <v>616</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>361</v>
+        <v>46</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>532</v>
+        <v>16</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="K16" s="12" t="n">
+        <v>115</v>
+      </c>
+      <c r="L16" s="12" t="n">
+        <v>100</v>
+      </c>
+      <c r="M16" s="12" t="n">
+        <v>467</v>
+      </c>
+      <c r="N16" s="12" t="n">
         <v>95</v>
-      </c>
-      <c r="L16" s="12" t="n">
-        <v>73</v>
-      </c>
-      <c r="M16" s="12" t="n">
-        <v>317</v>
-      </c>
-      <c r="N16" s="12" t="n">
-        <v>12</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1172,17 +1172,17 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>01507</t>
+          <t>01024</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>BERGAMO</t>
+          <t>GENOVA</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>VIA BROSETA</t>
+          <t>VIA CANTORE 20 A ROSSO</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1192,35 +1192,35 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>DALLORTO ILARIA</t>
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>346</v>
+        <v>373</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>582</v>
+        <v>443</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>40</v>
+        <v>381</v>
       </c>
       <c r="I17" s="12" t="n">
+        <v>560</v>
+      </c>
+      <c r="J17" s="12" t="n">
+        <v>294</v>
+      </c>
+      <c r="K17" s="12" t="n">
+        <v>100</v>
+      </c>
+      <c r="L17" s="12" t="n">
+        <v>81</v>
+      </c>
+      <c r="M17" s="12" t="n">
+        <v>345</v>
+      </c>
+      <c r="N17" s="12" t="n">
         <v>14</v>
-      </c>
-      <c r="J17" s="12" t="n">
-        <v>258</v>
-      </c>
-      <c r="K17" s="12" t="n">
-        <v>107</v>
-      </c>
-      <c r="L17" s="12" t="n">
-        <v>91</v>
-      </c>
-      <c r="M17" s="12" t="n">
-        <v>428</v>
-      </c>
-      <c r="N17" s="12" t="n">
-        <v>85</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1255,31 +1255,31 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>406</v>
+        <v>456</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1314,35 +1314,35 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
+        <v>304</v>
+      </c>
+      <c r="G19" s="12" t="n">
         <v>291</v>
       </c>
-      <c r="G19" s="12" t="n">
-        <v>257</v>
-      </c>
       <c r="H19" s="12" t="n">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="L19" s="12" t="n">
         <v>49</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1373,35 +1373,35 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1432,35 +1432,35 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>270</v>
+        <v>289</v>
       </c>
       <c r="H21" s="12" t="n">
         <v>32</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>271</v>
+        <v>293</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>315</v>
+        <v>347</v>
       </c>
       <c r="H22" s="12" t="n">
         <v>1</v>
@@ -1503,19 +1503,19 @@
         <v>7</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="K22" s="12" t="n">
         <v>23</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>244</v>
+        <v>267</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1526,17 +1526,17 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>01527</t>
+          <t>01032</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>DALMINE</t>
+          <t>GENOVA</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>STRADA PROVINCIALE 84</t>
+          <t>VIA BRIGATE PARTIGIANE, 1/R</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1546,56 +1546,56 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>DALLORTO ILARIA</t>
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>178</v>
+        <v>287</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>39</v>
+        <v>82</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>7</v>
+        <v>69</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>114</v>
+        <v>160</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>105</v>
+        <v>62</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>193</v>
+        <v>512</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>01032</t>
+          <t>01527</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>GENOVA</t>
+          <t>DALMINE</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>VIA BRIGATE PARTIGIANE, 1/R</t>
+          <t>STRADA PROVINCIALE 84</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1605,39 +1605,39 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>DALLORTO ILARIA</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>276</v>
+        <v>201</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>80</v>
+        <v>41</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>68</v>
+        <v>8</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>152</v>
+        <v>116</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>56</v>
+        <v>109</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>475</v>
+        <v>208</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1668,31 +1668,31 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>188</v>
+        <v>207</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="G26" s="12" t="n">
         <v>234</v>
@@ -1739,16 +1739,16 @@
         <v>80</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>269</v>
+        <v>288</v>
       </c>
       <c r="N26" s="12" t="n">
         <v>20</v>
@@ -1786,31 +1786,31 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>211</v>
+        <v>225</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="I27" s="12" t="n">
         <v>10</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>223</v>
+        <v>241</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
@@ -1845,10 +1845,10 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>170</v>
+        <v>192</v>
       </c>
       <c r="H28" s="12" t="n">
         <v>5</v>
@@ -1857,19 +1857,19 @@
         <v>10</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>203</v>
+        <v>217</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -1904,31 +1904,31 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>309</v>
+        <v>322</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
@@ -1966,13 +1966,13 @@
         <v>139</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>193</v>
+        <v>216</v>
       </c>
       <c r="H30" s="12" t="n">
         <v>53</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="J30" s="12" t="n">
         <v>80</v>
@@ -2022,35 +2022,35 @@
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2081,31 +2081,31 @@
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>166</v>
+        <v>186</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I32" s="12" t="n">
         <v>8</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>125</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="H33" s="12" t="n">
         <v>12</v>
@@ -2199,35 +2199,35 @@
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="K34" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="L34" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="L34" s="12" t="n">
-        <v>20</v>
-      </c>
       <c r="M34" s="12" t="n">
-        <v>142</v>
+        <v>157</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2258,28 +2258,28 @@
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K35" s="12" t="n">
         <v>28</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="N35" s="12" t="n">
         <v>20</v>
@@ -2320,13 +2320,13 @@
         <v>108</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="H36" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J36" s="12" t="n">
         <v>77</v>
@@ -2352,17 +2352,17 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>01378</t>
+          <t>01007</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>CARCARE</t>
+          <t>CHIAVARI</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>VIA VITTORIO VENETO 52</t>
+          <t>CORSO GENOVA 40</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2372,39 +2372,39 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>DELUGAS NADIA</t>
+          <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="H37" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="I37" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" s="12" t="n">
+        <v>52</v>
+      </c>
+      <c r="K37" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="I37" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="J37" s="12" t="n">
-        <v>49</v>
-      </c>
-      <c r="K37" s="12" t="n">
-        <v>17</v>
-      </c>
       <c r="L37" s="12" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>82</v>
+        <v>228</v>
       </c>
       <c r="N37" s="12" t="n">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2435,10 +2435,10 @@
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="H38" s="12" t="n">
         <v>6</v>
@@ -2447,19 +2447,19 @@
         <v>3</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="K38" s="12" t="n">
         <v>29</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="N38" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
@@ -2470,17 +2470,17 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>01577</t>
+          <t>01378</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>ZANICA</t>
+          <t>CARCARE</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>VIA PROVINCIALE</t>
+          <t>VIA VITTORIO VENETO 52</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -2490,56 +2490,56 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>DELUGAS NADIA</t>
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="N39" s="12" t="n">
         <v>2</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>01007</t>
+          <t>01577</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>CHIAVARI</t>
+          <t>ZANICA</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>CORSO GENOVA 40</t>
+          <t>VIA PROVINCIALE</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -2549,39 +2549,39 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="F40" s="12" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="H40" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="I40" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="I40" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="J40" s="12" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>213</v>
+        <v>107</v>
       </c>
       <c r="N40" s="12" t="n">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2612,13 +2612,13 @@
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I41" s="12" t="n">
         <v>12</v>
@@ -2630,13 +2630,13 @@
         <v>26</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="N41" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="F42" s="12" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="H42" s="12" t="n">
         <v>1</v>
@@ -2683,19 +2683,19 @@
         <v>8</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K42" s="12" t="n">
         <v>25</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="N42" s="12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
@@ -2730,10 +2730,10 @@
         </is>
       </c>
       <c r="F43" s="12" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="H43" s="12" t="n">
         <v>9</v>
@@ -2742,19 +2742,19 @@
         <v>8</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="N43" s="12" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
@@ -2789,31 +2789,31 @@
         </is>
       </c>
       <c r="F44" s="12" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H44" s="12" t="n">
         <v>7</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L44" s="12" t="n">
         <v>15</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="N44" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
@@ -2848,10 +2848,10 @@
         </is>
       </c>
       <c r="F45" s="12" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="H45" s="12" t="n">
         <v>5</v>
@@ -2860,23 +2860,23 @@
         <v>7</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K45" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="N45" s="12" t="n">
         <v>4</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2907,52 +2907,52 @@
         </is>
       </c>
       <c r="F46" s="12" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K46" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L46" s="12" t="n">
         <v>19</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="N46" s="12" t="n">
         <v>4</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>54151</t>
+          <t>55864</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>IMPERIA</t>
+          <t>OVADA</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>SS 28 KM 136 + 600</t>
+          <t>VIA GRAMSCI 9/A</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -2962,56 +2962,56 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>BARNABA SALVATORE</t>
+          <t>DELUGAS NADIA</t>
         </is>
       </c>
       <c r="F47" s="12" t="n">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>104</v>
+        <v>61</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="K47" s="12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="N47" s="12" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>55864</t>
+          <t>54151</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>OVADA</t>
+          <t>IMPERIA</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>VIA GRAMSCI 9/A</t>
+          <t>SS 28 KM 136 + 600</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -3021,56 +3021,56 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>DELUGAS NADIA</t>
+          <t>BARNABA SALVATORE</t>
         </is>
       </c>
       <c r="F48" s="12" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>61</v>
+        <v>110</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="J48" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K48" s="12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M48" s="12" t="n">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="N48" s="12" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>59894</t>
+          <t>01142</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA</t>
+          <t>SESTRI LEVANTE</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>V. DE GASP./TANG. S KM 6+930</t>
+          <t>VIA BRUNO PRIMI, 14</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -3080,56 +3080,56 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>SALVINELLI LUCA</t>
+          <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
       <c r="F49" s="12" t="n">
         <v>49</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="I49" s="12" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="J49" s="12" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="K49" s="12" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="M49" s="12" t="n">
-        <v>35</v>
+        <v>91</v>
       </c>
       <c r="N49" s="12" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>01142</t>
+          <t>59894</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>SESTRI LEVANTE</t>
+          <t>BRESCIA</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>VIA BRUNO PRIMI, 14</t>
+          <t>V. DE GASP./TANG. S KM 6+930</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -3139,56 +3139,56 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>SALVINELLI LUCA</t>
         </is>
       </c>
       <c r="F50" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="J50" s="12" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="K50" s="12" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="M50" s="12" t="n">
-        <v>82</v>
+        <v>35</v>
       </c>
       <c r="N50" s="12" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>11719</t>
+          <t>02075</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>MONTICHIARI</t>
+          <t>SUZZARA</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>S.S. 668 - VIA GHEDI</t>
+          <t>S.S. N. 62 CISA - LOCALITA' CROCILE C.M.</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -3198,56 +3198,56 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="F51" s="12" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="H51" s="12" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I51" s="12" t="n">
-        <v>114</v>
+        <v>63</v>
       </c>
       <c r="J51" s="12" t="n">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="K51" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="L51" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="L51" s="12" t="n">
-        <v>30</v>
-      </c>
       <c r="M51" s="12" t="n">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="N51" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>55973</t>
+          <t>11719</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>BOTTICINO</t>
+          <t>MONTICHIARI</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>GARIBALDI 18</t>
+          <t>S.S. 668 - VIA GHEDI</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -3257,32 +3257,32 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>GRAZIOSI DAVIDE</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="F52" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="I52" s="12" t="n">
+        <v>116</v>
+      </c>
+      <c r="J52" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="K52" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="J52" s="12" t="n">
-        <v>34</v>
-      </c>
-      <c r="K52" s="12" t="n">
-        <v>8</v>
-      </c>
       <c r="L52" s="12" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="M52" s="12" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="N52" s="12" t="n">
         <v>0</v>
@@ -3320,19 +3320,19 @@
         </is>
       </c>
       <c r="F53" s="12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="H53" s="12" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="I53" s="12" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="J53" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K53" s="12" t="n">
         <v>8</v>
@@ -3341,10 +3341,10 @@
         <v>13</v>
       </c>
       <c r="M53" s="12" t="n">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="N53" s="12" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
@@ -3355,17 +3355,17 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>11726</t>
+          <t>55973</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>REZZATO</t>
+          <t>BOTTICINO</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>S.S.45 KM.49+300</t>
+          <t>GARIBALDI 18</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -3379,31 +3379,31 @@
         </is>
       </c>
       <c r="F54" s="12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J54" s="12" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="K54" s="12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="M54" s="12" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="N54" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
@@ -3414,17 +3414,17 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>02075</t>
+          <t>11726</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>SUZZARA</t>
+          <t>REZZATO</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>S.S. N. 62 CISA - LOCALITA' CROCILE C.M.</t>
+          <t>S.S.45 KM.49+300</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -3434,56 +3434,56 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
       <c r="F55" s="12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>68</v>
+        <v>33</v>
       </c>
       <c r="H55" s="12" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="I55" s="12" t="n">
-        <v>59</v>
+        <v>4</v>
       </c>
       <c r="J55" s="12" t="n">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="K55" s="12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="M55" s="12" t="n">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="N55" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>01135</t>
+          <t>12082</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>GENOVA</t>
+          <t>VIADANA</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>VIA SIFFREDI, 62</t>
+          <t>S.S. 358  KM 22+202</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -3493,35 +3493,35 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>DALLORTO ILARIA</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="F56" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J56" s="12" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="K56" s="12" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="L56" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="M56" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="N56" s="12" t="n">
         <v>12</v>
-      </c>
-      <c r="M56" s="12" t="n">
-        <v>96</v>
-      </c>
-      <c r="N56" s="12" t="n">
-        <v>10</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
@@ -3556,19 +3556,19 @@
         </is>
       </c>
       <c r="F57" s="12" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G57" s="12" t="n">
         <v>81</v>
       </c>
       <c r="H57" s="12" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I57" s="12" t="n">
         <v>19</v>
       </c>
       <c r="J57" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K57" s="12" t="n">
         <v>8</v>
@@ -3577,7 +3577,7 @@
         <v>16</v>
       </c>
       <c r="M57" s="12" t="n">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="N57" s="12" t="n">
         <v>3</v>
@@ -3591,17 +3591,17 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>12082</t>
+          <t>01135</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>VIADANA</t>
+          <t>GENOVA</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>S.S. 358  KM 22+202</t>
+          <t>VIA SIFFREDI, 62</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -3611,56 +3611,56 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>DALLORTO ILARIA</t>
         </is>
       </c>
       <c r="F58" s="12" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J58" s="12" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K58" s="12" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="L58" s="12" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="M58" s="12" t="n">
-        <v>18</v>
+        <v>100</v>
       </c>
       <c r="N58" s="12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>01561</t>
+          <t>56297</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>PONTIROLO NUOVO</t>
+          <t>SAN PAOLO D'ARGON</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>STR PROVLE N 12</t>
+          <t>SS 42</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -3670,56 +3670,56 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="F59" s="12" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="H59" s="12" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I59" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J59" s="12" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="K59" s="12" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="M59" s="12" t="n">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="N59" s="12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>56297</t>
+          <t>01561</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>SAN PAOLO D'ARGON</t>
+          <t>PONTIROLO NUOVO</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>SS 42</t>
+          <t>STR PROVLE N 12</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -3729,35 +3729,35 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="F60" s="12" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I60" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J60" s="12" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K60" s="12" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L60" s="12" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="M60" s="12" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="N60" s="12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
@@ -3792,19 +3792,19 @@
         </is>
       </c>
       <c r="F61" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H61" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I61" s="12" t="n">
         <v>3</v>
       </c>
       <c r="J61" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="K61" s="12" t="n">
         <v>5</v>
@@ -3813,7 +3813,7 @@
         <v>2</v>
       </c>
       <c r="M61" s="12" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="N61" s="12" t="n">
         <v>0</v>
@@ -3851,10 +3851,10 @@
         </is>
       </c>
       <c r="F62" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H62" s="12" t="n">
         <v>1</v>
@@ -3863,16 +3863,16 @@
         <v>3</v>
       </c>
       <c r="J62" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K62" s="12" t="n">
         <v>7</v>
       </c>
       <c r="L62" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M62" s="12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N62" s="12" t="n">
         <v>3</v>
@@ -3910,22 +3910,22 @@
         </is>
       </c>
       <c r="F63" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G63" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H63" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I63" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J63" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K63" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L63" s="12" t="n">
         <v>0</v>
@@ -3938,24 +3938,24 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>02024</t>
+          <t>11725</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>CASALMAGGIORE</t>
+          <t>GAVARDO</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>VIA ROMA 36</t>
+          <t>LOC. ROCCOLINO SS45 BIS</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -3965,56 +3965,56 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
       <c r="F64" s="12" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v>16</v>
+        <v>83</v>
       </c>
       <c r="J64" s="12" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="K64" s="12" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L64" s="12" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="M64" s="12" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="N64" s="12" t="n">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>11725</t>
+          <t>02024</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>GAVARDO</t>
+          <t>CASALMAGGIORE</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>LOC. ROCCOLINO SS45 BIS</t>
+          <t>VIA ROMA 36</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -4024,39 +4024,39 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>GRAZIOSI DAVIDE</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="F65" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H65" s="12" t="n">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="I65" s="12" t="n">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="J65" s="12" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="K65" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L65" s="12" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="M65" s="12" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="N65" s="12" t="n">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -4087,19 +4087,19 @@
         </is>
       </c>
       <c r="F66" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I66" s="12" t="n">
         <v>21</v>
       </c>
       <c r="J66" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K66" s="12" t="n">
         <v>2</v>
@@ -4108,10 +4108,10 @@
         <v>1</v>
       </c>
       <c r="M66" s="12" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="N66" s="12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
@@ -4146,19 +4146,19 @@
         </is>
       </c>
       <c r="F67" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G67" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H67" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I67" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J67" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K67" s="12" t="n">
         <v>3</v>
@@ -4174,7 +4174,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -4205,35 +4205,35 @@
         </is>
       </c>
       <c r="F68" s="12" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G68" s="12" t="n">
         <v>28</v>
       </c>
       <c r="H68" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I68" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J68" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K68" s="12" t="n">
         <v>4</v>
       </c>
       <c r="L68" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M68" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="N68" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -4264,19 +4264,19 @@
         </is>
       </c>
       <c r="F69" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="H69" s="12" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I69" s="12" t="n">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="J69" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K69" s="12" t="n">
         <v>0</v>
@@ -4285,10 +4285,10 @@
         <v>6</v>
       </c>
       <c r="M69" s="12" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="N69" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
@@ -4299,17 +4299,17 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>01578</t>
+          <t>02074</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>VERDELLO</t>
+          <t>GOITO</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>S S 42</t>
+          <t>S.S. N. 236 KM 14+332</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -4319,56 +4319,56 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="F70" s="12" t="n">
         <v>13</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="H70" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I70" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J70" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K70" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="L70" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M70" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="N70" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="L70" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="M70" s="12" t="n">
-        <v>29</v>
-      </c>
-      <c r="N70" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>01671</t>
+          <t>01578</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA</t>
+          <t>VERDELLO</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>VIALE BORNATA</t>
+          <t>S S 42</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -4378,39 +4378,39 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>GRAZIOSI DAVIDE</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="F71" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>13</v>
+        <v>73</v>
       </c>
       <c r="H71" s="12" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="I71" s="12" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="J71" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K71" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L71" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M71" s="12" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="N71" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="F72" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G72" s="12" t="n">
         <v>0</v>
@@ -4453,7 +4453,7 @@
         <v>0</v>
       </c>
       <c r="J72" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K72" s="12" t="n">
         <v>0</v>
@@ -4476,17 +4476,17 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>02074</t>
+          <t>01671</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>GOITO</t>
+          <t>BRESCIA</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>S.S. N. 236 KM 14+332</t>
+          <t>VIALE BORNATA</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -4496,39 +4496,39 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
       <c r="F73" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H73" s="12" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I73" s="12" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="J73" s="12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K73" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L73" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M73" s="12" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="N73" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/Agente - Marcelli Emanuele.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Marcelli Emanuele.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W22</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>64</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>8829</v>
+        <v>9107</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>6151</v>
+        <v>6352</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>3227</v>
+        <v>3358</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>877</v>
+        <v>907</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>652</v>
+        <v>672</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>559</v>
+        <v>577</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>762</v>
+        <v>797</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,35 +901,35 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>590</v>
+        <v>618</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>398</v>
+        <v>419</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>391</v>
+        <v>410</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -960,31 +960,31 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>637</v>
+        <v>653</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>304</v>
+        <v>321</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>310</v>
+        <v>325</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1019,35 +1019,35 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>435</v>
+        <v>470</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>338</v>
+        <v>351</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>286</v>
+        <v>304</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>376</v>
+        <v>404</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1078,31 +1078,31 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>414</v>
+        <v>428</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>560</v>
+        <v>588</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>577</v>
+        <v>605</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1137,31 +1137,31 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>616</v>
+        <v>633</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="L16" s="12" t="n">
         <v>100</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>467</v>
+        <v>490</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1196,31 +1196,31 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>443</v>
+        <v>465</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>560</v>
+        <v>585</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L17" s="12" t="n">
         <v>81</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>345</v>
+        <v>364</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1255,31 +1255,31 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>456</v>
+        <v>472</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1314,31 +1314,31 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>291</v>
+        <v>301</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -1373,35 +1373,35 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K20" s="12" t="n">
         <v>91</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="N20" s="12" t="n">
         <v>22</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1432,31 +1432,31 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>293</v>
+        <v>312</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1467,17 +1467,17 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>01638</t>
+          <t>01032</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>GRUMELLO DEL MONTE</t>
+          <t>GENOVA</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>VIA LEGA LOMBARDA 2</t>
+          <t>VIA BRIGATE PARTIGIANE, 1/R</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1487,35 +1487,35 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>DALLORTO ILARIA</t>
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>347</v>
+        <v>296</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>1</v>
+        <v>87</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>7</v>
+        <v>69</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>90</v>
+        <v>166</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>132</v>
+        <v>64</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>267</v>
+        <v>534</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1526,17 +1526,17 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>01032</t>
+          <t>01638</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>GENOVA</t>
+          <t>GRUMELLO DEL MONTE</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>VIA BRIGATE PARTIGIANE, 1/R</t>
+          <t>VIA LEGA LOMBARDA 2</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1546,35 +1546,35 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>DALLORTO ILARIA</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>287</v>
+        <v>368</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>82</v>
+        <v>1</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>69</v>
+        <v>7</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>160</v>
+        <v>90</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>62</v>
+        <v>132</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>512</v>
+        <v>267</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -1609,13 +1609,13 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
+        <v>218</v>
+      </c>
+      <c r="G24" s="12" t="n">
         <v>215</v>
       </c>
-      <c r="G24" s="12" t="n">
-        <v>201</v>
-      </c>
       <c r="H24" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I24" s="12" t="n">
         <v>8</v>
@@ -1627,17 +1627,17 @@
         <v>29</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="N24" s="12" t="n">
         <v>8</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1668,28 +1668,28 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="N25" s="12" t="n">
         <v>28</v>
@@ -1727,31 +1727,31 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>288</v>
+        <v>305</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1786,31 +1786,31 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="I27" s="12" t="n">
         <v>10</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
@@ -1845,10 +1845,10 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="H28" s="12" t="n">
         <v>5</v>
@@ -1857,7 +1857,7 @@
         <v>10</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="K28" s="12" t="n">
         <v>23</v>
@@ -1866,10 +1866,10 @@
         <v>55</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -1904,31 +1904,31 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>322</v>
+        <v>338</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
@@ -1939,17 +1939,17 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>01525</t>
+          <t>55496</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>GAZZANIGA</t>
+          <t>MOZZO</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>CESARE BATTISTI</t>
+          <t>SS 470 KM 5 0000</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1963,31 +1963,31 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>216</v>
+        <v>193</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>53</v>
+        <v>8</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>73</v>
+        <v>8</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>89</v>
+        <v>145</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -1998,17 +1998,17 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>02036</t>
+          <t>01525</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>CREMONA</t>
+          <t>GAZZANIGA</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>VIA CASTELLEONE, 47</t>
+          <t>CESARE BATTISTI</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -2018,35 +2018,35 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>148</v>
+        <v>227</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>177</v>
+        <v>53</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>324</v>
+        <v>79</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="L31" s="12" t="n">
+        <v>60</v>
+      </c>
+      <c r="M31" s="12" t="n">
+        <v>89</v>
+      </c>
+      <c r="N31" s="12" t="n">
         <v>19</v>
-      </c>
-      <c r="M31" s="12" t="n">
-        <v>210</v>
-      </c>
-      <c r="N31" s="12" t="n">
-        <v>72</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
@@ -2057,17 +2057,17 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>55496</t>
+          <t>02036</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>MOZZO</t>
+          <t>CREMONA</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>SS 470 KM 5 0000</t>
+          <t>VIA CASTELLEONE, 47</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2077,35 +2077,35 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>186</v>
+        <v>155</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>6</v>
+        <v>182</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>8</v>
+        <v>333</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>66</v>
+        <v>118</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>69</v>
+        <v>19</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
@@ -2116,17 +2116,17 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>51674</t>
+          <t>01574</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>CARAVAGGIO</t>
+          <t>TREVIGLIO</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>SS 11 PADANA SUPERIORE KM. 182+719</t>
+          <t>VIALE MANZONI, 11</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2140,52 +2140,52 @@
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>248</v>
+        <v>1</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>106</v>
+        <v>169</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>01574</t>
+          <t>51674</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>TREVIGLIO</t>
+          <t>CARAVAGGIO</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>VIALE MANZONI, 11</t>
+          <t>SS 11 PADANA SUPERIORE KM. 182+719</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2199,35 +2199,35 @@
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>1</v>
+        <v>263</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>157</v>
+        <v>106</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2258,35 +2258,35 @@
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="H35" s="12" t="n">
         <v>23</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L35" s="12" t="n">
         <v>40</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2320,13 +2320,13 @@
         <v>108</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="H36" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J36" s="12" t="n">
         <v>77</v>
@@ -2352,17 +2352,17 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>01007</t>
+          <t>51037</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>CHIAVARI</t>
+          <t>ACQUI TERME</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>CORSO GENOVA 40</t>
+          <t>VIA NIZZA 152</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2372,56 +2372,56 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>DELUGAS NADIA</t>
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="K37" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="L37" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="M37" s="12" t="n">
+        <v>110</v>
+      </c>
+      <c r="N37" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="L37" s="12" t="n">
-        <v>46</v>
-      </c>
-      <c r="M37" s="12" t="n">
-        <v>228</v>
-      </c>
-      <c r="N37" s="12" t="n">
-        <v>56</v>
-      </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>51037</t>
+          <t>01007</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>ACQUI TERME</t>
+          <t>CHIAVARI</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>VIA NIZZA 152</t>
+          <t>CORSO GENOVA 40</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -2431,35 +2431,35 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>DELUGAS NADIA</t>
+          <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>118</v>
+        <v>0</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>101</v>
+        <v>236</v>
       </c>
       <c r="N38" s="12" t="n">
-        <v>9</v>
+        <v>56</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
@@ -2494,10 +2494,10 @@
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="H39" s="12" t="n">
         <v>9</v>
@@ -2506,16 +2506,16 @@
         <v>15</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="N39" s="12" t="n">
         <v>2</v>
@@ -2553,19 +2553,19 @@
         </is>
       </c>
       <c r="F40" s="12" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="I40" s="12" t="n">
         <v>13</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K40" s="12" t="n">
         <v>3</v>
@@ -2574,10 +2574,10 @@
         <v>36</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="N40" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
@@ -2612,28 +2612,28 @@
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I41" s="12" t="n">
         <v>12</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L41" s="12" t="n">
         <v>23</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="N41" s="12" t="n">
         <v>26</v>
@@ -2647,17 +2647,17 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>12112</t>
+          <t>01971</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>MANTOVA</t>
+          <t>CREMONA</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>VIA FRANCESCO VAINI</t>
+          <t>VIA BERGAMO 47</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -2667,56 +2667,56 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="F42" s="12" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I42" s="12" t="n">
         <v>8</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="K42" s="12" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>57</v>
+        <v>99</v>
       </c>
       <c r="N42" s="12" t="n">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>01971</t>
+          <t>12112</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>CREMONA</t>
+          <t>MANTOVA</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>VIA BERGAMO 47</t>
+          <t>VIA FRANCESCO VAINI</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -2726,56 +2726,56 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="F43" s="12" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I43" s="12" t="n">
         <v>8</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>94</v>
+        <v>60</v>
       </c>
       <c r="N43" s="12" t="n">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>51570</t>
+          <t>01637</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>VENTIMIGLIA</t>
+          <t>CURNO</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>CSO LIMONE PIEMONTE 1</t>
+          <t>SS671 VALSERIANA  KM0,9820</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -2785,35 +2785,35 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>BARNABA SALVATORE</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="F44" s="12" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H44" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="I44" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="I44" s="12" t="n">
-        <v>47</v>
-      </c>
       <c r="J44" s="12" t="n">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>56</v>
+        <v>90</v>
       </c>
       <c r="N44" s="12" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
@@ -2824,17 +2824,17 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>01637</t>
+          <t>51570</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>CURNO</t>
+          <t>VENTIMIGLIA</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>SS671 VALSERIANA  KM0,9820</t>
+          <t>CSO LIMONE PIEMONTE 1</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -2844,35 +2844,35 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>BARNABA SALVATORE</t>
         </is>
       </c>
       <c r="F45" s="12" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="K45" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>88</v>
+        <v>61</v>
       </c>
       <c r="N45" s="12" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
@@ -2907,28 +2907,28 @@
         </is>
       </c>
       <c r="F46" s="12" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K46" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L46" s="12" t="n">
         <v>19</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="N46" s="12" t="n">
         <v>4</v>
@@ -2966,10 +2966,10 @@
         </is>
       </c>
       <c r="F47" s="12" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H47" s="12" t="n">
         <v>9</v>
@@ -2978,7 +2978,7 @@
         <v>18</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K47" s="12" t="n">
         <v>10</v>
@@ -2987,10 +2987,10 @@
         <v>20</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="N47" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
@@ -3025,31 +3025,31 @@
         </is>
       </c>
       <c r="F48" s="12" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I48" s="12" t="n">
         <v>8</v>
       </c>
       <c r="J48" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K48" s="12" t="n">
         <v>11</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="M48" s="12" t="n">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="N48" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
@@ -3084,31 +3084,31 @@
         </is>
       </c>
       <c r="F49" s="12" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="I49" s="12" t="n">
         <v>21</v>
       </c>
       <c r="J49" s="12" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K49" s="12" t="n">
         <v>10</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M49" s="12" t="n">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="N49" s="12" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
@@ -3119,17 +3119,17 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>59894</t>
+          <t>11719</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA</t>
+          <t>MONTICHIARI</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>V. DE GASP./TANG. S KM 6+930</t>
+          <t>S.S. 668 - VIA GHEDI</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -3139,35 +3139,35 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>SALVINELLI LUCA</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="F50" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="G50" s="12" t="n">
+        <v>55</v>
+      </c>
+      <c r="H50" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="I50" s="12" t="n">
+        <v>120</v>
+      </c>
+      <c r="J50" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="K50" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L50" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="M50" s="12" t="n">
         <v>49</v>
       </c>
-      <c r="G50" s="12" t="n">
-        <v>75</v>
-      </c>
-      <c r="H50" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="I50" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="J50" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="K50" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="L50" s="12" t="n">
-        <v>27</v>
-      </c>
-      <c r="M50" s="12" t="n">
-        <v>35</v>
-      </c>
       <c r="N50" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
@@ -3178,17 +3178,17 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>02075</t>
+          <t>12082</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>SUZZARA</t>
+          <t>VIADANA</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>S.S. N. 62 CISA - LOCALITA' CROCILE C.M.</t>
+          <t>S.S. 358  KM 22+202</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -3202,52 +3202,52 @@
         </is>
       </c>
       <c r="F51" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="H51" s="12" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="I51" s="12" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="J51" s="12" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="K51" s="12" t="n">
         <v>12</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M51" s="12" t="n">
-        <v>69</v>
+        <v>19</v>
       </c>
       <c r="N51" s="12" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>11719</t>
+          <t>59894</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>MONTICHIARI</t>
+          <t>BRESCIA</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>S.S. 668 - VIA GHEDI</t>
+          <t>V. DE GASP./TANG. S KM 6+930</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -3257,35 +3257,35 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>SALVINELLI LUCA</t>
         </is>
       </c>
       <c r="F52" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>116</v>
+        <v>5</v>
       </c>
       <c r="J52" s="12" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="K52" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="L52" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="M52" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="N52" s="12" t="n">
         <v>1</v>
-      </c>
-      <c r="L52" s="12" t="n">
-        <v>30</v>
-      </c>
-      <c r="M52" s="12" t="n">
-        <v>47</v>
-      </c>
-      <c r="N52" s="12" t="n">
-        <v>0</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
@@ -3296,17 +3296,17 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>01334</t>
+          <t>02075</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>FINALE LIGURE</t>
+          <t>SUZZARA</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>VIA MAZZINI</t>
+          <t>S.S. N. 62 CISA - LOCALITA' CROCILE C.M.</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -3316,39 +3316,39 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>BARNABA SALVATORE</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="F53" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="H53" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="I53" s="12" t="n">
+        <v>65</v>
+      </c>
+      <c r="J53" s="12" t="n">
         <v>49</v>
       </c>
-      <c r="I53" s="12" t="n">
-        <v>50</v>
-      </c>
-      <c r="J53" s="12" t="n">
-        <v>34</v>
-      </c>
       <c r="K53" s="12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="M53" s="12" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="N53" s="12" t="n">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -3379,10 +3379,10 @@
         </is>
       </c>
       <c r="F54" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H54" s="12" t="n">
         <v>3</v>
@@ -3391,19 +3391,19 @@
         <v>1</v>
       </c>
       <c r="J54" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K54" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L54" s="12" t="n">
         <v>12</v>
       </c>
       <c r="M54" s="12" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N54" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
@@ -3414,17 +3414,17 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>11726</t>
+          <t>01334</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>REZZATO</t>
+          <t>FINALE LIGURE</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>S.S.45 KM.49+300</t>
+          <t>VIA MAZZINI</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -3434,56 +3434,56 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>GRAZIOSI DAVIDE</t>
+          <t>BARNABA SALVATORE</t>
         </is>
       </c>
       <c r="F55" s="12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="H55" s="12" t="n">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="I55" s="12" t="n">
-        <v>4</v>
+        <v>56</v>
       </c>
       <c r="J55" s="12" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="K55" s="12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="M55" s="12" t="n">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="N55" s="12" t="n">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>12082</t>
+          <t>11726</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>VIADANA</t>
+          <t>REZZATO</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>S.S. 358  KM 22+202</t>
+          <t>S.S.45 KM.49+300</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -3493,39 +3493,39 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
       <c r="F56" s="12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J56" s="12" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="K56" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="M56" s="12" t="n">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="N56" s="12" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -3559,7 +3559,7 @@
         <v>43</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="H57" s="12" t="n">
         <v>30</v>
@@ -3577,7 +3577,7 @@
         <v>16</v>
       </c>
       <c r="M57" s="12" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="N57" s="12" t="n">
         <v>3</v>
@@ -3618,7 +3618,7 @@
         <v>42</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H58" s="12" t="n">
         <v>11</v>
@@ -3636,14 +3636,14 @@
         <v>12</v>
       </c>
       <c r="M58" s="12" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="N58" s="12" t="n">
         <v>10</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
         </is>
       </c>
       <c r="F59" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G59" s="12" t="n">
         <v>0</v>
@@ -3686,7 +3686,7 @@
         <v>0</v>
       </c>
       <c r="J59" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K59" s="12" t="n">
         <v>9</v>
@@ -3695,14 +3695,14 @@
         <v>14</v>
       </c>
       <c r="M59" s="12" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="N59" s="12" t="n">
         <v>6</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -3733,10 +3733,10 @@
         </is>
       </c>
       <c r="F60" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="H60" s="12" t="n">
         <v>3</v>
@@ -3745,16 +3745,16 @@
         <v>1</v>
       </c>
       <c r="J60" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K60" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L60" s="12" t="n">
         <v>23</v>
       </c>
       <c r="M60" s="12" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="N60" s="12" t="n">
         <v>2</v>
@@ -3792,19 +3792,19 @@
         </is>
       </c>
       <c r="F61" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="H61" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I61" s="12" t="n">
         <v>3</v>
       </c>
       <c r="J61" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K61" s="12" t="n">
         <v>5</v>
@@ -3813,7 +3813,7 @@
         <v>2</v>
       </c>
       <c r="M61" s="12" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="N61" s="12" t="n">
         <v>0</v>
@@ -3827,17 +3827,17 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>02004</t>
+          <t>52510</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>RIVOLTA D'ADDA</t>
+          <t>PORTO MANTOVANO</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>VIA GIUSEPPE DI VITTORIO 17</t>
+          <t>SR CISA 4 S. ANTONIO</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -3847,56 +3847,56 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="F62" s="12" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J62" s="12" t="n">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="K62" s="12" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="L62" s="12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M62" s="12" t="n">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="N62" s="12" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>52510</t>
+          <t>02004</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>PORTO MANTOVANO</t>
+          <t>RIVOLTA D'ADDA</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>SR CISA 4 S. ANTONIO</t>
+          <t>VIA GIUSEPPE DI VITTORIO 17</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -3906,39 +3906,39 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="F63" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="H63" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I63" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J63" s="12" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="K63" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="L63" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="L63" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="M63" s="12" t="n">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="N63" s="12" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -3969,7 +3969,7 @@
         </is>
       </c>
       <c r="F64" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G64" s="12" t="n">
         <v>47</v>
@@ -3978,10 +3978,10 @@
         <v>26</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="J64" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K64" s="12" t="n">
         <v>1</v>
@@ -3990,7 +3990,7 @@
         <v>14</v>
       </c>
       <c r="M64" s="12" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="N64" s="12" t="n">
         <v>5</v>
@@ -4028,31 +4028,31 @@
         </is>
       </c>
       <c r="F65" s="12" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H65" s="12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I65" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J65" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K65" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="L65" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="L65" s="12" t="n">
-        <v>6</v>
-      </c>
       <c r="M65" s="12" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N65" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
@@ -4087,31 +4087,31 @@
         </is>
       </c>
       <c r="F66" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I66" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J66" s="12" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K66" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L66" s="12" t="n">
         <v>1</v>
       </c>
       <c r="M66" s="12" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="N66" s="12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
@@ -4146,19 +4146,19 @@
         </is>
       </c>
       <c r="F67" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G67" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H67" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I67" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J67" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K67" s="12" t="n">
         <v>3</v>
@@ -4167,10 +4167,10 @@
         <v>4</v>
       </c>
       <c r="M67" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="N67" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
@@ -4208,13 +4208,13 @@
         <v>20</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H68" s="12" t="n">
         <v>19</v>
       </c>
       <c r="I68" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J68" s="12" t="n">
         <v>17</v>
@@ -4233,7 +4233,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -4267,13 +4267,13 @@
         <v>18</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="H69" s="12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I69" s="12" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="J69" s="12" t="n">
         <v>12</v>
@@ -4285,7 +4285,7 @@
         <v>6</v>
       </c>
       <c r="M69" s="12" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="N69" s="12" t="n">
         <v>1</v>
@@ -4323,7 +4323,7 @@
         </is>
       </c>
       <c r="F70" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G70" s="12" t="n">
         <v>0</v>
@@ -4335,7 +4335,7 @@
         <v>0</v>
       </c>
       <c r="J70" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K70" s="12" t="n">
         <v>5</v>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -4385,7 +4385,7 @@
         <v>13</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H71" s="12" t="n">
         <v>1</v>
@@ -4462,14 +4462,14 @@
         <v>0</v>
       </c>
       <c r="M72" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="N72" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="N72" s="12" t="n">
-        <v>12</v>
-      </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -4503,13 +4503,13 @@
         <v>11</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H73" s="12" t="n">
         <v>30</v>
       </c>
       <c r="I73" s="12" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J73" s="12" t="n">
         <v>8</v>

--- a/docs/files/REPORT_FILTRI/Agente - Marcelli Emanuele.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Marcelli Emanuele.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W22</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>64</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>9107</v>
+        <v>9487</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>6352</v>
+        <v>6649</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>3358</v>
+        <v>3538</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,35 +842,35 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>907</v>
+        <v>950</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>672</v>
+        <v>689</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>577</v>
+        <v>602</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>335</v>
+        <v>353</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>797</v>
+        <v>848</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -901,35 +901,35 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>618</v>
+        <v>649</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>269</v>
+        <v>282</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>419</v>
+        <v>441</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>410</v>
+        <v>443</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -960,35 +960,35 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>520</v>
+        <v>543</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>291</v>
+        <v>308</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>653</v>
+        <v>672</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>321</v>
+        <v>350</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>359</v>
+        <v>380</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>325</v>
+        <v>342</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1019,35 +1019,35 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>470</v>
+        <v>489</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>351</v>
+        <v>366</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>404</v>
+        <v>432</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1078,31 +1078,31 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>428</v>
+        <v>458</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>588</v>
+        <v>620</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>330</v>
+        <v>354</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>605</v>
+        <v>643</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1137,31 +1137,31 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>386</v>
+        <v>401</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>633</v>
+        <v>673</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>490</v>
+        <v>513</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1196,31 +1196,31 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>378</v>
+        <v>398</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>465</v>
+        <v>488</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>386</v>
+        <v>400</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>585</v>
+        <v>622</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>299</v>
+        <v>318</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>364</v>
+        <v>383</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1255,31 +1255,31 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>331</v>
+        <v>349</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>472</v>
+        <v>501</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>277</v>
+        <v>291</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1314,31 +1314,31 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>301</v>
+        <v>316</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="L19" s="12" t="n">
         <v>51</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -1373,35 +1373,35 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1432,31 +1432,31 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I21" s="12" t="n">
         <v>40</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>312</v>
+        <v>328</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1491,31 +1491,31 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="L22" s="12" t="n">
         <v>64</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>534</v>
+        <v>557</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1526,17 +1526,17 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>01638</t>
+          <t>01527</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>GRUMELLO DEL MONTE</t>
+          <t>DALMINE</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>VIA LEGA LOMBARDA 2</t>
+          <t>STRADA PROVINCIALE 84</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1546,56 +1546,56 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>368</v>
+        <v>230</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>132</v>
+        <v>113</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>267</v>
+        <v>229</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>01527</t>
+          <t>01638</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>DALMINE</t>
+          <t>GRUMELLO DEL MONTE</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>STRADA PROVINCIALE 84</t>
+          <t>VIA LEGA LOMBARDA 2</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1605,39 +1605,39 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>215</v>
+        <v>387</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>116</v>
+        <v>90</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>215</v>
+        <v>267</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1668,31 +1668,31 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="L25" s="12" t="n">
         <v>44</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>215</v>
+        <v>231</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1727,31 +1727,31 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>246</v>
+        <v>260</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="L26" s="12" t="n">
         <v>54</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>305</v>
+        <v>324</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1786,31 +1786,31 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="L27" s="12" t="n">
         <v>27</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
@@ -1845,31 +1845,31 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I28" s="12" t="n">
         <v>10</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>229</v>
+        <v>242</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -1880,17 +1880,17 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>01034</t>
+          <t>55496</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>GENOVA</t>
+          <t>MOZZO</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>LUNGOBISAGNO D'ISTRIA</t>
+          <t>SS 470 KM 5 0000</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1900,56 +1900,56 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>DALLORTO ILARIA</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>153</v>
+        <v>204</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>134</v>
+        <v>9</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>338</v>
+        <v>8</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>176</v>
+        <v>154</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>55496</t>
+          <t>01034</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>MOZZO</t>
+          <t>GENOVA</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>SS 470 KM 5 0000</t>
+          <t>LUNGOBISAGNO D'ISTRIA</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1959,35 +1959,35 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>DALLORTO ILARIA</t>
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>193</v>
+        <v>161</v>
       </c>
       <c r="H30" s="12" t="n">
+        <v>137</v>
+      </c>
+      <c r="I30" s="12" t="n">
+        <v>350</v>
+      </c>
+      <c r="J30" s="12" t="n">
+        <v>92</v>
+      </c>
+      <c r="K30" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="L30" s="12" t="n">
+        <v>57</v>
+      </c>
+      <c r="M30" s="12" t="n">
+        <v>185</v>
+      </c>
+      <c r="N30" s="12" t="n">
         <v>8</v>
-      </c>
-      <c r="I30" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="J30" s="12" t="n">
-        <v>74</v>
-      </c>
-      <c r="K30" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="L30" s="12" t="n">
-        <v>70</v>
-      </c>
-      <c r="M30" s="12" t="n">
-        <v>145</v>
-      </c>
-      <c r="N30" s="12" t="n">
-        <v>25</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -1998,17 +1998,17 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>01525</t>
+          <t>02036</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>GAZZANIGA</t>
+          <t>CREMONA</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>CESARE BATTISTI</t>
+          <t>VIA CASTELLEONE, 47</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -2018,35 +2018,35 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>227</v>
+        <v>164</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>53</v>
+        <v>192</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>79</v>
+        <v>350</v>
       </c>
       <c r="J31" s="12" t="n">
+        <v>123</v>
+      </c>
+      <c r="K31" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="L31" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="M31" s="12" t="n">
+        <v>223</v>
+      </c>
+      <c r="N31" s="12" t="n">
         <v>80</v>
-      </c>
-      <c r="K31" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="L31" s="12" t="n">
-        <v>60</v>
-      </c>
-      <c r="M31" s="12" t="n">
-        <v>89</v>
-      </c>
-      <c r="N31" s="12" t="n">
-        <v>19</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
@@ -2057,17 +2057,17 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>02036</t>
+          <t>01574</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>CREMONA</t>
+          <t>TREVIGLIO</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>VIA CASTELLEONE, 47</t>
+          <t>VIALE MANZONI, 11</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2077,56 +2077,56 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>155</v>
+        <v>1</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>182</v>
+        <v>15</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>333</v>
+        <v>0</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>215</v>
+        <v>183</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>74</v>
+        <v>14</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>01574</t>
+          <t>01525</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>TREVIGLIO</t>
+          <t>GAZZANIGA</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>VIALE MANZONI, 11</t>
+          <t>CESARE BATTISTI</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2136,56 +2136,56 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>1</v>
+        <v>241</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>9</v>
+        <v>53</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>169</v>
+        <v>89</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>51674</t>
+          <t>01043</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>CARAVAGGIO</t>
+          <t>GENOVA</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>SS 11 PADANA SUPERIORE KM. 182+719</t>
+          <t>VIA RIGHETTI 1 R</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2195,56 +2195,56 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>DALLORTO ILARIA</t>
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>263</v>
+        <v>144</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="L34" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="M34" s="12" t="n">
+        <v>205</v>
+      </c>
+      <c r="N34" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="M34" s="12" t="n">
-        <v>106</v>
-      </c>
-      <c r="N34" s="12" t="n">
-        <v>39</v>
-      </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>01043</t>
+          <t>51674</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>GENOVA</t>
+          <t>CARAVAGGIO</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>VIA RIGHETTI 1 R</t>
+          <t>SS 11 PADANA SUPERIORE KM. 182+719</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2254,39 +2254,39 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>DALLORTO ILARIA</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>131</v>
+        <v>276</v>
       </c>
       <c r="H35" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I35" s="12" t="n">
+        <v>51</v>
+      </c>
+      <c r="J35" s="12" t="n">
+        <v>99</v>
+      </c>
+      <c r="K35" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="L35" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="I35" s="12" t="n">
-        <v>27</v>
-      </c>
-      <c r="J35" s="12" t="n">
-        <v>79</v>
-      </c>
-      <c r="K35" s="12" t="n">
-        <v>29</v>
-      </c>
-      <c r="L35" s="12" t="n">
-        <v>40</v>
-      </c>
       <c r="M35" s="12" t="n">
-        <v>194</v>
+        <v>106</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2320,13 +2320,13 @@
         <v>108</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="H36" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J36" s="12" t="n">
         <v>77</v>
@@ -2352,17 +2352,17 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>51037</t>
+          <t>01378</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>ACQUI TERME</t>
+          <t>CARCARE</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>VIA NIZZA 152</t>
+          <t>VIA VITTORIO VENETO 52</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2376,52 +2376,52 @@
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="N37" s="12" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>01007</t>
+          <t>51037</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>CHIAVARI</t>
+          <t>ACQUI TERME</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>CORSO GENOVA 40</t>
+          <t>VIA NIZZA 152</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -2431,56 +2431,56 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>DELUGAS NADIA</t>
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="K38" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="L38" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="M38" s="12" t="n">
+        <v>116</v>
+      </c>
+      <c r="N38" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="L38" s="12" t="n">
-        <v>46</v>
-      </c>
-      <c r="M38" s="12" t="n">
-        <v>236</v>
-      </c>
-      <c r="N38" s="12" t="n">
-        <v>56</v>
-      </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>01378</t>
+          <t>01007</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>CARCARE</t>
+          <t>CHIAVARI</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>VIA VITTORIO VENETO 52</t>
+          <t>CORSO GENOVA 40</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -2490,39 +2490,39 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>DELUGAS NADIA</t>
+          <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>127</v>
+        <v>0</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>88</v>
+        <v>250</v>
       </c>
       <c r="N39" s="12" t="n">
-        <v>2</v>
+        <v>57</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2553,19 +2553,19 @@
         </is>
       </c>
       <c r="F40" s="12" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K40" s="12" t="n">
         <v>3</v>
@@ -2574,7 +2574,7 @@
         <v>36</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="N40" s="12" t="n">
         <v>3</v>
@@ -2612,10 +2612,10 @@
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="H41" s="12" t="n">
         <v>9</v>
@@ -2624,7 +2624,7 @@
         <v>12</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K41" s="12" t="n">
         <v>27</v>
@@ -2633,7 +2633,7 @@
         <v>23</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="N41" s="12" t="n">
         <v>26</v>
@@ -2671,31 +2671,31 @@
         </is>
       </c>
       <c r="F42" s="12" t="n">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I42" s="12" t="n">
         <v>8</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="K42" s="12" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="N42" s="12" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>72</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="H43" s="12" t="n">
         <v>1</v>
@@ -2751,10 +2751,10 @@
         <v>6</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="N43" s="12" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
@@ -2765,17 +2765,17 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>01637</t>
+          <t>51570</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>CURNO</t>
+          <t>VENTIMIGLIA</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>SS671 VALSERIANA  KM0,9820</t>
+          <t>CSO LIMONE PIEMONTE 1</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -2785,35 +2785,35 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>BARNABA SALVATORE</t>
         </is>
       </c>
       <c r="F44" s="12" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="N44" s="12" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
@@ -2824,17 +2824,17 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>51570</t>
+          <t>01637</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>VENTIMIGLIA</t>
+          <t>CURNO</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>CSO LIMONE PIEMONTE 1</t>
+          <t>SS671 VALSERIANA  KM0,9820</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -2844,35 +2844,35 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>BARNABA SALVATORE</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="F45" s="12" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="K45" s="12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="N45" s="12" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
@@ -2907,35 +2907,35 @@
         </is>
       </c>
       <c r="F46" s="12" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K46" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="N46" s="12" t="n">
         <v>4</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2969,13 +2969,13 @@
         <v>62</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="H47" s="12" t="n">
         <v>9</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J47" s="12" t="n">
         <v>42</v>
@@ -2987,10 +2987,10 @@
         <v>20</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="N47" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
@@ -3001,17 +3001,17 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>54151</t>
+          <t>01142</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>IMPERIA</t>
+          <t>SESTRI LEVANTE</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>SS 28 KM 136 + 600</t>
+          <t>VIA BRUNO PRIMI, 14</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -3021,35 +3021,35 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>BARNABA SALVATORE</t>
+          <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
       <c r="F48" s="12" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="J48" s="12" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="K48" s="12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="M48" s="12" t="n">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="N48" s="12" t="n">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
@@ -3060,17 +3060,17 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>01142</t>
+          <t>54151</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>SESTRI LEVANTE</t>
+          <t>IMPERIA</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>VIA BRUNO PRIMI, 14</t>
+          <t>SS 28 KM 136 + 600</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -3080,35 +3080,35 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>BARNABA SALVATORE</t>
         </is>
       </c>
       <c r="F49" s="12" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="I49" s="12" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="J49" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K49" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="M49" s="12" t="n">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="N49" s="12" t="n">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
@@ -3146,13 +3146,13 @@
         <v>50</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H50" s="12" t="n">
         <v>40</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="J50" s="12" t="n">
         <v>17</v>
@@ -3164,7 +3164,7 @@
         <v>33</v>
       </c>
       <c r="M50" s="12" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="N50" s="12" t="n">
         <v>0</v>
@@ -3178,17 +3178,17 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>12082</t>
+          <t>02075</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>VIADANA</t>
+          <t>SUZZARA</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>S.S. 358  KM 22+202</t>
+          <t>S.S. N. 62 CISA - LOCALITA' CROCILE C.M.</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -3205,49 +3205,49 @@
         <v>49</v>
       </c>
       <c r="G51" s="12" t="n">
+        <v>79</v>
+      </c>
+      <c r="H51" s="12" t="n">
+        <v>37</v>
+      </c>
+      <c r="I51" s="12" t="n">
+        <v>70</v>
+      </c>
+      <c r="J51" s="12" t="n">
+        <v>51</v>
+      </c>
+      <c r="K51" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="L51" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H51" s="12" t="n">
-        <v>44</v>
-      </c>
-      <c r="I51" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" s="12" t="n">
-        <v>42</v>
-      </c>
-      <c r="K51" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="L51" s="12" t="n">
-        <v>7</v>
-      </c>
       <c r="M51" s="12" t="n">
-        <v>19</v>
+        <v>79</v>
       </c>
       <c r="N51" s="12" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>59894</t>
+          <t>12082</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA</t>
+          <t>VIADANA</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>V. DE GASP./TANG. S KM 6+930</t>
+          <t>S.S. 358  KM 22+202</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -3257,35 +3257,35 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>SALVINELLI LUCA</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="F52" s="12" t="n">
         <v>49</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J52" s="12" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="K52" s="12" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="M52" s="12" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="N52" s="12" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
@@ -3296,17 +3296,17 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>02075</t>
+          <t>01334</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>SUZZARA</t>
+          <t>FINALE LIGURE</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>S.S. N. 62 CISA - LOCALITA' CROCILE C.M.</t>
+          <t>VIA MAZZINI</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -3316,35 +3316,35 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>BARNABA SALVATORE</t>
         </is>
       </c>
       <c r="F53" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="H53" s="12" t="n">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="I53" s="12" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J53" s="12" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="K53" s="12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M53" s="12" t="n">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="N53" s="12" t="n">
-        <v>1</v>
+        <v>58</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
@@ -3379,10 +3379,10 @@
         </is>
       </c>
       <c r="F54" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="H54" s="12" t="n">
         <v>3</v>
@@ -3391,16 +3391,16 @@
         <v>1</v>
       </c>
       <c r="J54" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K54" s="12" t="n">
         <v>9</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M54" s="12" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="N54" s="12" t="n">
         <v>1</v>
@@ -3414,17 +3414,17 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>01334</t>
+          <t>59894</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>FINALE LIGURE</t>
+          <t>BRESCIA</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>VIA MAZZINI</t>
+          <t>V. DE GASP./TANG. S KM 6+930</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -3434,35 +3434,35 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>BARNABA SALVATORE</t>
+          <t>SALVINELLI LUCA</t>
         </is>
       </c>
       <c r="F55" s="12" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>64</v>
+        <v>85</v>
       </c>
       <c r="H55" s="12" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="I55" s="12" t="n">
-        <v>56</v>
+        <v>7</v>
       </c>
       <c r="J55" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="K55" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="L55" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="M55" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="K55" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="L55" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="M55" s="12" t="n">
-        <v>80</v>
-      </c>
       <c r="N55" s="12" t="n">
-        <v>55</v>
+        <v>1</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
@@ -3473,17 +3473,17 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>11726</t>
+          <t>56297</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>REZZATO</t>
+          <t>SAN PAOLO D'ARGON</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>S.S.45 KM.49+300</t>
+          <t>SS 42</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -3493,39 +3493,39 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>GRAZIOSI DAVIDE</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="F56" s="12" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J56" s="12" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="K56" s="12" t="n">
         <v>10</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="M56" s="12" t="n">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="N56" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -3556,19 +3556,19 @@
         </is>
       </c>
       <c r="F57" s="12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="H57" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I57" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J57" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K57" s="12" t="n">
         <v>8</v>
@@ -3577,7 +3577,7 @@
         <v>16</v>
       </c>
       <c r="M57" s="12" t="n">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="N57" s="12" t="n">
         <v>3</v>
@@ -3615,19 +3615,19 @@
         </is>
       </c>
       <c r="F58" s="12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J58" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K58" s="12" t="n">
         <v>14</v>
@@ -3650,17 +3650,17 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>56297</t>
+          <t>11726</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>SAN PAOLO D'ARGON</t>
+          <t>REZZATO</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>SS 42</t>
+          <t>S.S.45 KM.49+300</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -3670,39 +3670,39 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
       <c r="F59" s="12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="H59" s="12" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="I59" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J59" s="12" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="K59" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="M59" s="12" t="n">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="N59" s="12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -3733,10 +3733,10 @@
         </is>
       </c>
       <c r="F60" s="12" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="H60" s="12" t="n">
         <v>3</v>
@@ -3745,7 +3745,7 @@
         <v>1</v>
       </c>
       <c r="J60" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K60" s="12" t="n">
         <v>4</v>
@@ -3754,14 +3754,14 @@
         <v>23</v>
       </c>
       <c r="M60" s="12" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="N60" s="12" t="n">
         <v>2</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -3792,19 +3792,19 @@
         </is>
       </c>
       <c r="F61" s="12" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="H61" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I61" s="12" t="n">
         <v>3</v>
       </c>
       <c r="J61" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K61" s="12" t="n">
         <v>5</v>
@@ -3813,7 +3813,7 @@
         <v>2</v>
       </c>
       <c r="M61" s="12" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="N61" s="12" t="n">
         <v>0</v>
@@ -3851,7 +3851,7 @@
         </is>
       </c>
       <c r="F62" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G62" s="12" t="n">
         <v>0</v>
@@ -3863,23 +3863,23 @@
         <v>0</v>
       </c>
       <c r="J62" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K62" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L62" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M62" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N62" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -3910,10 +3910,10 @@
         </is>
       </c>
       <c r="F63" s="12" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="H63" s="12" t="n">
         <v>1</v>
@@ -3922,7 +3922,7 @@
         <v>3</v>
       </c>
       <c r="J63" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K63" s="12" t="n">
         <v>7</v>
@@ -3931,7 +3931,7 @@
         <v>10</v>
       </c>
       <c r="M63" s="12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N63" s="12" t="n">
         <v>3</v>
@@ -3945,17 +3945,17 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>11725</t>
+          <t>01280</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>GAVARDO</t>
+          <t>LA SPEZIA</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>LOC. ROCCOLINO SS45 BIS</t>
+          <t>VIALE ITALIA 160</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -3965,35 +3965,35 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>GRAZIOSI DAVIDE</t>
+          <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
       <c r="F64" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v>85</v>
+        <v>24</v>
       </c>
       <c r="J64" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="K64" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="L64" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M64" s="12" t="n">
+        <v>83</v>
+      </c>
+      <c r="N64" s="12" t="n">
         <v>18</v>
-      </c>
-      <c r="K64" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L64" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="M64" s="12" t="n">
-        <v>57</v>
-      </c>
-      <c r="N64" s="12" t="n">
-        <v>5</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
@@ -4004,17 +4004,17 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>02024</t>
+          <t>11725</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>CASALMAGGIORE</t>
+          <t>GAVARDO</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>VIA ROMA 36</t>
+          <t>LOC. ROCCOLINO SS45 BIS</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -4024,56 +4024,56 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
       <c r="F65" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G65" s="12" t="n">
         <v>49</v>
       </c>
       <c r="H65" s="12" t="n">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="I65" s="12" t="n">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J65" s="12" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="K65" s="12" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L65" s="12" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="M65" s="12" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="N65" s="12" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>01280</t>
+          <t>02024</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>LA SPEZIA</t>
+          <t>CASALMAGGIORE</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>VIALE ITALIA 160</t>
+          <t>VIA ROMA 36</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -4083,39 +4083,39 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="F66" s="12" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G66" s="12" t="n">
+        <v>49</v>
+      </c>
+      <c r="H66" s="12" t="n">
         <v>48</v>
       </c>
-      <c r="H66" s="12" t="n">
-        <v>16</v>
-      </c>
       <c r="I66" s="12" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J66" s="12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="K66" s="12" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L66" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="M66" s="12" t="n">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="N66" s="12" t="n">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -4152,7 +4152,7 @@
         <v>0</v>
       </c>
       <c r="H67" s="12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="I67" s="12" t="n">
         <v>0</v>
@@ -4167,14 +4167,14 @@
         <v>4</v>
       </c>
       <c r="M67" s="12" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="N67" s="12" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -4214,7 +4214,7 @@
         <v>19</v>
       </c>
       <c r="I68" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J68" s="12" t="n">
         <v>17</v>
@@ -4264,19 +4264,19 @@
         </is>
       </c>
       <c r="F69" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="H69" s="12" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I69" s="12" t="n">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="J69" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K69" s="12" t="n">
         <v>0</v>
@@ -4285,7 +4285,7 @@
         <v>6</v>
       </c>
       <c r="M69" s="12" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N69" s="12" t="n">
         <v>1</v>
@@ -4344,7 +4344,7 @@
         <v>1</v>
       </c>
       <c r="M70" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N70" s="12" t="n">
         <v>3</v>
@@ -4358,17 +4358,17 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>01578</t>
+          <t>01631</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>VERDELLO</t>
+          <t>TELGATE</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>S S 42</t>
+          <t>VIALE PAPA GIOVANNI</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -4378,56 +4378,56 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>SALVINELLI LUCA</t>
         </is>
       </c>
       <c r="F71" s="12" t="n">
         <v>13</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="H71" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I71" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J71" s="12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K71" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L71" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M71" s="12" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="N71" s="12" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>01631</t>
+          <t>01578</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>TELGATE</t>
+          <t>VERDELLO</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>VIALE PAPA GIOVANNI</t>
+          <t>S S 42</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -4437,39 +4437,39 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>SALVINELLI LUCA</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="F72" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="H72" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I72" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="J72" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="K72" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="L72" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="M72" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="N72" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="J72" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="K72" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L72" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M72" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="N72" s="12" t="n">
-        <v>13</v>
-      </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -4503,13 +4503,13 @@
         <v>11</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H73" s="12" t="n">
         <v>30</v>
       </c>
       <c r="I73" s="12" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J73" s="12" t="n">
         <v>8</v>

--- a/docs/files/REPORT_FILTRI/Agente - Marcelli Emanuele.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Marcelli Emanuele.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W23</t>
+          <t>W24</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>64</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>9487</v>
+        <v>9895</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>6649</v>
+        <v>6960</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>3538</v>
+        <v>3720</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>950</v>
+        <v>994</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>689</v>
+        <v>720</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>602</v>
+        <v>632</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>353</v>
+        <v>367</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>848</v>
+        <v>896</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,31 +901,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>649</v>
+        <v>680</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>441</v>
+        <v>462</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>443</v>
+        <v>472</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -960,35 +960,35 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>543</v>
+        <v>551</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>308</v>
+        <v>329</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>672</v>
+        <v>697</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>342</v>
+        <v>361</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1019,35 +1019,35 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>489</v>
+        <v>517</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>366</v>
+        <v>390</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>313</v>
+        <v>329</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>432</v>
+        <v>464</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1078,28 +1078,28 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>458</v>
+        <v>472</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>620</v>
+        <v>641</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>354</v>
+        <v>366</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>643</v>
+        <v>677</v>
       </c>
       <c r="N15" s="12" t="n">
         <v>38</v>
@@ -1137,31 +1137,31 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>401</v>
+        <v>427</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>673</v>
+        <v>697</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>297</v>
+        <v>322</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>513</v>
+        <v>546</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1196,31 +1196,31 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>398</v>
+        <v>414</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>488</v>
+        <v>516</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>622</v>
+        <v>658</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>383</v>
+        <v>408</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1255,31 +1255,31 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>501</v>
+        <v>514</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="L18" s="12" t="n">
         <v>58</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1314,35 +1314,35 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>317</v>
+        <v>340</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>259</v>
+        <v>279</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1373,28 +1373,28 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>275</v>
+        <v>293</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>217</v>
+        <v>231</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="N20" s="12" t="n">
         <v>23</v>
@@ -1432,31 +1432,31 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>313</v>
+        <v>332</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>328</v>
+        <v>355</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1491,31 +1491,31 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>237</v>
+        <v>255</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>308</v>
+        <v>324</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>557</v>
+        <v>597</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1550,52 +1550,52 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>230</v>
+        <v>247</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>229</v>
+        <v>244</v>
       </c>
       <c r="N23" s="12" t="n">
         <v>9</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>01638</t>
+          <t>01351</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>GRUMELLO DEL MONTE</t>
+          <t>SAVONA</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>VIA LEGA LOMBARDA 2</t>
+          <t>STALINGRADO</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1605,56 +1605,56 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>BARNABA SALVATORE</t>
         </is>
       </c>
       <c r="F24" s="12" t="n">
         <v>221</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>387</v>
+        <v>184</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>7</v>
+        <v>106</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>90</v>
+        <v>173</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>132</v>
+        <v>45</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>267</v>
+        <v>240</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>01351</t>
+          <t>01638</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>SAVONA</t>
+          <t>GRUMELLO DEL MONTE</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>STALINGRADO</t>
+          <t>VIA LEGA LOMBARDA 2</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1664,39 +1664,39 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>BARNABA SALVATORE</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>182</v>
+        <v>407</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>101</v>
+        <v>8</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>170</v>
+        <v>90</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>231</v>
+        <v>267</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1727,28 +1727,28 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>260</v>
+        <v>275</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="L26" s="12" t="n">
         <v>54</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>324</v>
+        <v>338</v>
       </c>
       <c r="N26" s="12" t="n">
         <v>25</v>
@@ -1786,31 +1786,31 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>248</v>
+        <v>263</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
@@ -1845,31 +1845,31 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="H28" s="12" t="n">
         <v>7</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>242</v>
+        <v>260</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -1880,17 +1880,17 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>55496</t>
+          <t>02036</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>MOZZO</t>
+          <t>CREMONA</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>SS 470 KM 5 0000</t>
+          <t>VIA CASTELLEONE, 47</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1900,35 +1900,35 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>204</v>
+        <v>177</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>9</v>
+        <v>202</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>8</v>
+        <v>361</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>82</v>
+        <v>132</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>154</v>
+        <v>235</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>28</v>
+        <v>86</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
@@ -1939,17 +1939,17 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>01034</t>
+          <t>01574</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>GENOVA</t>
+          <t>TREVIGLIO</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>LUNGOBISAGNO D'ISTRIA</t>
+          <t>VIALE MANZONI, 11</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1959,56 +1959,56 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>DALLORTO ILARIA</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>161</v>
+        <v>1</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>137</v>
+        <v>17</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>92</v>
+        <v>131</v>
       </c>
       <c r="K30" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="L30" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="L30" s="12" t="n">
-        <v>57</v>
-      </c>
       <c r="M30" s="12" t="n">
-        <v>185</v>
+        <v>202</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>02036</t>
+          <t>01034</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>CREMONA</t>
+          <t>GENOVA</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>VIA CASTELLEONE, 47</t>
+          <t>LUNGOBISAGNO D'ISTRIA</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -2018,35 +2018,35 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>DALLORTO ILARIA</t>
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>164</v>
+        <v>180</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>192</v>
+        <v>143</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>350</v>
+        <v>376</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>123</v>
+        <v>93</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>223</v>
+        <v>188</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>80</v>
+        <v>8</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
@@ -2057,17 +2057,17 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>01574</t>
+          <t>55496</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>TREVIGLIO</t>
+          <t>MOZZO</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>VIALE MANZONI, 11</t>
+          <t>SS 470 KM 5 0000</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2077,39 +2077,39 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>1</v>
+        <v>216</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>123</v>
+        <v>84</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>23</v>
+        <v>71</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2143,13 +2143,13 @@
         <v>139</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H33" s="12" t="n">
         <v>53</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J33" s="12" t="n">
         <v>80</v>
@@ -2161,7 +2161,7 @@
         <v>60</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="N33" s="12" t="n">
         <v>19</v>
@@ -2199,31 +2199,31 @@
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>205</v>
+        <v>219</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>125</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>276</v>
+        <v>290</v>
       </c>
       <c r="H35" s="12" t="n">
         <v>12</v>
@@ -2320,7 +2320,7 @@
         <v>108</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="H36" s="12" t="n">
         <v>2</v>
@@ -2352,17 +2352,17 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>01378</t>
+          <t>01007</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>CARCARE</t>
+          <t>CHIAVARI</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>VIA VITTORIO VENETO 52</t>
+          <t>CORSO GENOVA 40</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2372,56 +2372,56 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>DELUGAS NADIA</t>
+          <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>137</v>
+        <v>0</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>94</v>
+        <v>260</v>
       </c>
       <c r="N37" s="12" t="n">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>51037</t>
+          <t>01378</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>ACQUI TERME</t>
+          <t>CARCARE</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>VIA NIZZA 152</t>
+          <t>VIA VITTORIO VENETO 52</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -2435,31 +2435,31 @@
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="N38" s="12" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
@@ -2470,17 +2470,17 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>01007</t>
+          <t>51037</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>CHIAVARI</t>
+          <t>ACQUI TERME</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>CORSO GENOVA 40</t>
+          <t>VIA NIZZA 152</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -2490,39 +2490,39 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>DELUGAS NADIA</t>
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>250</v>
+        <v>121</v>
       </c>
       <c r="N39" s="12" t="n">
-        <v>57</v>
+        <v>12</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2553,35 +2553,35 @@
         </is>
       </c>
       <c r="F40" s="12" t="n">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="N40" s="12" t="n">
         <v>3</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2612,28 +2612,28 @@
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I41" s="12" t="n">
         <v>12</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="N41" s="12" t="n">
         <v>26</v>
@@ -2671,19 +2671,19 @@
         </is>
       </c>
       <c r="F42" s="12" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I42" s="12" t="n">
         <v>8</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K42" s="12" t="n">
         <v>24</v>
@@ -2692,10 +2692,10 @@
         <v>17</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="N42" s="12" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
@@ -2730,28 +2730,28 @@
         </is>
       </c>
       <c r="F43" s="12" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I43" s="12" t="n">
         <v>8</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L43" s="12" t="n">
         <v>6</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="N43" s="12" t="n">
         <v>44</v>
@@ -2789,16 +2789,16 @@
         </is>
       </c>
       <c r="F44" s="12" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="J44" s="12" t="n">
         <v>50</v>
@@ -2807,13 +2807,13 @@
         <v>13</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="N44" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
@@ -2824,17 +2824,17 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>01637</t>
+          <t>01717</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>CURNO</t>
+          <t>PAITONE</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>SS671 VALSERIANA  KM0,9820</t>
+          <t>SS 45 BIS KM 55+370</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -2844,56 +2844,56 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
       <c r="F45" s="12" t="n">
+        <v>74</v>
+      </c>
+      <c r="G45" s="12" t="n">
         <v>69</v>
       </c>
-      <c r="G45" s="12" t="n">
-        <v>106</v>
-      </c>
       <c r="H45" s="12" t="n">
-        <v>5</v>
+        <v>105</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>8</v>
+        <v>93</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="K45" s="12" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>92</v>
+        <v>60</v>
       </c>
       <c r="N45" s="12" t="n">
         <v>4</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>01717</t>
+          <t>01637</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>PAITONE</t>
+          <t>CURNO</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>SS 45 BIS KM 55+370</t>
+          <t>SS671 VALSERIANA  KM0,9820</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -2903,39 +2903,39 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>GRAZIOSI DAVIDE</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="F46" s="12" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>66</v>
+        <v>108</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>92</v>
+        <v>8</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="K46" s="12" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>59</v>
+        <v>96</v>
       </c>
       <c r="N46" s="12" t="n">
         <v>4</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2966,31 +2966,31 @@
         </is>
       </c>
       <c r="F47" s="12" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K47" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L47" s="12" t="n">
         <v>20</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="N47" s="12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
@@ -3025,31 +3025,31 @@
         </is>
       </c>
       <c r="F48" s="12" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J48" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K48" s="12" t="n">
         <v>10</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M48" s="12" t="n">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="N48" s="12" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
@@ -3084,31 +3084,31 @@
         </is>
       </c>
       <c r="F49" s="12" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I49" s="12" t="n">
         <v>8</v>
       </c>
       <c r="J49" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K49" s="12" t="n">
         <v>11</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M49" s="12" t="n">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="N49" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
@@ -3119,17 +3119,17 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>11719</t>
+          <t>12082</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>MONTICHIARI</t>
+          <t>VIADANA</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>S.S. 668 - VIA GHEDI</t>
+          <t>S.S. 358  KM 22+202</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -3139,39 +3139,39 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="F50" s="12" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="J50" s="12" t="n">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="K50" s="12" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="M50" s="12" t="n">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="N50" s="12" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -3202,28 +3202,28 @@
         </is>
       </c>
       <c r="F51" s="12" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="H51" s="12" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I51" s="12" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J51" s="12" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="K51" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L51" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M51" s="12" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="N51" s="12" t="n">
         <v>1</v>
@@ -3237,17 +3237,17 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>12082</t>
+          <t>55973</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>VIADANA</t>
+          <t>BOTTICINO</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>S.S. 358  KM 22+202</t>
+          <t>GARIBALDI 18</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -3257,35 +3257,35 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
       <c r="F52" s="12" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J52" s="12" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K52" s="12" t="n">
         <v>12</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="M52" s="12" t="n">
-        <v>22</v>
+        <v>59</v>
       </c>
       <c r="N52" s="12" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
@@ -3296,17 +3296,17 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>01334</t>
+          <t>11719</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>FINALE LIGURE</t>
+          <t>MONTICHIARI</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>VIA MAZZINI</t>
+          <t>S.S. 668 - VIA GHEDI</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -3316,35 +3316,35 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>BARNABA SALVATORE</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="F53" s="12" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H53" s="12" t="n">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="I53" s="12" t="n">
-        <v>66</v>
+        <v>135</v>
       </c>
       <c r="J53" s="12" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="K53" s="12" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="M53" s="12" t="n">
-        <v>84</v>
+        <v>58</v>
       </c>
       <c r="N53" s="12" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
@@ -3355,17 +3355,17 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>55973</t>
+          <t>01334</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>BOTTICINO</t>
+          <t>FINALE LIGURE</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>GARIBALDI 18</t>
+          <t>VIA MAZZINI</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -3375,56 +3375,56 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>GRAZIOSI DAVIDE</t>
+          <t>BARNABA SALVATORE</t>
         </is>
       </c>
       <c r="F54" s="12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G54" s="12" t="n">
+        <v>70</v>
+      </c>
+      <c r="H54" s="12" t="n">
+        <v>53</v>
+      </c>
+      <c r="I54" s="12" t="n">
+        <v>72</v>
+      </c>
+      <c r="J54" s="12" t="n">
+        <v>39</v>
+      </c>
+      <c r="K54" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="L54" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="M54" s="12" t="n">
+        <v>88</v>
+      </c>
+      <c r="N54" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="H54" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="I54" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J54" s="12" t="n">
-        <v>37</v>
-      </c>
-      <c r="K54" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="L54" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="M54" s="12" t="n">
-        <v>56</v>
-      </c>
-      <c r="N54" s="12" t="n">
-        <v>1</v>
-      </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>59894</t>
+          <t>56297</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA</t>
+          <t>SAN PAOLO D'ARGON</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>V. DE GASP./TANG. S KM 6+930</t>
+          <t>SS 42</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -3434,56 +3434,56 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>SALVINELLI LUCA</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="F55" s="12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="H55" s="12" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I55" s="12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J55" s="12" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="K55" s="12" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="M55" s="12" t="n">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="N55" s="12" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>56297</t>
+          <t>59894</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>SAN PAOLO D'ARGON</t>
+          <t>BRESCIA</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>SS 42</t>
+          <t>V. DE GASP./TANG. S KM 6+930</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -3493,39 +3493,39 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>SALVINELLI LUCA</t>
         </is>
       </c>
       <c r="F56" s="12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="H56" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I56" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="I56" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="J56" s="12" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="K56" s="12" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="M56" s="12" t="n">
-        <v>73</v>
+        <v>35</v>
       </c>
       <c r="N56" s="12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -3556,28 +3556,28 @@
         </is>
       </c>
       <c r="F57" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H57" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I57" s="12" t="n">
         <v>20</v>
       </c>
       <c r="J57" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K57" s="12" t="n">
         <v>8</v>
       </c>
       <c r="L57" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M57" s="12" t="n">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="N57" s="12" t="n">
         <v>3</v>
@@ -3615,19 +3615,19 @@
         </is>
       </c>
       <c r="F58" s="12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G58" s="12" t="n">
         <v>39</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I58" s="12" t="n">
         <v>6</v>
       </c>
       <c r="J58" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K58" s="12" t="n">
         <v>14</v>
@@ -3636,14 +3636,14 @@
         <v>12</v>
       </c>
       <c r="M58" s="12" t="n">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="N58" s="12" t="n">
         <v>10</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -3674,19 +3674,19 @@
         </is>
       </c>
       <c r="F59" s="12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H59" s="12" t="n">
         <v>17</v>
       </c>
       <c r="I59" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J59" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K59" s="12" t="n">
         <v>10</v>
@@ -3695,7 +3695,7 @@
         <v>19</v>
       </c>
       <c r="M59" s="12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N59" s="12" t="n">
         <v>3</v>
@@ -3733,10 +3733,10 @@
         </is>
       </c>
       <c r="F60" s="12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H60" s="12" t="n">
         <v>3</v>
@@ -3745,16 +3745,16 @@
         <v>1</v>
       </c>
       <c r="J60" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K60" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L60" s="12" t="n">
         <v>23</v>
       </c>
       <c r="M60" s="12" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="N60" s="12" t="n">
         <v>2</v>
@@ -3768,17 +3768,17 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>01283</t>
+          <t>01280</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>SARZANA</t>
+          <t>LA SPEZIA</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>LOCALITA' MONTECAVALLO - VIA AURELIA 67/A</t>
+          <t>VIALE ITALIA 160</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -3792,31 +3792,31 @@
         </is>
       </c>
       <c r="F61" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>86</v>
+        <v>56</v>
       </c>
       <c r="H61" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I61" s="12" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="J61" s="12" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="K61" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L61" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M61" s="12" t="n">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="N61" s="12" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
@@ -3851,10 +3851,10 @@
         </is>
       </c>
       <c r="F62" s="12" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H62" s="12" t="n">
         <v>6</v>
@@ -3863,7 +3863,7 @@
         <v>0</v>
       </c>
       <c r="J62" s="12" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="K62" s="12" t="n">
         <v>12</v>
@@ -3872,31 +3872,31 @@
         <v>0</v>
       </c>
       <c r="M62" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="N62" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>02004</t>
+          <t>01283</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>RIVOLTA D'ADDA</t>
+          <t>SARZANA</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>VIA GIUSEPPE DI VITTORIO 17</t>
+          <t>LOCALITA' MONTECAVALLO - VIA AURELIA 67/A</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -3906,35 +3906,35 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>MARLETTA ELEONORA SOFIA</t>
         </is>
       </c>
       <c r="F63" s="12" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="H63" s="12" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="I63" s="12" t="n">
         <v>3</v>
       </c>
       <c r="J63" s="12" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="K63" s="12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L63" s="12" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="M63" s="12" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N63" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
@@ -3945,17 +3945,17 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>01280</t>
+          <t>02024</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>LA SPEZIA</t>
+          <t>CASALMAGGIORE</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>VIALE ITALIA 160</t>
+          <t>VIA ROMA 36</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -3965,56 +3965,56 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="F64" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G64" s="12" t="n">
         <v>51</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J64" s="12" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="K64" s="12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L64" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="M64" s="12" t="n">
-        <v>83</v>
+        <v>62</v>
       </c>
       <c r="N64" s="12" t="n">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>11725</t>
+          <t>02004</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>GAVARDO</t>
+          <t>RIVOLTA D'ADDA</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>LOC. ROCCOLINO SS45 BIS</t>
+          <t>VIA GIUSEPPE DI VITTORIO 17</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -4024,35 +4024,35 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>GRAZIOSI DAVIDE</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="F65" s="12" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="H65" s="12" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="I65" s="12" t="n">
-        <v>91</v>
+        <v>3</v>
       </c>
       <c r="J65" s="12" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="K65" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L65" s="12" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="M65" s="12" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="N65" s="12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
@@ -4063,17 +4063,17 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>02024</t>
+          <t>11725</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>CASALMAGGIORE</t>
+          <t>GAVARDO</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>VIA ROMA 36</t>
+          <t>LOC. ROCCOLINO SS45 BIS</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -4083,39 +4083,39 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
       <c r="F66" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="I66" s="12" t="n">
-        <v>21</v>
+        <v>96</v>
       </c>
       <c r="J66" s="12" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="K66" s="12" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L66" s="12" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="M66" s="12" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="N66" s="12" t="n">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -4167,14 +4167,14 @@
         <v>4</v>
       </c>
       <c r="M67" s="12" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="N67" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -4208,13 +4208,13 @@
         <v>20</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H68" s="12" t="n">
         <v>19</v>
       </c>
       <c r="I68" s="12" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="J68" s="12" t="n">
         <v>17</v>
@@ -4226,7 +4226,7 @@
         <v>4</v>
       </c>
       <c r="M68" s="12" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="N68" s="12" t="n">
         <v>0</v>
@@ -4264,19 +4264,19 @@
         </is>
       </c>
       <c r="F69" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H69" s="12" t="n">
         <v>51</v>
       </c>
       <c r="I69" s="12" t="n">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="J69" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K69" s="12" t="n">
         <v>0</v>
@@ -4299,17 +4299,17 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>02074</t>
+          <t>01631</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>GOITO</t>
+          <t>TELGATE</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>S.S. N. 236 KM 14+332</t>
+          <t>VIALE PAPA GIOVANNI</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -4319,11 +4319,11 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>SALVINELLI LUCA</t>
         </is>
       </c>
       <c r="F70" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G70" s="12" t="n">
         <v>0</v>
@@ -4335,40 +4335,40 @@
         <v>0</v>
       </c>
       <c r="J70" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K70" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L70" s="12" t="n">
         <v>1</v>
       </c>
       <c r="M70" s="12" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="N70" s="12" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>01631</t>
+          <t>02074</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>TELGATE</t>
+          <t>GOITO</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>VIALE PAPA GIOVANNI</t>
+          <t>S.S. N. 236 KM 14+332</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -4378,11 +4378,11 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>SALVINELLI LUCA</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="F71" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G71" s="12" t="n">
         <v>0</v>
@@ -4397,16 +4397,16 @@
         <v>13</v>
       </c>
       <c r="K71" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L71" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M71" s="12" t="n">
         <v>22</v>
       </c>
       <c r="N71" s="12" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
@@ -4444,7 +4444,7 @@
         <v>13</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="H72" s="12" t="n">
         <v>1</v>
@@ -4509,7 +4509,7 @@
         <v>30</v>
       </c>
       <c r="I73" s="12" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="J73" s="12" t="n">
         <v>8</v>
@@ -4580,7 +4580,7 @@
         <v>0</v>
       </c>
       <c r="M74" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N74" s="12" t="n">
         <v>2</v>

--- a/docs/files/REPORT_FILTRI/Agente - Marcelli Emanuele.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Marcelli Emanuele.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W24</t>
+          <t>W25</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>64</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>9895</v>
+        <v>10300</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>6960</v>
+        <v>7272</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>3720</v>
+        <v>3964</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,35 +842,35 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>994</v>
+        <v>1036</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>720</v>
+        <v>744</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>632</v>
+        <v>664</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>896</v>
+        <v>941</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -901,35 +901,35 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>680</v>
+        <v>704</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>294</v>
+        <v>308</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>462</v>
+        <v>476</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>472</v>
+        <v>492</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -960,35 +960,35 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>551</v>
+        <v>566</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>329</v>
+        <v>342</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>697</v>
+        <v>730</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>361</v>
+        <v>390</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>361</v>
+        <v>384</v>
       </c>
       <c r="N13" s="12" t="n">
         <v>10</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1019,31 +1019,31 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>517</v>
+        <v>556</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>390</v>
+        <v>406</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>329</v>
+        <v>352</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>179</v>
+        <v>195</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>464</v>
+        <v>495</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1078,31 +1078,31 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>472</v>
+        <v>508</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>641</v>
+        <v>670</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>366</v>
+        <v>401</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>677</v>
+        <v>719</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1137,31 +1137,31 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>427</v>
+        <v>450</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>697</v>
+        <v>726</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>322</v>
+        <v>340</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>546</v>
+        <v>570</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1196,31 +1196,31 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>414</v>
+        <v>428</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>516</v>
+        <v>542</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>410</v>
+        <v>420</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>658</v>
+        <v>689</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>332</v>
+        <v>344</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>408</v>
+        <v>437</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1255,31 +1255,31 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>355</v>
+        <v>375</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>514</v>
+        <v>533</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>297</v>
+        <v>315</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>243</v>
+        <v>258</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1314,35 +1314,35 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>334</v>
+        <v>362</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1373,35 +1373,35 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L20" s="12" t="n">
         <v>64</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1432,31 +1432,31 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>332</v>
+        <v>344</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>355</v>
+        <v>368</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1491,31 +1491,31 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>324</v>
+        <v>339</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>597</v>
+        <v>628</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1550,31 +1550,31 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I23" s="12" t="n">
         <v>10</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>244</v>
+        <v>264</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -1609,31 +1609,31 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -1671,13 +1671,13 @@
         <v>221</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>407</v>
+        <v>425</v>
       </c>
       <c r="H25" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J25" s="12" t="n">
         <v>90</v>
@@ -1727,31 +1727,31 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>275</v>
+        <v>294</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="L26" s="12" t="n">
         <v>54</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>338</v>
+        <v>360</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1786,31 +1786,31 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>263</v>
+        <v>274</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>172</v>
+        <v>189</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>273</v>
+        <v>292</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
@@ -1845,31 +1845,31 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="H28" s="12" t="n">
         <v>7</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -1880,17 +1880,17 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>02036</t>
+          <t>01574</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>CREMONA</t>
+          <t>TREVIGLIO</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>VIA CASTELLEONE, 47</t>
+          <t>VIALE MANZONI, 11</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1900,56 +1900,56 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>157</v>
+        <v>177</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>177</v>
+        <v>1</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>202</v>
+        <v>22</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>361</v>
+        <v>0</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>235</v>
+        <v>218</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>86</v>
+        <v>16</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>01574</t>
+          <t>02036</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>TREVIGLIO</t>
+          <t>CREMONA</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>VIALE MANZONI, 11</t>
+          <t>VIA CASTELLEONE, 47</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1959,39 +1959,39 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>1</v>
+        <v>181</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>17</v>
+        <v>215</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>0</v>
+        <v>379</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="L30" s="12" t="n">
         <v>27</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>202</v>
+        <v>256</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>16</v>
+        <v>95</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2022,31 +2022,31 @@
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L31" s="12" t="n">
         <v>60</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
@@ -2081,19 +2081,19 @@
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I32" s="12" t="n">
         <v>9</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K32" s="12" t="n">
         <v>29</v>
@@ -2102,10 +2102,10 @@
         <v>71</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
@@ -2116,17 +2116,17 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>01525</t>
+          <t>01043</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>GAZZANIGA</t>
+          <t>GENOVA</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>CESARE BATTISTI</t>
+          <t>VIA RIGHETTI 1 R</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2136,56 +2136,56 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>DALLORTO ILARIA</t>
         </is>
       </c>
       <c r="F33" s="12" t="n">
         <v>139</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>242</v>
+        <v>162</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>90</v>
+        <v>35</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>90</v>
+        <v>240</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>01043</t>
+          <t>01525</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>GENOVA</t>
+          <t>GAZZANIGA</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>VIA RIGHETTI 1 R</t>
+          <t>CESARE BATTISTI</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2195,39 +2195,39 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>DALLORTO ILARIA</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>155</v>
+        <v>252</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>31</v>
+        <v>95</v>
       </c>
       <c r="J34" s="12" t="n">
+        <v>80</v>
+      </c>
+      <c r="K34" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="L34" s="12" t="n">
+        <v>60</v>
+      </c>
+      <c r="M34" s="12" t="n">
         <v>90</v>
       </c>
-      <c r="K34" s="12" t="n">
-        <v>35</v>
-      </c>
-      <c r="L34" s="12" t="n">
-        <v>41</v>
-      </c>
-      <c r="M34" s="12" t="n">
-        <v>219</v>
-      </c>
       <c r="N34" s="12" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2261,13 +2261,13 @@
         <v>125</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="H35" s="12" t="n">
         <v>12</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J35" s="12" t="n">
         <v>99</v>
@@ -2293,17 +2293,17 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>01718</t>
+          <t>01378</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>PONTEVICO</t>
+          <t>CARCARE</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>SS 45 BIS KM 16+700</t>
+          <t>VIA VITTORIO VENETO 52</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2313,35 +2313,35 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>DELUGAS NADIA</t>
         </is>
       </c>
       <c r="F36" s="12" t="n">
+        <v>111</v>
+      </c>
+      <c r="G36" s="12" t="n">
+        <v>139</v>
+      </c>
+      <c r="H36" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="I36" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="J36" s="12" t="n">
+        <v>57</v>
+      </c>
+      <c r="K36" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="L36" s="12" t="n">
+        <v>52</v>
+      </c>
+      <c r="M36" s="12" t="n">
         <v>108</v>
       </c>
-      <c r="G36" s="12" t="n">
-        <v>221</v>
-      </c>
-      <c r="H36" s="12" t="n">
+      <c r="N36" s="12" t="n">
         <v>2</v>
-      </c>
-      <c r="I36" s="12" t="n">
-        <v>53</v>
-      </c>
-      <c r="J36" s="12" t="n">
-        <v>77</v>
-      </c>
-      <c r="K36" s="12" t="n">
-        <v>29</v>
-      </c>
-      <c r="L36" s="12" t="n">
-        <v>32</v>
-      </c>
-      <c r="M36" s="12" t="n">
-        <v>124</v>
-      </c>
-      <c r="N36" s="12" t="n">
-        <v>16</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="G37" s="12" t="n">
         <v>0</v>
@@ -2388,40 +2388,40 @@
         <v>0</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L37" s="12" t="n">
         <v>48</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="N37" s="12" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>01378</t>
+          <t>01718</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>CARCARE</t>
+          <t>PONTEVICO</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>VIA VITTORIO VENETO 52</t>
+          <t>SS 45 BIS KM 16+700</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -2431,35 +2431,35 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>DELUGAS NADIA</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>139</v>
+        <v>224</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I38" s="12" t="n">
+        <v>54</v>
+      </c>
+      <c r="J38" s="12" t="n">
+        <v>77</v>
+      </c>
+      <c r="K38" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="L38" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="M38" s="12" t="n">
+        <v>124</v>
+      </c>
+      <c r="N38" s="12" t="n">
         <v>16</v>
-      </c>
-      <c r="J38" s="12" t="n">
-        <v>55</v>
-      </c>
-      <c r="K38" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="L38" s="12" t="n">
-        <v>49</v>
-      </c>
-      <c r="M38" s="12" t="n">
-        <v>101</v>
-      </c>
-      <c r="N38" s="12" t="n">
-        <v>2</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
@@ -2470,17 +2470,17 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>51037</t>
+          <t>01577</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>ACQUI TERME</t>
+          <t>ZANICA</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>VIA NIZZA 152</t>
+          <t>VIA PROVINCIALE</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -2490,35 +2490,35 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>DELUGAS NADIA</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H39" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="I39" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="J39" s="12" t="n">
+        <v>66</v>
+      </c>
+      <c r="K39" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I39" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="J39" s="12" t="n">
-        <v>78</v>
-      </c>
-      <c r="K39" s="12" t="n">
-        <v>31</v>
-      </c>
       <c r="L39" s="12" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="N39" s="12" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
@@ -2529,17 +2529,17 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>01577</t>
+          <t>51037</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>ZANICA</t>
+          <t>ACQUI TERME</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>VIA PROVINCIALE</t>
+          <t>VIA NIZZA 152</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -2549,35 +2549,35 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>DELUGAS NADIA</t>
         </is>
       </c>
       <c r="F40" s="12" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="N40" s="12" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
@@ -2612,31 +2612,31 @@
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I41" s="12" t="n">
         <v>12</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="L41" s="12" t="n">
         <v>24</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="N41" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
@@ -2671,35 +2671,35 @@
         </is>
       </c>
       <c r="F42" s="12" t="n">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="I42" s="12" t="n">
         <v>8</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="K42" s="12" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="N42" s="12" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2730,31 +2730,31 @@
         </is>
       </c>
       <c r="F43" s="12" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I43" s="12" t="n">
         <v>8</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L43" s="12" t="n">
         <v>6</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="N43" s="12" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
@@ -2765,17 +2765,17 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>51570</t>
+          <t>01717</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>VENTIMIGLIA</t>
+          <t>PAITONE</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>CSO LIMONE PIEMONTE 1</t>
+          <t>SS 45 BIS KM 55+370</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -2785,56 +2785,56 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>BARNABA SALVATORE</t>
+          <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
       <c r="F44" s="12" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>114</v>
+        <v>73</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>12</v>
+        <v>108</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>52</v>
+        <v>101</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="N44" s="12" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>01717</t>
+          <t>01637</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>PAITONE</t>
+          <t>CURNO</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>SS 45 BIS KM 55+370</t>
+          <t>SS671 VALSERIANA  KM0,9820</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -2844,56 +2844,56 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>GRAZIOSI DAVIDE</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="F45" s="12" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>69</v>
+        <v>116</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>105</v>
+        <v>5</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>93</v>
+        <v>9</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="K45" s="12" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>60</v>
+        <v>99</v>
       </c>
       <c r="N45" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>01637</t>
+          <t>51570</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>CURNO</t>
+          <t>VENTIMIGLIA</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>SS671 VALSERIANA  KM0,9820</t>
+          <t>CSO LIMONE PIEMONTE 1</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -2903,35 +2903,35 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>BARNABA SALVATORE</t>
         </is>
       </c>
       <c r="F46" s="12" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="K46" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="N46" s="12" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
@@ -2966,31 +2966,31 @@
         </is>
       </c>
       <c r="F47" s="12" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K47" s="12" t="n">
         <v>11</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="N47" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
@@ -3025,19 +3025,19 @@
         </is>
       </c>
       <c r="F48" s="12" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="J48" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K48" s="12" t="n">
         <v>10</v>
@@ -3046,10 +3046,10 @@
         <v>18</v>
       </c>
       <c r="M48" s="12" t="n">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="N48" s="12" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
@@ -3084,10 +3084,10 @@
         </is>
       </c>
       <c r="F49" s="12" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="H49" s="12" t="n">
         <v>22</v>
@@ -3096,19 +3096,19 @@
         <v>8</v>
       </c>
       <c r="J49" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="K49" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L49" s="12" t="n">
         <v>24</v>
       </c>
       <c r="M49" s="12" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="N49" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
@@ -3143,52 +3143,52 @@
         </is>
       </c>
       <c r="F50" s="12" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G50" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="I50" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J50" s="12" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="K50" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L50" s="12" t="n">
         <v>7</v>
       </c>
       <c r="M50" s="12" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="N50" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>02075</t>
+          <t>11719</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>SUZZARA</t>
+          <t>MONTICHIARI</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>S.S. N. 62 CISA - LOCALITA' CROCILE C.M.</t>
+          <t>S.S. 668 - VIA GHEDI</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -3198,56 +3198,56 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>CARMINATI SIMONE</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="F51" s="12" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="H51" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="I51" s="12" t="n">
+        <v>138</v>
+      </c>
+      <c r="J51" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="K51" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L51" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="I51" s="12" t="n">
-        <v>72</v>
-      </c>
-      <c r="J51" s="12" t="n">
-        <v>54</v>
-      </c>
-      <c r="K51" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="L51" s="12" t="n">
+      <c r="M51" s="12" t="n">
+        <v>62</v>
+      </c>
+      <c r="N51" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="M51" s="12" t="n">
-        <v>83</v>
-      </c>
-      <c r="N51" s="12" t="n">
-        <v>1</v>
-      </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>55973</t>
+          <t>01334</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>BOTTICINO</t>
+          <t>FINALE LIGURE</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>GARIBALDI 18</t>
+          <t>VIA MAZZINI</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -3257,56 +3257,56 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>GRAZIOSI DAVIDE</t>
+          <t>BARNABA SALVATORE</t>
         </is>
       </c>
       <c r="F52" s="12" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>3</v>
+        <v>61</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>3</v>
+        <v>76</v>
       </c>
       <c r="J52" s="12" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K52" s="12" t="n">
         <v>12</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M52" s="12" t="n">
-        <v>59</v>
+        <v>98</v>
       </c>
       <c r="N52" s="12" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>11719</t>
+          <t>02075</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>MONTICHIARI</t>
+          <t>SUZZARA</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>S.S. 668 - VIA GHEDI</t>
+          <t>S.S. N. 62 CISA - LOCALITA' CROCILE C.M.</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -3316,35 +3316,35 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>CARMINATI SIMONE</t>
         </is>
       </c>
       <c r="F53" s="12" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>64</v>
+        <v>87</v>
       </c>
       <c r="H53" s="12" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I53" s="12" t="n">
-        <v>135</v>
+        <v>78</v>
       </c>
       <c r="J53" s="12" t="n">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="K53" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="L53" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" s="12" t="n">
+        <v>88</v>
+      </c>
+      <c r="N53" s="12" t="n">
         <v>1</v>
-      </c>
-      <c r="L53" s="12" t="n">
-        <v>34</v>
-      </c>
-      <c r="M53" s="12" t="n">
-        <v>58</v>
-      </c>
-      <c r="N53" s="12" t="n">
-        <v>0</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
@@ -3355,17 +3355,17 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>01334</t>
+          <t>56297</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>FINALE LIGURE</t>
+          <t>SAN PAOLO D'ARGON</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>VIA MAZZINI</t>
+          <t>SS 42</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -3375,56 +3375,56 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>BARNABA SALVATORE</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="F54" s="12" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>70</v>
+        <v>2</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>72</v>
+        <v>2</v>
       </c>
       <c r="J54" s="12" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="K54" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="M54" s="12" t="n">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="N54" s="12" t="n">
-        <v>60</v>
+        <v>9</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>56297</t>
+          <t>55973</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>SAN PAOLO D'ARGON</t>
+          <t>BOTTICINO</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>SS 42</t>
+          <t>GARIBALDI 18</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -3434,35 +3434,35 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
       <c r="F55" s="12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="H55" s="12" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I55" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J55" s="12" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="K55" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="M55" s="12" t="n">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="N55" s="12" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         <v>49</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="H56" s="12" t="n">
         <v>2</v>
@@ -3559,13 +3559,13 @@
         <v>47</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="H57" s="12" t="n">
         <v>32</v>
       </c>
       <c r="I57" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J57" s="12" t="n">
         <v>30</v>
@@ -3577,10 +3577,10 @@
         <v>17</v>
       </c>
       <c r="M57" s="12" t="n">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="N57" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
@@ -3591,17 +3591,17 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>01135</t>
+          <t>11726</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>GENOVA</t>
+          <t>REZZATO</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>VIA SIFFREDI, 62</t>
+          <t>S.S.45 KM.49+300</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -3611,56 +3611,56 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>DALLORTO ILARIA</t>
+          <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
       <c r="F58" s="12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J58" s="12" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="K58" s="12" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="L58" s="12" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="M58" s="12" t="n">
-        <v>112</v>
+        <v>52</v>
       </c>
       <c r="N58" s="12" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>11726</t>
+          <t>01135</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>REZZATO</t>
+          <t>GENOVA</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>S.S.45 KM.49+300</t>
+          <t>VIA SIFFREDI, 62</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>GRAZIOSI DAVIDE</t>
+          <t>DALLORTO ILARIA</t>
         </is>
       </c>
       <c r="F59" s="12" t="n">
@@ -3680,29 +3680,29 @@
         <v>39</v>
       </c>
       <c r="H59" s="12" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I59" s="12" t="n">
         <v>6</v>
       </c>
       <c r="J59" s="12" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="K59" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="L59" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="M59" s="12" t="n">
+        <v>116</v>
+      </c>
+      <c r="N59" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="L59" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="M59" s="12" t="n">
-        <v>49</v>
-      </c>
-      <c r="N59" s="12" t="n">
-        <v>3</v>
-      </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -3733,19 +3733,19 @@
         </is>
       </c>
       <c r="F60" s="12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H60" s="12" t="n">
         <v>3</v>
       </c>
       <c r="I60" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J60" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K60" s="12" t="n">
         <v>5</v>
@@ -3754,7 +3754,7 @@
         <v>23</v>
       </c>
       <c r="M60" s="12" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="N60" s="12" t="n">
         <v>2</v>
@@ -3792,35 +3792,35 @@
         </is>
       </c>
       <c r="F61" s="12" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="H61" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I61" s="12" t="n">
         <v>27</v>
       </c>
       <c r="J61" s="12" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K61" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L61" s="12" t="n">
         <v>1</v>
       </c>
       <c r="M61" s="12" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="N61" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -3857,7 +3857,7 @@
         <v>1</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I62" s="12" t="n">
         <v>0</v>
@@ -3872,14 +3872,14 @@
         <v>0</v>
       </c>
       <c r="M62" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N62" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -3910,10 +3910,10 @@
         </is>
       </c>
       <c r="F63" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="H63" s="12" t="n">
         <v>20</v>
@@ -3928,13 +3928,13 @@
         <v>5</v>
       </c>
       <c r="L63" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M63" s="12" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="N63" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
@@ -3969,31 +3969,31 @@
         </is>
       </c>
       <c r="F64" s="12" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J64" s="12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K64" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L64" s="12" t="n">
         <v>7</v>
       </c>
       <c r="M64" s="12" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="N64" s="12" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         <v>35</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="H65" s="12" t="n">
         <v>1</v>
@@ -4090,13 +4090,13 @@
         <v>33</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I66" s="12" t="n">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="J66" s="12" t="n">
         <v>19</v>
@@ -4108,7 +4108,7 @@
         <v>14</v>
       </c>
       <c r="M66" s="12" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="N66" s="12" t="n">
         <v>6</v>
@@ -4152,7 +4152,7 @@
         <v>0</v>
       </c>
       <c r="H67" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I67" s="12" t="n">
         <v>0</v>
@@ -4167,7 +4167,7 @@
         <v>4</v>
       </c>
       <c r="M67" s="12" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N67" s="12" t="n">
         <v>27</v>
@@ -4214,7 +4214,7 @@
         <v>19</v>
       </c>
       <c r="I68" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J68" s="12" t="n">
         <v>17</v>
@@ -4226,7 +4226,7 @@
         <v>4</v>
       </c>
       <c r="M68" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="N68" s="12" t="n">
         <v>0</v>
@@ -4267,7 +4267,7 @@
         <v>20</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="H69" s="12" t="n">
         <v>51</v>
@@ -4285,7 +4285,7 @@
         <v>6</v>
       </c>
       <c r="M69" s="12" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="N69" s="12" t="n">
         <v>1</v>
@@ -4323,31 +4323,31 @@
         </is>
       </c>
       <c r="F70" s="12" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G70" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I70" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J70" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="K70" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L70" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="M70" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="N70" s="12" t="n">
         <v>15</v>
-      </c>
-      <c r="K70" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L70" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M70" s="12" t="n">
-        <v>30</v>
-      </c>
-      <c r="N70" s="12" t="n">
-        <v>14</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
@@ -4403,7 +4403,7 @@
         <v>1</v>
       </c>
       <c r="M71" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N71" s="12" t="n">
         <v>3</v>
@@ -4444,7 +4444,7 @@
         <v>13</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H72" s="12" t="n">
         <v>1</v>
@@ -4503,13 +4503,13 @@
         <v>11</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H73" s="12" t="n">
         <v>30</v>
       </c>
       <c r="I73" s="12" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="J73" s="12" t="n">
         <v>8</v>

--- a/docs/files/REPORT_FILTRI/Agente - Marcelli Emanuele.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Marcelli Emanuele.xlsx
@@ -528,7 +528,7 @@
     <col width="27" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -2372,7 +2372,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>DELUGAS NADIA</t>
         </is>
       </c>
       <c r="F37" s="12" t="n">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>DALLORTO ILARIA</t>
         </is>
       </c>
       <c r="F48" s="12" t="n">
@@ -3552,7 +3552,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>DELUGAS NADIA</t>
         </is>
       </c>
       <c r="F57" s="12" t="n">
@@ -3788,7 +3788,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="F61" s="12" t="n">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>DELUGAS NADIA</t>
         </is>
       </c>
       <c r="F63" s="12" t="n">
@@ -4201,7 +4201,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="F68" s="12" t="n">

--- a/docs/files/REPORT_FILTRI/Agente - Marcelli Emanuele.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Marcelli Emanuele.xlsx
@@ -684,13 +684,13 @@
         <v>64</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>10300</v>
+        <v>10299</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>7272</v>
+        <v>0</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>3964</v>
+        <v>3909</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>1036</v>
+        <v>1041</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>744</v>
+        <v>734</v>
       </c>
       <c r="H11" s="12" t="n">
         <v>121</v>
@@ -854,7 +854,7 @@
         <v>98</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>664</v>
+        <v>0</v>
       </c>
       <c r="K11" s="12" t="n">
         <v>220</v>
@@ -863,7 +863,7 @@
         <v>377</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>941</v>
+        <v>927</v>
       </c>
       <c r="N11" s="12" t="n">
         <v>118</v>
@@ -901,10 +901,10 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>704</v>
+        <v>692</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H12" s="12" t="n">
         <v>126</v>
@@ -913,7 +913,7 @@
         <v>59</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>476</v>
+        <v>0</v>
       </c>
       <c r="K12" s="12" t="n">
         <v>164</v>
@@ -922,10 +922,10 @@
         <v>216</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -963,16 +963,16 @@
         <v>566</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>730</v>
+        <v>718</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>395</v>
+        <v>0</v>
       </c>
       <c r="K13" s="12" t="n">
         <v>152</v>
@@ -981,14 +981,14 @@
         <v>171</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="N13" s="12" t="n">
         <v>10</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1019,19 +1019,19 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>556</v>
+        <v>547</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>406</v>
+        <v>397</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I14" s="12" t="n">
         <v>114</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>352</v>
+        <v>0</v>
       </c>
       <c r="K14" s="12" t="n">
         <v>121</v>
@@ -1040,7 +1040,7 @@
         <v>195</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="N14" s="12" t="n">
         <v>138</v>
@@ -1078,19 +1078,19 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>670</v>
+        <v>657</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>401</v>
+        <v>0</v>
       </c>
       <c r="K15" s="12" t="n">
         <v>152</v>
@@ -1099,10 +1099,10 @@
         <v>110</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>719</v>
+        <v>706</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1137,10 +1137,10 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="H16" s="12" t="n">
         <v>70</v>
@@ -1149,7 +1149,7 @@
         <v>35</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>340</v>
+        <v>0</v>
       </c>
       <c r="K16" s="12" t="n">
         <v>135</v>
@@ -1196,19 +1196,19 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>420</v>
+        <v>405</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>689</v>
+        <v>681</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>344</v>
+        <v>0</v>
       </c>
       <c r="K17" s="12" t="n">
         <v>123</v>
@@ -1217,7 +1217,7 @@
         <v>86</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>20</v>
@@ -1258,7 +1258,7 @@
         <v>375</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>533</v>
+        <v>524</v>
       </c>
       <c r="H18" s="12" t="n">
         <v>109</v>
@@ -1267,7 +1267,7 @@
         <v>77</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>315</v>
+        <v>0</v>
       </c>
       <c r="K18" s="12" t="n">
         <v>104</v>
@@ -1276,10 +1276,10 @@
         <v>60</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1314,19 +1314,19 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>286</v>
+        <v>0</v>
       </c>
       <c r="K19" s="12" t="n">
         <v>116</v>
@@ -1335,14 +1335,14 @@
         <v>55</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1373,10 +1373,10 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H20" s="12" t="n">
         <v>159</v>
@@ -1385,7 +1385,7 @@
         <v>88</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>237</v>
+        <v>0</v>
       </c>
       <c r="K20" s="12" t="n">
         <v>103</v>
@@ -1394,10 +1394,10 @@
         <v>64</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -1432,10 +1432,10 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="H21" s="12" t="n">
         <v>42</v>
@@ -1444,7 +1444,7 @@
         <v>42</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="K21" s="12" t="n">
         <v>47</v>
@@ -1453,14 +1453,14 @@
         <v>120</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="N21" s="12" t="n">
         <v>89</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1491,19 +1491,19 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="H22" s="12" t="n">
         <v>95</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>191</v>
+        <v>0</v>
       </c>
       <c r="K22" s="12" t="n">
         <v>57</v>
@@ -1512,7 +1512,7 @@
         <v>71</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>628</v>
+        <v>621</v>
       </c>
       <c r="N22" s="12" t="n">
         <v>39</v>
@@ -1550,10 +1550,10 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H23" s="12" t="n">
         <v>52</v>
@@ -1562,7 +1562,7 @@
         <v>10</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="K23" s="12" t="n">
         <v>33</v>
@@ -1609,19 +1609,19 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="H24" s="12" t="n">
         <v>50</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>185</v>
+        <v>0</v>
       </c>
       <c r="K24" s="12" t="n">
         <v>68</v>
@@ -1630,7 +1630,7 @@
         <v>46</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="N24" s="12" t="n">
         <v>34</v>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>425</v>
+        <v>416</v>
       </c>
       <c r="H25" s="12" t="n">
         <v>1</v>
@@ -1680,7 +1680,7 @@
         <v>9</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="K25" s="12" t="n">
         <v>23</v>
@@ -1730,16 +1730,16 @@
         <v>204</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="H26" s="12" t="n">
         <v>11</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="K26" s="12" t="n">
         <v>57</v>
@@ -1786,19 +1786,19 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="I27" s="12" t="n">
         <v>21</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>154</v>
+        <v>0</v>
       </c>
       <c r="K27" s="12" t="n">
         <v>46</v>
@@ -1807,7 +1807,7 @@
         <v>29</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="N27" s="12" t="n">
         <v>139</v>
@@ -1821,17 +1821,17 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>01008</t>
+          <t>01574</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>GENOVA</t>
+          <t>TREVIGLIO</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>VIA FERRIERE BRUZZO 13</t>
+          <t>VIALE MANZONI, 11</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1841,56 +1841,56 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>DALLORTO ILARIA</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>231</v>
+        <v>1</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>278</v>
+        <v>216</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>01574</t>
+          <t>01008</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>TREVIGLIO</t>
+          <t>GENOVA</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>VIALE MANZONI, 11</t>
+          <t>VIA FERRIERE BRUZZO 13</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1900,39 +1900,39 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>DALLORTO ILARIA</t>
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>1</v>
+        <v>229</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>149</v>
+        <v>0</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>218</v>
+        <v>277</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1975,7 +1975,7 @@
         <v>379</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="K30" s="12" t="n">
         <v>51</v>
@@ -2025,16 +2025,16 @@
         <v>156</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="K31" s="12" t="n">
         <v>29</v>
@@ -2043,7 +2043,7 @@
         <v>60</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="N31" s="12" t="n">
         <v>10</v>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="H32" s="12" t="n">
         <v>12</v>
@@ -2093,7 +2093,7 @@
         <v>9</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="K32" s="12" t="n">
         <v>29</v>
@@ -2102,7 +2102,7 @@
         <v>71</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="N32" s="12" t="n">
         <v>39</v>
@@ -2116,17 +2116,17 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>01043</t>
+          <t>01525</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>GENOVA</t>
+          <t>GAZZANIGA</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>VIA RIGHETTI 1 R</t>
+          <t>CESARE BATTISTI</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2136,56 +2136,56 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>DALLORTO ILARIA</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>162</v>
+        <v>251</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>35</v>
+        <v>93</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>240</v>
+        <v>90</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>01525</t>
+          <t>01043</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>GAZZANIGA</t>
+          <t>GENOVA</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>CESARE BATTISTI</t>
+          <t>VIA RIGHETTI 1 R</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2195,35 +2195,35 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>DALLORTO ILARIA</t>
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>252</v>
+        <v>159</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>95</v>
+        <v>33</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>90</v>
+        <v>236</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
@@ -2258,10 +2258,10 @@
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="H35" s="12" t="n">
         <v>12</v>
@@ -2270,7 +2270,7 @@
         <v>52</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="K35" s="12" t="n">
         <v>30</v>
@@ -2279,7 +2279,7 @@
         <v>23</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="N35" s="12" t="n">
         <v>39</v>
@@ -2293,17 +2293,17 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>01378</t>
+          <t>01007</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>CARCARE</t>
+          <t>CHIAVARI</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>VIA VITTORIO VENETO 52</t>
+          <t>CORSO GENOVA 40</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2317,52 +2317,52 @@
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>139</v>
+        <v>0</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>108</v>
+        <v>267</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>2</v>
+        <v>59</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>01007</t>
+          <t>01378</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>CHIAVARI</t>
+          <t>CARCARE</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>CORSO GENOVA 40</t>
+          <t>VIA VITTORIO VENETO 52</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2379,32 +2379,32 @@
         <v>109</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="H37" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="I37" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="I37" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="J37" s="12" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>271</v>
+        <v>107</v>
       </c>
       <c r="N37" s="12" t="n">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2435,10 +2435,10 @@
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="H38" s="12" t="n">
         <v>2</v>
@@ -2447,7 +2447,7 @@
         <v>54</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="K38" s="12" t="n">
         <v>29</v>
@@ -2497,7 +2497,7 @@
         <v>104</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H39" s="12" t="n">
         <v>30</v>
@@ -2506,7 +2506,7 @@
         <v>17</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="K39" s="12" t="n">
         <v>6</v>
@@ -2515,7 +2515,7 @@
         <v>38</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="N39" s="12" t="n">
         <v>3</v>
@@ -2553,10 +2553,10 @@
         </is>
       </c>
       <c r="F40" s="12" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="H40" s="12" t="n">
         <v>6</v>
@@ -2565,7 +2565,7 @@
         <v>5</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="K40" s="12" t="n">
         <v>31</v>
@@ -2574,7 +2574,7 @@
         <v>25</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="N40" s="12" t="n">
         <v>12</v>
@@ -2588,17 +2588,17 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>01371</t>
+          <t>01971</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>SAVONA</t>
+          <t>CREMONA</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>VIA NAZIONALE PIEMONTE 68 R</t>
+          <t>VIA BERGAMO 47</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -2608,56 +2608,56 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>DELUGAS NADIA</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>180</v>
+        <v>102</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="N41" s="12" t="n">
-        <v>27</v>
+        <v>81</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>01971</t>
+          <t>01371</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>CREMONA</t>
+          <t>SAVONA</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>VIA BERGAMO 47</t>
+          <t>VIA NAZIONALE PIEMONTE 68 R</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -2667,39 +2667,39 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>DELUGAS NADIA</t>
         </is>
       </c>
       <c r="F42" s="12" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>102</v>
+        <v>174</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="K42" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>120</v>
+        <v>157</v>
       </c>
       <c r="N42" s="12" t="n">
-        <v>81</v>
+        <v>27</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2730,19 +2730,19 @@
         </is>
       </c>
       <c r="F43" s="12" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="H43" s="12" t="n">
         <v>5</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="K43" s="12" t="n">
         <v>29</v>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="F44" s="12" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G44" s="12" t="n">
         <v>73</v>
@@ -2801,7 +2801,7 @@
         <v>101</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="K44" s="12" t="n">
         <v>20</v>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2848,19 +2848,19 @@
         </is>
       </c>
       <c r="F45" s="12" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="H45" s="12" t="n">
         <v>5</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K45" s="12" t="n">
         <v>14</v>
@@ -2869,7 +2869,7 @@
         <v>35</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="N45" s="12" t="n">
         <v>5</v>
@@ -2907,19 +2907,19 @@
         </is>
       </c>
       <c r="F46" s="12" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="H46" s="12" t="n">
         <v>14</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K46" s="12" t="n">
         <v>13</v>
@@ -2928,7 +2928,7 @@
         <v>23</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="N46" s="12" t="n">
         <v>24</v>
@@ -2969,7 +2969,7 @@
         <v>67</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="H47" s="12" t="n">
         <v>11</v>
@@ -2978,7 +2978,7 @@
         <v>22</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="K47" s="12" t="n">
         <v>11</v>
@@ -2987,31 +2987,31 @@
         <v>21</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="N47" s="12" t="n">
         <v>12</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>01142</t>
+          <t>54151</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>SESTRI LEVANTE</t>
+          <t>IMPERIA</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>VIA BRUNO PRIMI, 14</t>
+          <t>SS 28 KM 136 + 600</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -3021,35 +3021,35 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>DALLORTO ILARIA</t>
+          <t>BARNABA SALVATORE</t>
         </is>
       </c>
       <c r="F48" s="12" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>109</v>
+        <v>127</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="J48" s="12" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="K48" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="M48" s="12" t="n">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="N48" s="12" t="n">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
@@ -3060,17 +3060,17 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>54151</t>
+          <t>01142</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>IMPERIA</t>
+          <t>SESTRI LEVANTE</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>SS 28 KM 136 + 600</t>
+          <t>VIA BRUNO PRIMI, 14</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -3080,35 +3080,35 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>BARNABA SALVATORE</t>
+          <t>DALLORTO ILARIA</t>
         </is>
       </c>
       <c r="F49" s="12" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G49" s="12" t="n">
+        <v>104</v>
+      </c>
+      <c r="H49" s="12" t="n">
+        <v>64</v>
+      </c>
+      <c r="I49" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="J49" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="L49" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="M49" s="12" t="n">
         <v>128</v>
       </c>
-      <c r="H49" s="12" t="n">
-        <v>22</v>
-      </c>
-      <c r="I49" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="J49" s="12" t="n">
-        <v>40</v>
-      </c>
-      <c r="K49" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="L49" s="12" t="n">
-        <v>24</v>
-      </c>
-      <c r="M49" s="12" t="n">
-        <v>117</v>
-      </c>
       <c r="N49" s="12" t="n">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I50" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J50" s="12" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="K50" s="12" t="n">
         <v>16</v>
@@ -3164,31 +3164,31 @@
         <v>7</v>
       </c>
       <c r="M50" s="12" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N50" s="12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>11719</t>
+          <t>01334</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>MONTICHIARI</t>
+          <t>FINALE LIGURE</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>S.S. 668 - VIA GHEDI</t>
+          <t>VIA MAZZINI</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -3198,56 +3198,56 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>DODI JACOPO</t>
+          <t>BARNABA SALVATORE</t>
         </is>
       </c>
       <c r="F51" s="12" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H51" s="12" t="n">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="I51" s="12" t="n">
-        <v>138</v>
+        <v>75</v>
       </c>
       <c r="J51" s="12" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="K51" s="12" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="M51" s="12" t="n">
-        <v>62</v>
+        <v>92</v>
       </c>
       <c r="N51" s="12" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>01334</t>
+          <t>11719</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>FINALE LIGURE</t>
+          <t>MONTICHIARI</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>VIA MAZZINI</t>
+          <t>S.S. 668 - VIA GHEDI</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -3257,35 +3257,35 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>BARNABA SALVATORE</t>
+          <t>DODI JACOPO</t>
         </is>
       </c>
       <c r="F52" s="12" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="H52" s="12" t="n">
+        <v>45</v>
+      </c>
+      <c r="I52" s="12" t="n">
+        <v>137</v>
+      </c>
+      <c r="J52" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L52" s="12" t="n">
+        <v>39</v>
+      </c>
+      <c r="M52" s="12" t="n">
         <v>61</v>
       </c>
-      <c r="I52" s="12" t="n">
-        <v>76</v>
-      </c>
-      <c r="J52" s="12" t="n">
-        <v>43</v>
-      </c>
-      <c r="K52" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="L52" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="M52" s="12" t="n">
-        <v>98</v>
-      </c>
       <c r="N52" s="12" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
@@ -3320,19 +3320,19 @@
         </is>
       </c>
       <c r="F53" s="12" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="H53" s="12" t="n">
         <v>40</v>
       </c>
       <c r="I53" s="12" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="J53" s="12" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="K53" s="12" t="n">
         <v>15</v>
@@ -3341,7 +3341,7 @@
         <v>0</v>
       </c>
       <c r="M53" s="12" t="n">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="N53" s="12" t="n">
         <v>1</v>
@@ -3355,17 +3355,17 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>56297</t>
+          <t>55973</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>SAN PAOLO D'ARGON</t>
+          <t>BOTTICINO</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>SS 42</t>
+          <t>GARIBALDI 18</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -3375,56 +3375,56 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>BRIGNOLI STEFANO</t>
+          <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
       <c r="F54" s="12" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>2</v>
+        <v>62</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J54" s="12" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K54" s="12" t="n">
         <v>12</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="M54" s="12" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="N54" s="12" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>55973</t>
+          <t>56297</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>BOTTICINO</t>
+          <t>SAN PAOLO D'ARGON</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>GARIBALDI 18</t>
+          <t>SS 42</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -3434,35 +3434,35 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>GRAZIOSI DAVIDE</t>
+          <t>BRIGNOLI STEFANO</t>
         </is>
       </c>
       <c r="F55" s="12" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>63</v>
+        <v>2</v>
       </c>
       <c r="H55" s="12" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I55" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J55" s="12" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K55" s="12" t="n">
         <v>12</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="M55" s="12" t="n">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="N55" s="12" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="F56" s="12" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G56" s="12" t="n">
         <v>99</v>
@@ -3509,7 +3509,7 @@
         <v>9</v>
       </c>
       <c r="J56" s="12" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K56" s="12" t="n">
         <v>4</v>
@@ -3518,7 +3518,7 @@
         <v>27</v>
       </c>
       <c r="M56" s="12" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="N56" s="12" t="n">
         <v>1</v>
@@ -3559,16 +3559,16 @@
         <v>47</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H57" s="12" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I57" s="12" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J57" s="12" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K57" s="12" t="n">
         <v>8</v>
@@ -3577,7 +3577,7 @@
         <v>17</v>
       </c>
       <c r="M57" s="12" t="n">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="N57" s="12" t="n">
         <v>4</v>
@@ -3591,17 +3591,17 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>11726</t>
+          <t>01280</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>REZZATO</t>
+          <t>LA SPEZIA</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>S.S.45 KM.49+300</t>
+          <t>VIALE ITALIA 160</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -3611,56 +3611,56 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>GRAZIOSI DAVIDE</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="F58" s="12" t="n">
         <v>46</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="I58" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="J58" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="J58" s="12" t="n">
-        <v>26</v>
-      </c>
-      <c r="K58" s="12" t="n">
-        <v>10</v>
-      </c>
       <c r="L58" s="12" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="M58" s="12" t="n">
-        <v>52</v>
+        <v>91</v>
       </c>
       <c r="N58" s="12" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>01135</t>
+          <t>01561</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>GENOVA</t>
+          <t>PONTIROLO NUOVO</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>VIA SIFFREDI, 62</t>
+          <t>STR PROVLE N 12</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -3670,56 +3670,56 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>DALLORTO ILARIA</t>
+          <t>VINCENZI STEFANO</t>
         </is>
       </c>
       <c r="F59" s="12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>39</v>
+        <v>79</v>
       </c>
       <c r="H59" s="12" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="I59" s="12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J59" s="12" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K59" s="12" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="M59" s="12" t="n">
-        <v>116</v>
+        <v>68</v>
       </c>
       <c r="N59" s="12" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>01561</t>
+          <t>11726</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>PONTIROLO NUOVO</t>
+          <t>REZZATO</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>STR PROVLE N 12</t>
+          <t>S.S.45 KM.49+300</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -3729,56 +3729,56 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>VINCENZI STEFANO</t>
+          <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
       <c r="F60" s="12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="I60" s="12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J60" s="12" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K60" s="12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L60" s="12" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="M60" s="12" t="n">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="N60" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>01280</t>
+          <t>01135</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>LA SPEZIA</t>
+          <t>GENOVA</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>VIALE ITALIA 160</t>
+          <t>VIA SIFFREDI, 62</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -3788,35 +3788,35 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>DALLORTO ILARIA</t>
         </is>
       </c>
       <c r="F61" s="12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="H61" s="12" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="I61" s="12" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="J61" s="12" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="K61" s="12" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="L61" s="12" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="M61" s="12" t="n">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="N61" s="12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
@@ -3863,7 +3863,7 @@
         <v>0</v>
       </c>
       <c r="J62" s="12" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K62" s="12" t="n">
         <v>12</v>
@@ -3910,10 +3910,10 @@
         </is>
       </c>
       <c r="F63" s="12" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H63" s="12" t="n">
         <v>20</v>
@@ -3922,7 +3922,7 @@
         <v>3</v>
       </c>
       <c r="J63" s="12" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K63" s="12" t="n">
         <v>5</v>
@@ -3972,16 +3972,16 @@
         <v>39</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H64" s="12" t="n">
         <v>59</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J64" s="12" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K64" s="12" t="n">
         <v>11</v>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -4028,10 +4028,10 @@
         </is>
       </c>
       <c r="F65" s="12" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H65" s="12" t="n">
         <v>1</v>
@@ -4040,7 +4040,7 @@
         <v>3</v>
       </c>
       <c r="J65" s="12" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K65" s="12" t="n">
         <v>7</v>
@@ -4049,7 +4049,7 @@
         <v>10</v>
       </c>
       <c r="M65" s="12" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="N65" s="12" t="n">
         <v>3</v>
@@ -4093,13 +4093,13 @@
         <v>56</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I66" s="12" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="J66" s="12" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K66" s="12" t="n">
         <v>1</v>
@@ -4146,7 +4146,7 @@
         </is>
       </c>
       <c r="F67" s="12" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G67" s="12" t="n">
         <v>0</v>
@@ -4158,7 +4158,7 @@
         <v>0</v>
       </c>
       <c r="J67" s="12" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K67" s="12" t="n">
         <v>3</v>
@@ -4167,14 +4167,14 @@
         <v>4</v>
       </c>
       <c r="M67" s="12" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N67" s="12" t="n">
         <v>27</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -4205,19 +4205,19 @@
         </is>
       </c>
       <c r="F68" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H68" s="12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I68" s="12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J68" s="12" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K68" s="12" t="n">
         <v>4</v>
@@ -4226,7 +4226,7 @@
         <v>4</v>
       </c>
       <c r="M68" s="12" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="N68" s="12" t="n">
         <v>0</v>
@@ -4267,16 +4267,16 @@
         <v>20</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H69" s="12" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="I69" s="12" t="n">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="J69" s="12" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K69" s="12" t="n">
         <v>0</v>
@@ -4285,7 +4285,7 @@
         <v>6</v>
       </c>
       <c r="M69" s="12" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="N69" s="12" t="n">
         <v>1</v>
@@ -4335,7 +4335,7 @@
         <v>0</v>
       </c>
       <c r="J70" s="12" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K70" s="12" t="n">
         <v>1</v>
@@ -4394,7 +4394,7 @@
         <v>0</v>
       </c>
       <c r="J71" s="12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K71" s="12" t="n">
         <v>5</v>
@@ -4403,14 +4403,14 @@
         <v>1</v>
       </c>
       <c r="M71" s="12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N71" s="12" t="n">
         <v>3</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -4444,7 +4444,7 @@
         <v>13</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H72" s="12" t="n">
         <v>1</v>
@@ -4453,7 +4453,7 @@
         <v>4</v>
       </c>
       <c r="J72" s="12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K72" s="12" t="n">
         <v>3</v>
@@ -4462,7 +4462,7 @@
         <v>3</v>
       </c>
       <c r="M72" s="12" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="N72" s="12" t="n">
         <v>0</v>
@@ -4500,19 +4500,19 @@
         </is>
       </c>
       <c r="F73" s="12" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G73" s="12" t="n">
         <v>19</v>
       </c>
       <c r="H73" s="12" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I73" s="12" t="n">
         <v>59</v>
       </c>
       <c r="J73" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K73" s="12" t="n">
         <v>1</v>
@@ -4528,7 +4528,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -4571,7 +4571,7 @@
         <v>0</v>
       </c>
       <c r="J74" s="12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K74" s="12" t="n">
         <v>1</v>
@@ -4587,7 +4587,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
